--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -412,670 +412,670 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46079.01041666666</v>
+        <v>46094.01041666666</v>
       </c>
       <c r="B2">
-        <v>561</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1878</v>
+        <v>1270</v>
       </c>
       <c r="D2">
-        <v>1959.47900849434</v>
+        <v>2091.340550412438</v>
       </c>
       <c r="E2">
-        <v>2439</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46079.02083333334</v>
+        <v>46094.02083333334</v>
       </c>
       <c r="B3">
-        <v>572</v>
+        <v>632</v>
       </c>
       <c r="C3">
-        <v>1906</v>
+        <v>1262</v>
       </c>
       <c r="D3">
-        <v>1960.660038654925</v>
+        <v>2080.071689233596</v>
       </c>
       <c r="E3">
-        <v>2478</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46079.03125</v>
+        <v>46094.03125</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>616</v>
       </c>
       <c r="C4">
-        <v>1905</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1961.84106881551</v>
+        <v>2068.802828054754</v>
       </c>
       <c r="E4">
-        <v>1905</v>
+        <v>616</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46079.04166666666</v>
+        <v>46094.04166666666</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1963.022098976095</v>
+        <v>2057.533966875912</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>614</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46079.05208333334</v>
+        <v>46094.05208333334</v>
       </c>
       <c r="B6">
-        <v>360</v>
+        <v>603</v>
       </c>
       <c r="C6">
-        <v>1865</v>
+        <v>1173</v>
       </c>
       <c r="D6">
-        <v>1945.306646567321</v>
+        <v>2054.727993461867</v>
       </c>
       <c r="E6">
-        <v>2225</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46079.0625</v>
+        <v>46094.0625</v>
       </c>
       <c r="B7">
-        <v>353</v>
+        <v>595</v>
       </c>
       <c r="C7">
-        <v>1861</v>
+        <v>1163</v>
       </c>
       <c r="D7">
-        <v>1927.591194158546</v>
+        <v>2051.922020047821</v>
       </c>
       <c r="E7">
-        <v>2214</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46079.07291666666</v>
+        <v>46094.07291666666</v>
       </c>
       <c r="B8">
-        <v>354</v>
+        <v>596</v>
       </c>
       <c r="C8">
-        <v>1862</v>
+        <v>1161</v>
       </c>
       <c r="D8">
-        <v>1909.875741749772</v>
+        <v>2049.116046633776</v>
       </c>
       <c r="E8">
-        <v>2216</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46079.08333333334</v>
+        <v>46094.08333333334</v>
       </c>
       <c r="B9">
-        <v>352</v>
+        <v>603</v>
       </c>
       <c r="C9">
-        <v>1886</v>
+        <v>1162</v>
       </c>
       <c r="D9">
-        <v>1892.160289340997</v>
+        <v>2046.310073219731</v>
       </c>
       <c r="E9">
-        <v>2238</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46079.09375</v>
+        <v>46094.09375</v>
       </c>
       <c r="B10">
-        <v>300</v>
+        <v>574</v>
       </c>
       <c r="C10">
-        <v>1891</v>
+        <v>1113</v>
       </c>
       <c r="D10">
-        <v>1899.246470304557</v>
+        <v>2048.135754639828</v>
       </c>
       <c r="E10">
-        <v>2191</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46079.10416666666</v>
+        <v>46094.10416666666</v>
       </c>
       <c r="B11">
-        <v>295</v>
+        <v>566</v>
       </c>
       <c r="C11">
-        <v>1895</v>
+        <v>1112</v>
       </c>
       <c r="D11">
-        <v>1906.332651268116</v>
+        <v>2049.961436059925</v>
       </c>
       <c r="E11">
-        <v>2190</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46079.11458333334</v>
+        <v>46094.11458333334</v>
       </c>
       <c r="B12">
-        <v>296</v>
+        <v>549</v>
       </c>
       <c r="C12">
-        <v>1897</v>
+        <v>1110</v>
       </c>
       <c r="D12">
-        <v>1913.418832231676</v>
+        <v>2051.787117480023</v>
       </c>
       <c r="E12">
-        <v>2193</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46079.125</v>
+        <v>46094.125</v>
       </c>
       <c r="B13">
-        <v>295</v>
+        <v>540</v>
       </c>
       <c r="C13">
-        <v>1896</v>
+        <v>1111</v>
       </c>
       <c r="D13">
-        <v>1920.505013195236</v>
+        <v>2053.61279890012</v>
       </c>
       <c r="E13">
-        <v>2191</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46079.13541666666</v>
+        <v>46094.13541666666</v>
       </c>
       <c r="B14">
-        <v>296</v>
+        <v>535</v>
       </c>
       <c r="C14">
-        <v>1901</v>
+        <v>1108</v>
       </c>
       <c r="D14">
-        <v>1931.659186933993</v>
+        <v>2070.970262647262</v>
       </c>
       <c r="E14">
-        <v>2197</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46079.14583333334</v>
+        <v>46094.14583333334</v>
       </c>
       <c r="B15">
-        <v>294</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>1899</v>
+        <v>1109</v>
       </c>
       <c r="D15">
-        <v>1942.81336067275</v>
+        <v>2088.327726394403</v>
       </c>
       <c r="E15">
-        <v>2193</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46079.15625</v>
+        <v>46094.15625</v>
       </c>
       <c r="B16">
-        <v>296</v>
+        <v>533</v>
       </c>
       <c r="C16">
-        <v>1901</v>
+        <v>1108</v>
       </c>
       <c r="D16">
-        <v>1953.967534411508</v>
+        <v>2105.685190141544</v>
       </c>
       <c r="E16">
-        <v>2197</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46079.16666666666</v>
+        <v>46094.16666666666</v>
       </c>
       <c r="B17">
-        <v>303</v>
+        <v>535</v>
       </c>
       <c r="C17">
-        <v>1904</v>
+        <v>1126</v>
       </c>
       <c r="D17">
-        <v>1965.121708150265</v>
+        <v>2123.042653888685</v>
       </c>
       <c r="E17">
-        <v>2207</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46079.17708333334</v>
+        <v>46094.17708333334</v>
       </c>
       <c r="B18">
-        <v>361</v>
+        <v>532</v>
       </c>
       <c r="C18">
-        <v>1917</v>
+        <v>1257</v>
       </c>
       <c r="D18">
-        <v>2020.358301295883</v>
+        <v>2162.416216730578</v>
       </c>
       <c r="E18">
-        <v>2278</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46079.1875</v>
+        <v>46094.1875</v>
       </c>
       <c r="B19">
-        <v>368</v>
+        <v>535</v>
       </c>
       <c r="C19">
-        <v>1912</v>
+        <v>1261</v>
       </c>
       <c r="D19">
-        <v>2075.594894441501</v>
+        <v>2201.78977957247</v>
       </c>
       <c r="E19">
-        <v>2280</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46079.19791666666</v>
+        <v>46094.19791666666</v>
       </c>
       <c r="B20">
-        <v>381</v>
+        <v>536</v>
       </c>
       <c r="C20">
-        <v>1861</v>
+        <v>1262</v>
       </c>
       <c r="D20">
-        <v>2130.831487587119</v>
+        <v>2241.163342414363</v>
       </c>
       <c r="E20">
-        <v>2242</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46079.20833333334</v>
+        <v>46094.20833333334</v>
       </c>
       <c r="B21">
-        <v>394</v>
+        <v>563</v>
       </c>
       <c r="C21">
-        <v>1860</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>2186.068080732738</v>
+        <v>2280.536905256256</v>
       </c>
       <c r="E21">
-        <v>2254</v>
+        <v>563</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46079.21875</v>
+        <v>46094.21875</v>
       </c>
       <c r="B22">
-        <v>505</v>
+        <v>654</v>
       </c>
       <c r="C22">
-        <v>1899</v>
+        <v>1236</v>
       </c>
       <c r="D22">
-        <v>2259.591894856595</v>
+        <v>2281.346320664222</v>
       </c>
       <c r="E22">
-        <v>2404</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46079.22916666666</v>
+        <v>46094.22916666666</v>
       </c>
       <c r="B23">
-        <v>506</v>
+        <v>672</v>
       </c>
       <c r="C23">
-        <v>1895</v>
+        <v>1234</v>
       </c>
       <c r="D23">
-        <v>2333.115708980453</v>
+        <v>2282.155736072188</v>
       </c>
       <c r="E23">
-        <v>2401</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46079.23958333334</v>
+        <v>46094.23958333334</v>
       </c>
       <c r="B24">
-        <v>508</v>
+        <v>671</v>
       </c>
       <c r="C24">
-        <v>1888</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>2406.639523104311</v>
+        <v>2282.965151480154</v>
       </c>
       <c r="E24">
-        <v>2396</v>
+        <v>671</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46079.25</v>
+        <v>46094.25</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>677</v>
       </c>
       <c r="C25">
-        <v>1880</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>2480.163337228169</v>
+        <v>2283.77456688812</v>
       </c>
       <c r="E25">
-        <v>1880</v>
+        <v>677</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46079.26041666666</v>
+        <v>46094.26041666666</v>
       </c>
       <c r="B26">
-        <v>609</v>
+        <v>829</v>
       </c>
       <c r="C26">
-        <v>1867</v>
+        <v>1272</v>
       </c>
       <c r="D26">
-        <v>2478.616750113181</v>
+        <v>2201.457019904916</v>
       </c>
       <c r="E26">
-        <v>2476</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46079.27083333334</v>
+        <v>46094.27083333334</v>
       </c>
       <c r="B27">
-        <v>616</v>
+        <v>818</v>
       </c>
       <c r="C27">
-        <v>1872</v>
+        <v>1259</v>
       </c>
       <c r="D27">
-        <v>2477.070162998194</v>
+        <v>2119.139472921711</v>
       </c>
       <c r="E27">
-        <v>2488</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46079.28125</v>
+        <v>46094.28125</v>
       </c>
       <c r="B28">
-        <v>609</v>
+        <v>809</v>
       </c>
       <c r="C28">
-        <v>1893</v>
+        <v>1245</v>
       </c>
       <c r="D28">
-        <v>2475.523575883206</v>
+        <v>2036.821925938507</v>
       </c>
       <c r="E28">
-        <v>2502</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46079.29166666666</v>
+        <v>46094.29166666666</v>
       </c>
       <c r="B29">
-        <v>605</v>
+        <v>807</v>
       </c>
       <c r="C29">
-        <v>1879</v>
+        <v>1243</v>
       </c>
       <c r="D29">
-        <v>2473.976988768219</v>
+        <v>1954.504378955303</v>
       </c>
       <c r="E29">
-        <v>2484</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46079.30208333334</v>
+        <v>46094.30208333334</v>
       </c>
       <c r="B30">
-        <v>301</v>
+        <v>785</v>
       </c>
       <c r="C30">
-        <v>1823</v>
+        <v>1200</v>
       </c>
       <c r="D30">
-        <v>2462.832188284604</v>
+        <v>1847.64355810364</v>
       </c>
       <c r="E30">
-        <v>2124</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46079.3125</v>
+        <v>46094.3125</v>
       </c>
       <c r="B31">
-        <v>280</v>
+        <v>776</v>
       </c>
       <c r="C31">
-        <v>1849</v>
+        <v>1181</v>
       </c>
       <c r="D31">
-        <v>2451.687387800989</v>
+        <v>1740.782737251977</v>
       </c>
       <c r="E31">
-        <v>2129</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46079.32291666666</v>
+        <v>46094.32291666666</v>
       </c>
       <c r="B32">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>1859</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>2440.542587317374</v>
+        <v>1633.921916400314</v>
       </c>
       <c r="E32">
-        <v>2125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46079.33333333334</v>
+        <v>46094.33333333334</v>
       </c>
       <c r="B33">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>1833</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>2429.397786833758</v>
+        <v>1527.061095548651</v>
       </c>
       <c r="E33">
-        <v>2098</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46079.34375</v>
+        <v>46094.34375</v>
       </c>
       <c r="B34">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>1841</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>2331.82219975691</v>
+        <v>1447.846307629147</v>
       </c>
       <c r="E34">
-        <v>2055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46079.35416666666</v>
+        <v>46094.35416666666</v>
       </c>
       <c r="B35">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>1833</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>2234.246612680063</v>
+        <v>1368.631519709642</v>
       </c>
       <c r="E35">
-        <v>2039</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46079.36458333334</v>
+        <v>46094.36458333334</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36">
-        <v>1793</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>2136.671025603215</v>
+        <v>1289.416731790137</v>
       </c>
       <c r="E36">
-        <v>1793</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46079.375</v>
+        <v>46094.375</v>
       </c>
       <c r="B37">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>1784</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>2039.095438526367</v>
+        <v>1210.201943870633</v>
       </c>
       <c r="E37">
-        <v>1989</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46079.38541666666</v>
+        <v>46094.38541666666</v>
       </c>
       <c r="B38">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>1335</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>1974.091913417927</v>
+        <v>1178.886561089553</v>
       </c>
       <c r="E38">
-        <v>1492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46079.39583333334</v>
+        <v>46094.39583333334</v>
       </c>
       <c r="B39">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>1267</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>1909.088388309488</v>
+        <v>1147.571178308474</v>
       </c>
       <c r="E39">
-        <v>1412</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46079.40625</v>
+        <v>46094.40625</v>
       </c>
       <c r="B40">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>1263</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>1844.084863201048</v>
+        <v>1116.255795527395</v>
       </c>
       <c r="E40">
-        <v>1402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46079.41666666666</v>
+        <v>46094.41666666666</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>1779.081338092608</v>
+        <v>1084.940412746315</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46079.42708333334</v>
+        <v>46094.42708333334</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>1767.674086462197</v>
+        <v>1073.140934799977</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46079.4375</v>
+        <v>46094.4375</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>1756.266834831785</v>
+        <v>1061.34145685364</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46079.44791666666</v>
+        <v>46094.44791666666</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>1744.859583201373</v>
+        <v>1049.541978907302</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46079.45833333334</v>
+        <v>46094.45833333334</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>1733.452331570961</v>
+        <v>1037.742500960964</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46079.46875</v>
+        <v>46094.46875</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1169,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>1710.009820208873</v>
+        <v>1030.772534948603</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46079.47916666666</v>
+        <v>46094.47916666666</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>1686.567308846786</v>
+        <v>1023.802568936242</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46079.48958333334</v>
+        <v>46094.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>1663.124797484699</v>
+        <v>1016.832602923882</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46079.5</v>
+        <v>46094.5</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>1639.682286122611</v>
+        <v>1009.862636911521</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46079.51041666666</v>
+        <v>46094.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>1662.149978939454</v>
+        <v>1000.842151865609</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46079.52083333334</v>
+        <v>46094.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>1684.617671756297</v>
+        <v>991.821666819697</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46079.53125</v>
+        <v>46094.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>1707.085364573139</v>
+        <v>982.8011817737851</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46079.54166666666</v>
+        <v>46094.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>1729.553057389982</v>
+        <v>973.7806967278731</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46079.55208333334</v>
+        <v>46094.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>1758.657014918683</v>
+        <v>1001.975333436465</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46079.5625</v>
+        <v>46094.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1787.760972447384</v>
+        <v>1030.169970145057</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46079.57291666666</v>
+        <v>46094.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1816.864929976084</v>
+        <v>1058.364606853649</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46079.58333333334</v>
+        <v>46094.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>1845.968887504785</v>
+        <v>1086.559243562241</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46079.59375</v>
+        <v>46094.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>1968.945996289627</v>
+        <v>1191.549415471005</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46079.60416666666</v>
+        <v>46094.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>2091.923105074468</v>
+        <v>1296.539587379769</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46079.61458333334</v>
+        <v>46094.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>2214.90021385931</v>
+        <v>1401.529759288534</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46079.625</v>
+        <v>46094.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>2337.877322644151</v>
+        <v>1506.519931197298</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46079.63541666666</v>
+        <v>46094.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>2412.329089037028</v>
+        <v>1720.169624864299</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46079.64583333334</v>
+        <v>46094.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>2486.780855429905</v>
+        <v>1933.8193185313</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46079.65625</v>
+        <v>46094.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>2561.232621822782</v>
+        <v>2147.469012198301</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46079.66666666666</v>
+        <v>46094.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>2635.684388215659</v>
+        <v>2361.118705865302</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46079.67708333334</v>
+        <v>46094.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>2665.182022464694</v>
+        <v>2398.387788646658</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46079.6875</v>
+        <v>46094.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>2694.67965671373</v>
+        <v>2435.656871428014</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46079.69791666666</v>
+        <v>46094.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>2724.177290962765</v>
+        <v>2472.92595420937</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46079.70833333334</v>
+        <v>46094.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>2753.674925211801</v>
+        <v>2510.195036990726</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46079.71875</v>
+        <v>46094.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>2754.846582117072</v>
+        <v>2527.300682610889</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46079.72916666666</v>
+        <v>46094.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>2756.018239022343</v>
+        <v>2544.406328231051</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46079.73958333334</v>
+        <v>46094.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>2757.189895927614</v>
+        <v>2561.511973851213</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46079.75</v>
+        <v>46094.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>2758.361552832885</v>
+        <v>2578.617619471376</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46079.76041666666</v>
+        <v>46094.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2756.824338973004</v>
+        <v>2573.086614184075</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46079.77083333334</v>
+        <v>46094.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2755.287125113124</v>
+        <v>2567.555608896774</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46079.78125</v>
+        <v>46094.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2753.749911253244</v>
+        <v>2562.024603609474</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46079.79166666666</v>
+        <v>46094.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2752.212697393363</v>
+        <v>2556.493598322173</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46079.80208333334</v>
+        <v>46094.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2728.292150014106</v>
+        <v>2538.866329439142</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46079.8125</v>
+        <v>46094.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2704.371602634847</v>
+        <v>2521.239060556111</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46079.82291666666</v>
+        <v>46094.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2680.451055255589</v>
+        <v>2503.611791673081</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46079.83333333334</v>
+        <v>46094.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2656.530507876332</v>
+        <v>2485.98452279005</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46079.84375</v>
+        <v>46094.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2614.172767434133</v>
+        <v>2459.120924752233</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46079.85416666666</v>
+        <v>46094.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2571.815026991933</v>
+        <v>2432.257326714417</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46079.86458333334</v>
+        <v>46094.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2529.457286549734</v>
+        <v>2405.3937286766</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46079.875</v>
+        <v>46094.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2487.099546107535</v>
+        <v>2378.530130638784</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46079.88541666666</v>
+        <v>46094.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2435.415416699268</v>
+        <v>2342.547119005738</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46079.89583333334</v>
+        <v>46094.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2383.731287290999</v>
+        <v>2306.564107372692</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46079.90625</v>
+        <v>46094.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2332.047157882731</v>
+        <v>2270.581095739645</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46079.91666666666</v>
+        <v>46094.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2280.363028474463</v>
+        <v>2234.598084106599</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46079.92708333334</v>
+        <v>46094.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>2184.071577365808</v>
+        <v>2201.753805554754</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46079.9375</v>
+        <v>46094.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>2087.780126257152</v>
+        <v>2168.909527002908</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46079.94791666666</v>
+        <v>46094.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>1991.488675148497</v>
+        <v>2136.065248451063</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46079.95833333334</v>
+        <v>46094.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>1895.197224039841</v>
+        <v>2103.220969899218</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46079.96875</v>
+        <v>46094.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>1922.662308765296</v>
+        <v>2079.702246046563</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46079.97916666666</v>
+        <v>46094.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>1950.127393490751</v>
+        <v>2056.183522193909</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46079.98958333334</v>
+        <v>46094.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1977.592478216206</v>
+        <v>2032.664798341254</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46080</v>
+        <v>46095</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>2005.057562941661</v>
+        <v>2009.1460744886</v>
       </c>
       <c r="E97">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -412,517 +412,517 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46094.01041666666</v>
+        <v>46107.01041666666</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1270</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>2091.340550412438</v>
+        <v>1422.355612799569</v>
       </c>
       <c r="E2">
-        <v>1270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46094.02083333334</v>
+        <v>46107.02083333334</v>
       </c>
       <c r="B3">
-        <v>632</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>1262</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>2080.071689233596</v>
+        <v>1409.66828342666</v>
       </c>
       <c r="E3">
-        <v>1894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46094.03125</v>
+        <v>46107.03125</v>
       </c>
       <c r="B4">
-        <v>616</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>2068.802828054754</v>
+        <v>1396.980954053752</v>
       </c>
       <c r="E4">
-        <v>616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46094.04166666666</v>
+        <v>46107.04166666666</v>
       </c>
       <c r="B5">
-        <v>614</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>2057.533966875912</v>
+        <v>1384.293624680843</v>
       </c>
       <c r="E5">
-        <v>614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46094.05208333334</v>
+        <v>46107.05208333334</v>
       </c>
       <c r="B6">
-        <v>603</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1173</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>2054.727993461867</v>
+        <v>1379.581787717703</v>
       </c>
       <c r="E6">
-        <v>1776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46094.0625</v>
+        <v>46107.0625</v>
       </c>
       <c r="B7">
-        <v>595</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1163</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>2051.922020047821</v>
+        <v>1374.869950754563</v>
       </c>
       <c r="E7">
-        <v>1758</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46094.07291666666</v>
+        <v>46107.07291666666</v>
       </c>
       <c r="B8">
-        <v>596</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1161</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>2049.116046633776</v>
+        <v>1370.158113791423</v>
       </c>
       <c r="E8">
-        <v>1757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46094.08333333334</v>
+        <v>46107.08333333334</v>
       </c>
       <c r="B9">
-        <v>603</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>1162</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>2046.310073219731</v>
+        <v>1365.446276828284</v>
       </c>
       <c r="E9">
-        <v>1765</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46094.09375</v>
+        <v>46107.09375</v>
       </c>
       <c r="B10">
-        <v>574</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>1113</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>2048.135754639828</v>
+        <v>1364.48082248399</v>
       </c>
       <c r="E10">
-        <v>1687</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46094.10416666666</v>
+        <v>46107.10416666666</v>
       </c>
       <c r="B11">
-        <v>566</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>1112</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>2049.961436059925</v>
+        <v>1363.515368139696</v>
       </c>
       <c r="E11">
-        <v>1678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46094.11458333334</v>
+        <v>46107.11458333334</v>
       </c>
       <c r="B12">
-        <v>549</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>1110</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>2051.787117480023</v>
+        <v>1362.549913795403</v>
       </c>
       <c r="E12">
-        <v>1659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46094.125</v>
+        <v>46107.125</v>
       </c>
       <c r="B13">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>1111</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>2053.61279890012</v>
+        <v>1361.584459451109</v>
       </c>
       <c r="E13">
-        <v>1651</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46094.13541666666</v>
+        <v>46107.13541666666</v>
       </c>
       <c r="B14">
-        <v>535</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>1108</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>2070.970262647262</v>
+        <v>1380.347854751841</v>
       </c>
       <c r="E14">
-        <v>1643</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46094.14583333334</v>
+        <v>46107.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>1109</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>2088.327726394403</v>
+        <v>1399.111250052573</v>
       </c>
       <c r="E15">
-        <v>1109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46094.15625</v>
+        <v>46107.15625</v>
       </c>
       <c r="B16">
-        <v>533</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>1108</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>2105.685190141544</v>
+        <v>1417.874645353305</v>
       </c>
       <c r="E16">
-        <v>1641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46094.16666666666</v>
+        <v>46107.16666666666</v>
       </c>
       <c r="B17">
-        <v>535</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>1126</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>2123.042653888685</v>
+        <v>1436.638040654037</v>
       </c>
       <c r="E17">
-        <v>1661</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46094.17708333334</v>
+        <v>46107.17708333334</v>
       </c>
       <c r="B18">
-        <v>532</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>1257</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>2162.416216730578</v>
+        <v>1474.343230428215</v>
       </c>
       <c r="E18">
-        <v>1789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46094.1875</v>
+        <v>46107.1875</v>
       </c>
       <c r="B19">
-        <v>535</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>1261</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>2201.78977957247</v>
+        <v>1512.048420202392</v>
       </c>
       <c r="E19">
-        <v>1796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46094.19791666666</v>
+        <v>46107.19791666666</v>
       </c>
       <c r="B20">
-        <v>536</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>1262</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>2241.163342414363</v>
+        <v>1549.753609976569</v>
       </c>
       <c r="E20">
-        <v>1798</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46094.20833333334</v>
+        <v>46107.20833333334</v>
       </c>
       <c r="B21">
-        <v>563</v>
+        <v>0</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>2280.536905256256</v>
+        <v>1587.458799750746</v>
       </c>
       <c r="E21">
-        <v>563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46094.21875</v>
+        <v>46107.21875</v>
       </c>
       <c r="B22">
-        <v>654</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>1236</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>2281.346320664222</v>
+        <v>1646.456455445116</v>
       </c>
       <c r="E22">
-        <v>1890</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46094.22916666666</v>
+        <v>46107.22916666666</v>
       </c>
       <c r="B23">
-        <v>672</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>1234</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>2282.155736072188</v>
+        <v>1705.454111139486</v>
       </c>
       <c r="E23">
-        <v>1906</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46094.23958333334</v>
+        <v>46107.23958333334</v>
       </c>
       <c r="B24">
-        <v>671</v>
+        <v>0</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>2282.965151480154</v>
+        <v>1764.451766833855</v>
       </c>
       <c r="E24">
-        <v>671</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46094.25</v>
+        <v>46107.25</v>
       </c>
       <c r="B25">
-        <v>677</v>
+        <v>0</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>2283.77456688812</v>
+        <v>1823.449422528225</v>
       </c>
       <c r="E25">
-        <v>677</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46094.26041666666</v>
+        <v>46107.26041666666</v>
       </c>
       <c r="B26">
-        <v>829</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>1272</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>2201.457019904916</v>
+        <v>1805.032331503035</v>
       </c>
       <c r="E26">
-        <v>2101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46094.27083333334</v>
+        <v>46107.27083333334</v>
       </c>
       <c r="B27">
-        <v>818</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>1259</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>2119.139472921711</v>
+        <v>1786.615240477845</v>
       </c>
       <c r="E27">
-        <v>2077</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46094.28125</v>
+        <v>46107.28125</v>
       </c>
       <c r="B28">
-        <v>809</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>1245</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>2036.821925938507</v>
+        <v>1768.198149452655</v>
       </c>
       <c r="E28">
-        <v>2054</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46094.29166666666</v>
+        <v>46107.29166666666</v>
       </c>
       <c r="B29">
-        <v>807</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>1243</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>1954.504378955303</v>
+        <v>1749.781058427465</v>
       </c>
       <c r="E29">
-        <v>2050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46094.30208333334</v>
+        <v>46107.30208333334</v>
       </c>
       <c r="B30">
-        <v>785</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>1847.64355810364</v>
+        <v>1678.379413222112</v>
       </c>
       <c r="E30">
-        <v>1985</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46094.3125</v>
+        <v>46107.3125</v>
       </c>
       <c r="B31">
-        <v>776</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>1181</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>1740.782737251977</v>
+        <v>1606.97776801676</v>
       </c>
       <c r="E31">
-        <v>1957</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46094.32291666666</v>
+        <v>46107.32291666666</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -931,7 +931,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>1633.921916400314</v>
+        <v>1535.576122811407</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -939,7 +939,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46094.33333333334</v>
+        <v>46107.33333333334</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -948,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>1527.061095548651</v>
+        <v>1464.174477606055</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -956,7 +956,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46094.34375</v>
+        <v>46107.34375</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -965,7 +965,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>1447.846307629147</v>
+        <v>1409.867670736905</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -973,7 +973,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46094.35416666666</v>
+        <v>46107.35416666666</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -982,7 +982,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>1368.631519709642</v>
+        <v>1355.560863867754</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -990,7 +990,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46094.36458333334</v>
+        <v>46107.36458333334</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -999,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>1289.416731790137</v>
+        <v>1301.254056998604</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46094.375</v>
+        <v>46107.375</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1016,7 +1016,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>1210.201943870633</v>
+        <v>1246.947250129453</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1024,7 +1024,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46094.38541666666</v>
+        <v>46107.38541666666</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>1178.886561089553</v>
+        <v>1217.38545786843</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1041,7 +1041,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46094.39583333334</v>
+        <v>46107.39583333334</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>1147.571178308474</v>
+        <v>1187.823665607406</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46094.40625</v>
+        <v>46107.40625</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1067,7 +1067,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>1116.255795527395</v>
+        <v>1158.261873346382</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1075,7 +1075,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46094.41666666666</v>
+        <v>46107.41666666666</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>1084.940412746315</v>
+        <v>1128.700081085359</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46094.42708333334</v>
+        <v>46107.42708333334</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>1073.140934799977</v>
+        <v>1128.017966603099</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46094.4375</v>
+        <v>46107.4375</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>1061.34145685364</v>
+        <v>1127.335852120839</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46094.44791666666</v>
+        <v>46107.44791666666</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>1049.541978907302</v>
+        <v>1126.65373763858</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46094.45833333334</v>
+        <v>46107.45833333334</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>1037.742500960964</v>
+        <v>1125.97162315632</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46094.46875</v>
+        <v>46107.46875</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1169,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>1030.772534948603</v>
+        <v>1111.080539301651</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46094.47916666666</v>
+        <v>46107.47916666666</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>1023.802568936242</v>
+        <v>1096.189455446981</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46094.48958333334</v>
+        <v>46107.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>1016.832602923882</v>
+        <v>1081.298371592312</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46094.5</v>
+        <v>46107.5</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>1009.862636911521</v>
+        <v>1066.407287737643</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46094.51041666666</v>
+        <v>46107.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>1000.842151865609</v>
+        <v>1096.924040274087</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46094.52083333334</v>
+        <v>46107.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>991.821666819697</v>
+        <v>1127.440792810532</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46094.53125</v>
+        <v>46107.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>982.8011817737851</v>
+        <v>1157.957545346977</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46094.54166666666</v>
+        <v>46107.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>973.7806967278731</v>
+        <v>1188.474297883421</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46094.55208333334</v>
+        <v>46107.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>1001.975333436465</v>
+        <v>1204.970974288766</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46094.5625</v>
+        <v>46107.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1030.169970145057</v>
+        <v>1221.467650694111</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46094.57291666666</v>
+        <v>46107.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1058.364606853649</v>
+        <v>1237.964327099456</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46094.58333333334</v>
+        <v>46107.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>1086.559243562241</v>
+        <v>1254.461003504801</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46094.59375</v>
+        <v>46107.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>1191.549415471005</v>
+        <v>1296.74160734553</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46094.60416666666</v>
+        <v>46107.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1296.539587379769</v>
+        <v>1339.02221118626</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46094.61458333334</v>
+        <v>46107.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>1401.529759288534</v>
+        <v>1381.30281502699</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46094.625</v>
+        <v>46107.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1506.519931197298</v>
+        <v>1423.58341886772</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46094.63541666666</v>
+        <v>46107.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1720.169624864299</v>
+        <v>1588.382277819099</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46094.64583333334</v>
+        <v>46107.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1933.8193185313</v>
+        <v>1753.181136770479</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46094.65625</v>
+        <v>46107.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>2147.469012198301</v>
+        <v>1917.979995721859</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46094.66666666666</v>
+        <v>46107.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>2361.118705865302</v>
+        <v>2082.778854673239</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46094.67708333334</v>
+        <v>46107.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>2398.387788646658</v>
+        <v>2150.685974914918</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46094.6875</v>
+        <v>46107.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>2435.656871428014</v>
+        <v>2218.593095156597</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46094.69791666666</v>
+        <v>46107.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>2472.92595420937</v>
+        <v>2286.500215398276</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46094.70833333334</v>
+        <v>46107.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>2510.195036990726</v>
+        <v>2354.407335639956</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46094.71875</v>
+        <v>46107.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>2527.300682610889</v>
+        <v>2385.09199327948</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46094.72916666666</v>
+        <v>46107.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>2544.406328231051</v>
+        <v>2415.776650919004</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46094.73958333334</v>
+        <v>46107.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>2561.511973851213</v>
+        <v>2446.461308558528</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46094.75</v>
+        <v>46107.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>2578.617619471376</v>
+        <v>2477.145966198052</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46094.76041666666</v>
+        <v>46107.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2573.086614184075</v>
+        <v>2479.874424127795</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46094.77083333334</v>
+        <v>46107.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2567.555608896774</v>
+        <v>2482.602882057537</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46094.78125</v>
+        <v>46107.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2562.024603609474</v>
+        <v>2485.33133998728</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46094.79166666666</v>
+        <v>46107.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2556.493598322173</v>
+        <v>2488.059797917023</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46094.80208333334</v>
+        <v>46107.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2538.866329439142</v>
+        <v>2462.003024688791</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46094.8125</v>
+        <v>46107.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2521.239060556111</v>
+        <v>2435.946251460559</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46094.82291666666</v>
+        <v>46107.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2503.611791673081</v>
+        <v>2409.889478232328</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46094.83333333334</v>
+        <v>46107.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2485.98452279005</v>
+        <v>2383.832705004096</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46094.84375</v>
+        <v>46107.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2459.120924752233</v>
+        <v>2342.895341990269</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46094.85416666666</v>
+        <v>46107.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2432.257326714417</v>
+        <v>2301.957978976441</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46094.86458333334</v>
+        <v>46107.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2405.3937286766</v>
+        <v>2261.020615962614</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46094.875</v>
+        <v>46107.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2378.530130638784</v>
+        <v>2220.083252948787</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46094.88541666666</v>
+        <v>46107.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2342.547119005738</v>
+        <v>2166.521524975881</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46094.89583333334</v>
+        <v>46107.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2306.564107372692</v>
+        <v>2112.959797002975</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46094.90625</v>
+        <v>46107.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2270.581095739645</v>
+        <v>2059.39806903007</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46094.91666666666</v>
+        <v>46107.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2234.598084106599</v>
+        <v>2005.836341057164</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46094.92708333334</v>
+        <v>46107.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>2201.753805554754</v>
+        <v>1924.759164270302</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46094.9375</v>
+        <v>46107.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>2168.909527002908</v>
+        <v>1843.681987483441</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46094.94791666666</v>
+        <v>46107.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>2136.065248451063</v>
+        <v>1762.604810696579</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46094.95833333334</v>
+        <v>46107.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>2103.220969899218</v>
+        <v>1681.527633909717</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46094.96875</v>
+        <v>46107.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>2079.702246046563</v>
+        <v>1624.793757216004</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46094.97916666666</v>
+        <v>46107.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>2056.183522193909</v>
+        <v>1568.059880522291</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46094.98958333334</v>
+        <v>46107.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>2032.664798341254</v>
+        <v>1511.326003828578</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46095</v>
+        <v>46108</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>2009.1460744886</v>
+        <v>1454.592127134865</v>
       </c>
       <c r="E97">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -412,7 +412,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46107.01041666666</v>
+        <v>46108.01041666666</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -421,7 +421,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1422.355612799569</v>
+        <v>1488.719005294963</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -429,7 +429,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46107.02083333334</v>
+        <v>46108.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -438,7 +438,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1409.66828342666</v>
+        <v>1471.130451305404</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -446,7 +446,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46107.03125</v>
+        <v>46108.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -455,7 +455,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1396.980954053752</v>
+        <v>1453.541897315845</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -463,7 +463,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46107.04166666666</v>
+        <v>46108.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -472,7 +472,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1384.293624680843</v>
+        <v>1435.953343326285</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -480,7 +480,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46107.05208333334</v>
+        <v>46108.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -489,7 +489,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1379.581787717703</v>
+        <v>1431.160546546744</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -497,7 +497,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46107.0625</v>
+        <v>46108.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -506,7 +506,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1374.869950754563</v>
+        <v>1426.367749767202</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46107.07291666666</v>
+        <v>46108.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -523,7 +523,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1370.158113791423</v>
+        <v>1421.574952987661</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46107.08333333334</v>
+        <v>46108.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1365.446276828284</v>
+        <v>1416.782156208119</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -548,7 +548,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46107.09375</v>
+        <v>46108.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -557,7 +557,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1364.48082248399</v>
+        <v>1419.475999831185</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -565,7 +565,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46107.10416666666</v>
+        <v>46108.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -574,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1363.515368139696</v>
+        <v>1422.169843454251</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -582,7 +582,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46107.11458333334</v>
+        <v>46108.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>1362.549913795403</v>
+        <v>1424.863687077318</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -599,7 +599,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46107.125</v>
+        <v>46108.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -608,7 +608,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>1361.584459451109</v>
+        <v>1427.557530700384</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -616,7 +616,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46107.13541666666</v>
+        <v>46108.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -625,7 +625,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>1380.347854751841</v>
+        <v>1453.418429482779</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -633,7 +633,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46107.14583333334</v>
+        <v>46108.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>1399.111250052573</v>
+        <v>1479.279328265175</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46107.15625</v>
+        <v>46108.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -659,7 +659,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>1417.874645353305</v>
+        <v>1505.14022704757</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -667,7 +667,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46107.16666666666</v>
+        <v>46108.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>1436.638040654037</v>
+        <v>1531.001125829966</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -684,7 +684,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46107.17708333334</v>
+        <v>46108.17708333334</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -693,7 +693,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>1474.343230428215</v>
+        <v>1579.894387590457</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -701,7 +701,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46107.1875</v>
+        <v>46108.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -710,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>1512.048420202392</v>
+        <v>1628.787649350949</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -718,7 +718,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46107.19791666666</v>
+        <v>46108.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -727,7 +727,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>1549.753609976569</v>
+        <v>1677.680911111441</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46107.20833333334</v>
+        <v>46108.20833333334</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -744,7 +744,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>1587.458799750746</v>
+        <v>1726.574172871932</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -752,7 +752,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46107.21875</v>
+        <v>46108.21875</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>1646.456455445116</v>
+        <v>1776.017427705191</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -769,7 +769,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46107.22916666666</v>
+        <v>46108.22916666666</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>1705.454111139486</v>
+        <v>1825.46068253845</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46107.23958333334</v>
+        <v>46108.23958333334</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>1764.451766833855</v>
+        <v>1874.903937371709</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -803,7 +803,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46107.25</v>
+        <v>46108.25</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -812,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>1823.449422528225</v>
+        <v>1924.347192204967</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -820,7 +820,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46107.26041666666</v>
+        <v>46108.26041666666</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -829,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>1805.032331503035</v>
+        <v>1896.01693676818</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -837,7 +837,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46107.27083333334</v>
+        <v>46108.27083333334</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>1786.615240477845</v>
+        <v>1867.686681331392</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -854,7 +854,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46107.28125</v>
+        <v>46108.28125</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -863,7 +863,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>1768.198149452655</v>
+        <v>1839.356425894605</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -871,7 +871,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46107.29166666666</v>
+        <v>46108.29166666666</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>1749.781058427465</v>
+        <v>1811.026170457817</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -888,7 +888,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46107.30208333334</v>
+        <v>46108.30208333334</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>1678.379413222112</v>
+        <v>1725.30582149913</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46107.3125</v>
+        <v>46108.3125</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>1606.97776801676</v>
+        <v>1639.585472540442</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46107.32291666666</v>
+        <v>46108.32291666666</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -931,7 +931,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>1535.576122811407</v>
+        <v>1553.865123581754</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -939,7 +939,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46107.33333333334</v>
+        <v>46108.33333333334</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -948,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>1464.174477606055</v>
+        <v>1468.144774623066</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -956,7 +956,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46107.34375</v>
+        <v>46108.34375</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -965,7 +965,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>1409.867670736905</v>
+        <v>1403.25681635004</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -973,7 +973,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46107.35416666666</v>
+        <v>46108.35416666666</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -982,7 +982,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>1355.560863867754</v>
+        <v>1338.368858077014</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -990,7 +990,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46107.36458333334</v>
+        <v>46108.36458333334</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -999,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>1301.254056998604</v>
+        <v>1273.480899803989</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46107.375</v>
+        <v>46108.375</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1016,7 +1016,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>1246.947250129453</v>
+        <v>1208.592941530963</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1024,7 +1024,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46107.38541666666</v>
+        <v>46108.38541666666</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>1217.38545786843</v>
+        <v>1158.6333666699</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1041,7 +1041,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46107.39583333334</v>
+        <v>46108.39583333334</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>1187.823665607406</v>
+        <v>1108.673791808837</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46107.40625</v>
+        <v>46108.40625</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1067,7 +1067,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>1158.261873346382</v>
+        <v>1058.714216947775</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1075,7 +1075,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46107.41666666666</v>
+        <v>46108.41666666666</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>1128.700081085359</v>
+        <v>1008.754642086712</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46107.42708333334</v>
+        <v>46108.42708333334</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>1128.017966603099</v>
+        <v>1015.983122475495</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46107.4375</v>
+        <v>46108.4375</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>1127.335852120839</v>
+        <v>1023.211602864278</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46107.44791666666</v>
+        <v>46108.44791666666</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>1126.65373763858</v>
+        <v>1030.440083253061</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46107.45833333334</v>
+        <v>46108.45833333334</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>1125.97162315632</v>
+        <v>1037.668563641844</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46107.46875</v>
+        <v>46108.46875</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1169,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>1111.080539301651</v>
+        <v>1042.236873452684</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46107.47916666666</v>
+        <v>46108.47916666666</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>1096.189455446981</v>
+        <v>1046.805183263522</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46107.48958333334</v>
+        <v>46108.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>1081.298371592312</v>
+        <v>1051.373493074361</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46107.5</v>
+        <v>46108.5</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>1066.407287737643</v>
+        <v>1055.9418028852</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46107.51041666666</v>
+        <v>46108.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>1096.924040274087</v>
+        <v>1086.112851464716</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46107.52083333334</v>
+        <v>46108.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>1127.440792810532</v>
+        <v>1116.283900044232</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46107.53125</v>
+        <v>46108.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>1157.957545346977</v>
+        <v>1146.454948623747</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46107.54166666666</v>
+        <v>46108.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>1188.474297883421</v>
+        <v>1176.625997203263</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46107.55208333334</v>
+        <v>46108.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>1204.970974288766</v>
+        <v>1198.535925338226</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46107.5625</v>
+        <v>46108.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1221.467650694111</v>
+        <v>1220.445853473189</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46107.57291666666</v>
+        <v>46108.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1237.964327099456</v>
+        <v>1242.355781608152</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46107.58333333334</v>
+        <v>46108.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>1254.461003504801</v>
+        <v>1264.265709743115</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46107.59375</v>
+        <v>46108.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>1296.74160734553</v>
+        <v>1326.684311361591</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46107.60416666666</v>
+        <v>46108.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1339.02221118626</v>
+        <v>1389.102912980066</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46107.61458333334</v>
+        <v>46108.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>1381.30281502699</v>
+        <v>1451.521514598541</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46107.625</v>
+        <v>46108.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1423.58341886772</v>
+        <v>1513.940116217016</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46107.63541666666</v>
+        <v>46108.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1588.382277819099</v>
+        <v>1675.267676198983</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46107.64583333334</v>
+        <v>46108.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1753.181136770479</v>
+        <v>1836.59523618095</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46107.65625</v>
+        <v>46108.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1917.979995721859</v>
+        <v>1997.922796162916</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46107.66666666666</v>
+        <v>46108.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>2082.778854673239</v>
+        <v>2159.250356144883</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46107.67708333334</v>
+        <v>46108.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>2150.685974914918</v>
+        <v>2230.087219085513</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46107.6875</v>
+        <v>46108.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>2218.593095156597</v>
+        <v>2300.924082026141</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46107.69791666666</v>
+        <v>46108.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>2286.500215398276</v>
+        <v>2371.76094496677</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46107.70833333334</v>
+        <v>46108.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>2354.407335639956</v>
+        <v>2442.597807907399</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46107.71875</v>
+        <v>46108.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>2385.09199327948</v>
+        <v>2475.45147576179</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46107.72916666666</v>
+        <v>46108.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>2415.776650919004</v>
+        <v>2508.305143616181</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46107.73958333334</v>
+        <v>46108.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>2446.461308558528</v>
+        <v>2541.158811470572</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46107.75</v>
+        <v>46108.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>2477.145966198052</v>
+        <v>2574.012479324963</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46107.76041666666</v>
+        <v>46108.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2479.874424127795</v>
+        <v>2581.095043184019</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46107.77083333334</v>
+        <v>46108.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2482.602882057537</v>
+        <v>2588.177607043075</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46107.78125</v>
+        <v>46108.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2485.33133998728</v>
+        <v>2595.260170902131</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46107.79166666666</v>
+        <v>46108.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2488.059797917023</v>
+        <v>2602.342734761186</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46107.80208333334</v>
+        <v>46108.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2462.003024688791</v>
+        <v>2573.597178432204</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46107.8125</v>
+        <v>46108.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2435.946251460559</v>
+        <v>2544.851622103221</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46107.82291666666</v>
+        <v>46108.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2409.889478232328</v>
+        <v>2516.106065774239</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46107.83333333334</v>
+        <v>46108.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2383.832705004096</v>
+        <v>2487.360509445256</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46107.84375</v>
+        <v>46108.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2342.895341990269</v>
+        <v>2432.159163867705</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46107.85416666666</v>
+        <v>46108.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2301.957978976441</v>
+        <v>2376.957818290152</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46107.86458333334</v>
+        <v>46108.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2261.020615962614</v>
+        <v>2321.7564727126</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46107.875</v>
+        <v>46108.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2220.083252948787</v>
+        <v>2266.555127135049</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46107.88541666666</v>
+        <v>46108.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2166.521524975881</v>
+        <v>2207.178323940908</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46107.89583333334</v>
+        <v>46108.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2112.959797002975</v>
+        <v>2147.801520746767</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46107.90625</v>
+        <v>46108.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2059.39806903007</v>
+        <v>2088.424717552627</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46107.91666666666</v>
+        <v>46108.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2005.836341057164</v>
+        <v>2029.047914358486</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46107.92708333334</v>
+        <v>46108.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>1924.759164270302</v>
+        <v>1956.841680909403</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46107.9375</v>
+        <v>46108.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>1843.681987483441</v>
+        <v>1884.63544746032</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46107.94791666666</v>
+        <v>46108.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>1762.604810696579</v>
+        <v>1812.429214011237</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46107.95833333334</v>
+        <v>46108.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>1681.527633909717</v>
+        <v>1740.222980562154</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46107.96875</v>
+        <v>46108.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>1624.793757216004</v>
+        <v>1667.386112617813</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46107.97916666666</v>
+        <v>46108.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>1568.059880522291</v>
+        <v>1594.549244673471</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46107.98958333334</v>
+        <v>46108.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1511.326003828578</v>
+        <v>1521.712376729129</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1454.592127134865</v>
+        <v>1448.875508784787</v>
       </c>
       <c r="E97">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -412,517 +412,517 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46108.01041666666</v>
+        <v>46111.01041666666</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="D2">
-        <v>1488.719005294963</v>
+        <v>1414.729394929594</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46108.02083333334</v>
+        <v>46111.02083333334</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>287</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1035</v>
       </c>
       <c r="D3">
-        <v>1471.130451305404</v>
+        <v>1403.211378762572</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46108.03125</v>
+        <v>46111.03125</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1053</v>
       </c>
       <c r="D4">
-        <v>1453.541897315845</v>
+        <v>1391.693362595549</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46108.04166666666</v>
+        <v>46111.04166666666</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1054</v>
       </c>
       <c r="D5">
-        <v>1435.953343326285</v>
+        <v>1380.175346428527</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46108.05208333334</v>
+        <v>46111.05208333334</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1072</v>
       </c>
       <c r="D6">
-        <v>1431.160546546744</v>
+        <v>1368.275157553823</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46108.0625</v>
+        <v>46111.0625</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1075</v>
       </c>
       <c r="D7">
-        <v>1426.367749767202</v>
+        <v>1356.374968679118</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46108.07291666666</v>
+        <v>46111.07291666666</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1077</v>
       </c>
       <c r="D8">
-        <v>1421.574952987661</v>
+        <v>1344.474779804413</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46108.08333333334</v>
+        <v>46111.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1072</v>
       </c>
       <c r="D9">
-        <v>1416.782156208119</v>
+        <v>1332.574590929709</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46108.09375</v>
+        <v>46111.09375</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1066</v>
       </c>
       <c r="D10">
-        <v>1419.475999831185</v>
+        <v>1333.390010117023</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46108.10416666666</v>
+        <v>46111.10416666666</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1065</v>
       </c>
       <c r="D11">
-        <v>1422.169843454251</v>
+        <v>1334.205429304337</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46108.11458333334</v>
+        <v>46111.11458333334</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1066</v>
       </c>
       <c r="D12">
-        <v>1424.863687077318</v>
+        <v>1335.020848491651</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46108.125</v>
+        <v>46111.125</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="D13">
-        <v>1427.557530700384</v>
+        <v>1335.836267678965</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46108.13541666666</v>
+        <v>46111.13541666666</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>1058</v>
       </c>
       <c r="D14">
-        <v>1453.418429482779</v>
+        <v>1363.183630835206</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46108.14583333334</v>
+        <v>46111.14583333334</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1057</v>
       </c>
       <c r="D15">
-        <v>1479.279328265175</v>
+        <v>1390.530993991447</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46108.15625</v>
+        <v>46111.15625</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>1075</v>
       </c>
       <c r="D16">
-        <v>1505.14022704757</v>
+        <v>1417.878357147688</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46108.16666666666</v>
+        <v>46111.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1244</v>
       </c>
       <c r="D17">
-        <v>1531.001125829966</v>
+        <v>1445.225720303929</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46108.17708333334</v>
+        <v>46111.17708333334</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1271</v>
       </c>
       <c r="D18">
-        <v>1579.894387590457</v>
+        <v>1507.317337732642</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46108.1875</v>
+        <v>46111.1875</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="D19">
-        <v>1628.787649350949</v>
+        <v>1569.408955161355</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46108.19791666666</v>
+        <v>46111.19791666666</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1266</v>
       </c>
       <c r="D20">
-        <v>1677.680911111441</v>
+        <v>1631.500572590067</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46108.20833333334</v>
+        <v>46111.20833333334</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>304</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>1264</v>
       </c>
       <c r="D21">
-        <v>1726.574172871932</v>
+        <v>1693.59219001878</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46108.21875</v>
+        <v>46111.21875</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1387</v>
       </c>
       <c r="D22">
-        <v>1776.017427705191</v>
+        <v>1746.279188742539</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46108.22916666666</v>
+        <v>46111.22916666666</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1373</v>
       </c>
       <c r="D23">
-        <v>1825.46068253845</v>
+        <v>1798.966187466299</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46108.23958333334</v>
+        <v>46111.23958333334</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>1874.903937371709</v>
+        <v>1851.653186190058</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>369</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46108.25</v>
+        <v>46111.25</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>406</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1395</v>
       </c>
       <c r="D25">
-        <v>1924.347192204967</v>
+        <v>1904.340184913817</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46108.26041666666</v>
+        <v>46111.26041666666</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1441</v>
       </c>
       <c r="D26">
-        <v>1896.01693676818</v>
+        <v>1894.322680944701</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46108.27083333334</v>
+        <v>46111.27083333334</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>717</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1451</v>
       </c>
       <c r="D27">
-        <v>1867.686681331392</v>
+        <v>1884.305176975584</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46108.28125</v>
+        <v>46111.28125</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>725</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1454</v>
       </c>
       <c r="D28">
-        <v>1839.356425894605</v>
+        <v>1874.287673006468</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46108.29166666666</v>
+        <v>46111.29166666666</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1456</v>
       </c>
       <c r="D29">
-        <v>1811.026170457817</v>
+        <v>1864.270169037351</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46108.30208333334</v>
+        <v>46111.30208333334</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1513</v>
       </c>
       <c r="D30">
-        <v>1725.30582149913</v>
+        <v>1803.362054187044</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46108.3125</v>
+        <v>46111.3125</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>922</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1522</v>
       </c>
       <c r="D31">
-        <v>1639.585472540442</v>
+        <v>1742.453939336736</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46108.32291666666</v>
+        <v>46111.32291666666</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -931,7 +931,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>1553.865123581754</v>
+        <v>1681.545824486428</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -939,7 +939,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46108.33333333334</v>
+        <v>46111.33333333334</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -948,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>1468.144774623066</v>
+        <v>1620.63770963612</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -956,7 +956,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46108.34375</v>
+        <v>46111.34375</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -965,7 +965,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>1403.25681635004</v>
+        <v>1552.15306488534</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -973,7 +973,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46108.35416666666</v>
+        <v>46111.35416666666</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -982,7 +982,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>1338.368858077014</v>
+        <v>1483.66842013456</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -990,7 +990,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46108.36458333334</v>
+        <v>46111.36458333334</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -999,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>1273.480899803989</v>
+        <v>1415.183775383779</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46108.375</v>
+        <v>46111.375</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1016,7 +1016,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>1208.592941530963</v>
+        <v>1346.699130632999</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1024,7 +1024,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46108.38541666666</v>
+        <v>46111.38541666666</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>1158.6333666699</v>
+        <v>1304.536851269272</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1041,7 +1041,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46108.39583333334</v>
+        <v>46111.39583333334</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>1108.673791808837</v>
+        <v>1262.374571905546</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46108.40625</v>
+        <v>46111.40625</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1067,7 +1067,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>1058.714216947775</v>
+        <v>1220.212292541819</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1075,7 +1075,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46108.41666666666</v>
+        <v>46111.41666666666</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>1008.754642086712</v>
+        <v>1178.050013178093</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46108.42708333334</v>
+        <v>46111.42708333334</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>1015.983122475495</v>
+        <v>1156.577894965849</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46108.4375</v>
+        <v>46111.4375</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>1023.211602864278</v>
+        <v>1135.105776753606</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46108.44791666666</v>
+        <v>46111.44791666666</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>1030.440083253061</v>
+        <v>1113.633658541362</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46108.45833333334</v>
+        <v>46111.45833333334</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>1037.668563641844</v>
+        <v>1092.161540329119</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46108.46875</v>
+        <v>46111.46875</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1169,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>1042.236873452684</v>
+        <v>1097.983950336447</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46108.47916666666</v>
+        <v>46111.47916666666</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>1046.805183263522</v>
+        <v>1103.806360343776</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46108.48958333334</v>
+        <v>46111.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>1051.373493074361</v>
+        <v>1109.628770351104</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46108.5</v>
+        <v>46111.5</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>1055.9418028852</v>
+        <v>1115.451180358432</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46108.51041666666</v>
+        <v>46111.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>1086.112851464716</v>
+        <v>1139.765818156968</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46108.52083333334</v>
+        <v>46111.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>1116.283900044232</v>
+        <v>1164.080455955504</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46108.53125</v>
+        <v>46111.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>1146.454948623747</v>
+        <v>1188.39509375404</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46108.54166666666</v>
+        <v>46111.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>1176.625997203263</v>
+        <v>1212.709731552576</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46108.55208333334</v>
+        <v>46111.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>1198.535925338226</v>
+        <v>1248.045737114481</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46108.5625</v>
+        <v>46111.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1220.445853473189</v>
+        <v>1283.381742676387</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46108.57291666666</v>
+        <v>46111.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1242.355781608152</v>
+        <v>1318.717748238293</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46108.58333333334</v>
+        <v>46111.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>1264.265709743115</v>
+        <v>1354.053753800198</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46108.59375</v>
+        <v>46111.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>1326.684311361591</v>
+        <v>1389.347491412807</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46108.60416666666</v>
+        <v>46111.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1389.102912980066</v>
+        <v>1424.641229025415</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46108.61458333334</v>
+        <v>46111.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>1451.521514598541</v>
+        <v>1459.934966638024</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46108.625</v>
+        <v>46111.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1513.940116217016</v>
+        <v>1495.228704250632</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46108.63541666666</v>
+        <v>46111.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1675.267676198983</v>
+        <v>1610.894947337178</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46108.64583333334</v>
+        <v>46111.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1836.59523618095</v>
+        <v>1726.561190423724</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46108.65625</v>
+        <v>46111.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1997.922796162916</v>
+        <v>1842.22743351027</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46108.66666666666</v>
+        <v>46111.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>2159.250356144883</v>
+        <v>1957.893676596816</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46108.67708333334</v>
+        <v>46111.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>2230.087219085513</v>
+        <v>2044.585240481448</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46108.6875</v>
+        <v>46111.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>2300.924082026141</v>
+        <v>2131.276804366081</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46108.69791666666</v>
+        <v>46111.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>2371.76094496677</v>
+        <v>2217.968368250713</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46108.70833333334</v>
+        <v>46111.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>2442.597807907399</v>
+        <v>2304.659932135346</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46108.71875</v>
+        <v>46111.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>2475.45147576179</v>
+        <v>2331.140802332024</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46108.72916666666</v>
+        <v>46111.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>2508.305143616181</v>
+        <v>2357.621672528702</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46108.73958333334</v>
+        <v>46111.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>2541.158811470572</v>
+        <v>2384.10254272538</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46108.75</v>
+        <v>46111.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>2574.012479324963</v>
+        <v>2410.583412922058</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46108.76041666666</v>
+        <v>46111.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2581.095043184019</v>
+        <v>2430.248576304549</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46108.77083333334</v>
+        <v>46111.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2588.177607043075</v>
+        <v>2449.913739687039</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46108.78125</v>
+        <v>46111.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2595.260170902131</v>
+        <v>2469.578903069529</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46108.79166666666</v>
+        <v>46111.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2602.342734761186</v>
+        <v>2489.24406645202</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46108.80208333334</v>
+        <v>46111.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2573.597178432204</v>
+        <v>2467.845917150985</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46108.8125</v>
+        <v>46111.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2544.851622103221</v>
+        <v>2446.447767849951</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46108.82291666666</v>
+        <v>46111.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2516.106065774239</v>
+        <v>2425.049618548916</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46108.83333333334</v>
+        <v>46111.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2487.360509445256</v>
+        <v>2403.651469247881</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46108.84375</v>
+        <v>46111.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2432.159163867705</v>
+        <v>2355.846418660934</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46108.85416666666</v>
+        <v>46111.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2376.957818290152</v>
+        <v>2308.041368073988</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46108.86458333334</v>
+        <v>46111.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2321.7564727126</v>
+        <v>2260.236317487042</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46108.875</v>
+        <v>46111.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2266.555127135049</v>
+        <v>2212.431266900095</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46108.88541666666</v>
+        <v>46111.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2207.178323940908</v>
+        <v>2149.314651702558</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46108.89583333334</v>
+        <v>46111.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2147.801520746767</v>
+        <v>2086.198036505022</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46108.90625</v>
+        <v>46111.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2088.424717552627</v>
+        <v>2023.081421307486</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46108.91666666666</v>
+        <v>46111.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2029.047914358486</v>
+        <v>1959.96480610995</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46108.92708333334</v>
+        <v>46111.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>1956.841680909403</v>
+        <v>1871.857265925752</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46108.9375</v>
+        <v>46111.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>1884.63544746032</v>
+        <v>1783.749725741554</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46108.94791666666</v>
+        <v>46111.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>1812.429214011237</v>
+        <v>1695.642185557357</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46108.95833333334</v>
+        <v>46111.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>1740.222980562154</v>
+        <v>1607.534645373159</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46108.96875</v>
+        <v>46111.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>1667.386112617813</v>
+        <v>1581.001689026799</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46108.97916666666</v>
+        <v>46111.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>1594.549244673471</v>
+        <v>1554.46873268044</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46108.98958333334</v>
+        <v>46111.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1521.712376729129</v>
+        <v>1527.935776334081</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46109</v>
+        <v>46112</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1448.875508784787</v>
+        <v>1501.402819987721</v>
       </c>
       <c r="E97">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -412,874 +412,874 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46111.01041666666</v>
+        <v>46115.01041666666</v>
       </c>
       <c r="B2">
-        <v>290</v>
+        <v>479</v>
       </c>
       <c r="C2">
-        <v>1023</v>
+        <v>1726</v>
       </c>
       <c r="D2">
-        <v>1414.729394929594</v>
+        <v>2190.000220583806</v>
       </c>
       <c r="E2">
-        <v>1313</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46111.02083333334</v>
+        <v>46115.02083333334</v>
       </c>
       <c r="B3">
-        <v>287</v>
+        <v>482</v>
       </c>
       <c r="C3">
-        <v>1035</v>
+        <v>1715</v>
       </c>
       <c r="D3">
-        <v>1403.211378762572</v>
+        <v>2191.009764657763</v>
       </c>
       <c r="E3">
-        <v>1322</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46111.03125</v>
+        <v>46115.03125</v>
       </c>
       <c r="B4">
-        <v>286</v>
+        <v>488</v>
       </c>
       <c r="C4">
-        <v>1053</v>
+        <v>1724</v>
       </c>
       <c r="D4">
-        <v>1391.693362595549</v>
+        <v>2192.019308731721</v>
       </c>
       <c r="E4">
-        <v>1339</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46111.04166666666</v>
+        <v>46115.04166666666</v>
       </c>
       <c r="B5">
-        <v>285</v>
+        <v>480</v>
       </c>
       <c r="C5">
-        <v>1054</v>
+        <v>1715</v>
       </c>
       <c r="D5">
-        <v>1380.175346428527</v>
+        <v>2193.028852805678</v>
       </c>
       <c r="E5">
-        <v>1339</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46111.05208333334</v>
+        <v>46115.05208333334</v>
       </c>
       <c r="B6">
-        <v>292</v>
+        <v>485</v>
       </c>
       <c r="C6">
-        <v>1072</v>
+        <v>1684</v>
       </c>
       <c r="D6">
-        <v>1368.275157553823</v>
+        <v>2212.21019021087</v>
       </c>
       <c r="E6">
-        <v>1364</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46111.0625</v>
+        <v>46115.0625</v>
       </c>
       <c r="B7">
-        <v>286</v>
+        <v>486</v>
       </c>
       <c r="C7">
-        <v>1075</v>
+        <v>1675</v>
       </c>
       <c r="D7">
-        <v>1356.374968679118</v>
+        <v>2231.391527616062</v>
       </c>
       <c r="E7">
-        <v>1361</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46111.07291666666</v>
+        <v>46115.07291666666</v>
       </c>
       <c r="B8">
-        <v>291</v>
+        <v>487</v>
       </c>
       <c r="C8">
-        <v>1077</v>
+        <v>1674</v>
       </c>
       <c r="D8">
-        <v>1344.474779804413</v>
+        <v>2250.572865021254</v>
       </c>
       <c r="E8">
-        <v>1368</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46111.08333333334</v>
+        <v>46115.08333333334</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>489</v>
       </c>
       <c r="C9">
-        <v>1072</v>
+        <v>1675</v>
       </c>
       <c r="D9">
-        <v>1332.574590929709</v>
+        <v>2269.754202426446</v>
       </c>
       <c r="E9">
-        <v>1072</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46111.09375</v>
+        <v>46115.09375</v>
       </c>
       <c r="B10">
-        <v>293</v>
+        <v>488</v>
       </c>
       <c r="C10">
-        <v>1066</v>
+        <v>1644</v>
       </c>
       <c r="D10">
-        <v>1333.390010117023</v>
+        <v>2251.669653644861</v>
       </c>
       <c r="E10">
-        <v>1359</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46111.10416666666</v>
+        <v>46115.10416666666</v>
       </c>
       <c r="B11">
-        <v>290</v>
+        <v>487</v>
       </c>
       <c r="C11">
-        <v>1065</v>
+        <v>1639</v>
       </c>
       <c r="D11">
-        <v>1334.205429304337</v>
+        <v>2233.585104863276</v>
       </c>
       <c r="E11">
-        <v>1355</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46111.11458333334</v>
+        <v>46115.11458333334</v>
       </c>
       <c r="B12">
-        <v>291</v>
+        <v>490</v>
       </c>
       <c r="C12">
-        <v>1066</v>
+        <v>1640</v>
       </c>
       <c r="D12">
-        <v>1335.020848491651</v>
+        <v>2215.500556081691</v>
       </c>
       <c r="E12">
-        <v>1357</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46111.125</v>
+        <v>46115.125</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>488</v>
       </c>
       <c r="C13">
-        <v>1064</v>
+        <v>1639</v>
       </c>
       <c r="D13">
-        <v>1335.836267678965</v>
+        <v>2197.416007300106</v>
       </c>
       <c r="E13">
-        <v>1064</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46111.13541666666</v>
+        <v>46115.13541666666</v>
       </c>
       <c r="B14">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="C14">
-        <v>1058</v>
+        <v>1593</v>
       </c>
       <c r="D14">
-        <v>1363.183630835206</v>
+        <v>2211.163255615948</v>
       </c>
       <c r="E14">
-        <v>1353</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46111.14583333334</v>
+        <v>46115.14583333334</v>
       </c>
       <c r="B15">
-        <v>310</v>
+        <v>512</v>
       </c>
       <c r="C15">
-        <v>1057</v>
+        <v>1590</v>
       </c>
       <c r="D15">
-        <v>1390.530993991447</v>
+        <v>2224.91050393179</v>
       </c>
       <c r="E15">
-        <v>1367</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46111.15625</v>
+        <v>46115.15625</v>
       </c>
       <c r="B16">
-        <v>307</v>
+        <v>513</v>
       </c>
       <c r="C16">
-        <v>1075</v>
+        <v>1593</v>
       </c>
       <c r="D16">
-        <v>1417.878357147688</v>
+        <v>2238.657752247632</v>
       </c>
       <c r="E16">
-        <v>1382</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46111.16666666666</v>
+        <v>46115.16666666666</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="C17">
-        <v>1244</v>
+        <v>1592</v>
       </c>
       <c r="D17">
-        <v>1445.225720303929</v>
+        <v>2252.405000563474</v>
       </c>
       <c r="E17">
-        <v>1244</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46111.17708333334</v>
+        <v>46115.17708333334</v>
       </c>
       <c r="B18">
-        <v>293</v>
+        <v>532</v>
       </c>
       <c r="C18">
-        <v>1271</v>
+        <v>1701</v>
       </c>
       <c r="D18">
-        <v>1507.317337732642</v>
+        <v>2318.77317579566</v>
       </c>
       <c r="E18">
-        <v>1564</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46111.1875</v>
+        <v>46115.1875</v>
       </c>
       <c r="B19">
-        <v>300</v>
+        <v>534</v>
       </c>
       <c r="C19">
-        <v>1272</v>
+        <v>1713</v>
       </c>
       <c r="D19">
-        <v>1569.408955161355</v>
+        <v>2385.141351027845</v>
       </c>
       <c r="E19">
-        <v>1572</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46111.19791666666</v>
+        <v>46115.19791666666</v>
       </c>
       <c r="B20">
-        <v>292</v>
+        <v>532</v>
       </c>
       <c r="C20">
-        <v>1266</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>1631.500572590067</v>
+        <v>2451.50952626003</v>
       </c>
       <c r="E20">
-        <v>1558</v>
+        <v>532</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46111.20833333334</v>
+        <v>46115.20833333334</v>
       </c>
       <c r="B21">
-        <v>304</v>
+        <v>553</v>
       </c>
       <c r="C21">
-        <v>1264</v>
+        <v>1712</v>
       </c>
       <c r="D21">
-        <v>1693.59219001878</v>
+        <v>2517.877701492215</v>
       </c>
       <c r="E21">
-        <v>1568</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46111.21875</v>
+        <v>46115.21875</v>
       </c>
       <c r="B22">
-        <v>390</v>
+        <v>653</v>
       </c>
       <c r="C22">
-        <v>1387</v>
+        <v>1722</v>
       </c>
       <c r="D22">
-        <v>1746.279188742539</v>
+        <v>2572.692205656035</v>
       </c>
       <c r="E22">
-        <v>1777</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46111.22916666666</v>
+        <v>46115.22916666666</v>
       </c>
       <c r="B23">
-        <v>373</v>
+        <v>655</v>
       </c>
       <c r="C23">
-        <v>1373</v>
+        <v>1726</v>
       </c>
       <c r="D23">
-        <v>1798.966187466299</v>
+        <v>2627.506709819855</v>
       </c>
       <c r="E23">
-        <v>1746</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46111.23958333334</v>
+        <v>46115.23958333334</v>
       </c>
       <c r="B24">
-        <v>369</v>
+        <v>657</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1730</v>
       </c>
       <c r="D24">
-        <v>1851.653186190058</v>
+        <v>2682.321213983675</v>
       </c>
       <c r="E24">
-        <v>369</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46111.25</v>
+        <v>46115.25</v>
       </c>
       <c r="B25">
-        <v>406</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>1395</v>
+        <v>1729</v>
       </c>
       <c r="D25">
-        <v>1904.340184913817</v>
+        <v>2737.135718147495</v>
       </c>
       <c r="E25">
-        <v>1801</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46111.26041666666</v>
+        <v>46115.26041666666</v>
       </c>
       <c r="B26">
-        <v>678</v>
+        <v>698</v>
       </c>
       <c r="C26">
-        <v>1441</v>
+        <v>1909</v>
       </c>
       <c r="D26">
-        <v>1894.322680944701</v>
+        <v>2761.115505780943</v>
       </c>
       <c r="E26">
-        <v>2119</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46111.27083333334</v>
+        <v>46115.27083333334</v>
       </c>
       <c r="B27">
-        <v>717</v>
+        <v>695</v>
       </c>
       <c r="C27">
-        <v>1451</v>
+        <v>1907</v>
       </c>
       <c r="D27">
-        <v>1884.305176975584</v>
+        <v>2785.095293414392</v>
       </c>
       <c r="E27">
-        <v>2168</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46111.28125</v>
+        <v>46115.28125</v>
       </c>
       <c r="B28">
-        <v>725</v>
+        <v>700</v>
       </c>
       <c r="C28">
-        <v>1454</v>
+        <v>1910</v>
       </c>
       <c r="D28">
-        <v>1874.287673006468</v>
+        <v>2809.075081047839</v>
       </c>
       <c r="E28">
-        <v>2179</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46111.29166666666</v>
+        <v>46115.29166666666</v>
       </c>
       <c r="B29">
-        <v>720</v>
+        <v>704</v>
       </c>
       <c r="C29">
-        <v>1456</v>
+        <v>1918</v>
       </c>
       <c r="D29">
-        <v>1864.270169037351</v>
+        <v>2833.054868681288</v>
       </c>
       <c r="E29">
-        <v>2176</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46111.30208333334</v>
+        <v>46115.30208333334</v>
       </c>
       <c r="B30">
-        <v>750</v>
+        <v>760</v>
       </c>
       <c r="C30">
-        <v>1513</v>
+        <v>1943</v>
       </c>
       <c r="D30">
-        <v>1803.362054187044</v>
+        <v>2797.982559741334</v>
       </c>
       <c r="E30">
-        <v>2263</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46111.3125</v>
+        <v>46115.3125</v>
       </c>
       <c r="B31">
-        <v>922</v>
+        <v>761</v>
       </c>
       <c r="C31">
-        <v>1522</v>
+        <v>1951</v>
       </c>
       <c r="D31">
-        <v>1742.453939336736</v>
+        <v>2762.91025080138</v>
       </c>
       <c r="E31">
-        <v>2444</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46111.32291666666</v>
+        <v>46115.32291666666</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>754</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>1681.545824486428</v>
+        <v>2727.837941861427</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>754</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46111.33333333334</v>
+        <v>46115.33333333334</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>752</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1953</v>
       </c>
       <c r="D33">
-        <v>1620.63770963612</v>
+        <v>2692.765632921473</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46111.34375</v>
+        <v>46115.34375</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>646</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>1945</v>
       </c>
       <c r="D34">
-        <v>1552.15306488534</v>
+        <v>2635.283938241495</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46111.35416666666</v>
+        <v>46115.35416666666</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>619</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>1947</v>
       </c>
       <c r="D35">
-        <v>1483.66842013456</v>
+        <v>2577.802243561516</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46111.36458333334</v>
+        <v>46115.36458333334</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>625</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>1945</v>
       </c>
       <c r="D36">
-        <v>1415.183775383779</v>
+        <v>2520.320548881537</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46111.375</v>
+        <v>46115.375</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>619</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1943</v>
       </c>
       <c r="D37">
-        <v>1346.699130632999</v>
+        <v>2462.838854201559</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46111.38541666666</v>
+        <v>46115.38541666666</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>577</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1721</v>
       </c>
       <c r="D38">
-        <v>1304.536851269272</v>
+        <v>2435.593627711736</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46111.39583333334</v>
+        <v>46115.39583333334</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>563</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="D39">
-        <v>1262.374571905546</v>
+        <v>2408.348401221914</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46111.40625</v>
+        <v>46115.40625</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>578</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>1703</v>
       </c>
       <c r="D40">
-        <v>1220.212292541819</v>
+        <v>2381.103174732092</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46111.41666666666</v>
+        <v>46115.41666666666</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>582</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>1666</v>
       </c>
       <c r="D41">
-        <v>1178.050013178093</v>
+        <v>2353.85794824227</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46111.42708333334</v>
+        <v>46115.42708333334</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>486</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>1554</v>
       </c>
       <c r="D42">
-        <v>1156.577894965849</v>
+        <v>2307.468774868566</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46111.4375</v>
+        <v>46115.4375</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>526</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>1486</v>
       </c>
       <c r="D43">
-        <v>1135.105776753606</v>
+        <v>2261.079601494862</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46111.44791666666</v>
+        <v>46115.44791666666</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>548</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>1466</v>
       </c>
       <c r="D44">
-        <v>1113.633658541362</v>
+        <v>2214.690428121158</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46111.45833333334</v>
+        <v>46115.45833333334</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>543</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>1464</v>
       </c>
       <c r="D45">
-        <v>1092.161540329119</v>
+        <v>2168.301254747454</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46111.46875</v>
+        <v>46115.46875</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>1456</v>
       </c>
       <c r="D46">
-        <v>1097.983950336447</v>
+        <v>2147.050975165956</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46111.47916666666</v>
+        <v>46115.47916666666</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>468</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>1502</v>
       </c>
       <c r="D47">
-        <v>1103.806360343776</v>
+        <v>2125.800695584458</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46111.48958333334</v>
+        <v>46115.48958333334</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>494</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>1451</v>
       </c>
       <c r="D48">
-        <v>1109.628770351104</v>
+        <v>2104.55041600296</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46111.5</v>
+        <v>46115.5</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>487</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>1444</v>
       </c>
       <c r="D49">
-        <v>1115.451180358432</v>
+        <v>2083.300136421462</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46111.51041666666</v>
+        <v>46115.51041666666</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1396</v>
       </c>
       <c r="D50">
-        <v>1139.765818156968</v>
+        <v>2076.968674821872</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46111.52083333334</v>
+        <v>46115.52083333334</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>468</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>1412</v>
       </c>
       <c r="D51">
-        <v>1164.080455955504</v>
+        <v>2070.637213222283</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46111.53125</v>
+        <v>46115.53125</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1411</v>
       </c>
       <c r="D52">
-        <v>1188.39509375404</v>
+        <v>2064.305751622694</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46111.54166666666</v>
+        <v>46115.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>1212.709731552576</v>
+        <v>2057.974290023105</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46111.55208333334</v>
+        <v>46115.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>1248.045737114481</v>
+        <v>2079.723109888087</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46111.5625</v>
+        <v>46115.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1283.381742676387</v>
+        <v>2101.47192975307</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46111.57291666666</v>
+        <v>46115.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1318.717748238293</v>
+        <v>2123.220749618052</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46111.58333333334</v>
+        <v>46115.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>1354.053753800198</v>
+        <v>2144.969569483034</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46111.59375</v>
+        <v>46115.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>1389.347491412807</v>
+        <v>2195.995167492546</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46111.60416666666</v>
+        <v>46115.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1424.641229025415</v>
+        <v>2247.020765502057</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46111.61458333334</v>
+        <v>46115.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>1459.934966638024</v>
+        <v>2298.046363511568</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46111.625</v>
+        <v>46115.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1495.228704250632</v>
+        <v>2349.071961521079</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46111.63541666666</v>
+        <v>46115.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1610.894947337178</v>
+        <v>2479.228366019014</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46111.64583333334</v>
+        <v>46115.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1726.561190423724</v>
+        <v>2609.384770516948</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46111.65625</v>
+        <v>46115.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1842.22743351027</v>
+        <v>2739.541175014883</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46111.66666666666</v>
+        <v>46115.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>1957.893676596816</v>
+        <v>2869.697579512818</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46111.67708333334</v>
+        <v>46115.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>2044.585240481448</v>
+        <v>2957.727330060626</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46111.6875</v>
+        <v>46115.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>2131.276804366081</v>
+        <v>3045.757080608434</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46111.69791666666</v>
+        <v>46115.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>2217.968368250713</v>
+        <v>3133.786831156242</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46111.70833333334</v>
+        <v>46115.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>2304.659932135346</v>
+        <v>3221.816581704049</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46111.71875</v>
+        <v>46115.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>2331.140802332024</v>
+        <v>3255.567758892655</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46111.72916666666</v>
+        <v>46115.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>2357.621672528702</v>
+        <v>3289.31893608126</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46111.73958333334</v>
+        <v>46115.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>2384.10254272538</v>
+        <v>3323.070113269866</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46111.75</v>
+        <v>46115.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>2410.583412922058</v>
+        <v>3356.821290458472</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46111.76041666666</v>
+        <v>46115.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2430.248576304549</v>
+        <v>3352.247183357875</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46111.77083333334</v>
+        <v>46115.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2449.913739687039</v>
+        <v>3347.673076257278</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46111.78125</v>
+        <v>46115.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2469.578903069529</v>
+        <v>3343.098969156681</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46111.79166666666</v>
+        <v>46115.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2489.24406645202</v>
+        <v>3338.524862056084</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46111.80208333334</v>
+        <v>46115.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2467.845917150985</v>
+        <v>3328.429421316726</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46111.8125</v>
+        <v>46115.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2446.447767849951</v>
+        <v>3318.333980577369</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46111.82291666666</v>
+        <v>46115.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2425.049618548916</v>
+        <v>3308.238539838012</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46111.83333333334</v>
+        <v>46115.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2403.651469247881</v>
+        <v>3298.143099098655</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46111.84375</v>
+        <v>46115.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2355.846418660934</v>
+        <v>3269.913255548886</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46111.85416666666</v>
+        <v>46115.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2308.041368073988</v>
+        <v>3241.683411999117</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46111.86458333334</v>
+        <v>46115.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2260.236317487042</v>
+        <v>3213.453568449348</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46111.875</v>
+        <v>46115.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2212.431266900095</v>
+        <v>3185.223724899579</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46111.88541666666</v>
+        <v>46115.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2149.314651702558</v>
+        <v>3105.494670071237</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46111.89583333334</v>
+        <v>46115.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2086.198036505022</v>
+        <v>3025.765615242895</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46111.90625</v>
+        <v>46115.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2023.081421307486</v>
+        <v>2946.036560414553</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46111.91666666666</v>
+        <v>46115.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>1959.96480610995</v>
+        <v>2866.307505586211</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46111.92708333334</v>
+        <v>46115.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>1871.857265925752</v>
+        <v>2748.327947511006</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46111.9375</v>
+        <v>46115.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>1783.749725741554</v>
+        <v>2630.348389435801</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46111.94791666666</v>
+        <v>46115.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>1695.642185557357</v>
+        <v>2512.368831360597</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46111.95833333334</v>
+        <v>46115.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>1607.534645373159</v>
+        <v>2394.389273285392</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46111.96875</v>
+        <v>46115.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>1581.001689026799</v>
+        <v>2287.524311281194</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46111.97916666666</v>
+        <v>46115.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>1554.46873268044</v>
+        <v>2180.659349276995</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46111.98958333334</v>
+        <v>46115.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1527.935776334081</v>
+        <v>2073.794387272796</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46112</v>
+        <v>46116</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1501.402819987721</v>
+        <v>1966.929425268597</v>
       </c>
       <c r="E97">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -412,874 +412,874 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46115.01041666666</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="B2">
-        <v>479</v>
+        <v>452</v>
       </c>
       <c r="C2">
-        <v>1726</v>
+        <v>1296</v>
       </c>
       <c r="D2">
-        <v>2190.000220583806</v>
+        <v>2022.329757712791</v>
       </c>
       <c r="E2">
-        <v>2205</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46115.02083333334</v>
+        <v>46129.02083333334</v>
       </c>
       <c r="B3">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="C3">
-        <v>1715</v>
+        <v>1292</v>
       </c>
       <c r="D3">
-        <v>2191.009764657763</v>
+        <v>2014.675837888009</v>
       </c>
       <c r="E3">
-        <v>2197</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46115.03125</v>
+        <v>46129.03125</v>
       </c>
       <c r="B4">
-        <v>488</v>
+        <v>453</v>
       </c>
       <c r="C4">
-        <v>1724</v>
+        <v>1289</v>
       </c>
       <c r="D4">
-        <v>2192.019308731721</v>
+        <v>2007.021918063228</v>
       </c>
       <c r="E4">
-        <v>2212</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46115.04166666666</v>
+        <v>46129.04166666666</v>
       </c>
       <c r="B5">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="C5">
-        <v>1715</v>
+        <v>1291</v>
       </c>
       <c r="D5">
-        <v>2193.028852805678</v>
+        <v>1999.367998238447</v>
       </c>
       <c r="E5">
-        <v>2195</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46115.05208333334</v>
+        <v>46129.05208333334</v>
       </c>
       <c r="B6">
-        <v>485</v>
+        <v>596</v>
       </c>
       <c r="C6">
-        <v>1684</v>
+        <v>1227</v>
       </c>
       <c r="D6">
-        <v>2212.21019021087</v>
+        <v>1987.530292402217</v>
       </c>
       <c r="E6">
-        <v>2169</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46115.0625</v>
+        <v>46129.0625</v>
       </c>
       <c r="B7">
-        <v>486</v>
+        <v>599</v>
       </c>
       <c r="C7">
-        <v>1675</v>
+        <v>1222</v>
       </c>
       <c r="D7">
-        <v>2231.391527616062</v>
+        <v>1975.692586565988</v>
       </c>
       <c r="E7">
-        <v>2161</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46115.07291666666</v>
+        <v>46129.07291666666</v>
       </c>
       <c r="B8">
-        <v>487</v>
+        <v>598</v>
       </c>
       <c r="C8">
-        <v>1674</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>2250.572865021254</v>
+        <v>1963.854880729758</v>
       </c>
       <c r="E8">
-        <v>2161</v>
+        <v>598</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46115.08333333334</v>
+        <v>46129.08333333334</v>
       </c>
       <c r="B9">
-        <v>489</v>
+        <v>565</v>
       </c>
       <c r="C9">
-        <v>1675</v>
+        <v>1221</v>
       </c>
       <c r="D9">
-        <v>2269.754202426446</v>
+        <v>1952.017174893529</v>
       </c>
       <c r="E9">
-        <v>2164</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46115.09375</v>
+        <v>46129.09375</v>
       </c>
       <c r="B10">
-        <v>488</v>
+        <v>599</v>
       </c>
       <c r="C10">
-        <v>1644</v>
+        <v>1220</v>
       </c>
       <c r="D10">
-        <v>2251.669653644861</v>
+        <v>1955.906579373255</v>
       </c>
       <c r="E10">
-        <v>2132</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46115.10416666666</v>
+        <v>46129.10416666666</v>
       </c>
       <c r="B11">
-        <v>487</v>
+        <v>545</v>
       </c>
       <c r="C11">
-        <v>1639</v>
+        <v>1216</v>
       </c>
       <c r="D11">
-        <v>2233.585104863276</v>
+        <v>1959.79598385298</v>
       </c>
       <c r="E11">
-        <v>2126</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46115.11458333334</v>
+        <v>46129.11458333334</v>
       </c>
       <c r="B12">
-        <v>490</v>
+        <v>565</v>
       </c>
       <c r="C12">
-        <v>1640</v>
+        <v>1217</v>
       </c>
       <c r="D12">
-        <v>2215.500556081691</v>
+        <v>1963.685388332706</v>
       </c>
       <c r="E12">
-        <v>2130</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46115.125</v>
+        <v>46129.125</v>
       </c>
       <c r="B13">
-        <v>488</v>
+        <v>579</v>
       </c>
       <c r="C13">
-        <v>1639</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>2197.416007300106</v>
+        <v>1967.574792812432</v>
       </c>
       <c r="E13">
-        <v>2127</v>
+        <v>579</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46115.13541666666</v>
+        <v>46129.13541666666</v>
       </c>
       <c r="B14">
-        <v>508</v>
+        <v>604</v>
       </c>
       <c r="C14">
-        <v>1593</v>
+        <v>1220</v>
       </c>
       <c r="D14">
-        <v>2211.163255615948</v>
+        <v>1970.340195080243</v>
       </c>
       <c r="E14">
-        <v>2101</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46115.14583333334</v>
+        <v>46129.14583333334</v>
       </c>
       <c r="B15">
-        <v>512</v>
+        <v>603</v>
       </c>
       <c r="C15">
-        <v>1590</v>
+        <v>1218</v>
       </c>
       <c r="D15">
-        <v>2224.91050393179</v>
+        <v>1973.105597348055</v>
       </c>
       <c r="E15">
-        <v>2102</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46115.15625</v>
+        <v>46129.15625</v>
       </c>
       <c r="B16">
-        <v>513</v>
+        <v>602</v>
       </c>
       <c r="C16">
-        <v>1593</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>2238.657752247632</v>
+        <v>1975.870999615866</v>
       </c>
       <c r="E16">
-        <v>2106</v>
+        <v>602</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46115.16666666666</v>
+        <v>46129.16666666666</v>
       </c>
       <c r="B17">
-        <v>515</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>1592</v>
+        <v>1219</v>
       </c>
       <c r="D17">
-        <v>2252.405000563474</v>
+        <v>1978.636401883678</v>
       </c>
       <c r="E17">
-        <v>2107</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46115.17708333334</v>
+        <v>46129.17708333334</v>
       </c>
       <c r="B18">
-        <v>532</v>
+        <v>625</v>
       </c>
       <c r="C18">
-        <v>1701</v>
+        <v>1221</v>
       </c>
       <c r="D18">
-        <v>2318.77317579566</v>
+        <v>2002.793528789747</v>
       </c>
       <c r="E18">
-        <v>2233</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46115.1875</v>
+        <v>46129.1875</v>
       </c>
       <c r="B19">
-        <v>534</v>
+        <v>618</v>
       </c>
       <c r="C19">
-        <v>1713</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>2385.141351027845</v>
+        <v>2026.950655695817</v>
       </c>
       <c r="E19">
-        <v>2247</v>
+        <v>618</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46115.19791666666</v>
+        <v>46129.19791666666</v>
       </c>
       <c r="B20">
-        <v>532</v>
+        <v>633</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1222</v>
       </c>
       <c r="D20">
-        <v>2451.50952626003</v>
+        <v>2051.107782601886</v>
       </c>
       <c r="E20">
-        <v>532</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46115.20833333334</v>
+        <v>46129.20833333334</v>
       </c>
       <c r="B21">
-        <v>553</v>
+        <v>631</v>
       </c>
       <c r="C21">
-        <v>1712</v>
+        <v>1223</v>
       </c>
       <c r="D21">
-        <v>2517.877701492215</v>
+        <v>2075.264909507956</v>
       </c>
       <c r="E21">
-        <v>2265</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46115.21875</v>
+        <v>46129.21875</v>
       </c>
       <c r="B22">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="C22">
-        <v>1722</v>
+        <v>1236</v>
       </c>
       <c r="D22">
-        <v>2572.692205656035</v>
+        <v>2125.27408729065</v>
       </c>
       <c r="E22">
-        <v>2375</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46115.22916666666</v>
+        <v>46129.22916666666</v>
       </c>
       <c r="B23">
-        <v>655</v>
+        <v>688</v>
       </c>
       <c r="C23">
-        <v>1726</v>
+        <v>1237</v>
       </c>
       <c r="D23">
-        <v>2627.506709819855</v>
+        <v>2175.283265073344</v>
       </c>
       <c r="E23">
-        <v>2381</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46115.23958333334</v>
+        <v>46129.23958333334</v>
       </c>
       <c r="B24">
-        <v>657</v>
+        <v>696</v>
       </c>
       <c r="C24">
-        <v>1730</v>
+        <v>1239</v>
       </c>
       <c r="D24">
-        <v>2682.321213983675</v>
+        <v>2225.292442856039</v>
       </c>
       <c r="E24">
-        <v>2387</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46115.25</v>
+        <v>46129.25</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25">
-        <v>1729</v>
+        <v>1241</v>
       </c>
       <c r="D25">
-        <v>2737.135718147495</v>
+        <v>2275.301620638733</v>
       </c>
       <c r="E25">
-        <v>1729</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46115.26041666666</v>
+        <v>46129.26041666666</v>
       </c>
       <c r="B26">
-        <v>698</v>
+        <v>711</v>
       </c>
       <c r="C26">
-        <v>1909</v>
+        <v>1320</v>
       </c>
       <c r="D26">
-        <v>2761.115505780943</v>
+        <v>2256.309551516733</v>
       </c>
       <c r="E26">
-        <v>2607</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46115.27083333334</v>
+        <v>46129.27083333334</v>
       </c>
       <c r="B27">
-        <v>695</v>
+        <v>708</v>
       </c>
       <c r="C27">
-        <v>1907</v>
+        <v>1321</v>
       </c>
       <c r="D27">
-        <v>2785.095293414392</v>
+        <v>2237.317482394733</v>
       </c>
       <c r="E27">
-        <v>2602</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46115.28125</v>
+        <v>46129.28125</v>
       </c>
       <c r="B28">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C28">
-        <v>1910</v>
+        <v>1319</v>
       </c>
       <c r="D28">
-        <v>2809.075081047839</v>
+        <v>2218.325413272733</v>
       </c>
       <c r="E28">
-        <v>2610</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46115.29166666666</v>
+        <v>46129.29166666666</v>
       </c>
       <c r="B29">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C29">
-        <v>1918</v>
+        <v>1324</v>
       </c>
       <c r="D29">
-        <v>2833.054868681288</v>
+        <v>2199.333344150733</v>
       </c>
       <c r="E29">
-        <v>2622</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46115.30208333334</v>
+        <v>46129.30208333334</v>
       </c>
       <c r="B30">
-        <v>760</v>
+        <v>704</v>
       </c>
       <c r="C30">
-        <v>1943</v>
+        <v>1328</v>
       </c>
       <c r="D30">
-        <v>2797.982559741334</v>
+        <v>2120.23391864222</v>
       </c>
       <c r="E30">
-        <v>2703</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46115.3125</v>
+        <v>46129.3125</v>
       </c>
       <c r="B31">
-        <v>761</v>
+        <v>706</v>
       </c>
       <c r="C31">
-        <v>1951</v>
+        <v>1316</v>
       </c>
       <c r="D31">
-        <v>2762.91025080138</v>
+        <v>2041.134493133707</v>
       </c>
       <c r="E31">
-        <v>2712</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46115.32291666666</v>
+        <v>46129.32291666666</v>
       </c>
       <c r="B32">
-        <v>754</v>
+        <v>688</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1312</v>
       </c>
       <c r="D32">
-        <v>2727.837941861427</v>
+        <v>1962.035067625194</v>
       </c>
       <c r="E32">
-        <v>754</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46115.33333333334</v>
+        <v>46129.33333333334</v>
       </c>
       <c r="B33">
-        <v>752</v>
+        <v>694</v>
       </c>
       <c r="C33">
-        <v>1953</v>
+        <v>1313</v>
       </c>
       <c r="D33">
-        <v>2692.765632921473</v>
+        <v>1882.935642116681</v>
       </c>
       <c r="E33">
-        <v>2705</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46115.34375</v>
+        <v>46129.34375</v>
       </c>
       <c r="B34">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C34">
-        <v>1945</v>
+        <v>1291</v>
       </c>
       <c r="D34">
-        <v>2635.283938241495</v>
+        <v>1806.09314168441</v>
       </c>
       <c r="E34">
-        <v>2591</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46115.35416666666</v>
+        <v>46129.35416666666</v>
       </c>
       <c r="B35">
-        <v>619</v>
+        <v>640</v>
       </c>
       <c r="C35">
-        <v>1947</v>
+        <v>1293</v>
       </c>
       <c r="D35">
-        <v>2577.802243561516</v>
+        <v>1729.250641252139</v>
       </c>
       <c r="E35">
-        <v>2566</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46115.36458333334</v>
+        <v>46129.36458333334</v>
       </c>
       <c r="B36">
-        <v>625</v>
+        <v>593</v>
       </c>
       <c r="C36">
-        <v>1945</v>
+        <v>1287</v>
       </c>
       <c r="D36">
-        <v>2520.320548881537</v>
+        <v>1652.408140819868</v>
       </c>
       <c r="E36">
-        <v>2570</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46115.375</v>
+        <v>46129.375</v>
       </c>
       <c r="B37">
-        <v>619</v>
+        <v>558</v>
       </c>
       <c r="C37">
-        <v>1943</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>2462.838854201559</v>
+        <v>1575.565640387596</v>
       </c>
       <c r="E37">
-        <v>2562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46115.38541666666</v>
+        <v>46129.38541666666</v>
       </c>
       <c r="B38">
-        <v>577</v>
+        <v>416</v>
       </c>
       <c r="C38">
-        <v>1721</v>
+        <v>1026</v>
       </c>
       <c r="D38">
-        <v>2435.593627711736</v>
+        <v>1529.008755113134</v>
       </c>
       <c r="E38">
-        <v>2298</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46115.39583333334</v>
+        <v>46129.39583333334</v>
       </c>
       <c r="B39">
-        <v>563</v>
+        <v>405</v>
       </c>
       <c r="C39">
-        <v>1700</v>
+        <v>993</v>
       </c>
       <c r="D39">
-        <v>2408.348401221914</v>
+        <v>1482.451869838671</v>
       </c>
       <c r="E39">
-        <v>2263</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46115.40625</v>
+        <v>46129.40625</v>
       </c>
       <c r="B40">
-        <v>578</v>
+        <v>398</v>
       </c>
       <c r="C40">
-        <v>1703</v>
+        <v>999</v>
       </c>
       <c r="D40">
-        <v>2381.103174732092</v>
+        <v>1435.894984564208</v>
       </c>
       <c r="E40">
-        <v>2281</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46115.41666666666</v>
+        <v>46129.41666666666</v>
       </c>
       <c r="B41">
-        <v>582</v>
+        <v>410</v>
       </c>
       <c r="C41">
-        <v>1666</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>2353.85794824227</v>
+        <v>1389.338099289745</v>
       </c>
       <c r="E41">
-        <v>2248</v>
+        <v>410</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46115.42708333334</v>
+        <v>46129.42708333334</v>
       </c>
       <c r="B42">
-        <v>486</v>
+        <v>282</v>
       </c>
       <c r="C42">
-        <v>1554</v>
+        <v>911</v>
       </c>
       <c r="D42">
-        <v>2307.468774868566</v>
+        <v>1361.086392896954</v>
       </c>
       <c r="E42">
-        <v>2040</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46115.4375</v>
+        <v>46129.4375</v>
       </c>
       <c r="B43">
-        <v>526</v>
+        <v>274</v>
       </c>
       <c r="C43">
-        <v>1486</v>
+        <v>900</v>
       </c>
       <c r="D43">
-        <v>2261.079601494862</v>
+        <v>1332.834686504162</v>
       </c>
       <c r="E43">
-        <v>2012</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46115.44791666666</v>
+        <v>46129.44791666666</v>
       </c>
       <c r="B44">
-        <v>548</v>
+        <v>278</v>
       </c>
       <c r="C44">
-        <v>1466</v>
+        <v>903</v>
       </c>
       <c r="D44">
-        <v>2214.690428121158</v>
+        <v>1304.58298011137</v>
       </c>
       <c r="E44">
-        <v>2014</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46115.45833333334</v>
+        <v>46129.45833333334</v>
       </c>
       <c r="B45">
-        <v>543</v>
+        <v>272</v>
       </c>
       <c r="C45">
-        <v>1464</v>
+        <v>899</v>
       </c>
       <c r="D45">
-        <v>2168.301254747454</v>
+        <v>1276.331273718579</v>
       </c>
       <c r="E45">
-        <v>2007</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46115.46875</v>
+        <v>46129.46875</v>
       </c>
       <c r="B46">
-        <v>511</v>
+        <v>237</v>
       </c>
       <c r="C46">
-        <v>1456</v>
+        <v>876</v>
       </c>
       <c r="D46">
-        <v>2147.050975165956</v>
+        <v>1268.240241922415</v>
       </c>
       <c r="E46">
-        <v>1967</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46115.47916666666</v>
+        <v>46129.47916666666</v>
       </c>
       <c r="B47">
-        <v>468</v>
+        <v>265</v>
       </c>
       <c r="C47">
-        <v>1502</v>
+        <v>866</v>
       </c>
       <c r="D47">
-        <v>2125.800695584458</v>
+        <v>1260.149210126251</v>
       </c>
       <c r="E47">
-        <v>1970</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46115.48958333334</v>
+        <v>46129.48958333334</v>
       </c>
       <c r="B48">
-        <v>494</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>1451</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>2104.55041600296</v>
+        <v>1252.058178330086</v>
       </c>
       <c r="E48">
-        <v>1945</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46115.5</v>
+        <v>46129.5</v>
       </c>
       <c r="B49">
-        <v>487</v>
+        <v>250</v>
       </c>
       <c r="C49">
-        <v>1444</v>
+        <v>864</v>
       </c>
       <c r="D49">
-        <v>2083.300136421462</v>
+        <v>1243.967146533922</v>
       </c>
       <c r="E49">
-        <v>1931</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46115.51041666666</v>
+        <v>46129.51041666666</v>
       </c>
       <c r="B50">
-        <v>443</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>1396</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>2076.968674821872</v>
+        <v>1242.994795414027</v>
       </c>
       <c r="E50">
-        <v>1839</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46115.52083333334</v>
+        <v>46129.52083333334</v>
       </c>
       <c r="B51">
-        <v>468</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>1412</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>2070.637213222283</v>
+        <v>1242.022444294132</v>
       </c>
       <c r="E51">
-        <v>1880</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46115.53125</v>
+        <v>46129.53125</v>
       </c>
       <c r="B52">
-        <v>470</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>1411</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>2064.305751622694</v>
+        <v>1241.050093174237</v>
       </c>
       <c r="E52">
-        <v>1881</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46115.54166666666</v>
+        <v>46129.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>2057.974290023105</v>
+        <v>1240.077742054342</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46115.55208333334</v>
+        <v>46129.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>2079.723109888087</v>
+        <v>1250.880652203306</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46115.5625</v>
+        <v>46129.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>2101.47192975307</v>
+        <v>1261.683562352271</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46115.57291666666</v>
+        <v>46129.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>2123.220749618052</v>
+        <v>1272.486472501235</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46115.58333333334</v>
+        <v>46129.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>2144.969569483034</v>
+        <v>1283.289382650199</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46115.59375</v>
+        <v>46129.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>2195.995167492546</v>
+        <v>1314.128078261197</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46115.60416666666</v>
+        <v>46129.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>2247.020765502057</v>
+        <v>1344.966773872196</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46115.61458333334</v>
+        <v>46129.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>2298.046363511568</v>
+        <v>1375.805469483194</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46115.625</v>
+        <v>46129.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>2349.071961521079</v>
+        <v>1406.644165094192</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46115.63541666666</v>
+        <v>46129.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>2479.228366019014</v>
+        <v>1464.164532262246</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46115.64583333334</v>
+        <v>46129.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>2609.384770516948</v>
+        <v>1521.6848994303</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46115.65625</v>
+        <v>46129.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>2739.541175014883</v>
+        <v>1579.205266598353</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46115.66666666666</v>
+        <v>46129.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>2869.697579512818</v>
+        <v>1636.725633766406</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46115.67708333334</v>
+        <v>46129.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>2957.727330060626</v>
+        <v>1807.440160207877</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46115.6875</v>
+        <v>46129.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>3045.757080608434</v>
+        <v>1978.154686649347</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46115.69791666666</v>
+        <v>46129.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>3133.786831156242</v>
+        <v>2148.869213090817</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46115.70833333334</v>
+        <v>46129.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>3221.816581704049</v>
+        <v>2319.583739532287</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46115.71875</v>
+        <v>46129.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>3255.567758892655</v>
+        <v>2373.179019610927</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46115.72916666666</v>
+        <v>46129.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>3289.31893608126</v>
+        <v>2426.774299689567</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46115.73958333334</v>
+        <v>46129.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>3323.070113269866</v>
+        <v>2480.369579768206</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46115.75</v>
+        <v>46129.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>3356.821290458472</v>
+        <v>2533.964859846846</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46115.76041666666</v>
+        <v>46129.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>3352.247183357875</v>
+        <v>2539.468902424582</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46115.77083333334</v>
+        <v>46129.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>3347.673076257278</v>
+        <v>2544.972945002318</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46115.78125</v>
+        <v>46129.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>3343.098969156681</v>
+        <v>2550.476987580054</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46115.79166666666</v>
+        <v>46129.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>3338.524862056084</v>
+        <v>2555.98103015779</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46115.80208333334</v>
+        <v>46129.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>3328.429421316726</v>
+        <v>2552.751753961395</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46115.8125</v>
+        <v>46129.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>3318.333980577369</v>
+        <v>2549.522477765001</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46115.82291666666</v>
+        <v>46129.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>3308.238539838012</v>
+        <v>2546.293201568607</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46115.83333333334</v>
+        <v>46129.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>3298.143099098655</v>
+        <v>2543.063925372212</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46115.84375</v>
+        <v>46129.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>3269.913255548886</v>
+        <v>2523.893443200426</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46115.85416666666</v>
+        <v>46129.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>3241.683411999117</v>
+        <v>2504.722961028639</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46115.86458333334</v>
+        <v>46129.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>3213.453568449348</v>
+        <v>2485.552478856853</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46115.875</v>
+        <v>46129.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>3185.223724899579</v>
+        <v>2466.381996685067</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46115.88541666666</v>
+        <v>46129.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>3105.494670071237</v>
+        <v>2443.286427423504</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46115.89583333334</v>
+        <v>46129.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>3025.765615242895</v>
+        <v>2420.190858161941</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46115.90625</v>
+        <v>46129.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2946.036560414553</v>
+        <v>2397.095288900377</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46115.91666666666</v>
+        <v>46129.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2866.307505586211</v>
+        <v>2373.999719638814</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46115.92708333334</v>
+        <v>46129.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>2748.327947511006</v>
+        <v>2313.892363252532</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46115.9375</v>
+        <v>46129.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>2630.348389435801</v>
+        <v>2253.78500686625</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46115.94791666666</v>
+        <v>46129.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>2512.368831360597</v>
+        <v>2193.677650479967</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46115.95833333334</v>
+        <v>46129.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>2394.389273285392</v>
+        <v>2133.570294093685</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46115.96875</v>
+        <v>46129.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>2287.524311281194</v>
+        <v>2052.791270204776</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46115.97916666666</v>
+        <v>46129.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>2180.659349276995</v>
+        <v>1972.012246315867</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46115.98958333334</v>
+        <v>46129.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>2073.794387272796</v>
+        <v>1891.233222426958</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46116</v>
+        <v>46130</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1966.929425268597</v>
+        <v>1810.45419853805</v>
       </c>
       <c r="E97">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -412,789 +412,789 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46129.01041666666</v>
+        <v>46132.01041666666</v>
       </c>
       <c r="B2">
-        <v>452</v>
+        <v>532</v>
       </c>
       <c r="C2">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="D2">
-        <v>2022.329757712791</v>
+        <v>1972.279226927004</v>
       </c>
       <c r="E2">
-        <v>1748</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46129.02083333334</v>
+        <v>46132.02083333334</v>
       </c>
       <c r="B3">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="C3">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="D3">
-        <v>2014.675837888009</v>
+        <v>1967.969172046834</v>
       </c>
       <c r="E3">
-        <v>1748</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46129.03125</v>
+        <v>46132.03125</v>
       </c>
       <c r="B4">
-        <v>453</v>
+        <v>481</v>
       </c>
       <c r="C4">
-        <v>1289</v>
+        <v>1322</v>
       </c>
       <c r="D4">
-        <v>2007.021918063228</v>
+        <v>1963.659117166665</v>
       </c>
       <c r="E4">
-        <v>1742</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46129.04166666666</v>
+        <v>46132.04166666666</v>
       </c>
       <c r="B5">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="C5">
-        <v>1291</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1999.367998238447</v>
+        <v>1959.349062286495</v>
       </c>
       <c r="E5">
-        <v>1755</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46129.05208333334</v>
+        <v>46132.05208333334</v>
       </c>
       <c r="B6">
-        <v>596</v>
+        <v>450</v>
       </c>
       <c r="C6">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="D6">
-        <v>1987.530292402217</v>
+        <v>1956.265062405061</v>
       </c>
       <c r="E6">
-        <v>1823</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46129.0625</v>
+        <v>46132.0625</v>
       </c>
       <c r="B7">
-        <v>599</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="D7">
-        <v>1975.692586565988</v>
+        <v>1953.181062523627</v>
       </c>
       <c r="E7">
-        <v>1821</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46129.07291666666</v>
+        <v>46132.07291666666</v>
       </c>
       <c r="B8">
-        <v>598</v>
+        <v>478</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1218</v>
       </c>
       <c r="D8">
-        <v>1963.854880729758</v>
+        <v>1950.097062642193</v>
       </c>
       <c r="E8">
-        <v>598</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46129.08333333334</v>
+        <v>46132.08333333334</v>
       </c>
       <c r="B9">
-        <v>565</v>
+        <v>398</v>
       </c>
       <c r="C9">
-        <v>1221</v>
+        <v>1156</v>
       </c>
       <c r="D9">
-        <v>1952.017174893529</v>
+        <v>1947.013062760759</v>
       </c>
       <c r="E9">
-        <v>1786</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46129.09375</v>
+        <v>46132.09375</v>
       </c>
       <c r="B10">
-        <v>599</v>
+        <v>362</v>
       </c>
       <c r="C10">
-        <v>1220</v>
+        <v>1045</v>
       </c>
       <c r="D10">
-        <v>1955.906579373255</v>
+        <v>1951.511741486888</v>
       </c>
       <c r="E10">
-        <v>1819</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46129.10416666666</v>
+        <v>46132.10416666666</v>
       </c>
       <c r="B11">
-        <v>545</v>
+        <v>378</v>
       </c>
       <c r="C11">
-        <v>1216</v>
+        <v>1038</v>
       </c>
       <c r="D11">
-        <v>1959.79598385298</v>
+        <v>1956.010420213016</v>
       </c>
       <c r="E11">
-        <v>1761</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46129.11458333334</v>
+        <v>46132.11458333334</v>
       </c>
       <c r="B12">
-        <v>565</v>
+        <v>384</v>
       </c>
       <c r="C12">
-        <v>1217</v>
+        <v>1037</v>
       </c>
       <c r="D12">
-        <v>1963.685388332706</v>
+        <v>1960.509098939145</v>
       </c>
       <c r="E12">
-        <v>1782</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46129.125</v>
+        <v>46132.125</v>
       </c>
       <c r="B13">
-        <v>579</v>
+        <v>400</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>1054</v>
       </c>
       <c r="D13">
-        <v>1967.574792812432</v>
+        <v>1965.007777665274</v>
       </c>
       <c r="E13">
-        <v>579</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46129.13541666666</v>
+        <v>46132.13541666666</v>
       </c>
       <c r="B14">
-        <v>604</v>
+        <v>420</v>
       </c>
       <c r="C14">
-        <v>1220</v>
+        <v>1091</v>
       </c>
       <c r="D14">
-        <v>1970.340195080243</v>
+        <v>1974.042859886662</v>
       </c>
       <c r="E14">
-        <v>1824</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46129.14583333334</v>
+        <v>46132.14583333334</v>
       </c>
       <c r="B15">
-        <v>603</v>
+        <v>417</v>
       </c>
       <c r="C15">
-        <v>1218</v>
+        <v>1094</v>
       </c>
       <c r="D15">
-        <v>1973.105597348055</v>
+        <v>1983.07794210805</v>
       </c>
       <c r="E15">
-        <v>1821</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46129.15625</v>
+        <v>46132.15625</v>
       </c>
       <c r="B16">
-        <v>602</v>
+        <v>463</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>1079</v>
       </c>
       <c r="D16">
-        <v>1975.870999615866</v>
+        <v>1992.113024329439</v>
       </c>
       <c r="E16">
-        <v>602</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46129.16666666666</v>
+        <v>46132.16666666666</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>464</v>
       </c>
       <c r="C17">
-        <v>1219</v>
+        <v>1075</v>
       </c>
       <c r="D17">
-        <v>1978.636401883678</v>
+        <v>2001.148106550827</v>
       </c>
       <c r="E17">
-        <v>1219</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46129.17708333334</v>
+        <v>46132.17708333334</v>
       </c>
       <c r="B18">
-        <v>625</v>
+        <v>488</v>
       </c>
       <c r="C18">
-        <v>1221</v>
+        <v>1214</v>
       </c>
       <c r="D18">
-        <v>2002.793528789747</v>
+        <v>2026.15962852515</v>
       </c>
       <c r="E18">
-        <v>1846</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46129.1875</v>
+        <v>46132.1875</v>
       </c>
       <c r="B19">
-        <v>618</v>
+        <v>498</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1225</v>
       </c>
       <c r="D19">
-        <v>2026.950655695817</v>
+        <v>2051.171150499474</v>
       </c>
       <c r="E19">
-        <v>618</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46129.19791666666</v>
+        <v>46132.19791666666</v>
       </c>
       <c r="B20">
-        <v>633</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>1222</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>2051.107782601886</v>
+        <v>2076.182672473797</v>
       </c>
       <c r="E20">
-        <v>1855</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46129.20833333334</v>
+        <v>46132.20833333334</v>
       </c>
       <c r="B21">
-        <v>631</v>
+        <v>526</v>
       </c>
       <c r="C21">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="D21">
-        <v>2075.264909507956</v>
+        <v>2101.19419444812</v>
       </c>
       <c r="E21">
-        <v>1854</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46129.21875</v>
+        <v>46132.21875</v>
       </c>
       <c r="B22">
-        <v>662</v>
+        <v>715</v>
       </c>
       <c r="C22">
-        <v>1236</v>
+        <v>1176</v>
       </c>
       <c r="D22">
-        <v>2125.27408729065</v>
+        <v>2127.790156728313</v>
       </c>
       <c r="E22">
-        <v>1898</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46129.22916666666</v>
+        <v>46132.22916666666</v>
       </c>
       <c r="B23">
-        <v>688</v>
+        <v>784</v>
       </c>
       <c r="C23">
-        <v>1237</v>
+        <v>1177</v>
       </c>
       <c r="D23">
-        <v>2175.283265073344</v>
+        <v>2154.386119008506</v>
       </c>
       <c r="E23">
-        <v>1925</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46129.23958333334</v>
+        <v>46132.23958333334</v>
       </c>
       <c r="B24">
-        <v>696</v>
+        <v>782</v>
       </c>
       <c r="C24">
-        <v>1239</v>
+        <v>1197</v>
       </c>
       <c r="D24">
-        <v>2225.292442856039</v>
+        <v>2180.9820812887</v>
       </c>
       <c r="E24">
-        <v>1935</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46129.25</v>
+        <v>46132.25</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>795</v>
       </c>
       <c r="C25">
-        <v>1241</v>
+        <v>1198</v>
       </c>
       <c r="D25">
-        <v>2275.301620638733</v>
+        <v>2207.578043568893</v>
       </c>
       <c r="E25">
-        <v>1241</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46129.26041666666</v>
+        <v>46132.26041666666</v>
       </c>
       <c r="B26">
-        <v>711</v>
+        <v>805</v>
       </c>
       <c r="C26">
-        <v>1320</v>
+        <v>1218</v>
       </c>
       <c r="D26">
-        <v>2256.309551516733</v>
+        <v>2174.568870526084</v>
       </c>
       <c r="E26">
-        <v>2031</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46129.27083333334</v>
+        <v>46132.27083333334</v>
       </c>
       <c r="B27">
-        <v>708</v>
+        <v>795</v>
       </c>
       <c r="C27">
-        <v>1321</v>
+        <v>1217</v>
       </c>
       <c r="D27">
-        <v>2237.317482394733</v>
+        <v>2141.559697483275</v>
       </c>
       <c r="E27">
-        <v>2029</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46129.28125</v>
+        <v>46132.28125</v>
       </c>
       <c r="B28">
-        <v>699</v>
+        <v>789</v>
       </c>
       <c r="C28">
-        <v>1319</v>
+        <v>1221</v>
       </c>
       <c r="D28">
-        <v>2218.325413272733</v>
+        <v>2108.550524440466</v>
       </c>
       <c r="E28">
-        <v>2018</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46129.29166666666</v>
+        <v>46132.29166666666</v>
       </c>
       <c r="B29">
-        <v>705</v>
+        <v>780</v>
       </c>
       <c r="C29">
-        <v>1324</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>2199.333344150733</v>
+        <v>2075.541351397657</v>
       </c>
       <c r="E29">
-        <v>2029</v>
+        <v>780</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46129.30208333334</v>
+        <v>46132.30208333334</v>
       </c>
       <c r="B30">
-        <v>704</v>
+        <v>768</v>
       </c>
       <c r="C30">
-        <v>1328</v>
+        <v>1166</v>
       </c>
       <c r="D30">
-        <v>2120.23391864222</v>
+        <v>2013.078564808182</v>
       </c>
       <c r="E30">
-        <v>2032</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46129.3125</v>
+        <v>46132.3125</v>
       </c>
       <c r="B31">
-        <v>706</v>
+        <v>802</v>
       </c>
       <c r="C31">
-        <v>1316</v>
+        <v>1193</v>
       </c>
       <c r="D31">
-        <v>2041.134493133707</v>
+        <v>1950.615778218707</v>
       </c>
       <c r="E31">
-        <v>2022</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46129.32291666666</v>
+        <v>46132.32291666666</v>
       </c>
       <c r="B32">
-        <v>688</v>
+        <v>815</v>
       </c>
       <c r="C32">
-        <v>1312</v>
+        <v>1203</v>
       </c>
       <c r="D32">
-        <v>1962.035067625194</v>
+        <v>1888.152991629233</v>
       </c>
       <c r="E32">
-        <v>2000</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46129.33333333334</v>
+        <v>46132.33333333334</v>
       </c>
       <c r="B33">
-        <v>694</v>
+        <v>767</v>
       </c>
       <c r="C33">
-        <v>1313</v>
+        <v>1146</v>
       </c>
       <c r="D33">
-        <v>1882.935642116681</v>
+        <v>1825.690205039758</v>
       </c>
       <c r="E33">
-        <v>2007</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46129.34375</v>
+        <v>46132.34375</v>
       </c>
       <c r="B34">
-        <v>645</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>1291</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>1806.09314168441</v>
+        <v>1750.919712501458</v>
       </c>
       <c r="E34">
-        <v>1936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46129.35416666666</v>
+        <v>46132.35416666666</v>
       </c>
       <c r="B35">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>1293</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>1729.250641252139</v>
+        <v>1676.149219963158</v>
       </c>
       <c r="E35">
-        <v>1933</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46129.36458333334</v>
+        <v>46132.36458333334</v>
       </c>
       <c r="B36">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>1287</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>1652.408140819868</v>
+        <v>1601.378727424857</v>
       </c>
       <c r="E36">
-        <v>1880</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46129.375</v>
+        <v>46132.375</v>
       </c>
       <c r="B37">
-        <v>558</v>
+        <v>0</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>1575.565640387596</v>
+        <v>1526.608234886557</v>
       </c>
       <c r="E37">
-        <v>558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46129.38541666666</v>
+        <v>46132.38541666666</v>
       </c>
       <c r="B38">
-        <v>416</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>1026</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>1529.008755113134</v>
+        <v>1474.114218556219</v>
       </c>
       <c r="E38">
-        <v>1442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46129.39583333334</v>
+        <v>46132.39583333334</v>
       </c>
       <c r="B39">
-        <v>405</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>993</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>1482.451869838671</v>
+        <v>1421.620202225881</v>
       </c>
       <c r="E39">
-        <v>1398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46129.40625</v>
+        <v>46132.40625</v>
       </c>
       <c r="B40">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>1435.894984564208</v>
+        <v>1369.126185895542</v>
       </c>
       <c r="E40">
-        <v>1397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46129.41666666666</v>
+        <v>46132.41666666666</v>
       </c>
       <c r="B41">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>1389.338099289745</v>
+        <v>1316.632169565204</v>
       </c>
       <c r="E41">
-        <v>410</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46129.42708333334</v>
+        <v>46132.42708333334</v>
       </c>
       <c r="B42">
-        <v>282</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>911</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>1361.086392896954</v>
+        <v>1277.841675643565</v>
       </c>
       <c r="E42">
-        <v>1193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46129.4375</v>
+        <v>46132.4375</v>
       </c>
       <c r="B43">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>1332.834686504162</v>
+        <v>1239.051181721927</v>
       </c>
       <c r="E43">
-        <v>1174</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46129.44791666666</v>
+        <v>46132.44791666666</v>
       </c>
       <c r="B44">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>903</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>1304.58298011137</v>
+        <v>1200.260687800288</v>
       </c>
       <c r="E44">
-        <v>1181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46129.45833333334</v>
+        <v>46132.45833333334</v>
       </c>
       <c r="B45">
-        <v>272</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>899</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>1276.331273718579</v>
+        <v>1161.47019387865</v>
       </c>
       <c r="E45">
-        <v>1171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46129.46875</v>
+        <v>46132.46875</v>
       </c>
       <c r="B46">
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>876</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>1268.240241922415</v>
+        <v>1152.274781388171</v>
       </c>
       <c r="E46">
-        <v>1113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46129.47916666666</v>
+        <v>46132.47916666666</v>
       </c>
       <c r="B47">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>866</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>1260.149210126251</v>
+        <v>1143.079368897691</v>
       </c>
       <c r="E47">
-        <v>1131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46129.48958333334</v>
+        <v>46132.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>1252.058178330086</v>
+        <v>1133.883956407212</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1211,24 +1211,24 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46129.5</v>
+        <v>46132.5</v>
       </c>
       <c r="B49">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>864</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>1243.967146533922</v>
+        <v>1124.688543916733</v>
       </c>
       <c r="E49">
-        <v>1114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46129.51041666666</v>
+        <v>46132.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>1242.994795414027</v>
+        <v>1127.35757133716</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46129.52083333334</v>
+        <v>46132.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>1242.022444294132</v>
+        <v>1130.026598757587</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46129.53125</v>
+        <v>46132.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>1241.050093174237</v>
+        <v>1132.695626178014</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46129.54166666666</v>
+        <v>46132.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>1240.077742054342</v>
+        <v>1135.364653598441</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46129.55208333334</v>
+        <v>46132.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>1250.880652203306</v>
+        <v>1142.758708359835</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46129.5625</v>
+        <v>46132.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1261.683562352271</v>
+        <v>1150.152763121229</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46129.57291666666</v>
+        <v>46132.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1272.486472501235</v>
+        <v>1157.546817882623</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46129.58333333334</v>
+        <v>46132.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>1283.289382650199</v>
+        <v>1164.940872644017</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46129.59375</v>
+        <v>46132.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>1314.128078261197</v>
+        <v>1208.220614099559</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46129.60416666666</v>
+        <v>46132.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1344.966773872196</v>
+        <v>1251.5003555551</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46129.61458333334</v>
+        <v>46132.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>1375.805469483194</v>
+        <v>1294.780097010641</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46129.625</v>
+        <v>46132.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1406.644165094192</v>
+        <v>1338.059838466182</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46129.63541666666</v>
+        <v>46132.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1464.164532262246</v>
+        <v>1417.866587691467</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46129.64583333334</v>
+        <v>46132.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1521.6848994303</v>
+        <v>1497.673336916753</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46129.65625</v>
+        <v>46132.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1579.205266598353</v>
+        <v>1577.480086142038</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46129.66666666666</v>
+        <v>46132.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>1636.725633766406</v>
+        <v>1657.286835367323</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46129.67708333334</v>
+        <v>46132.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>1807.440160207877</v>
+        <v>1800.235417027555</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46129.6875</v>
+        <v>46132.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>1978.154686649347</v>
+        <v>1943.183998687786</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46129.69791666666</v>
+        <v>46132.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>2148.869213090817</v>
+        <v>2086.132580348018</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46129.70833333334</v>
+        <v>46132.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>2319.583739532287</v>
+        <v>2229.08116200825</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46129.71875</v>
+        <v>46132.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>2373.179019610927</v>
+        <v>2292.694554058013</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46129.72916666666</v>
+        <v>46132.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>2426.774299689567</v>
+        <v>2356.307946107776</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46129.73958333334</v>
+        <v>46132.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>2480.369579768206</v>
+        <v>2419.921338157539</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46129.75</v>
+        <v>46132.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>2533.964859846846</v>
+        <v>2483.534730207302</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46129.76041666666</v>
+        <v>46132.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2539.468902424582</v>
+        <v>2492.588674813347</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46129.77083333334</v>
+        <v>46132.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2544.972945002318</v>
+        <v>2501.642619419392</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46129.78125</v>
+        <v>46132.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2550.476987580054</v>
+        <v>2510.696564025437</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46129.79166666666</v>
+        <v>46132.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2555.98103015779</v>
+        <v>2519.750508631482</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46129.80208333334</v>
+        <v>46132.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2552.751753961395</v>
+        <v>2515.270692289949</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46129.8125</v>
+        <v>46132.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2549.522477765001</v>
+        <v>2510.790875948417</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46129.82291666666</v>
+        <v>46132.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2546.293201568607</v>
+        <v>2506.311059606884</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46129.83333333334</v>
+        <v>46132.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2543.063925372212</v>
+        <v>2501.831243265352</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46129.84375</v>
+        <v>46132.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2523.893443200426</v>
+        <v>2482.11062017031</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46129.85416666666</v>
+        <v>46132.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2504.722961028639</v>
+        <v>2462.389997075268</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46129.86458333334</v>
+        <v>46132.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2485.552478856853</v>
+        <v>2442.669373980227</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46129.875</v>
+        <v>46132.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2466.381996685067</v>
+        <v>2422.948750885185</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46129.88541666666</v>
+        <v>46132.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2443.286427423504</v>
+        <v>2388.317412767064</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46129.89583333334</v>
+        <v>46132.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2420.190858161941</v>
+        <v>2353.686074648942</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46129.90625</v>
+        <v>46132.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2397.095288900377</v>
+        <v>2319.05473653082</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46129.91666666666</v>
+        <v>46132.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2373.999719638814</v>
+        <v>2284.423398412699</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46129.92708333334</v>
+        <v>46132.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>2313.892363252532</v>
+        <v>2230.184611507111</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46129.9375</v>
+        <v>46132.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>2253.78500686625</v>
+        <v>2175.945824601523</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46129.94791666666</v>
+        <v>46132.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>2193.677650479967</v>
+        <v>2121.707037695935</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46129.95833333334</v>
+        <v>46132.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>2133.570294093685</v>
+        <v>2067.468250790348</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46129.96875</v>
+        <v>46132.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>2052.791270204776</v>
+        <v>2074.788379428544</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46129.97916666666</v>
+        <v>46132.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>1972.012246315867</v>
+        <v>2082.10850806674</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46129.98958333334</v>
+        <v>46132.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1891.233222426958</v>
+        <v>2089.428636704935</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46130</v>
+        <v>46133</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1810.45419853805</v>
+        <v>2096.748765343131</v>
       </c>
       <c r="E97">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -412,687 +412,687 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46132.01041666666</v>
+        <v>46133.01041666666</v>
       </c>
       <c r="B2">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="C2">
-        <v>1298</v>
+        <v>1363</v>
       </c>
       <c r="D2">
-        <v>1972.279226927004</v>
+        <v>1971.759249664522</v>
       </c>
       <c r="E2">
-        <v>1830</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46132.02083333334</v>
+        <v>46133.02083333334</v>
       </c>
       <c r="B3">
-        <v>467</v>
+        <v>552</v>
       </c>
       <c r="C3">
-        <v>1290</v>
+        <v>1332</v>
       </c>
       <c r="D3">
-        <v>1967.969172046834</v>
+        <v>1962.147475999393</v>
       </c>
       <c r="E3">
-        <v>1757</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46132.03125</v>
+        <v>46133.03125</v>
       </c>
       <c r="B4">
-        <v>481</v>
+        <v>518</v>
       </c>
       <c r="C4">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="D4">
-        <v>1963.659117166665</v>
+        <v>1952.535702334265</v>
       </c>
       <c r="E4">
-        <v>1803</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46132.04166666666</v>
+        <v>46133.04166666666</v>
       </c>
       <c r="B5">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1290</v>
       </c>
       <c r="D5">
-        <v>1959.349062286495</v>
+        <v>1942.923928669136</v>
       </c>
       <c r="E5">
-        <v>478</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46132.05208333334</v>
+        <v>46133.05208333334</v>
       </c>
       <c r="B6">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="C6">
-        <v>1230</v>
+        <v>1262</v>
       </c>
       <c r="D6">
-        <v>1956.265062405061</v>
+        <v>1930.957270456051</v>
       </c>
       <c r="E6">
-        <v>1680</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46132.0625</v>
+        <v>46133.0625</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="C7">
-        <v>1226</v>
+        <v>1260</v>
       </c>
       <c r="D7">
-        <v>1953.181062523627</v>
+        <v>1918.990612242965</v>
       </c>
       <c r="E7">
-        <v>1226</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46132.07291666666</v>
+        <v>46133.07291666666</v>
       </c>
       <c r="B8">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="C8">
-        <v>1218</v>
+        <v>1259</v>
       </c>
       <c r="D8">
-        <v>1950.097062642193</v>
+        <v>1907.02395402988</v>
       </c>
       <c r="E8">
-        <v>1696</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46132.08333333334</v>
+        <v>46133.08333333334</v>
       </c>
       <c r="B9">
         <v>398</v>
       </c>
       <c r="C9">
-        <v>1156</v>
+        <v>1213</v>
       </c>
       <c r="D9">
-        <v>1947.013062760759</v>
+        <v>1895.057295816794</v>
       </c>
       <c r="E9">
-        <v>1554</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46132.09375</v>
+        <v>46133.09375</v>
       </c>
       <c r="B10">
-        <v>362</v>
+        <v>400</v>
       </c>
       <c r="C10">
-        <v>1045</v>
+        <v>1182</v>
       </c>
       <c r="D10">
-        <v>1951.511741486888</v>
+        <v>1903.438762452846</v>
       </c>
       <c r="E10">
-        <v>1407</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46132.10416666666</v>
+        <v>46133.10416666666</v>
       </c>
       <c r="B11">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="C11">
-        <v>1038</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>1956.010420213016</v>
+        <v>1911.820229088897</v>
       </c>
       <c r="E11">
-        <v>1416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46132.11458333334</v>
+        <v>46133.11458333334</v>
       </c>
       <c r="B12">
-        <v>384</v>
+        <v>419</v>
       </c>
       <c r="C12">
-        <v>1037</v>
+        <v>1180</v>
       </c>
       <c r="D12">
-        <v>1960.509098939145</v>
+        <v>1920.201695724948</v>
       </c>
       <c r="E12">
-        <v>1421</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46132.125</v>
+        <v>46133.125</v>
       </c>
       <c r="B13">
-        <v>400</v>
+        <v>434</v>
       </c>
       <c r="C13">
-        <v>1054</v>
+        <v>1183</v>
       </c>
       <c r="D13">
-        <v>1965.007777665274</v>
+        <v>1928.583162361</v>
       </c>
       <c r="E13">
-        <v>1454</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46132.13541666666</v>
+        <v>46133.13541666666</v>
       </c>
       <c r="B14">
-        <v>420</v>
+        <v>325</v>
       </c>
       <c r="C14">
-        <v>1091</v>
+        <v>1174</v>
       </c>
       <c r="D14">
-        <v>1974.042859886662</v>
+        <v>1944.26957698237</v>
       </c>
       <c r="E14">
-        <v>1511</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46132.14583333334</v>
+        <v>46133.14583333334</v>
       </c>
       <c r="B15">
-        <v>417</v>
+        <v>329</v>
       </c>
       <c r="C15">
-        <v>1094</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>1983.07794210805</v>
+        <v>1959.95599160374</v>
       </c>
       <c r="E15">
-        <v>1511</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46132.15625</v>
+        <v>46133.15625</v>
       </c>
       <c r="B16">
-        <v>463</v>
+        <v>336</v>
       </c>
       <c r="C16">
-        <v>1079</v>
+        <v>1173</v>
       </c>
       <c r="D16">
-        <v>1992.113024329439</v>
+        <v>1975.64240622511</v>
       </c>
       <c r="E16">
-        <v>1542</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46132.16666666666</v>
+        <v>46133.16666666666</v>
       </c>
       <c r="B17">
-        <v>464</v>
+        <v>312</v>
       </c>
       <c r="C17">
-        <v>1075</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>2001.148106550827</v>
+        <v>1991.328820846481</v>
       </c>
       <c r="E17">
-        <v>1539</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46132.17708333334</v>
+        <v>46133.17708333334</v>
       </c>
       <c r="B18">
-        <v>488</v>
+        <v>350</v>
       </c>
       <c r="C18">
-        <v>1214</v>
+        <v>1183</v>
       </c>
       <c r="D18">
-        <v>2026.15962852515</v>
+        <v>2024.672063691003</v>
       </c>
       <c r="E18">
-        <v>1702</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46132.1875</v>
+        <v>46133.1875</v>
       </c>
       <c r="B19">
-        <v>498</v>
+        <v>371</v>
       </c>
       <c r="C19">
-        <v>1225</v>
+        <v>1182</v>
       </c>
       <c r="D19">
-        <v>2051.171150499474</v>
+        <v>2058.015306535526</v>
       </c>
       <c r="E19">
-        <v>1723</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46132.19791666666</v>
+        <v>46133.19791666666</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>359</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1183</v>
       </c>
       <c r="D20">
-        <v>2076.182672473797</v>
+        <v>2091.358549380049</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46132.20833333334</v>
+        <v>46133.20833333334</v>
       </c>
       <c r="B21">
-        <v>526</v>
+        <v>417</v>
       </c>
       <c r="C21">
-        <v>1227</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>2101.19419444812</v>
+        <v>2124.701792224571</v>
       </c>
       <c r="E21">
-        <v>1753</v>
+        <v>417</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46132.21875</v>
+        <v>46133.21875</v>
       </c>
       <c r="B22">
-        <v>715</v>
+        <v>655</v>
       </c>
       <c r="C22">
-        <v>1176</v>
+        <v>1121</v>
       </c>
       <c r="D22">
-        <v>2127.790156728313</v>
+        <v>2141.022583907763</v>
       </c>
       <c r="E22">
-        <v>1891</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46132.22916666666</v>
+        <v>46133.22916666666</v>
       </c>
       <c r="B23">
-        <v>784</v>
+        <v>750</v>
       </c>
       <c r="C23">
-        <v>1177</v>
+        <v>1141</v>
       </c>
       <c r="D23">
-        <v>2154.386119008506</v>
+        <v>2157.343375590955</v>
       </c>
       <c r="E23">
-        <v>1961</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46132.23958333334</v>
+        <v>46133.23958333334</v>
       </c>
       <c r="B24">
-        <v>782</v>
+        <v>741</v>
       </c>
       <c r="C24">
-        <v>1197</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>2180.9820812887</v>
+        <v>2173.664167274147</v>
       </c>
       <c r="E24">
-        <v>1979</v>
+        <v>741</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46132.25</v>
+        <v>46133.25</v>
       </c>
       <c r="B25">
-        <v>795</v>
+        <v>740</v>
       </c>
       <c r="C25">
-        <v>1198</v>
+        <v>1137</v>
       </c>
       <c r="D25">
-        <v>2207.578043568893</v>
+        <v>2189.984958957339</v>
       </c>
       <c r="E25">
-        <v>1993</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46132.26041666666</v>
+        <v>46133.26041666666</v>
       </c>
       <c r="B26">
-        <v>805</v>
+        <v>748</v>
       </c>
       <c r="C26">
-        <v>1218</v>
+        <v>1190</v>
       </c>
       <c r="D26">
-        <v>2174.568870526084</v>
+        <v>2157.670175895179</v>
       </c>
       <c r="E26">
-        <v>2023</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46132.27083333334</v>
+        <v>46133.27083333334</v>
       </c>
       <c r="B27">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="C27">
-        <v>1217</v>
+        <v>1185</v>
       </c>
       <c r="D27">
-        <v>2141.559697483275</v>
+        <v>2125.35539283302</v>
       </c>
       <c r="E27">
-        <v>2012</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46132.28125</v>
+        <v>46133.28125</v>
       </c>
       <c r="B28">
-        <v>789</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>1221</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>2108.550524440466</v>
+        <v>2093.040609770861</v>
       </c>
       <c r="E28">
-        <v>2010</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46132.29166666666</v>
+        <v>46133.29166666666</v>
       </c>
       <c r="B29">
-        <v>780</v>
+        <v>801</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1187</v>
       </c>
       <c r="D29">
-        <v>2075.541351397657</v>
+        <v>2060.725826708702</v>
       </c>
       <c r="E29">
-        <v>780</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46132.30208333334</v>
+        <v>46133.30208333334</v>
       </c>
       <c r="B30">
-        <v>768</v>
+        <v>792</v>
       </c>
       <c r="C30">
-        <v>1166</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>2013.078564808182</v>
+        <v>2011.840345848034</v>
       </c>
       <c r="E30">
-        <v>1934</v>
+        <v>792</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46132.3125</v>
+        <v>46133.3125</v>
       </c>
       <c r="B31">
-        <v>802</v>
+        <v>793</v>
       </c>
       <c r="C31">
-        <v>1193</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>1950.615778218707</v>
+        <v>1962.954864987366</v>
       </c>
       <c r="E31">
-        <v>1995</v>
+        <v>793</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46132.32291666666</v>
+        <v>46133.32291666666</v>
       </c>
       <c r="B32">
-        <v>815</v>
+        <v>794</v>
       </c>
       <c r="C32">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="D32">
-        <v>1888.152991629233</v>
+        <v>1914.069384126698</v>
       </c>
       <c r="E32">
-        <v>2018</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46132.33333333334</v>
+        <v>46133.33333333334</v>
       </c>
       <c r="B33">
-        <v>767</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>1146</v>
+        <v>1210</v>
       </c>
       <c r="D33">
-        <v>1825.690205039758</v>
+        <v>1865.18390326603</v>
       </c>
       <c r="E33">
-        <v>1913</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46132.34375</v>
+        <v>46133.34375</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>710</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>1173</v>
       </c>
       <c r="D34">
-        <v>1750.919712501458</v>
+        <v>1777.591809855597</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46132.35416666666</v>
+        <v>46133.35416666666</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>637</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>1167</v>
       </c>
       <c r="D35">
-        <v>1676.149219963158</v>
+        <v>1689.999716445165</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46132.36458333334</v>
+        <v>46133.36458333334</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>616</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>1185</v>
       </c>
       <c r="D36">
-        <v>1601.378727424857</v>
+        <v>1602.407623034732</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46132.375</v>
+        <v>46133.375</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>622</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1189</v>
       </c>
       <c r="D37">
-        <v>1526.608234886557</v>
+        <v>1514.815529624299</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46132.38541666666</v>
+        <v>46133.38541666666</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>591</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1135</v>
       </c>
       <c r="D38">
-        <v>1474.114218556219</v>
+        <v>1450.916458298523</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46132.39583333334</v>
+        <v>46133.39583333334</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1127</v>
       </c>
       <c r="D39">
-        <v>1421.620202225881</v>
+        <v>1387.017386972746</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46132.40625</v>
+        <v>46133.40625</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>1137</v>
       </c>
       <c r="D40">
-        <v>1369.126185895542</v>
+        <v>1323.11831564697</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46132.41666666666</v>
+        <v>46133.41666666666</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>610</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>1130</v>
       </c>
       <c r="D41">
-        <v>1316.632169565204</v>
+        <v>1259.219244321194</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46132.42708333334</v>
+        <v>46133.42708333334</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>1277.841675643565</v>
+        <v>1225.039777167927</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46132.4375</v>
+        <v>46133.4375</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>1239.051181721927</v>
+        <v>1190.860310014661</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46132.44791666666</v>
+        <v>46133.44791666666</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>1200.260687800288</v>
+        <v>1156.680842861394</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46132.45833333334</v>
+        <v>46133.45833333334</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>1161.47019387865</v>
+        <v>1122.501375708127</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46132.46875</v>
+        <v>46133.46875</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1169,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>1152.274781388171</v>
+        <v>1110.255976058855</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46132.47916666666</v>
+        <v>46133.47916666666</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>1143.079368897691</v>
+        <v>1098.010576409582</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46132.48958333334</v>
+        <v>46133.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>1133.883956407212</v>
+        <v>1085.765176760309</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46132.5</v>
+        <v>46133.5</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>1124.688543916733</v>
+        <v>1073.519777111037</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46132.51041666666</v>
+        <v>46133.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>1127.35757133716</v>
+        <v>1073.817742094689</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46132.52083333334</v>
+        <v>46133.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>1130.026598757587</v>
+        <v>1074.115707078341</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46132.53125</v>
+        <v>46133.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>1132.695626178014</v>
+        <v>1074.413672061992</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46132.54166666666</v>
+        <v>46133.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>1135.364653598441</v>
+        <v>1074.711637045644</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46132.55208333334</v>
+        <v>46133.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>1142.758708359835</v>
+        <v>1081.305313779857</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46132.5625</v>
+        <v>46133.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1150.152763121229</v>
+        <v>1087.89899051407</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46132.57291666666</v>
+        <v>46133.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1157.546817882623</v>
+        <v>1094.492667248282</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46132.58333333334</v>
+        <v>46133.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>1164.940872644017</v>
+        <v>1101.086343982495</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46132.59375</v>
+        <v>46133.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>1208.220614099559</v>
+        <v>1140.619569067092</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46132.60416666666</v>
+        <v>46133.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1251.5003555551</v>
+        <v>1180.15279415169</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46132.61458333334</v>
+        <v>46133.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>1294.780097010641</v>
+        <v>1219.686019236288</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46132.625</v>
+        <v>46133.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1338.059838466182</v>
+        <v>1259.219244320886</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46132.63541666666</v>
+        <v>46133.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1417.866587691467</v>
+        <v>1345.244618623866</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46132.64583333334</v>
+        <v>46133.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1497.673336916753</v>
+        <v>1431.269992926846</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46132.65625</v>
+        <v>46133.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1577.480086142038</v>
+        <v>1517.295367229825</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46132.66666666666</v>
+        <v>46133.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>1657.286835367323</v>
+        <v>1603.320741532805</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46132.67708333334</v>
+        <v>46133.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>1800.235417027555</v>
+        <v>1766.221081609408</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46132.6875</v>
+        <v>46133.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>1943.183998687786</v>
+        <v>1929.121421686011</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46132.69791666666</v>
+        <v>46133.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>2086.132580348018</v>
+        <v>2092.021761762614</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46132.70833333334</v>
+        <v>46133.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>2229.08116200825</v>
+        <v>2254.922101839217</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46132.71875</v>
+        <v>46133.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>2292.694554058013</v>
+        <v>2313.131003155389</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46132.72916666666</v>
+        <v>46133.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>2356.307946107776</v>
+        <v>2371.339904471561</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46132.73958333334</v>
+        <v>46133.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>2419.921338157539</v>
+        <v>2429.548805787733</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46132.75</v>
+        <v>46133.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>2483.534730207302</v>
+        <v>2487.757707103905</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46132.76041666666</v>
+        <v>46133.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2492.588674813347</v>
+        <v>2494.120701269992</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46132.77083333334</v>
+        <v>46133.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2501.642619419392</v>
+        <v>2500.483695436078</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46132.78125</v>
+        <v>46133.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2510.696564025437</v>
+        <v>2506.846689602164</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46132.79166666666</v>
+        <v>46133.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2519.750508631482</v>
+        <v>2513.20968376825</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46132.80208333334</v>
+        <v>46133.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2515.270692289949</v>
+        <v>2519.726466313362</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46132.8125</v>
+        <v>46133.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2510.790875948417</v>
+        <v>2526.243248858474</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46132.82291666666</v>
+        <v>46133.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2506.311059606884</v>
+        <v>2532.760031403586</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46132.83333333334</v>
+        <v>46133.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2501.831243265352</v>
+        <v>2539.276813948698</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46132.84375</v>
+        <v>46133.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2482.11062017031</v>
+        <v>2516.073992320924</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46132.85416666666</v>
+        <v>46133.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2462.389997075268</v>
+        <v>2492.871170693151</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46132.86458333334</v>
+        <v>46133.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2442.669373980227</v>
+        <v>2469.668349065378</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46132.875</v>
+        <v>46133.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2422.948750885185</v>
+        <v>2446.465527437604</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46132.88541666666</v>
+        <v>46133.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2388.317412767064</v>
+        <v>2408.864268859695</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46132.89583333334</v>
+        <v>46133.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2353.686074648942</v>
+        <v>2371.263010281786</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46132.90625</v>
+        <v>46133.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2319.05473653082</v>
+        <v>2333.661751703877</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46132.91666666666</v>
+        <v>46133.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2284.423398412699</v>
+        <v>2296.060493125968</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46132.92708333334</v>
+        <v>46133.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>2230.184611507111</v>
+        <v>2245.108480927184</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46132.9375</v>
+        <v>46133.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>2175.945824601523</v>
+        <v>2194.1564687284</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46132.94791666666</v>
+        <v>46133.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>2121.707037695935</v>
+        <v>2143.204456529616</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46132.95833333334</v>
+        <v>46133.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>2067.468250790348</v>
+        <v>2092.252444330833</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46132.96875</v>
+        <v>46133.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>2074.788379428544</v>
+        <v>2108.728718848242</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46132.97916666666</v>
+        <v>46133.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>2082.10850806674</v>
+        <v>2125.204993365653</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46132.98958333334</v>
+        <v>46133.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>2089.428636704935</v>
+        <v>2141.681267883062</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>2096.748765343131</v>
+        <v>2158.157542400472</v>
       </c>
       <c r="E97">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -412,789 +412,789 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46133.01041666666</v>
+        <v>46139.01041666666</v>
       </c>
       <c r="B2">
-        <v>547</v>
+        <v>589</v>
       </c>
       <c r="C2">
-        <v>1363</v>
+        <v>1215</v>
       </c>
       <c r="D2">
-        <v>1971.759249664522</v>
+        <v>1940.104256792429</v>
       </c>
       <c r="E2">
-        <v>1910</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46133.02083333334</v>
+        <v>46139.02083333334</v>
       </c>
       <c r="B3">
-        <v>552</v>
+        <v>593</v>
       </c>
       <c r="C3">
-        <v>1332</v>
+        <v>1174</v>
       </c>
       <c r="D3">
-        <v>1962.147475999393</v>
+        <v>1891.744710459967</v>
       </c>
       <c r="E3">
-        <v>1884</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46133.03125</v>
+        <v>46139.03125</v>
       </c>
       <c r="B4">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="C4">
-        <v>1319</v>
+        <v>1173</v>
       </c>
       <c r="D4">
-        <v>1952.535702334265</v>
+        <v>1843.385164127505</v>
       </c>
       <c r="E4">
-        <v>1837</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46133.04166666666</v>
+        <v>46139.04166666666</v>
       </c>
       <c r="B5">
-        <v>467</v>
+        <v>524</v>
       </c>
       <c r="C5">
-        <v>1290</v>
+        <v>1171</v>
       </c>
       <c r="D5">
-        <v>1942.923928669136</v>
+        <v>1795.025617795043</v>
       </c>
       <c r="E5">
-        <v>1757</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46133.05208333334</v>
+        <v>46139.05208333334</v>
       </c>
       <c r="B6">
-        <v>480</v>
+        <v>513</v>
       </c>
       <c r="C6">
-        <v>1262</v>
+        <v>1158</v>
       </c>
       <c r="D6">
-        <v>1930.957270456051</v>
+        <v>1759.22489044516</v>
       </c>
       <c r="E6">
-        <v>1742</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46133.0625</v>
+        <v>46139.0625</v>
       </c>
       <c r="B7">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C7">
-        <v>1260</v>
+        <v>1146</v>
       </c>
       <c r="D7">
-        <v>1918.990612242965</v>
+        <v>1723.424163095277</v>
       </c>
       <c r="E7">
-        <v>1775</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46133.07291666666</v>
+        <v>46139.07291666666</v>
       </c>
       <c r="B8">
-        <v>460</v>
+        <v>511</v>
       </c>
       <c r="C8">
-        <v>1259</v>
+        <v>1134</v>
       </c>
       <c r="D8">
-        <v>1907.02395402988</v>
+        <v>1687.623435745394</v>
       </c>
       <c r="E8">
-        <v>1719</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46133.08333333334</v>
+        <v>46139.08333333334</v>
       </c>
       <c r="B9">
-        <v>398</v>
+        <v>497</v>
       </c>
       <c r="C9">
-        <v>1213</v>
+        <v>1196</v>
       </c>
       <c r="D9">
-        <v>1895.057295816794</v>
+        <v>1651.822708395511</v>
       </c>
       <c r="E9">
-        <v>1611</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46133.09375</v>
+        <v>46139.09375</v>
       </c>
       <c r="B10">
-        <v>400</v>
+        <v>512</v>
       </c>
       <c r="C10">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="D10">
-        <v>1903.438762452846</v>
+        <v>1647.042930435392</v>
       </c>
       <c r="E10">
-        <v>1582</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46133.10416666666</v>
+        <v>46139.10416666666</v>
       </c>
       <c r="B11">
-        <v>415</v>
+        <v>523</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1911.820229088897</v>
+        <v>1642.263152475272</v>
       </c>
       <c r="E11">
-        <v>415</v>
+        <v>523</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46133.11458333334</v>
+        <v>46139.11458333334</v>
       </c>
       <c r="B12">
-        <v>419</v>
+        <v>533</v>
       </c>
       <c r="C12">
-        <v>1180</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>1920.201695724948</v>
+        <v>1637.483374515152</v>
       </c>
       <c r="E12">
-        <v>1599</v>
+        <v>533</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46133.125</v>
+        <v>46139.125</v>
       </c>
       <c r="B13">
-        <v>434</v>
+        <v>523</v>
       </c>
       <c r="C13">
-        <v>1183</v>
+        <v>1203</v>
       </c>
       <c r="D13">
-        <v>1928.583162361</v>
+        <v>1632.703596555033</v>
       </c>
       <c r="E13">
-        <v>1617</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46133.13541666666</v>
+        <v>46139.13541666666</v>
       </c>
       <c r="B14">
-        <v>325</v>
+        <v>534</v>
       </c>
       <c r="C14">
-        <v>1174</v>
+        <v>1208</v>
       </c>
       <c r="D14">
-        <v>1944.26957698237</v>
+        <v>1655.650339351153</v>
       </c>
       <c r="E14">
-        <v>1499</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46133.14583333334</v>
+        <v>46139.14583333334</v>
       </c>
       <c r="B15">
-        <v>329</v>
+        <v>544</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1206</v>
       </c>
       <c r="D15">
-        <v>1959.95599160374</v>
+        <v>1678.597082147273</v>
       </c>
       <c r="E15">
-        <v>329</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46133.15625</v>
+        <v>46139.15625</v>
       </c>
       <c r="B16">
-        <v>336</v>
+        <v>548</v>
       </c>
       <c r="C16">
-        <v>1173</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>1975.64240622511</v>
+        <v>1701.543824943393</v>
       </c>
       <c r="E16">
-        <v>1509</v>
+        <v>548</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46133.16666666666</v>
+        <v>46139.16666666666</v>
       </c>
       <c r="B17">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1229</v>
       </c>
       <c r="D17">
-        <v>1991.328820846481</v>
+        <v>1724.490567739512</v>
       </c>
       <c r="E17">
-        <v>312</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46133.17708333334</v>
+        <v>46139.17708333334</v>
       </c>
       <c r="B18">
-        <v>350</v>
+        <v>509</v>
       </c>
       <c r="C18">
-        <v>1183</v>
+        <v>1332</v>
       </c>
       <c r="D18">
-        <v>2024.672063691003</v>
+        <v>1772.269304399473</v>
       </c>
       <c r="E18">
-        <v>1533</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46133.1875</v>
+        <v>46139.1875</v>
       </c>
       <c r="B19">
-        <v>371</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>1182</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>2058.015306535526</v>
+        <v>1820.048041059433</v>
       </c>
       <c r="E19">
-        <v>1553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46133.19791666666</v>
+        <v>46139.19791666666</v>
       </c>
       <c r="B20">
-        <v>359</v>
+        <v>512</v>
       </c>
       <c r="C20">
-        <v>1183</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>2091.358549380049</v>
+        <v>1867.826777719393</v>
       </c>
       <c r="E20">
-        <v>1542</v>
+        <v>512</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46133.20833333334</v>
+        <v>46139.20833333334</v>
       </c>
       <c r="B21">
-        <v>417</v>
+        <v>521</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>2124.701792224571</v>
+        <v>1915.605514379353</v>
       </c>
       <c r="E21">
-        <v>417</v>
+        <v>521</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46133.21875</v>
+        <v>46139.21875</v>
       </c>
       <c r="B22">
-        <v>655</v>
+        <v>454</v>
       </c>
       <c r="C22">
-        <v>1121</v>
+        <v>1323</v>
       </c>
       <c r="D22">
-        <v>2141.022583907763</v>
+        <v>1927.669216919986</v>
       </c>
       <c r="E22">
-        <v>1776</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46133.22916666666</v>
+        <v>46139.22916666666</v>
       </c>
       <c r="B23">
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="C23">
-        <v>1141</v>
+        <v>1329</v>
       </c>
       <c r="D23">
-        <v>2157.343375590955</v>
+        <v>1939.73291946062</v>
       </c>
       <c r="E23">
-        <v>1891</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46133.23958333334</v>
+        <v>46139.23958333334</v>
       </c>
       <c r="B24">
-        <v>741</v>
+        <v>455</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1332</v>
       </c>
       <c r="D24">
-        <v>2173.664167274147</v>
+        <v>1951.796622001252</v>
       </c>
       <c r="E24">
-        <v>741</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46133.25</v>
+        <v>46139.25</v>
       </c>
       <c r="B25">
-        <v>740</v>
+        <v>461</v>
       </c>
       <c r="C25">
-        <v>1137</v>
+        <v>1331</v>
       </c>
       <c r="D25">
-        <v>2189.984958957339</v>
+        <v>1963.860324541886</v>
       </c>
       <c r="E25">
-        <v>1877</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46133.26041666666</v>
+        <v>46139.26041666666</v>
       </c>
       <c r="B26">
-        <v>748</v>
+        <v>607</v>
       </c>
       <c r="C26">
-        <v>1190</v>
+        <v>1369</v>
       </c>
       <c r="D26">
-        <v>2157.670175895179</v>
+        <v>1947.159666091778</v>
       </c>
       <c r="E26">
-        <v>1938</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46133.27083333334</v>
+        <v>46139.27083333334</v>
       </c>
       <c r="B27">
-        <v>788</v>
+        <v>620</v>
       </c>
       <c r="C27">
-        <v>1185</v>
+        <v>1366</v>
       </c>
       <c r="D27">
-        <v>2125.35539283302</v>
+        <v>1930.459007641669</v>
       </c>
       <c r="E27">
-        <v>1973</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46133.28125</v>
+        <v>46139.28125</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>621</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1362</v>
       </c>
       <c r="D28">
-        <v>2093.040609770861</v>
+        <v>1913.758349191561</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46133.29166666666</v>
+        <v>46139.29166666666</v>
       </c>
       <c r="B29">
-        <v>801</v>
+        <v>611</v>
       </c>
       <c r="C29">
-        <v>1187</v>
+        <v>1360</v>
       </c>
       <c r="D29">
-        <v>2060.725826708702</v>
+        <v>1897.057690741453</v>
       </c>
       <c r="E29">
-        <v>1988</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46133.30208333334</v>
+        <v>46139.30208333334</v>
       </c>
       <c r="B30">
-        <v>792</v>
+        <v>644</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1324</v>
       </c>
       <c r="D30">
-        <v>2011.840345848034</v>
+        <v>1822.856874720994</v>
       </c>
       <c r="E30">
-        <v>792</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46133.3125</v>
+        <v>46139.3125</v>
       </c>
       <c r="B31">
-        <v>793</v>
+        <v>630</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1316</v>
       </c>
       <c r="D31">
-        <v>1962.954864987366</v>
+        <v>1748.656058700534</v>
       </c>
       <c r="E31">
-        <v>793</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46133.32291666666</v>
+        <v>46139.32291666666</v>
       </c>
       <c r="B32">
-        <v>794</v>
+        <v>641</v>
       </c>
       <c r="C32">
-        <v>1199</v>
+        <v>1309</v>
       </c>
       <c r="D32">
-        <v>1914.069384126698</v>
+        <v>1674.455242680075</v>
       </c>
       <c r="E32">
-        <v>1993</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46133.33333333334</v>
+        <v>46139.33333333334</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>629</v>
       </c>
       <c r="C33">
-        <v>1210</v>
+        <v>1313</v>
       </c>
       <c r="D33">
-        <v>1865.18390326603</v>
+        <v>1600.254426659615</v>
       </c>
       <c r="E33">
-        <v>1210</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46133.34375</v>
+        <v>46139.34375</v>
       </c>
       <c r="B34">
-        <v>710</v>
+        <v>529</v>
       </c>
       <c r="C34">
-        <v>1173</v>
+        <v>1311</v>
       </c>
       <c r="D34">
-        <v>1777.591809855597</v>
+        <v>1545.277458649403</v>
       </c>
       <c r="E34">
-        <v>1883</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46133.35416666666</v>
+        <v>46139.35416666666</v>
       </c>
       <c r="B35">
-        <v>637</v>
+        <v>527</v>
       </c>
       <c r="C35">
-        <v>1167</v>
+        <v>1310</v>
       </c>
       <c r="D35">
-        <v>1689.999716445165</v>
+        <v>1490.300490639191</v>
       </c>
       <c r="E35">
-        <v>1804</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46133.36458333334</v>
+        <v>46139.36458333334</v>
       </c>
       <c r="B36">
-        <v>616</v>
+        <v>501</v>
       </c>
       <c r="C36">
-        <v>1185</v>
+        <v>1255</v>
       </c>
       <c r="D36">
-        <v>1602.407623034732</v>
+        <v>1435.323522628979</v>
       </c>
       <c r="E36">
-        <v>1801</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46133.375</v>
+        <v>46139.375</v>
       </c>
       <c r="B37">
-        <v>622</v>
+        <v>492</v>
       </c>
       <c r="C37">
-        <v>1189</v>
+        <v>1252</v>
       </c>
       <c r="D37">
-        <v>1514.815529624299</v>
+        <v>1380.346554618767</v>
       </c>
       <c r="E37">
-        <v>1811</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46133.38541666666</v>
+        <v>46139.38541666666</v>
       </c>
       <c r="B38">
-        <v>591</v>
+        <v>346</v>
       </c>
       <c r="C38">
-        <v>1135</v>
+        <v>1013</v>
       </c>
       <c r="D38">
-        <v>1450.916458298523</v>
+        <v>1321.837121223781</v>
       </c>
       <c r="E38">
-        <v>1726</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46133.39583333334</v>
+        <v>46139.39583333334</v>
       </c>
       <c r="B39">
-        <v>593</v>
+        <v>336</v>
       </c>
       <c r="C39">
-        <v>1127</v>
+        <v>981</v>
       </c>
       <c r="D39">
-        <v>1387.017386972746</v>
+        <v>1263.327687828796</v>
       </c>
       <c r="E39">
-        <v>1720</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46133.40625</v>
+        <v>46139.40625</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="C40">
-        <v>1137</v>
+        <v>976</v>
       </c>
       <c r="D40">
-        <v>1323.11831564697</v>
+        <v>1204.81825443381</v>
       </c>
       <c r="E40">
-        <v>1137</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46133.41666666666</v>
+        <v>46139.41666666666</v>
       </c>
       <c r="B41">
-        <v>610</v>
+        <v>301</v>
       </c>
       <c r="C41">
-        <v>1130</v>
+        <v>1007</v>
       </c>
       <c r="D41">
-        <v>1259.219244321194</v>
+        <v>1146.308821038825</v>
       </c>
       <c r="E41">
-        <v>1740</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46133.42708333334</v>
+        <v>46139.42708333334</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="D42">
-        <v>1225.039777167927</v>
+        <v>1125.590102232125</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>778</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46133.4375</v>
+        <v>46139.4375</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>574</v>
       </c>
       <c r="D43">
-        <v>1190.860310014661</v>
+        <v>1104.871383425425</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>702</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46133.44791666666</v>
+        <v>46139.44791666666</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>573</v>
       </c>
       <c r="D44">
-        <v>1156.680842861394</v>
+        <v>1084.152664618725</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>703</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46133.45833333334</v>
+        <v>46139.45833333334</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>572</v>
       </c>
       <c r="D45">
-        <v>1122.501375708127</v>
+        <v>1063.433945812025</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>700</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46133.46875</v>
+        <v>46139.46875</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>569</v>
       </c>
       <c r="D46">
-        <v>1110.255976058855</v>
+        <v>1058.463738451217</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>714</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46133.47916666666</v>
+        <v>46139.47916666666</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>575</v>
       </c>
       <c r="D47">
-        <v>1098.010576409582</v>
+        <v>1053.49353109041</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>704</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46133.48958333334</v>
+        <v>46139.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>1085.765176760309</v>
+        <v>1048.523323729602</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46133.5</v>
+        <v>46139.5</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>1073.519777111037</v>
+        <v>1043.553116368794</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46133.51041666666</v>
+        <v>46139.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>1073.817742094689</v>
+        <v>1026.176433546048</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46133.52083333334</v>
+        <v>46139.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>1074.115707078341</v>
+        <v>1008.799750723301</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46133.53125</v>
+        <v>46139.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>1074.413672061992</v>
+        <v>991.4230679005539</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46133.54166666666</v>
+        <v>46139.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>1074.711637045644</v>
+        <v>974.046385077807</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46133.55208333334</v>
+        <v>46139.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>1081.305313779857</v>
+        <v>970.8662140843976</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46133.5625</v>
+        <v>46139.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1087.89899051407</v>
+        <v>967.6860430909881</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46133.57291666666</v>
+        <v>46139.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1094.492667248282</v>
+        <v>964.5058720975786</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46133.58333333334</v>
+        <v>46139.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>1101.086343982495</v>
+        <v>961.3257011041692</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46133.59375</v>
+        <v>46139.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>1140.619569067092</v>
+        <v>961.8112960763619</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46133.60416666666</v>
+        <v>46139.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1180.15279415169</v>
+        <v>962.2968910485548</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46133.61458333334</v>
+        <v>46139.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>1219.686019236288</v>
+        <v>962.7824860207477</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46133.625</v>
+        <v>46139.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1259.219244320886</v>
+        <v>963.2680809929404</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46133.63541666666</v>
+        <v>46139.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1345.244618623866</v>
+        <v>1036.345363548853</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46133.64583333334</v>
+        <v>46139.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1431.269992926846</v>
+        <v>1109.422646104766</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46133.65625</v>
+        <v>46139.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1517.295367229825</v>
+        <v>1182.499928660679</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46133.66666666666</v>
+        <v>46139.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>1603.320741532805</v>
+        <v>1255.577211216592</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46133.67708333334</v>
+        <v>46139.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>1766.221081609408</v>
+        <v>1394.83823201938</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46133.6875</v>
+        <v>46139.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>1929.121421686011</v>
+        <v>1534.099252822169</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46133.69791666666</v>
+        <v>46139.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>2092.021761762614</v>
+        <v>1673.360273624957</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46133.70833333334</v>
+        <v>46139.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>2254.922101839217</v>
+        <v>1812.621294427745</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46133.71875</v>
+        <v>46139.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>2313.131003155389</v>
+        <v>1944.465090069963</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46133.72916666666</v>
+        <v>46139.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>2371.339904471561</v>
+        <v>2076.30888571218</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46133.73958333334</v>
+        <v>46139.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>2429.548805787733</v>
+        <v>2208.152681354397</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46133.75</v>
+        <v>46139.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>2487.757707103905</v>
+        <v>2339.996476996615</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46133.76041666666</v>
+        <v>46139.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2494.120701269992</v>
+        <v>2368.570408586161</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46133.77083333334</v>
+        <v>46139.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2500.483695436078</v>
+        <v>2397.144340175706</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46133.78125</v>
+        <v>46139.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2506.846689602164</v>
+        <v>2425.718271765252</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46133.79166666666</v>
+        <v>46139.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2513.20968376825</v>
+        <v>2454.292203354798</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46133.80208333334</v>
+        <v>46139.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2519.726466313362</v>
+        <v>2472.935241692763</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46133.8125</v>
+        <v>46139.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2526.243248858474</v>
+        <v>2491.578280030727</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46133.82291666666</v>
+        <v>46139.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2532.760031403586</v>
+        <v>2510.221318368692</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46133.83333333334</v>
+        <v>46139.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2539.276813948698</v>
+        <v>2528.864356706656</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46133.84375</v>
+        <v>46139.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2516.073992320924</v>
+        <v>2515.715206581692</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46133.85416666666</v>
+        <v>46139.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2492.871170693151</v>
+        <v>2502.566056456727</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46133.86458333334</v>
+        <v>46139.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2469.668349065378</v>
+        <v>2489.416906331763</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46133.875</v>
+        <v>46139.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2446.465527437604</v>
+        <v>2476.267756206798</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46133.88541666666</v>
+        <v>46139.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2408.864268859695</v>
+        <v>2439.029286880824</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46133.89583333334</v>
+        <v>46139.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2371.263010281786</v>
+        <v>2401.790817554849</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46133.90625</v>
+        <v>46139.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2333.661751703877</v>
+        <v>2364.552348228874</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46133.91666666666</v>
+        <v>46139.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2296.060493125968</v>
+        <v>2327.313878902899</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46133.92708333334</v>
+        <v>46139.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>2245.108480927184</v>
+        <v>2284.790993704956</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46133.9375</v>
+        <v>46139.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>2194.1564687284</v>
+        <v>2242.268108507013</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46133.94791666666</v>
+        <v>46139.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>2143.204456529616</v>
+        <v>2199.74522330907</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46133.95833333334</v>
+        <v>46139.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>2092.252444330833</v>
+        <v>2157.222338111127</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46133.96875</v>
+        <v>46139.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>2108.728718848242</v>
+        <v>2131.402606731292</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46133.97916666666</v>
+        <v>46139.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>2125.204993365653</v>
+        <v>2105.582875351456</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46133.98958333334</v>
+        <v>46139.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>2141.681267883062</v>
+        <v>2079.763143971621</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>2158.157542400472</v>
+        <v>2053.943412591785</v>
       </c>
       <c r="E97">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -412,789 +412,789 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46139.01041666666</v>
+        <v>46142.01041666666</v>
       </c>
       <c r="B2">
-        <v>589</v>
+        <v>628</v>
       </c>
       <c r="C2">
-        <v>1215</v>
+        <v>1000</v>
       </c>
       <c r="D2">
-        <v>1940.104256792429</v>
+        <v>1917.679011228841</v>
       </c>
       <c r="E2">
-        <v>1804</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46139.02083333334</v>
+        <v>46142.02083333334</v>
       </c>
       <c r="B3">
-        <v>593</v>
+        <v>625</v>
       </c>
       <c r="C3">
-        <v>1174</v>
+        <v>995</v>
       </c>
       <c r="D3">
-        <v>1891.744710459967</v>
+        <v>1864.473864495583</v>
       </c>
       <c r="E3">
-        <v>1767</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46139.03125</v>
+        <v>46142.03125</v>
       </c>
       <c r="B4">
-        <v>532</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>1173</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1843.385164127505</v>
+        <v>1811.268717762324</v>
       </c>
       <c r="E4">
-        <v>1705</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46139.04166666666</v>
+        <v>46142.04166666666</v>
       </c>
       <c r="B5">
-        <v>524</v>
+        <v>623</v>
       </c>
       <c r="C5">
-        <v>1171</v>
+        <v>993</v>
       </c>
       <c r="D5">
-        <v>1795.025617795043</v>
+        <v>1758.063571029066</v>
       </c>
       <c r="E5">
-        <v>1695</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46139.05208333334</v>
+        <v>46142.05208333334</v>
       </c>
       <c r="B6">
-        <v>513</v>
+        <v>648</v>
       </c>
       <c r="C6">
-        <v>1158</v>
+        <v>954</v>
       </c>
       <c r="D6">
-        <v>1759.22489044516</v>
+        <v>1735.276077249592</v>
       </c>
       <c r="E6">
-        <v>1671</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46139.0625</v>
+        <v>46142.0625</v>
       </c>
       <c r="B7">
-        <v>505</v>
+        <v>644</v>
       </c>
       <c r="C7">
-        <v>1146</v>
+        <v>955</v>
       </c>
       <c r="D7">
-        <v>1723.424163095277</v>
+        <v>1712.488583470118</v>
       </c>
       <c r="E7">
-        <v>1651</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46139.07291666666</v>
+        <v>46142.07291666666</v>
       </c>
       <c r="B8">
-        <v>511</v>
+        <v>645</v>
       </c>
       <c r="C8">
-        <v>1134</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1687.623435745394</v>
+        <v>1689.701089690644</v>
       </c>
       <c r="E8">
-        <v>1645</v>
+        <v>645</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46139.08333333334</v>
+        <v>46142.08333333334</v>
       </c>
       <c r="B9">
-        <v>497</v>
+        <v>643</v>
       </c>
       <c r="C9">
-        <v>1196</v>
+        <v>954</v>
       </c>
       <c r="D9">
-        <v>1651.822708395511</v>
+        <v>1666.91359591117</v>
       </c>
       <c r="E9">
-        <v>1693</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46139.09375</v>
+        <v>46142.09375</v>
       </c>
       <c r="B10">
-        <v>512</v>
+        <v>636</v>
       </c>
       <c r="C10">
-        <v>1201</v>
+        <v>955</v>
       </c>
       <c r="D10">
-        <v>1647.042930435392</v>
+        <v>1661.249490021095</v>
       </c>
       <c r="E10">
-        <v>1713</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46139.10416666666</v>
+        <v>46142.10416666666</v>
       </c>
       <c r="B11">
-        <v>523</v>
+        <v>641</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>956</v>
       </c>
       <c r="D11">
-        <v>1642.263152475272</v>
+        <v>1655.58538413102</v>
       </c>
       <c r="E11">
-        <v>523</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46139.11458333334</v>
+        <v>46142.11458333334</v>
       </c>
       <c r="B12">
-        <v>533</v>
+        <v>642</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="D12">
-        <v>1637.483374515152</v>
+        <v>1649.921278240946</v>
       </c>
       <c r="E12">
-        <v>533</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46139.125</v>
+        <v>46142.125</v>
       </c>
       <c r="B13">
-        <v>523</v>
+        <v>634</v>
       </c>
       <c r="C13">
-        <v>1203</v>
+        <v>966</v>
       </c>
       <c r="D13">
-        <v>1632.703596555033</v>
+        <v>1644.257172350871</v>
       </c>
       <c r="E13">
-        <v>1726</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46139.13541666666</v>
+        <v>46142.13541666666</v>
       </c>
       <c r="B14">
-        <v>534</v>
+        <v>637</v>
       </c>
       <c r="C14">
-        <v>1208</v>
+        <v>970</v>
       </c>
       <c r="D14">
-        <v>1655.650339351153</v>
+        <v>1664.984991260847</v>
       </c>
       <c r="E14">
-        <v>1742</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46139.14583333334</v>
+        <v>46142.14583333334</v>
       </c>
       <c r="B15">
-        <v>544</v>
+        <v>646</v>
       </c>
       <c r="C15">
-        <v>1206</v>
+        <v>969</v>
       </c>
       <c r="D15">
-        <v>1678.597082147273</v>
+        <v>1685.712810170822</v>
       </c>
       <c r="E15">
-        <v>1750</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46139.15625</v>
+        <v>46142.15625</v>
       </c>
       <c r="B16">
-        <v>548</v>
+        <v>652</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="D16">
-        <v>1701.543824943393</v>
+        <v>1706.440629080797</v>
       </c>
       <c r="E16">
-        <v>548</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46139.16666666666</v>
+        <v>46142.16666666666</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>646</v>
       </c>
       <c r="C17">
-        <v>1229</v>
+        <v>969</v>
       </c>
       <c r="D17">
-        <v>1724.490567739512</v>
+        <v>1727.168447990773</v>
       </c>
       <c r="E17">
-        <v>1229</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46139.17708333334</v>
+        <v>46142.17708333334</v>
       </c>
       <c r="B18">
-        <v>509</v>
+        <v>657</v>
       </c>
       <c r="C18">
-        <v>1332</v>
+        <v>972</v>
       </c>
       <c r="D18">
-        <v>1772.269304399473</v>
+        <v>1775.804861378377</v>
       </c>
       <c r="E18">
-        <v>1841</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46139.1875</v>
+        <v>46142.1875</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>658</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>1820.048041059433</v>
+        <v>1824.441274765982</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>658</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46139.19791666666</v>
+        <v>46142.19791666666</v>
       </c>
       <c r="B20">
-        <v>512</v>
+        <v>669</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>971</v>
       </c>
       <c r="D20">
-        <v>1867.826777719393</v>
+        <v>1873.077688153587</v>
       </c>
       <c r="E20">
-        <v>512</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46139.20833333334</v>
+        <v>46142.20833333334</v>
       </c>
       <c r="B21">
-        <v>521</v>
+        <v>674</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="D21">
-        <v>1915.605514379353</v>
+        <v>1921.714101541192</v>
       </c>
       <c r="E21">
-        <v>521</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46139.21875</v>
+        <v>46142.21875</v>
       </c>
       <c r="B22">
-        <v>454</v>
+        <v>652</v>
       </c>
       <c r="C22">
-        <v>1323</v>
+        <v>1057</v>
       </c>
       <c r="D22">
-        <v>1927.669216919986</v>
+        <v>1927.602899235028</v>
       </c>
       <c r="E22">
-        <v>1777</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46139.22916666666</v>
+        <v>46142.22916666666</v>
       </c>
       <c r="B23">
-        <v>450</v>
+        <v>668</v>
       </c>
       <c r="C23">
-        <v>1329</v>
+        <v>1067</v>
       </c>
       <c r="D23">
-        <v>1939.73291946062</v>
+        <v>1933.491696928863</v>
       </c>
       <c r="E23">
-        <v>1779</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46139.23958333334</v>
+        <v>46142.23958333334</v>
       </c>
       <c r="B24">
-        <v>455</v>
+        <v>675</v>
       </c>
       <c r="C24">
-        <v>1332</v>
+        <v>1064</v>
       </c>
       <c r="D24">
-        <v>1951.796622001252</v>
+        <v>1939.380494622699</v>
       </c>
       <c r="E24">
-        <v>1787</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46139.25</v>
+        <v>46142.25</v>
       </c>
       <c r="B25">
-        <v>461</v>
+        <v>680</v>
       </c>
       <c r="C25">
-        <v>1331</v>
+        <v>1069</v>
       </c>
       <c r="D25">
-        <v>1963.860324541886</v>
+        <v>1945.269292316535</v>
       </c>
       <c r="E25">
-        <v>1792</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46139.26041666666</v>
+        <v>46142.26041666666</v>
       </c>
       <c r="B26">
-        <v>607</v>
+        <v>735</v>
       </c>
       <c r="C26">
-        <v>1369</v>
+        <v>1132</v>
       </c>
       <c r="D26">
-        <v>1947.159666091778</v>
+        <v>1919.560805086414</v>
       </c>
       <c r="E26">
-        <v>1976</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46139.27083333334</v>
+        <v>46142.27083333334</v>
       </c>
       <c r="B27">
-        <v>620</v>
+        <v>821</v>
       </c>
       <c r="C27">
-        <v>1366</v>
+        <v>1138</v>
       </c>
       <c r="D27">
-        <v>1930.459007641669</v>
+        <v>1893.852317856294</v>
       </c>
       <c r="E27">
-        <v>1986</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46139.28125</v>
+        <v>46142.28125</v>
       </c>
       <c r="B28">
-        <v>621</v>
+        <v>1052</v>
       </c>
       <c r="C28">
-        <v>1362</v>
+        <v>1137</v>
       </c>
       <c r="D28">
-        <v>1913.758349191561</v>
+        <v>1868.143830626174</v>
       </c>
       <c r="E28">
-        <v>1983</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46139.29166666666</v>
+        <v>46142.29166666666</v>
       </c>
       <c r="B29">
-        <v>611</v>
+        <v>1110</v>
       </c>
       <c r="C29">
-        <v>1360</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>1897.057690741453</v>
+        <v>1842.435343396053</v>
       </c>
       <c r="E29">
-        <v>1971</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46139.30208333334</v>
+        <v>46142.30208333334</v>
       </c>
       <c r="B30">
-        <v>644</v>
+        <v>1034</v>
       </c>
       <c r="C30">
-        <v>1324</v>
+        <v>1138</v>
       </c>
       <c r="D30">
-        <v>1822.856874720994</v>
+        <v>1761.471396721622</v>
       </c>
       <c r="E30">
-        <v>1968</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46139.3125</v>
+        <v>46142.3125</v>
       </c>
       <c r="B31">
-        <v>630</v>
+        <v>1089</v>
       </c>
       <c r="C31">
-        <v>1316</v>
+        <v>1148</v>
       </c>
       <c r="D31">
-        <v>1748.656058700534</v>
+        <v>1680.507450047191</v>
       </c>
       <c r="E31">
-        <v>1946</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46139.32291666666</v>
+        <v>46142.32291666666</v>
       </c>
       <c r="B32">
-        <v>641</v>
+        <v>1088</v>
       </c>
       <c r="C32">
-        <v>1309</v>
+        <v>1152</v>
       </c>
       <c r="D32">
-        <v>1674.455242680075</v>
+        <v>1599.54350337276</v>
       </c>
       <c r="E32">
-        <v>1950</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46139.33333333334</v>
+        <v>46142.33333333334</v>
       </c>
       <c r="B33">
-        <v>629</v>
+        <v>1078</v>
       </c>
       <c r="C33">
-        <v>1313</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>1600.254426659615</v>
+        <v>1518.579556698329</v>
       </c>
       <c r="E33">
-        <v>1942</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46139.34375</v>
+        <v>46142.34375</v>
       </c>
       <c r="B34">
-        <v>529</v>
+        <v>1113</v>
       </c>
       <c r="C34">
-        <v>1311</v>
+        <v>936</v>
       </c>
       <c r="D34">
-        <v>1545.277458649403</v>
+        <v>1458.680466640581</v>
       </c>
       <c r="E34">
-        <v>1840</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46139.35416666666</v>
+        <v>46142.35416666666</v>
       </c>
       <c r="B35">
-        <v>527</v>
+        <v>1087</v>
       </c>
       <c r="C35">
-        <v>1310</v>
+        <v>916</v>
       </c>
       <c r="D35">
-        <v>1490.300490639191</v>
+        <v>1398.781376582834</v>
       </c>
       <c r="E35">
-        <v>1837</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46139.36458333334</v>
+        <v>46142.36458333334</v>
       </c>
       <c r="B36">
-        <v>501</v>
+        <v>1040</v>
       </c>
       <c r="C36">
-        <v>1255</v>
+        <v>955</v>
       </c>
       <c r="D36">
-        <v>1435.323522628979</v>
+        <v>1338.882286525086</v>
       </c>
       <c r="E36">
-        <v>1756</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46139.375</v>
+        <v>46142.375</v>
       </c>
       <c r="B37">
-        <v>492</v>
+        <v>922</v>
       </c>
       <c r="C37">
-        <v>1252</v>
+        <v>959</v>
       </c>
       <c r="D37">
-        <v>1380.346554618767</v>
+        <v>1278.983196467339</v>
       </c>
       <c r="E37">
-        <v>1744</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46139.38541666666</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="B38">
-        <v>346</v>
+        <v>920</v>
       </c>
       <c r="C38">
-        <v>1013</v>
+        <v>904</v>
       </c>
       <c r="D38">
-        <v>1321.837121223781</v>
+        <v>1173.406135107004</v>
       </c>
       <c r="E38">
-        <v>1359</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46139.39583333334</v>
+        <v>46142.39583333334</v>
       </c>
       <c r="B39">
-        <v>336</v>
+        <v>905</v>
       </c>
       <c r="C39">
-        <v>981</v>
+        <v>899</v>
       </c>
       <c r="D39">
-        <v>1263.327687828796</v>
+        <v>1067.829073746669</v>
       </c>
       <c r="E39">
-        <v>1317</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46139.40625</v>
+        <v>46142.40625</v>
       </c>
       <c r="B40">
-        <v>311</v>
+        <v>663</v>
       </c>
       <c r="C40">
-        <v>976</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>1204.81825443381</v>
+        <v>962.2520123863337</v>
       </c>
       <c r="E40">
-        <v>1287</v>
+        <v>663</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46139.41666666666</v>
+        <v>46142.41666666666</v>
       </c>
       <c r="B41">
-        <v>301</v>
+        <v>581</v>
       </c>
       <c r="C41">
-        <v>1007</v>
+        <v>898</v>
       </c>
       <c r="D41">
-        <v>1146.308821038825</v>
+        <v>856.6749510259987</v>
       </c>
       <c r="E41">
-        <v>1308</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46139.42708333334</v>
+        <v>46142.42708333334</v>
       </c>
       <c r="B42">
-        <v>137</v>
+        <v>303</v>
       </c>
       <c r="C42">
-        <v>641</v>
+        <v>658</v>
       </c>
       <c r="D42">
-        <v>1125.590102232125</v>
+        <v>838.006806984718</v>
       </c>
       <c r="E42">
-        <v>778</v>
+        <v>961</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46139.4375</v>
+        <v>46142.4375</v>
       </c>
       <c r="B43">
-        <v>128</v>
+        <v>283</v>
       </c>
       <c r="C43">
-        <v>574</v>
+        <v>643</v>
       </c>
       <c r="D43">
-        <v>1104.871383425425</v>
+        <v>819.3386629434373</v>
       </c>
       <c r="E43">
-        <v>702</v>
+        <v>926</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46139.44791666666</v>
+        <v>46142.44791666666</v>
       </c>
       <c r="B44">
-        <v>130</v>
+        <v>284</v>
       </c>
       <c r="C44">
-        <v>573</v>
+        <v>650</v>
       </c>
       <c r="D44">
-        <v>1084.152664618725</v>
+        <v>800.6705189021566</v>
       </c>
       <c r="E44">
-        <v>703</v>
+        <v>934</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46139.45833333334</v>
+        <v>46142.45833333334</v>
       </c>
       <c r="B45">
-        <v>128</v>
+        <v>307</v>
       </c>
       <c r="C45">
-        <v>572</v>
+        <v>595</v>
       </c>
       <c r="D45">
-        <v>1063.433945812025</v>
+        <v>782.0023748608759</v>
       </c>
       <c r="E45">
-        <v>700</v>
+        <v>902</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46139.46875</v>
+        <v>46142.46875</v>
       </c>
       <c r="B46">
-        <v>145</v>
+        <v>260</v>
       </c>
       <c r="C46">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="D46">
-        <v>1058.463738451217</v>
+        <v>782.4236719932819</v>
       </c>
       <c r="E46">
-        <v>714</v>
+        <v>823</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46139.47916666666</v>
+        <v>46142.47916666666</v>
       </c>
       <c r="B47">
-        <v>129</v>
+        <v>250</v>
       </c>
       <c r="C47">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="D47">
-        <v>1053.49353109041</v>
+        <v>782.8449691256878</v>
       </c>
       <c r="E47">
-        <v>704</v>
+        <v>811</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46139.48958333334</v>
+        <v>46142.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>1048.523323729602</v>
+        <v>783.2662662580939</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46139.5</v>
+        <v>46142.5</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>1043.553116368794</v>
+        <v>783.6875633904999</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46139.51041666666</v>
+        <v>46142.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>1026.176433546048</v>
+        <v>769.8222066577432</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46139.52083333334</v>
+        <v>46142.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>1008.799750723301</v>
+        <v>755.9568499249866</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46139.53125</v>
+        <v>46142.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>991.4230679005539</v>
+        <v>742.09149319223</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46139.54166666666</v>
+        <v>46142.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>974.046385077807</v>
+        <v>728.2261364594733</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46139.55208333334</v>
+        <v>46142.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>970.8662140843976</v>
+        <v>733.7685342891818</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46139.5625</v>
+        <v>46142.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>967.6860430909881</v>
+        <v>739.3109321188904</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46139.57291666666</v>
+        <v>46142.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>964.5058720975786</v>
+        <v>744.8533299485989</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46139.58333333334</v>
+        <v>46142.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>961.3257011041692</v>
+        <v>750.3957277783074</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46139.59375</v>
+        <v>46142.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>961.8112960763619</v>
+        <v>760.8158101844238</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46139.60416666666</v>
+        <v>46142.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>962.2968910485548</v>
+        <v>771.2358925905401</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46139.61458333334</v>
+        <v>46142.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>962.7824860207477</v>
+        <v>781.6559749966564</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46139.625</v>
+        <v>46142.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>963.2680809929404</v>
+        <v>792.0760574027727</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46139.63541666666</v>
+        <v>46142.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1036.345363548853</v>
+        <v>887.4202795269431</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46139.64583333334</v>
+        <v>46142.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1109.422646104766</v>
+        <v>982.7645016511135</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46139.65625</v>
+        <v>46142.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1182.499928660679</v>
+        <v>1078.108723775284</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46139.66666666666</v>
+        <v>46142.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>1255.577211216592</v>
+        <v>1173.452945899454</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46139.67708333334</v>
+        <v>46142.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>1394.83823201938</v>
+        <v>1289.169224911024</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46139.6875</v>
+        <v>46142.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>1534.099252822169</v>
+        <v>1404.885503922593</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46139.69791666666</v>
+        <v>46142.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>1673.360273624957</v>
+        <v>1520.601782934162</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46139.70833333334</v>
+        <v>46142.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>1812.621294427745</v>
+        <v>1636.318061945731</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46139.71875</v>
+        <v>46142.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>1944.465090069963</v>
+        <v>1814.685905613224</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46139.72916666666</v>
+        <v>46142.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>2076.30888571218</v>
+        <v>1993.053749280717</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46139.73958333334</v>
+        <v>46142.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>2208.152681354397</v>
+        <v>2171.42159294821</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46139.75</v>
+        <v>46142.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>2339.996476996615</v>
+        <v>2349.789436615703</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46139.76041666666</v>
+        <v>46142.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2368.570408586161</v>
+        <v>2380.6564731773</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46139.77083333334</v>
+        <v>46142.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2397.144340175706</v>
+        <v>2411.523509738896</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46139.78125</v>
+        <v>46142.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2425.718271765252</v>
+        <v>2442.390546300493</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46139.79166666666</v>
+        <v>46142.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2454.292203354798</v>
+        <v>2473.257582862089</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46139.80208333334</v>
+        <v>46142.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2472.935241692763</v>
+        <v>2476.515614018727</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46139.8125</v>
+        <v>46142.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2491.578280030727</v>
+        <v>2479.773645175365</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46139.82291666666</v>
+        <v>46142.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2510.221318368692</v>
+        <v>2483.031676332003</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46139.83333333334</v>
+        <v>46142.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2528.864356706656</v>
+        <v>2486.289707488641</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46139.84375</v>
+        <v>46142.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2515.715206581692</v>
+        <v>2478.032283694836</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46139.85416666666</v>
+        <v>46142.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2502.566056456727</v>
+        <v>2469.77485990103</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46139.86458333334</v>
+        <v>46142.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2489.416906331763</v>
+        <v>2461.517436107225</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46139.875</v>
+        <v>46142.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2476.267756206798</v>
+        <v>2453.260012313419</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46139.88541666666</v>
+        <v>46142.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2439.029286880824</v>
+        <v>2426.222098576979</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46139.89583333334</v>
+        <v>46142.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2401.790817554849</v>
+        <v>2399.184184840539</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46139.90625</v>
+        <v>46142.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2364.552348228874</v>
+        <v>2372.146271104099</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46139.91666666666</v>
+        <v>46142.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2327.313878902899</v>
+        <v>2345.10835736766</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46139.92708333334</v>
+        <v>46142.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>2284.790993704956</v>
+        <v>2287.03488821651</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46139.9375</v>
+        <v>46142.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>2242.268108507013</v>
+        <v>2228.961419065361</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46139.94791666666</v>
+        <v>46142.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>2199.74522330907</v>
+        <v>2170.887949914212</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46139.95833333334</v>
+        <v>46142.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>2157.222338111127</v>
+        <v>2112.814480763063</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46139.96875</v>
+        <v>46142.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>2131.402606731292</v>
+        <v>2027.381820980512</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46139.97916666666</v>
+        <v>46142.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>2105.582875351456</v>
+        <v>1941.949161197961</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46139.98958333334</v>
+        <v>46142.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>2079.763143971621</v>
+        <v>1856.51650141541</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46140</v>
+        <v>46143</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>2053.943412591785</v>
+        <v>1771.08384163286</v>
       </c>
       <c r="E97">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -412,789 +412,789 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46142.01041666666</v>
+        <v>46146.01041666666</v>
       </c>
       <c r="B2">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="C2">
-        <v>1000</v>
+        <v>907</v>
       </c>
       <c r="D2">
-        <v>1917.679011228841</v>
+        <v>1759.273989735453</v>
       </c>
       <c r="E2">
-        <v>1628</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46142.02083333334</v>
+        <v>46146.02083333334</v>
       </c>
       <c r="B3">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="C3">
-        <v>995</v>
+        <v>874</v>
       </c>
       <c r="D3">
-        <v>1864.473864495583</v>
+        <v>1737.180671180532</v>
       </c>
       <c r="E3">
-        <v>1620</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46142.03125</v>
+        <v>46146.03125</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>595</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>871</v>
       </c>
       <c r="D4">
-        <v>1811.268717762324</v>
+        <v>1715.08735262561</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46142.04166666666</v>
+        <v>46146.04166666666</v>
       </c>
       <c r="B5">
-        <v>623</v>
+        <v>592</v>
       </c>
       <c r="C5">
-        <v>993</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1758.063571029066</v>
+        <v>1692.994034070689</v>
       </c>
       <c r="E5">
-        <v>1616</v>
+        <v>592</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46142.05208333334</v>
+        <v>46146.05208333334</v>
       </c>
       <c r="B6">
-        <v>648</v>
+        <v>582</v>
       </c>
       <c r="C6">
-        <v>954</v>
+        <v>863</v>
       </c>
       <c r="D6">
-        <v>1735.276077249592</v>
+        <v>1688.232385728134</v>
       </c>
       <c r="E6">
-        <v>1602</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46142.0625</v>
+        <v>46146.0625</v>
       </c>
       <c r="B7">
-        <v>644</v>
+        <v>574</v>
       </c>
       <c r="C7">
-        <v>955</v>
+        <v>860</v>
       </c>
       <c r="D7">
-        <v>1712.488583470118</v>
+        <v>1683.470737385578</v>
       </c>
       <c r="E7">
-        <v>1599</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46142.07291666666</v>
+        <v>46146.07291666666</v>
       </c>
       <c r="B8">
-        <v>645</v>
+        <v>570</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1689.701089690644</v>
+        <v>1678.709089043023</v>
       </c>
       <c r="E8">
-        <v>645</v>
+        <v>570</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46142.08333333334</v>
+        <v>46146.08333333334</v>
       </c>
       <c r="B9">
-        <v>643</v>
+        <v>583</v>
       </c>
       <c r="C9">
-        <v>954</v>
+        <v>862</v>
       </c>
       <c r="D9">
-        <v>1666.91359591117</v>
+        <v>1673.947440700468</v>
       </c>
       <c r="E9">
-        <v>1597</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46142.09375</v>
+        <v>46146.09375</v>
       </c>
       <c r="B10">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="C10">
-        <v>955</v>
+        <v>794</v>
       </c>
       <c r="D10">
-        <v>1661.249490021095</v>
+        <v>1664.469753673929</v>
       </c>
       <c r="E10">
-        <v>1591</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46142.10416666666</v>
+        <v>46146.10416666666</v>
       </c>
       <c r="B11">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="C11">
-        <v>956</v>
+        <v>787</v>
       </c>
       <c r="D11">
-        <v>1655.58538413102</v>
+        <v>1654.992066647389</v>
       </c>
       <c r="E11">
-        <v>1597</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46142.11458333334</v>
+        <v>46146.11458333334</v>
       </c>
       <c r="B12">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="C12">
-        <v>969</v>
+        <v>802</v>
       </c>
       <c r="D12">
-        <v>1649.921278240946</v>
+        <v>1645.51437962085</v>
       </c>
       <c r="E12">
-        <v>1611</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46142.125</v>
+        <v>46146.125</v>
       </c>
       <c r="B13">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="C13">
-        <v>966</v>
+        <v>805</v>
       </c>
       <c r="D13">
-        <v>1644.257172350871</v>
+        <v>1636.036692594311</v>
       </c>
       <c r="E13">
-        <v>1600</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46142.13541666666</v>
+        <v>46146.13541666666</v>
       </c>
       <c r="B14">
-        <v>637</v>
+        <v>663</v>
       </c>
       <c r="C14">
-        <v>970</v>
+        <v>807</v>
       </c>
       <c r="D14">
-        <v>1664.984991260847</v>
+        <v>1644.292040774234</v>
       </c>
       <c r="E14">
-        <v>1607</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46142.14583333334</v>
+        <v>46146.14583333334</v>
       </c>
       <c r="B15">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="C15">
-        <v>969</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>1685.712810170822</v>
+        <v>1652.547388954156</v>
       </c>
       <c r="E15">
-        <v>1615</v>
+        <v>629</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46142.15625</v>
+        <v>46146.15625</v>
       </c>
       <c r="B16">
-        <v>652</v>
+        <v>628</v>
       </c>
       <c r="C16">
-        <v>970</v>
+        <v>806</v>
       </c>
       <c r="D16">
-        <v>1706.440629080797</v>
+        <v>1660.802737134079</v>
       </c>
       <c r="E16">
-        <v>1622</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46142.16666666666</v>
+        <v>46146.16666666666</v>
       </c>
       <c r="B17">
-        <v>646</v>
+        <v>626</v>
       </c>
       <c r="C17">
-        <v>969</v>
+        <v>804</v>
       </c>
       <c r="D17">
-        <v>1727.168447990773</v>
+        <v>1669.058085314002</v>
       </c>
       <c r="E17">
-        <v>1615</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46142.17708333334</v>
+        <v>46146.17708333334</v>
       </c>
       <c r="B18">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="C18">
-        <v>972</v>
+        <v>821</v>
       </c>
       <c r="D18">
-        <v>1775.804861378377</v>
+        <v>1697.45465866727</v>
       </c>
       <c r="E18">
-        <v>1629</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46142.1875</v>
+        <v>46146.1875</v>
       </c>
       <c r="B19">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>822</v>
       </c>
       <c r="D19">
-        <v>1824.441274765982</v>
+        <v>1725.851232020538</v>
       </c>
       <c r="E19">
-        <v>658</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46142.19791666666</v>
+        <v>46146.19791666666</v>
       </c>
       <c r="B20">
-        <v>669</v>
+        <v>653</v>
       </c>
       <c r="C20">
-        <v>971</v>
+        <v>823</v>
       </c>
       <c r="D20">
-        <v>1873.077688153587</v>
+        <v>1754.247805373807</v>
       </c>
       <c r="E20">
-        <v>1640</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46142.20833333334</v>
+        <v>46146.20833333334</v>
       </c>
       <c r="B21">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="C21">
-        <v>975</v>
+        <v>825</v>
       </c>
       <c r="D21">
-        <v>1921.714101541192</v>
+        <v>1782.644378727075</v>
       </c>
       <c r="E21">
-        <v>1649</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46142.21875</v>
+        <v>46146.21875</v>
       </c>
       <c r="B22">
-        <v>652</v>
+        <v>672</v>
       </c>
       <c r="C22">
-        <v>1057</v>
+        <v>828</v>
       </c>
       <c r="D22">
-        <v>1927.602899235028</v>
+        <v>1796.391129785188</v>
       </c>
       <c r="E22">
-        <v>1709</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46142.22916666666</v>
+        <v>46146.22916666666</v>
       </c>
       <c r="B23">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C23">
-        <v>1067</v>
+        <v>830</v>
       </c>
       <c r="D23">
-        <v>1933.491696928863</v>
+        <v>1810.1378808433</v>
       </c>
       <c r="E23">
-        <v>1735</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46142.23958333334</v>
+        <v>46146.23958333334</v>
       </c>
       <c r="B24">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="C24">
-        <v>1064</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>1939.380494622699</v>
+        <v>1823.884631901412</v>
       </c>
       <c r="E24">
-        <v>1739</v>
+        <v>671</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46142.25</v>
+        <v>46146.25</v>
       </c>
       <c r="B25">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C25">
-        <v>1069</v>
+        <v>827</v>
       </c>
       <c r="D25">
-        <v>1945.269292316535</v>
+        <v>1837.631382959524</v>
       </c>
       <c r="E25">
-        <v>1749</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46142.26041666666</v>
+        <v>46146.26041666666</v>
       </c>
       <c r="B26">
-        <v>735</v>
+        <v>694</v>
       </c>
       <c r="C26">
-        <v>1132</v>
+        <v>860</v>
       </c>
       <c r="D26">
-        <v>1919.560805086414</v>
+        <v>1835.24143685616</v>
       </c>
       <c r="E26">
-        <v>1867</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46142.27083333334</v>
+        <v>46146.27083333334</v>
       </c>
       <c r="B27">
-        <v>821</v>
+        <v>703</v>
       </c>
       <c r="C27">
-        <v>1138</v>
+        <v>858</v>
       </c>
       <c r="D27">
-        <v>1893.852317856294</v>
+        <v>1832.851490752795</v>
       </c>
       <c r="E27">
-        <v>1959</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46142.28125</v>
+        <v>46146.28125</v>
       </c>
       <c r="B28">
-        <v>1052</v>
+        <v>712</v>
       </c>
       <c r="C28">
-        <v>1137</v>
+        <v>860</v>
       </c>
       <c r="D28">
-        <v>1868.143830626174</v>
+        <v>1830.46154464943</v>
       </c>
       <c r="E28">
-        <v>2189</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46142.29166666666</v>
+        <v>46146.29166666666</v>
       </c>
       <c r="B29">
-        <v>1110</v>
+        <v>715</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>1842.435343396053</v>
+        <v>1828.071598546066</v>
       </c>
       <c r="E29">
-        <v>1110</v>
+        <v>715</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46142.30208333334</v>
+        <v>46146.30208333334</v>
       </c>
       <c r="B30">
-        <v>1034</v>
+        <v>782</v>
       </c>
       <c r="C30">
-        <v>1138</v>
+        <v>818</v>
       </c>
       <c r="D30">
-        <v>1761.471396721622</v>
+        <v>1735.055261096211</v>
       </c>
       <c r="E30">
-        <v>2172</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46142.3125</v>
+        <v>46146.3125</v>
       </c>
       <c r="B31">
-        <v>1089</v>
+        <v>766</v>
       </c>
       <c r="C31">
-        <v>1148</v>
+        <v>808</v>
       </c>
       <c r="D31">
-        <v>1680.507450047191</v>
+        <v>1642.038923646357</v>
       </c>
       <c r="E31">
-        <v>2237</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46142.32291666666</v>
+        <v>46146.32291666666</v>
       </c>
       <c r="B32">
-        <v>1088</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>1152</v>
+        <v>807</v>
       </c>
       <c r="D32">
-        <v>1599.54350337276</v>
+        <v>1549.022586196502</v>
       </c>
       <c r="E32">
-        <v>2240</v>
+        <v>807</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46142.33333333334</v>
+        <v>46146.33333333334</v>
       </c>
       <c r="B33">
-        <v>1078</v>
+        <v>771</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>804</v>
       </c>
       <c r="D33">
-        <v>1518.579556698329</v>
+        <v>1456.006248746648</v>
       </c>
       <c r="E33">
-        <v>1078</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46142.34375</v>
+        <v>46146.34375</v>
       </c>
       <c r="B34">
-        <v>1113</v>
+        <v>732</v>
       </c>
       <c r="C34">
-        <v>936</v>
+        <v>815</v>
       </c>
       <c r="D34">
-        <v>1458.680466640581</v>
+        <v>1392.043263731073</v>
       </c>
       <c r="E34">
-        <v>2049</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46142.35416666666</v>
+        <v>46146.35416666666</v>
       </c>
       <c r="B35">
-        <v>1087</v>
+        <v>729</v>
       </c>
       <c r="C35">
-        <v>916</v>
+        <v>816</v>
       </c>
       <c r="D35">
-        <v>1398.781376582834</v>
+        <v>1328.080278715498</v>
       </c>
       <c r="E35">
-        <v>2003</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46142.36458333334</v>
+        <v>46146.36458333334</v>
       </c>
       <c r="B36">
-        <v>1040</v>
+        <v>730</v>
       </c>
       <c r="C36">
-        <v>955</v>
+        <v>827</v>
       </c>
       <c r="D36">
-        <v>1338.882286525086</v>
+        <v>1264.117293699923</v>
       </c>
       <c r="E36">
-        <v>1995</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46142.375</v>
+        <v>46146.375</v>
       </c>
       <c r="B37">
-        <v>922</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>959</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>1278.983196467339</v>
+        <v>1200.154308684348</v>
       </c>
       <c r="E37">
-        <v>1881</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46142.38541666666</v>
+        <v>46146.38541666666</v>
       </c>
       <c r="B38">
-        <v>920</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>904</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>1173.406135107004</v>
+        <v>1098.098136928655</v>
       </c>
       <c r="E38">
-        <v>1824</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46142.39583333334</v>
+        <v>46146.39583333334</v>
       </c>
       <c r="B39">
-        <v>905</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>899</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>1067.829073746669</v>
+        <v>996.0419651729627</v>
       </c>
       <c r="E39">
-        <v>1804</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46142.40625</v>
+        <v>46146.40625</v>
       </c>
       <c r="B40">
-        <v>663</v>
+        <v>0</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>962.2520123863337</v>
+        <v>893.9857934172701</v>
       </c>
       <c r="E40">
-        <v>663</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46142.41666666666</v>
+        <v>46146.41666666666</v>
       </c>
       <c r="B41">
-        <v>581</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>898</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>856.6749510259987</v>
+        <v>791.9296216615774</v>
       </c>
       <c r="E41">
-        <v>1479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46142.42708333334</v>
+        <v>46146.42708333334</v>
       </c>
       <c r="B42">
-        <v>303</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>658</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>838.006806984718</v>
+        <v>784.9878316448841</v>
       </c>
       <c r="E42">
-        <v>961</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46142.4375</v>
+        <v>46146.4375</v>
       </c>
       <c r="B43">
-        <v>283</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>643</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>819.3386629434373</v>
+        <v>778.0460416281908</v>
       </c>
       <c r="E43">
-        <v>926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46142.44791666666</v>
+        <v>46146.44791666666</v>
       </c>
       <c r="B44">
-        <v>284</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>800.6705189021566</v>
+        <v>771.1042516114975</v>
       </c>
       <c r="E44">
-        <v>934</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46142.45833333334</v>
+        <v>46146.45833333334</v>
       </c>
       <c r="B45">
-        <v>307</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>595</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>782.0023748608759</v>
+        <v>764.1624615948042</v>
       </c>
       <c r="E45">
-        <v>902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46142.46875</v>
+        <v>46146.46875</v>
       </c>
       <c r="B46">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>563</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>782.4236719932819</v>
+        <v>765.2023618076014</v>
       </c>
       <c r="E46">
-        <v>823</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46142.47916666666</v>
+        <v>46146.47916666666</v>
       </c>
       <c r="B47">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>561</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>782.8449691256878</v>
+        <v>766.2422620203986</v>
       </c>
       <c r="E47">
-        <v>811</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46142.48958333334</v>
+        <v>46146.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>783.2662662580939</v>
+        <v>767.2821622331958</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46142.5</v>
+        <v>46146.5</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>783.6875633904999</v>
+        <v>768.322062445993</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46142.51041666666</v>
+        <v>46146.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>769.8222066577432</v>
+        <v>760.9241758448188</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46142.52083333334</v>
+        <v>46146.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>755.9568499249866</v>
+        <v>753.5262892436446</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46142.53125</v>
+        <v>46146.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>742.09149319223</v>
+        <v>746.1284026424703</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46142.54166666666</v>
+        <v>46146.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>728.2261364594733</v>
+        <v>738.7305160412961</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46142.55208333334</v>
+        <v>46146.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>733.7685342891818</v>
+        <v>747.7794722784629</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46142.5625</v>
+        <v>46146.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>739.3109321188904</v>
+        <v>756.8284285156295</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46142.57291666666</v>
+        <v>46146.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>744.8533299485989</v>
+        <v>765.8773847527962</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46142.58333333334</v>
+        <v>46146.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>750.3957277783074</v>
+        <v>774.9263409899629</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46142.59375</v>
+        <v>46146.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>760.8158101844238</v>
+        <v>787.8794839907839</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46142.60416666666</v>
+        <v>46146.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>771.2358925905401</v>
+        <v>800.8326269916049</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46142.61458333334</v>
+        <v>46146.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>781.6559749966564</v>
+        <v>813.7857699924258</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46142.625</v>
+        <v>46146.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>792.0760574027727</v>
+        <v>826.7389129932468</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46142.63541666666</v>
+        <v>46146.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>887.4202795269431</v>
+        <v>931.4678107344369</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46142.64583333334</v>
+        <v>46146.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>982.7645016511135</v>
+        <v>1036.196708475627</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46142.65625</v>
+        <v>46146.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1078.108723775284</v>
+        <v>1140.925606216817</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46142.66666666666</v>
+        <v>46146.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>1173.452945899454</v>
+        <v>1245.654503958007</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46142.67708333334</v>
+        <v>46146.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>1289.169224911024</v>
+        <v>1375.6146647557</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46142.6875</v>
+        <v>46146.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>1404.885503922593</v>
+        <v>1505.574825553393</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46142.69791666666</v>
+        <v>46146.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>1520.601782934162</v>
+        <v>1635.534986351085</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46142.70833333334</v>
+        <v>46146.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>1636.318061945731</v>
+        <v>1765.495147148778</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46142.71875</v>
+        <v>46146.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>1814.685905613224</v>
+        <v>1909.074351960632</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46142.72916666666</v>
+        <v>46146.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>1993.053749280717</v>
+        <v>2052.653556772486</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46142.73958333334</v>
+        <v>46146.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>2171.42159294821</v>
+        <v>2196.23276158434</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46142.75</v>
+        <v>46146.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>2349.789436615703</v>
+        <v>2339.811966396193</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46142.76041666666</v>
+        <v>46146.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2380.6564731773</v>
+        <v>2366.010154212115</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46142.77083333334</v>
+        <v>46146.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2411.523509738896</v>
+        <v>2392.208342028036</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46142.78125</v>
+        <v>46146.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2442.390546300493</v>
+        <v>2418.406529843957</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46142.79166666666</v>
+        <v>46146.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2473.257582862089</v>
+        <v>2444.604717659878</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46142.80208333334</v>
+        <v>46146.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2476.515614018727</v>
+        <v>2445.352716058341</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46142.8125</v>
+        <v>46146.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2479.773645175365</v>
+        <v>2446.100714456804</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46142.82291666666</v>
+        <v>46146.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2483.031676332003</v>
+        <v>2446.848712855267</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46142.83333333334</v>
+        <v>46146.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2486.289707488641</v>
+        <v>2447.59671125373</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46142.84375</v>
+        <v>46146.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2478.032283694836</v>
+        <v>2414.894586142585</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46142.85416666666</v>
+        <v>46146.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2469.77485990103</v>
+        <v>2382.192461031441</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46142.86458333334</v>
+        <v>46146.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2461.517436107225</v>
+        <v>2349.490335920297</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46142.875</v>
+        <v>46146.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2453.260012313419</v>
+        <v>2316.788210809153</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46142.88541666666</v>
+        <v>46146.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2426.222098576979</v>
+        <v>2276.496638531085</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46142.89583333334</v>
+        <v>46146.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2399.184184840539</v>
+        <v>2236.205066253018</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46142.90625</v>
+        <v>46146.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2372.146271104099</v>
+        <v>2195.913493974952</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46142.91666666666</v>
+        <v>46146.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2345.10835736766</v>
+        <v>2155.621921696884</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46142.92708333334</v>
+        <v>46146.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>2287.03488821651</v>
+        <v>2098.035166933453</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46142.9375</v>
+        <v>46146.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>2228.961419065361</v>
+        <v>2040.448412170021</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46142.94791666666</v>
+        <v>46146.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>2170.887949914212</v>
+        <v>1982.86165740659</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46142.95833333334</v>
+        <v>46146.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>2112.814480763063</v>
+        <v>1925.274902643158</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46142.96875</v>
+        <v>46146.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>2027.381820980512</v>
+        <v>1893.28197582127</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46142.97916666666</v>
+        <v>46146.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>1941.949161197961</v>
+        <v>1861.289048999383</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46142.98958333334</v>
+        <v>46146.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1856.51650141541</v>
+        <v>1829.296122177495</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1771.08384163286</v>
+        <v>1797.303195355607</v>
       </c>
       <c r="E97">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -412,602 +412,602 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46146.01041666666</v>
+        <v>46148.01041666666</v>
       </c>
       <c r="B2">
-        <v>611</v>
+        <v>639</v>
       </c>
       <c r="C2">
-        <v>907</v>
+        <v>817</v>
       </c>
       <c r="D2">
-        <v>1759.273989735453</v>
+        <v>1612.634436882246</v>
       </c>
       <c r="E2">
-        <v>1518</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46146.02083333334</v>
+        <v>46148.02083333334</v>
       </c>
       <c r="B3">
-        <v>597</v>
+        <v>648</v>
       </c>
       <c r="C3">
-        <v>874</v>
+        <v>816</v>
       </c>
       <c r="D3">
-        <v>1737.180671180532</v>
+        <v>1591.187091488078</v>
       </c>
       <c r="E3">
-        <v>1471</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46146.03125</v>
+        <v>46148.03125</v>
       </c>
       <c r="B4">
-        <v>595</v>
+        <v>636</v>
       </c>
       <c r="C4">
-        <v>871</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1715.08735262561</v>
+        <v>1569.739746093909</v>
       </c>
       <c r="E4">
-        <v>1466</v>
+        <v>636</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46146.04166666666</v>
+        <v>46148.04166666666</v>
       </c>
       <c r="B5">
-        <v>592</v>
+        <v>651</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1692.994034070689</v>
+        <v>1548.292400699741</v>
       </c>
       <c r="E5">
-        <v>592</v>
+        <v>651</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46146.05208333334</v>
+        <v>46148.05208333334</v>
       </c>
       <c r="B6">
-        <v>582</v>
+        <v>645</v>
       </c>
       <c r="C6">
-        <v>863</v>
+        <v>834</v>
       </c>
       <c r="D6">
-        <v>1688.232385728134</v>
+        <v>1541.383838477984</v>
       </c>
       <c r="E6">
-        <v>1445</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46146.0625</v>
+        <v>46148.0625</v>
       </c>
       <c r="B7">
-        <v>574</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>860</v>
+        <v>835</v>
       </c>
       <c r="D7">
-        <v>1683.470737385578</v>
+        <v>1534.475276256226</v>
       </c>
       <c r="E7">
-        <v>1434</v>
+        <v>835</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46146.07291666666</v>
+        <v>46148.07291666666</v>
       </c>
       <c r="B8">
-        <v>570</v>
+        <v>644</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>834</v>
       </c>
       <c r="D8">
-        <v>1678.709089043023</v>
+        <v>1527.566714034469</v>
       </c>
       <c r="E8">
-        <v>570</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46146.08333333334</v>
+        <v>46148.08333333334</v>
       </c>
       <c r="B9">
-        <v>583</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>862</v>
+        <v>835</v>
       </c>
       <c r="D9">
-        <v>1673.947440700468</v>
+        <v>1520.658151812712</v>
       </c>
       <c r="E9">
-        <v>1445</v>
+        <v>835</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46146.09375</v>
+        <v>46148.09375</v>
       </c>
       <c r="B10">
-        <v>632</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>794</v>
+        <v>839</v>
       </c>
       <c r="D10">
-        <v>1664.469753673929</v>
+        <v>1515.676946440025</v>
       </c>
       <c r="E10">
-        <v>1426</v>
+        <v>839</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46146.10416666666</v>
+        <v>46148.10416666666</v>
       </c>
       <c r="B11">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="C11">
-        <v>787</v>
+        <v>837</v>
       </c>
       <c r="D11">
-        <v>1654.992066647389</v>
+        <v>1510.695741067338</v>
       </c>
       <c r="E11">
-        <v>1417</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46146.11458333334</v>
+        <v>46148.11458333334</v>
       </c>
       <c r="B12">
-        <v>631</v>
+        <v>642</v>
       </c>
       <c r="C12">
-        <v>802</v>
+        <v>836</v>
       </c>
       <c r="D12">
-        <v>1645.51437962085</v>
+        <v>1505.71453569465</v>
       </c>
       <c r="E12">
-        <v>1433</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46146.125</v>
+        <v>46148.125</v>
       </c>
       <c r="B13">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="C13">
-        <v>805</v>
+        <v>838</v>
       </c>
       <c r="D13">
-        <v>1636.036692594311</v>
+        <v>1500.733330321963</v>
       </c>
       <c r="E13">
-        <v>1445</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46146.13541666666</v>
+        <v>46148.13541666666</v>
       </c>
       <c r="B14">
-        <v>663</v>
+        <v>712</v>
       </c>
       <c r="C14">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D14">
-        <v>1644.292040774234</v>
+        <v>1512.543891470553</v>
       </c>
       <c r="E14">
-        <v>1470</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46146.14583333334</v>
+        <v>46148.14583333334</v>
       </c>
       <c r="B15">
-        <v>629</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>805</v>
       </c>
       <c r="D15">
-        <v>1652.547388954156</v>
+        <v>1524.354452619143</v>
       </c>
       <c r="E15">
-        <v>629</v>
+        <v>805</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46146.15625</v>
+        <v>46148.15625</v>
       </c>
       <c r="B16">
-        <v>628</v>
+        <v>713</v>
       </c>
       <c r="C16">
-        <v>806</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>1660.802737134079</v>
+        <v>1536.165013767733</v>
       </c>
       <c r="E16">
-        <v>1434</v>
+        <v>713</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46146.16666666666</v>
+        <v>46148.16666666666</v>
       </c>
       <c r="B17">
-        <v>626</v>
+        <v>714</v>
       </c>
       <c r="C17">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="D17">
-        <v>1669.058085314002</v>
+        <v>1547.975574916323</v>
       </c>
       <c r="E17">
-        <v>1430</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46146.17708333334</v>
+        <v>46148.17708333334</v>
       </c>
       <c r="B18">
-        <v>650</v>
+        <v>735</v>
       </c>
       <c r="C18">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="D18">
-        <v>1697.45465866727</v>
+        <v>1568.745265162749</v>
       </c>
       <c r="E18">
-        <v>1471</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46146.1875</v>
+        <v>46148.1875</v>
       </c>
       <c r="B19">
-        <v>652</v>
+        <v>736</v>
       </c>
       <c r="C19">
-        <v>822</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>1725.851232020538</v>
+        <v>1589.514955409175</v>
       </c>
       <c r="E19">
-        <v>1474</v>
+        <v>736</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46146.19791666666</v>
+        <v>46148.19791666666</v>
       </c>
       <c r="B20">
-        <v>653</v>
+        <v>739</v>
       </c>
       <c r="C20">
-        <v>823</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>1754.247805373807</v>
+        <v>1610.284645655601</v>
       </c>
       <c r="E20">
-        <v>1476</v>
+        <v>739</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46146.20833333334</v>
+        <v>46148.20833333334</v>
       </c>
       <c r="B21">
-        <v>658</v>
+        <v>745</v>
       </c>
       <c r="C21">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="D21">
-        <v>1782.644378727075</v>
+        <v>1631.054335902027</v>
       </c>
       <c r="E21">
-        <v>1483</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46146.21875</v>
+        <v>46148.21875</v>
       </c>
       <c r="B22">
-        <v>672</v>
+        <v>817</v>
       </c>
       <c r="C22">
-        <v>828</v>
+        <v>809</v>
       </c>
       <c r="D22">
-        <v>1796.391129785188</v>
+        <v>1646.006752735999</v>
       </c>
       <c r="E22">
-        <v>1500</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46146.22916666666</v>
+        <v>46148.22916666666</v>
       </c>
       <c r="B23">
-        <v>669</v>
+        <v>820</v>
       </c>
       <c r="C23">
-        <v>830</v>
+        <v>810</v>
       </c>
       <c r="D23">
-        <v>1810.1378808433</v>
+        <v>1660.959169569971</v>
       </c>
       <c r="E23">
-        <v>1499</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46146.23958333334</v>
+        <v>46148.23958333334</v>
       </c>
       <c r="B24">
-        <v>671</v>
+        <v>819</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>809</v>
       </c>
       <c r="D24">
-        <v>1823.884631901412</v>
+        <v>1675.911586403942</v>
       </c>
       <c r="E24">
-        <v>671</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46146.25</v>
+        <v>46148.25</v>
       </c>
       <c r="B25">
-        <v>679</v>
+        <v>820</v>
       </c>
       <c r="C25">
-        <v>827</v>
+        <v>807</v>
       </c>
       <c r="D25">
-        <v>1837.631382959524</v>
+        <v>1690.864003237914</v>
       </c>
       <c r="E25">
-        <v>1506</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46146.26041666666</v>
+        <v>46148.26041666666</v>
       </c>
       <c r="B26">
-        <v>694</v>
+        <v>909</v>
       </c>
       <c r="C26">
-        <v>860</v>
+        <v>835</v>
       </c>
       <c r="D26">
-        <v>1835.24143685616</v>
+        <v>1687.783752565793</v>
       </c>
       <c r="E26">
-        <v>1554</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46146.27083333334</v>
+        <v>46148.27083333334</v>
       </c>
       <c r="B27">
-        <v>703</v>
+        <v>893</v>
       </c>
       <c r="C27">
-        <v>858</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>1832.851490752795</v>
+        <v>1684.703501893672</v>
       </c>
       <c r="E27">
-        <v>1561</v>
+        <v>893</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46146.28125</v>
+        <v>46148.28125</v>
       </c>
       <c r="B28">
-        <v>712</v>
+        <v>875</v>
       </c>
       <c r="C28">
-        <v>860</v>
+        <v>834</v>
       </c>
       <c r="D28">
-        <v>1830.46154464943</v>
+        <v>1681.623251221551</v>
       </c>
       <c r="E28">
-        <v>1572</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46146.29166666666</v>
+        <v>46148.29166666666</v>
       </c>
       <c r="B29">
-        <v>715</v>
+        <v>876</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>835</v>
       </c>
       <c r="D29">
-        <v>1828.071598546066</v>
+        <v>1678.54300054943</v>
       </c>
       <c r="E29">
-        <v>715</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46146.30208333334</v>
+        <v>46148.30208333334</v>
       </c>
       <c r="B30">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="C30">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="D30">
-        <v>1735.055261096211</v>
+        <v>1604.256155053971</v>
       </c>
       <c r="E30">
-        <v>1600</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46146.3125</v>
+        <v>46148.3125</v>
       </c>
       <c r="B31">
-        <v>766</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="D31">
-        <v>1642.038923646357</v>
+        <v>1529.969309558513</v>
       </c>
       <c r="E31">
-        <v>1574</v>
+        <v>815</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46146.32291666666</v>
+        <v>46148.32291666666</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>807</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>1549.022586196502</v>
+        <v>1455.682464063055</v>
       </c>
       <c r="E32">
-        <v>807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46146.33333333334</v>
+        <v>46148.33333333334</v>
       </c>
       <c r="B33">
-        <v>771</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>804</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>1456.006248746648</v>
+        <v>1381.395618567596</v>
       </c>
       <c r="E33">
-        <v>1575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46146.34375</v>
+        <v>46148.34375</v>
       </c>
       <c r="B34">
-        <v>732</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>1392.043263731073</v>
+        <v>1346.166351594843</v>
       </c>
       <c r="E34">
-        <v>1547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46146.35416666666</v>
+        <v>46148.35416666666</v>
       </c>
       <c r="B35">
-        <v>729</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>816</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>1328.080278715498</v>
+        <v>1310.93708462209</v>
       </c>
       <c r="E35">
-        <v>1545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46146.36458333334</v>
+        <v>46148.36458333334</v>
       </c>
       <c r="B36">
-        <v>730</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>827</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>1264.117293699923</v>
+        <v>1275.707817649336</v>
       </c>
       <c r="E36">
-        <v>1557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46146.375</v>
+        <v>46148.375</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1016,7 +1016,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>1200.154308684348</v>
+        <v>1240.478550676583</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1024,7 +1024,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46146.38541666666</v>
+        <v>46148.38541666666</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>1098.098136928655</v>
+        <v>1139.613542238992</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1041,7 +1041,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46146.39583333334</v>
+        <v>46148.39583333334</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>996.0419651729627</v>
+        <v>1038.748533801401</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46146.40625</v>
+        <v>46148.40625</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1067,7 +1067,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>893.9857934172701</v>
+        <v>937.8835253638097</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1075,7 +1075,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46146.41666666666</v>
+        <v>46148.41666666666</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>791.9296216615774</v>
+        <v>837.0185169262187</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46146.42708333334</v>
+        <v>46148.42708333334</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>784.9878316448841</v>
+        <v>822.5061359022728</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46146.4375</v>
+        <v>46148.4375</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>778.0460416281908</v>
+        <v>807.9937548783271</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46146.44791666666</v>
+        <v>46148.44791666666</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>771.1042516114975</v>
+        <v>793.4813738543812</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46146.45833333334</v>
+        <v>46148.45833333334</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>764.1624615948042</v>
+        <v>778.9689928304354</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46146.46875</v>
+        <v>46148.46875</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1169,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>765.2023618076014</v>
+        <v>764.5622204012039</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46146.47916666666</v>
+        <v>46148.47916666666</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>766.2422620203986</v>
+        <v>750.1554479719725</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46146.48958333334</v>
+        <v>46148.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>767.2821622331958</v>
+        <v>735.7486755427411</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46146.5</v>
+        <v>46148.5</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>768.322062445993</v>
+        <v>721.3419031135097</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46146.51041666666</v>
+        <v>46148.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>760.9241758448188</v>
+        <v>708.9240925468101</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46146.52083333334</v>
+        <v>46148.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>753.5262892436446</v>
+        <v>696.5062819801105</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46146.53125</v>
+        <v>46148.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>746.1284026424703</v>
+        <v>684.088471413411</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46146.54166666666</v>
+        <v>46148.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>738.7305160412961</v>
+        <v>671.6706608467114</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46146.55208333334</v>
+        <v>46148.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>747.7794722784629</v>
+        <v>682.3019260235808</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46146.5625</v>
+        <v>46148.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>756.8284285156295</v>
+        <v>692.9331912004502</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46146.57291666666</v>
+        <v>46148.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>765.8773847527962</v>
+        <v>703.5644563773196</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46146.58333333334</v>
+        <v>46148.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>774.9263409899629</v>
+        <v>714.195721554189</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46146.59375</v>
+        <v>46148.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>787.8794839907839</v>
+        <v>760.1618622984067</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46146.60416666666</v>
+        <v>46148.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>800.8326269916049</v>
+        <v>806.1280030426244</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46146.61458333334</v>
+        <v>46148.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>813.7857699924258</v>
+        <v>852.094143786842</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46146.625</v>
+        <v>46148.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>826.7389129932468</v>
+        <v>898.0602845310597</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46146.63541666666</v>
+        <v>46148.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>931.4678107344369</v>
+        <v>988.8308714803977</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46146.64583333334</v>
+        <v>46148.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1036.196708475627</v>
+        <v>1079.601458429736</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46146.65625</v>
+        <v>46148.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1140.925606216817</v>
+        <v>1170.372045379074</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46146.66666666666</v>
+        <v>46148.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>1245.654503958007</v>
+        <v>1261.142632328412</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46146.67708333334</v>
+        <v>46148.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>1375.6146647557</v>
+        <v>1374.786280697396</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46146.6875</v>
+        <v>46148.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>1505.574825553393</v>
+        <v>1488.429929066381</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46146.69791666666</v>
+        <v>46148.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>1635.534986351085</v>
+        <v>1602.073577435366</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46146.70833333334</v>
+        <v>46148.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>1765.495147148778</v>
+        <v>1715.717225804351</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46146.71875</v>
+        <v>46148.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>1909.074351960632</v>
+        <v>1825.550164055686</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46146.72916666666</v>
+        <v>46148.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>2052.653556772486</v>
+        <v>1935.383102307021</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46146.73958333334</v>
+        <v>46148.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>2196.23276158434</v>
+        <v>2045.216040558356</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46146.75</v>
+        <v>46148.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>2339.811966396193</v>
+        <v>2155.048978809691</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46146.76041666666</v>
+        <v>46148.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2366.010154212115</v>
+        <v>2193.085674252447</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46146.77083333334</v>
+        <v>46148.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2392.208342028036</v>
+        <v>2231.122369695203</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46146.78125</v>
+        <v>46148.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2418.406529843957</v>
+        <v>2269.159065137959</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46146.79166666666</v>
+        <v>46148.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2444.604717659878</v>
+        <v>2307.195760580715</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46146.80208333334</v>
+        <v>46148.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2445.352716058341</v>
+        <v>2319.164734620957</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46146.8125</v>
+        <v>46148.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2446.100714456804</v>
+        <v>2331.133708661198</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46146.82291666666</v>
+        <v>46148.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2446.848712855267</v>
+        <v>2343.10268270144</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46146.83333333334</v>
+        <v>46148.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2447.59671125373</v>
+        <v>2355.071656741682</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46146.84375</v>
+        <v>46148.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2414.894586142585</v>
+        <v>2319.974400511914</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46146.85416666666</v>
+        <v>46148.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2382.192461031441</v>
+        <v>2284.877144282146</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46146.86458333334</v>
+        <v>46148.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2349.490335920297</v>
+        <v>2249.779888052379</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46146.875</v>
+        <v>46148.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2316.788210809153</v>
+        <v>2214.682631822611</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46146.88541666666</v>
+        <v>46148.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2276.496638531085</v>
+        <v>2170.79346010299</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46146.89583333334</v>
+        <v>46148.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2236.205066253018</v>
+        <v>2126.904288383368</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46146.90625</v>
+        <v>46148.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2195.913493974952</v>
+        <v>2083.015116663747</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46146.91666666666</v>
+        <v>46148.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2155.621921696884</v>
+        <v>2039.125944944125</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46146.92708333334</v>
+        <v>46148.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>2098.035166933453</v>
+        <v>1973.252584141832</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46146.9375</v>
+        <v>46148.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>2040.448412170021</v>
+        <v>1907.37922333954</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46146.94791666666</v>
+        <v>46148.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>1982.86165740659</v>
+        <v>1841.505862537248</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46146.95833333334</v>
+        <v>46148.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>1925.274902643158</v>
+        <v>1775.632501734955</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46146.96875</v>
+        <v>46148.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>1893.28197582127</v>
+        <v>1737.218883440209</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46146.97916666666</v>
+        <v>46148.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>1861.289048999383</v>
+        <v>1698.805265145463</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46146.98958333334</v>
+        <v>46148.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1829.296122177495</v>
+        <v>1660.391646850717</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1797.303195355607</v>
+        <v>1621.978028555971</v>
       </c>
       <c r="E97">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -412,568 +412,568 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46148.01041666666</v>
+        <v>46150.01041666666</v>
       </c>
       <c r="B2">
-        <v>639</v>
+        <v>663</v>
       </c>
       <c r="C2">
-        <v>817</v>
+        <v>928</v>
       </c>
       <c r="D2">
-        <v>1612.634436882246</v>
+        <v>1570.069652478017</v>
       </c>
       <c r="E2">
-        <v>1456</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46148.02083333334</v>
+        <v>46150.02083333334</v>
       </c>
       <c r="B3">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="C3">
-        <v>816</v>
+        <v>922</v>
       </c>
       <c r="D3">
-        <v>1591.187091488078</v>
+        <v>1561.329413109992</v>
       </c>
       <c r="E3">
-        <v>1464</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46148.03125</v>
+        <v>46150.03125</v>
       </c>
       <c r="B4">
-        <v>636</v>
+        <v>655</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1569.739746093909</v>
+        <v>1552.589173741967</v>
       </c>
       <c r="E4">
-        <v>636</v>
+        <v>655</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46148.04166666666</v>
+        <v>46150.04166666666</v>
       </c>
       <c r="B5">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>920</v>
       </c>
       <c r="D5">
-        <v>1548.292400699741</v>
+        <v>1543.848934373942</v>
       </c>
       <c r="E5">
-        <v>651</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46148.05208333334</v>
+        <v>46150.05208333334</v>
       </c>
       <c r="B6">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="C6">
-        <v>834</v>
+        <v>894</v>
       </c>
       <c r="D6">
-        <v>1541.383838477984</v>
+        <v>1539.407899968891</v>
       </c>
       <c r="E6">
-        <v>1479</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46148.0625</v>
+        <v>46150.0625</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>647</v>
       </c>
       <c r="C7">
-        <v>835</v>
+        <v>888</v>
       </c>
       <c r="D7">
-        <v>1534.475276256226</v>
+        <v>1534.96686556384</v>
       </c>
       <c r="E7">
-        <v>835</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46148.07291666666</v>
+        <v>46150.07291666666</v>
       </c>
       <c r="B8">
-        <v>644</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>834</v>
+        <v>889</v>
       </c>
       <c r="D8">
-        <v>1527.566714034469</v>
+        <v>1530.525831158789</v>
       </c>
       <c r="E8">
-        <v>1478</v>
+        <v>889</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46148.08333333334</v>
+        <v>46150.08333333334</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>653</v>
       </c>
       <c r="C9">
-        <v>835</v>
+        <v>888</v>
       </c>
       <c r="D9">
-        <v>1520.658151812712</v>
+        <v>1526.084796753737</v>
       </c>
       <c r="E9">
-        <v>835</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46148.09375</v>
+        <v>46150.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>839</v>
+        <v>890</v>
       </c>
       <c r="D10">
-        <v>1515.676946440025</v>
+        <v>1520.668684934403</v>
       </c>
       <c r="E10">
-        <v>839</v>
+        <v>890</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46148.10416666666</v>
+        <v>46150.10416666666</v>
       </c>
       <c r="B11">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="C11">
-        <v>837</v>
+        <v>888</v>
       </c>
       <c r="D11">
-        <v>1510.695741067338</v>
+        <v>1515.252573115069</v>
       </c>
       <c r="E11">
-        <v>1478</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46148.11458333334</v>
+        <v>46150.11458333334</v>
       </c>
       <c r="B12">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="C12">
-        <v>836</v>
+        <v>890</v>
       </c>
       <c r="D12">
-        <v>1505.71453569465</v>
+        <v>1509.836461295735</v>
       </c>
       <c r="E12">
-        <v>1478</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46148.125</v>
+        <v>46150.125</v>
       </c>
       <c r="B13">
-        <v>645</v>
+        <v>655</v>
       </c>
       <c r="C13">
-        <v>838</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>1500.733330321963</v>
+        <v>1504.420349476401</v>
       </c>
       <c r="E13">
-        <v>1483</v>
+        <v>655</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46148.13541666666</v>
+        <v>46150.13541666666</v>
       </c>
       <c r="B14">
-        <v>712</v>
+        <v>659</v>
       </c>
       <c r="C14">
-        <v>806</v>
+        <v>903</v>
       </c>
       <c r="D14">
-        <v>1512.543891470553</v>
+        <v>1511.751158763724</v>
       </c>
       <c r="E14">
-        <v>1518</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46148.14583333334</v>
+        <v>46150.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>805</v>
+        <v>904</v>
       </c>
       <c r="D15">
-        <v>1524.354452619143</v>
+        <v>1519.081968051046</v>
       </c>
       <c r="E15">
-        <v>805</v>
+        <v>904</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46148.15625</v>
+        <v>46150.15625</v>
       </c>
       <c r="B16">
-        <v>713</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>903</v>
       </c>
       <c r="D16">
-        <v>1536.165013767733</v>
+        <v>1526.412777338368</v>
       </c>
       <c r="E16">
-        <v>713</v>
+        <v>903</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46148.16666666666</v>
+        <v>46150.16666666666</v>
       </c>
       <c r="B17">
-        <v>714</v>
+        <v>660</v>
       </c>
       <c r="C17">
-        <v>807</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>1547.975574916323</v>
+        <v>1533.74358662569</v>
       </c>
       <c r="E17">
-        <v>1521</v>
+        <v>660</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46148.17708333334</v>
+        <v>46150.17708333334</v>
       </c>
       <c r="B18">
-        <v>735</v>
+        <v>693</v>
       </c>
       <c r="C18">
-        <v>817</v>
+        <v>907</v>
       </c>
       <c r="D18">
-        <v>1568.745265162749</v>
+        <v>1544.43398082222</v>
       </c>
       <c r="E18">
-        <v>1552</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46148.1875</v>
+        <v>46150.1875</v>
       </c>
       <c r="B19">
-        <v>736</v>
+        <v>691</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>906</v>
       </c>
       <c r="D19">
-        <v>1589.514955409175</v>
+        <v>1555.124375018749</v>
       </c>
       <c r="E19">
-        <v>736</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46148.19791666666</v>
+        <v>46150.19791666666</v>
       </c>
       <c r="B20">
-        <v>739</v>
+        <v>682</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>905</v>
       </c>
       <c r="D20">
-        <v>1610.284645655601</v>
+        <v>1565.814769215278</v>
       </c>
       <c r="E20">
-        <v>739</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46148.20833333334</v>
+        <v>46150.20833333334</v>
       </c>
       <c r="B21">
-        <v>745</v>
+        <v>706</v>
       </c>
       <c r="C21">
-        <v>820</v>
+        <v>903</v>
       </c>
       <c r="D21">
-        <v>1631.054335902027</v>
+        <v>1576.505163411808</v>
       </c>
       <c r="E21">
-        <v>1565</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46148.21875</v>
+        <v>46150.21875</v>
       </c>
       <c r="B22">
-        <v>817</v>
+        <v>756</v>
       </c>
       <c r="C22">
-        <v>809</v>
+        <v>925</v>
       </c>
       <c r="D22">
-        <v>1646.006752735999</v>
+        <v>1589.35845660026</v>
       </c>
       <c r="E22">
-        <v>1626</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46148.22916666666</v>
+        <v>46150.22916666666</v>
       </c>
       <c r="B23">
-        <v>820</v>
+        <v>759</v>
       </c>
       <c r="C23">
-        <v>810</v>
+        <v>928</v>
       </c>
       <c r="D23">
-        <v>1660.959169569971</v>
+        <v>1602.211749788712</v>
       </c>
       <c r="E23">
-        <v>1630</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46148.23958333334</v>
+        <v>46150.23958333334</v>
       </c>
       <c r="B24">
-        <v>819</v>
+        <v>755</v>
       </c>
       <c r="C24">
-        <v>809</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>1675.911586403942</v>
+        <v>1615.065042977164</v>
       </c>
       <c r="E24">
-        <v>1628</v>
+        <v>755</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46148.25</v>
+        <v>46150.25</v>
       </c>
       <c r="B25">
-        <v>820</v>
+        <v>750</v>
       </c>
       <c r="C25">
-        <v>807</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>1690.864003237914</v>
+        <v>1627.918336165617</v>
       </c>
       <c r="E25">
-        <v>1627</v>
+        <v>750</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46148.26041666666</v>
+        <v>46150.26041666666</v>
       </c>
       <c r="B26">
-        <v>909</v>
+        <v>854</v>
       </c>
       <c r="C26">
-        <v>835</v>
+        <v>950</v>
       </c>
       <c r="D26">
-        <v>1687.783752565793</v>
+        <v>1605.021745610056</v>
       </c>
       <c r="E26">
-        <v>1744</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46148.27083333334</v>
+        <v>46150.27083333334</v>
       </c>
       <c r="B27">
-        <v>893</v>
+        <v>860</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>947</v>
       </c>
       <c r="D27">
-        <v>1684.703501893672</v>
+        <v>1582.125155054495</v>
       </c>
       <c r="E27">
-        <v>893</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46148.28125</v>
+        <v>46150.28125</v>
       </c>
       <c r="B28">
-        <v>875</v>
+        <v>861</v>
       </c>
       <c r="C28">
-        <v>834</v>
+        <v>948</v>
       </c>
       <c r="D28">
-        <v>1681.623251221551</v>
+        <v>1559.228564498934</v>
       </c>
       <c r="E28">
-        <v>1709</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46148.29166666666</v>
+        <v>46150.29166666666</v>
       </c>
       <c r="B29">
-        <v>876</v>
+        <v>862</v>
       </c>
       <c r="C29">
-        <v>835</v>
+        <v>953</v>
       </c>
       <c r="D29">
-        <v>1678.54300054943</v>
+        <v>1536.331973943373</v>
       </c>
       <c r="E29">
-        <v>1711</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46148.30208333334</v>
+        <v>46150.30208333334</v>
       </c>
       <c r="B30">
-        <v>777</v>
+        <v>868</v>
       </c>
       <c r="C30">
-        <v>821</v>
+        <v>939</v>
       </c>
       <c r="D30">
-        <v>1604.256155053971</v>
+        <v>1485.468390278551</v>
       </c>
       <c r="E30">
-        <v>1598</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46148.3125</v>
+        <v>46150.3125</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>872</v>
       </c>
       <c r="C31">
-        <v>815</v>
+        <v>935</v>
       </c>
       <c r="D31">
-        <v>1529.969309558513</v>
+        <v>1434.604806613729</v>
       </c>
       <c r="E31">
-        <v>815</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46148.32291666666</v>
+        <v>46150.32291666666</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>867</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>1455.682464063055</v>
+        <v>1383.741222948907</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>867</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46148.33333333334</v>
+        <v>46150.33333333334</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>865</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>933</v>
       </c>
       <c r="D33">
-        <v>1381.395618567596</v>
+        <v>1332.877639284085</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46148.34375</v>
+        <v>46150.34375</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>821</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>839</v>
       </c>
       <c r="D34">
-        <v>1346.166351594843</v>
+        <v>1300.15935986469</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46148.35416666666</v>
+        <v>46150.35416666666</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -982,7 +982,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>1310.93708462209</v>
+        <v>1267.441080445294</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -990,7 +990,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46148.36458333334</v>
+        <v>46150.36458333334</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -999,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>1275.707817649336</v>
+        <v>1234.722801025899</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46148.375</v>
+        <v>46150.375</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1016,7 +1016,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>1240.478550676583</v>
+        <v>1202.004521606503</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1024,7 +1024,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46148.38541666666</v>
+        <v>46150.38541666666</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>1139.613542238992</v>
+        <v>1138.252187392683</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1041,7 +1041,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46148.39583333334</v>
+        <v>46150.39583333334</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>1038.748533801401</v>
+        <v>1074.499853178864</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46148.40625</v>
+        <v>46150.40625</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1067,7 +1067,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>937.8835253638097</v>
+        <v>1010.747518965044</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1075,7 +1075,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46148.41666666666</v>
+        <v>46150.41666666666</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>837.0185169262187</v>
+        <v>946.9951847512237</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46148.42708333334</v>
+        <v>46150.42708333334</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>822.5061359022728</v>
+        <v>930.7468492932576</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46148.4375</v>
+        <v>46150.4375</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>807.9937548783271</v>
+        <v>914.4985138352913</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46148.44791666666</v>
+        <v>46150.44791666666</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>793.4813738543812</v>
+        <v>898.2501783773251</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46148.45833333334</v>
+        <v>46150.45833333334</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>778.9689928304354</v>
+        <v>882.001842919359</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46148.46875</v>
+        <v>46150.46875</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1169,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>764.5622204012039</v>
+        <v>866.0017089849928</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46148.47916666666</v>
+        <v>46150.47916666666</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>750.1554479719725</v>
+        <v>850.0015750506265</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46148.48958333334</v>
+        <v>46150.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>735.7486755427411</v>
+        <v>834.0014411162601</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46148.5</v>
+        <v>46150.5</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>721.3419031135097</v>
+        <v>818.0013071818939</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46148.51041666666</v>
+        <v>46150.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>708.9240925468101</v>
+        <v>807.0183897609312</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46148.52083333334</v>
+        <v>46150.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>696.5062819801105</v>
+        <v>796.0354723399685</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46148.53125</v>
+        <v>46150.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>684.088471413411</v>
+        <v>785.0525549190057</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46148.54166666666</v>
+        <v>46150.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>671.6706608467114</v>
+        <v>774.069637498043</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46148.55208333334</v>
+        <v>46150.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>682.3019260235808</v>
+        <v>784.1483922257618</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46148.5625</v>
+        <v>46150.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>692.9331912004502</v>
+        <v>794.2271469534805</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46148.57291666666</v>
+        <v>46150.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>703.5644563773196</v>
+        <v>804.3059016811994</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46148.58333333334</v>
+        <v>46150.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>714.195721554189</v>
+        <v>814.3846564089182</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46148.59375</v>
+        <v>46150.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>760.1618622984067</v>
+        <v>872.1358323548834</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46148.60416666666</v>
+        <v>46150.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>806.1280030426244</v>
+        <v>929.8870083008487</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46148.61458333334</v>
+        <v>46150.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>852.094143786842</v>
+        <v>987.6381842468139</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46148.625</v>
+        <v>46150.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>898.0602845310597</v>
+        <v>1045.389360192779</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46148.63541666666</v>
+        <v>46150.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>988.8308714803977</v>
+        <v>1106.75718691169</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46148.64583333334</v>
+        <v>46150.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1079.601458429736</v>
+        <v>1168.125013630601</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46148.65625</v>
+        <v>46150.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1170.372045379074</v>
+        <v>1229.492840349512</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46148.66666666666</v>
+        <v>46150.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>1261.142632328412</v>
+        <v>1290.860667068423</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46148.67708333334</v>
+        <v>46150.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>1374.786280697396</v>
+        <v>1419.89000199823</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46148.6875</v>
+        <v>46150.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>1488.429929066381</v>
+        <v>1548.919336928037</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46148.69791666666</v>
+        <v>46150.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>1602.073577435366</v>
+        <v>1677.948671857845</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46148.70833333334</v>
+        <v>46150.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>1715.717225804351</v>
+        <v>1806.978006787652</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46148.71875</v>
+        <v>46150.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>1825.550164055686</v>
+        <v>1892.793683584877</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46148.72916666666</v>
+        <v>46150.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>1935.383102307021</v>
+        <v>1978.609360382102</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46148.73958333334</v>
+        <v>46150.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>2045.216040558356</v>
+        <v>2064.425037179328</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46148.75</v>
+        <v>46150.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>2155.048978809691</v>
+        <v>2150.240713976553</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46148.76041666666</v>
+        <v>46150.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2193.085674252447</v>
+        <v>2187.213876657873</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46148.77083333334</v>
+        <v>46150.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2231.122369695203</v>
+        <v>2224.187039339193</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46148.78125</v>
+        <v>46150.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2269.159065137959</v>
+        <v>2261.160202020514</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46148.79166666666</v>
+        <v>46150.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2307.195760580715</v>
+        <v>2298.133364701834</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46148.80208333334</v>
+        <v>46150.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2319.164734620957</v>
+        <v>2312.803847616985</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46148.8125</v>
+        <v>46150.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2331.133708661198</v>
+        <v>2327.474330532137</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46148.82291666666</v>
+        <v>46150.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2343.10268270144</v>
+        <v>2342.144813447289</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46148.83333333334</v>
+        <v>46150.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2355.071656741682</v>
+        <v>2356.815296362441</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46148.84375</v>
+        <v>46150.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2319.974400511914</v>
+        <v>2326.410609716991</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46148.85416666666</v>
+        <v>46150.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2284.877144282146</v>
+        <v>2296.005923071541</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46148.86458333334</v>
+        <v>46150.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2249.779888052379</v>
+        <v>2265.601236426092</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46148.875</v>
+        <v>46150.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2214.682631822611</v>
+        <v>2235.196549780642</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46148.88541666666</v>
+        <v>46150.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2170.79346010299</v>
+        <v>2192.266550531658</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46148.89583333334</v>
+        <v>46150.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2126.904288383368</v>
+        <v>2149.336551282674</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46148.90625</v>
+        <v>46150.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2083.015116663747</v>
+        <v>2106.406552033689</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46148.91666666666</v>
+        <v>46150.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2039.125944944125</v>
+        <v>2063.476552784705</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46148.92708333334</v>
+        <v>46150.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>1973.252584141832</v>
+        <v>1990.39893275437</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46148.9375</v>
+        <v>46150.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>1907.37922333954</v>
+        <v>1917.321312724035</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46148.94791666666</v>
+        <v>46150.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>1841.505862537248</v>
+        <v>1844.2436926937</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46148.95833333334</v>
+        <v>46150.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>1775.632501734955</v>
+        <v>1771.166072663364</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46148.96875</v>
+        <v>46150.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>1737.218883440209</v>
+        <v>1696.421320721274</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46148.97916666666</v>
+        <v>46150.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>1698.805265145463</v>
+        <v>1621.676568779183</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46148.98958333334</v>
+        <v>46150.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1660.391646850717</v>
+        <v>1546.931816837092</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46149</v>
+        <v>46151</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1621.978028555971</v>
+        <v>1472.187064895001</v>
       </c>
       <c r="E97">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -412,738 +412,738 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46150.01041666666</v>
+        <v>46154.01041666666</v>
       </c>
       <c r="B2">
-        <v>663</v>
+        <v>604</v>
       </c>
       <c r="C2">
-        <v>928</v>
+        <v>965</v>
       </c>
       <c r="D2">
-        <v>1570.069652478017</v>
+        <v>1761.390148130992</v>
       </c>
       <c r="E2">
-        <v>1591</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46150.02083333334</v>
+        <v>46154.02083333334</v>
       </c>
       <c r="B3">
-        <v>656</v>
+        <v>599</v>
       </c>
       <c r="C3">
-        <v>922</v>
+        <v>964</v>
       </c>
       <c r="D3">
-        <v>1561.329413109992</v>
+        <v>1752.652293198724</v>
       </c>
       <c r="E3">
-        <v>1578</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46150.03125</v>
+        <v>46154.03125</v>
       </c>
       <c r="B4">
-        <v>655</v>
+        <v>595</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>961</v>
       </c>
       <c r="D4">
-        <v>1552.589173741967</v>
+        <v>1743.914438266456</v>
       </c>
       <c r="E4">
-        <v>655</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46150.04166666666</v>
+        <v>46154.04166666666</v>
       </c>
       <c r="B5">
-        <v>645</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>920</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1543.848934373942</v>
+        <v>1735.176583334188</v>
       </c>
       <c r="E5">
-        <v>1565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46150.05208333334</v>
+        <v>46154.05208333334</v>
       </c>
       <c r="B6">
-        <v>651</v>
+        <v>584</v>
       </c>
       <c r="C6">
-        <v>894</v>
+        <v>964</v>
       </c>
       <c r="D6">
-        <v>1539.407899968891</v>
+        <v>1729.726632766399</v>
       </c>
       <c r="E6">
-        <v>1545</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46150.0625</v>
+        <v>46154.0625</v>
       </c>
       <c r="B7">
-        <v>647</v>
+        <v>581</v>
       </c>
       <c r="C7">
-        <v>888</v>
+        <v>960</v>
       </c>
       <c r="D7">
-        <v>1534.96686556384</v>
+        <v>1724.27668219861</v>
       </c>
       <c r="E7">
-        <v>1535</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46150.07291666666</v>
+        <v>46154.07291666666</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>577</v>
       </c>
       <c r="C8">
-        <v>889</v>
+        <v>961</v>
       </c>
       <c r="D8">
-        <v>1530.525831158789</v>
+        <v>1718.826731630822</v>
       </c>
       <c r="E8">
-        <v>889</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46150.08333333334</v>
+        <v>46154.08333333334</v>
       </c>
       <c r="B9">
-        <v>653</v>
+        <v>566</v>
       </c>
       <c r="C9">
-        <v>888</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1526.084796753737</v>
+        <v>1713.376781063033</v>
       </c>
       <c r="E9">
-        <v>1541</v>
+        <v>566</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46150.09375</v>
+        <v>46154.09375</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>572</v>
       </c>
       <c r="C10">
-        <v>890</v>
+        <v>957</v>
       </c>
       <c r="D10">
-        <v>1520.668684934403</v>
+        <v>1711.453855177303</v>
       </c>
       <c r="E10">
-        <v>890</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46150.10416666666</v>
+        <v>46154.10416666666</v>
       </c>
       <c r="B11">
-        <v>646</v>
+        <v>570</v>
       </c>
       <c r="C11">
-        <v>888</v>
+        <v>954</v>
       </c>
       <c r="D11">
-        <v>1515.252573115069</v>
+        <v>1709.530929291573</v>
       </c>
       <c r="E11">
-        <v>1534</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46150.11458333334</v>
+        <v>46154.11458333334</v>
       </c>
       <c r="B12">
-        <v>648</v>
+        <v>564</v>
       </c>
       <c r="C12">
-        <v>890</v>
+        <v>956</v>
       </c>
       <c r="D12">
-        <v>1509.836461295735</v>
+        <v>1707.608003405843</v>
       </c>
       <c r="E12">
-        <v>1538</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46150.125</v>
+        <v>46154.125</v>
       </c>
       <c r="B13">
-        <v>655</v>
+        <v>528</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>918</v>
       </c>
       <c r="D13">
-        <v>1504.420349476401</v>
+        <v>1705.685077520113</v>
       </c>
       <c r="E13">
-        <v>655</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46150.13541666666</v>
+        <v>46154.13541666666</v>
       </c>
       <c r="B14">
-        <v>659</v>
+        <v>530</v>
       </c>
       <c r="C14">
-        <v>903</v>
+        <v>945</v>
       </c>
       <c r="D14">
-        <v>1511.751158763724</v>
+        <v>1719.773249554585</v>
       </c>
       <c r="E14">
-        <v>1562</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46150.14583333334</v>
+        <v>46154.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>904</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>1519.081968051046</v>
+        <v>1733.861421589057</v>
       </c>
       <c r="E15">
-        <v>904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46150.15625</v>
+        <v>46154.15625</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="C16">
-        <v>903</v>
+        <v>967</v>
       </c>
       <c r="D16">
-        <v>1526.412777338368</v>
+        <v>1747.949593623529</v>
       </c>
       <c r="E16">
-        <v>903</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46150.16666666666</v>
+        <v>46154.16666666666</v>
       </c>
       <c r="B17">
-        <v>660</v>
+        <v>581</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>1533.74358662569</v>
+        <v>1762.037765658001</v>
       </c>
       <c r="E17">
-        <v>660</v>
+        <v>581</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46150.17708333334</v>
+        <v>46154.17708333334</v>
       </c>
       <c r="B18">
-        <v>693</v>
+        <v>637</v>
       </c>
       <c r="C18">
-        <v>907</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>1544.43398082222</v>
+        <v>1783.708044423779</v>
       </c>
       <c r="E18">
-        <v>1600</v>
+        <v>637</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46150.1875</v>
+        <v>46154.1875</v>
       </c>
       <c r="B19">
-        <v>691</v>
+        <v>650</v>
       </c>
       <c r="C19">
-        <v>906</v>
+        <v>997</v>
       </c>
       <c r="D19">
-        <v>1555.124375018749</v>
+        <v>1805.378323189557</v>
       </c>
       <c r="E19">
-        <v>1597</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46150.19791666666</v>
+        <v>46154.19791666666</v>
       </c>
       <c r="B20">
-        <v>682</v>
+        <v>634</v>
       </c>
       <c r="C20">
-        <v>905</v>
+        <v>1022</v>
       </c>
       <c r="D20">
-        <v>1565.814769215278</v>
+        <v>1827.048601955335</v>
       </c>
       <c r="E20">
-        <v>1587</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46150.20833333334</v>
+        <v>46154.20833333334</v>
       </c>
       <c r="B21">
-        <v>706</v>
+        <v>639</v>
       </c>
       <c r="C21">
-        <v>903</v>
+        <v>1025</v>
       </c>
       <c r="D21">
-        <v>1576.505163411808</v>
+        <v>1848.718880721113</v>
       </c>
       <c r="E21">
-        <v>1609</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46150.21875</v>
+        <v>46154.21875</v>
       </c>
       <c r="B22">
-        <v>756</v>
+        <v>686</v>
       </c>
       <c r="C22">
-        <v>925</v>
+        <v>1041</v>
       </c>
       <c r="D22">
-        <v>1589.35845660026</v>
+        <v>1877.393392118063</v>
       </c>
       <c r="E22">
-        <v>1681</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46150.22916666666</v>
+        <v>46154.22916666666</v>
       </c>
       <c r="B23">
-        <v>759</v>
+        <v>688</v>
       </c>
       <c r="C23">
-        <v>928</v>
+        <v>1033</v>
       </c>
       <c r="D23">
-        <v>1602.211749788712</v>
+        <v>1906.067903515013</v>
       </c>
       <c r="E23">
-        <v>1687</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46150.23958333334</v>
+        <v>46154.23958333334</v>
       </c>
       <c r="B24">
-        <v>755</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1042</v>
       </c>
       <c r="D24">
-        <v>1615.065042977164</v>
+        <v>1934.742414911964</v>
       </c>
       <c r="E24">
-        <v>755</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46150.25</v>
+        <v>46154.25</v>
       </c>
       <c r="B25">
-        <v>750</v>
+        <v>691</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1043</v>
       </c>
       <c r="D25">
-        <v>1627.918336165617</v>
+        <v>1963.416926308914</v>
       </c>
       <c r="E25">
-        <v>750</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46150.26041666666</v>
+        <v>46154.26041666666</v>
       </c>
       <c r="B26">
-        <v>854</v>
+        <v>711</v>
       </c>
       <c r="C26">
-        <v>950</v>
+        <v>1045</v>
       </c>
       <c r="D26">
-        <v>1605.021745610056</v>
+        <v>1934.104760732186</v>
       </c>
       <c r="E26">
-        <v>1804</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46150.27083333334</v>
+        <v>46154.27083333334</v>
       </c>
       <c r="B27">
-        <v>860</v>
+        <v>759</v>
       </c>
       <c r="C27">
-        <v>947</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>1582.125155054495</v>
+        <v>1904.792595155458</v>
       </c>
       <c r="E27">
-        <v>1807</v>
+        <v>759</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46150.28125</v>
+        <v>46154.28125</v>
       </c>
       <c r="B28">
-        <v>861</v>
+        <v>750</v>
       </c>
       <c r="C28">
-        <v>948</v>
+        <v>1053</v>
       </c>
       <c r="D28">
-        <v>1559.228564498934</v>
+        <v>1875.480429578729</v>
       </c>
       <c r="E28">
-        <v>1809</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46150.29166666666</v>
+        <v>46154.29166666666</v>
       </c>
       <c r="B29">
-        <v>862</v>
+        <v>749</v>
       </c>
       <c r="C29">
-        <v>953</v>
+        <v>1054</v>
       </c>
       <c r="D29">
-        <v>1536.331973943373</v>
+        <v>1846.168264002001</v>
       </c>
       <c r="E29">
-        <v>1815</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46150.30208333334</v>
+        <v>46154.30208333334</v>
       </c>
       <c r="B30">
-        <v>868</v>
+        <v>745</v>
       </c>
       <c r="C30">
-        <v>939</v>
+        <v>1022</v>
       </c>
       <c r="D30">
-        <v>1485.468390278551</v>
+        <v>1827.038638608663</v>
       </c>
       <c r="E30">
-        <v>1807</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46150.3125</v>
+        <v>46154.3125</v>
       </c>
       <c r="B31">
-        <v>872</v>
+        <v>733</v>
       </c>
       <c r="C31">
-        <v>935</v>
+        <v>1014</v>
       </c>
       <c r="D31">
-        <v>1434.604806613729</v>
+        <v>1807.909013215326</v>
       </c>
       <c r="E31">
-        <v>1807</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46150.32291666666</v>
+        <v>46154.32291666666</v>
       </c>
       <c r="B32">
-        <v>867</v>
+        <v>731</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="D32">
-        <v>1383.741222948907</v>
+        <v>1788.779387821989</v>
       </c>
       <c r="E32">
-        <v>867</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46150.33333333334</v>
+        <v>46154.33333333334</v>
       </c>
       <c r="B33">
-        <v>865</v>
+        <v>734</v>
       </c>
       <c r="C33">
-        <v>933</v>
+        <v>974</v>
       </c>
       <c r="D33">
-        <v>1332.877639284085</v>
+        <v>1769.649762428651</v>
       </c>
       <c r="E33">
-        <v>1798</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46150.34375</v>
+        <v>46154.34375</v>
       </c>
       <c r="B34">
-        <v>821</v>
+        <v>597</v>
       </c>
       <c r="C34">
-        <v>839</v>
+        <v>863</v>
       </c>
       <c r="D34">
-        <v>1300.15935986469</v>
+        <v>1739.281482116676</v>
       </c>
       <c r="E34">
-        <v>1660</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46150.35416666666</v>
+        <v>46154.35416666666</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>644</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>852</v>
       </c>
       <c r="D35">
-        <v>1267.441080445294</v>
+        <v>1708.913201804701</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46150.36458333334</v>
+        <v>46154.36458333334</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="D36">
-        <v>1234.722801025899</v>
+        <v>1678.544921492725</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46150.375</v>
+        <v>46154.375</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>748</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="D37">
-        <v>1202.004521606503</v>
+        <v>1648.17664118075</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46150.38541666666</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>782</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1013</v>
       </c>
       <c r="D38">
-        <v>1138.252187392683</v>
+        <v>1568.599392213873</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46150.39583333334</v>
+        <v>46154.39583333334</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>826</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1222</v>
       </c>
       <c r="D39">
-        <v>1074.499853178864</v>
+        <v>1489.022143246996</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46150.40625</v>
+        <v>46154.40625</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>804</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>1329</v>
       </c>
       <c r="D40">
-        <v>1010.747518965044</v>
+        <v>1409.444894280119</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46150.41666666666</v>
+        <v>46154.41666666666</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>1342</v>
       </c>
       <c r="D41">
-        <v>946.9951847512237</v>
+        <v>1329.867645313242</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46150.42708333334</v>
+        <v>46154.42708333334</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>914</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>1170</v>
       </c>
       <c r="D42">
-        <v>930.7468492932576</v>
+        <v>1312.491568914291</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46150.4375</v>
+        <v>46154.4375</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>672</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>948</v>
       </c>
       <c r="D43">
-        <v>914.4985138352913</v>
+        <v>1295.115492515341</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46150.44791666666</v>
+        <v>46154.44791666666</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>681</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="D44">
-        <v>898.2501783773251</v>
+        <v>1277.739416116391</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46150.45833333334</v>
+        <v>46154.45833333334</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>882.001842919359</v>
+        <v>1260.36333971744</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46150.46875</v>
+        <v>46154.46875</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1169,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>866.0017089849928</v>
+        <v>1246.623884812498</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46150.47916666666</v>
+        <v>46154.47916666666</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>850.0015750506265</v>
+        <v>1232.884429907556</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46150.48958333334</v>
+        <v>46154.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>834.0014411162601</v>
+        <v>1219.144975002614</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46150.5</v>
+        <v>46154.5</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>818.0013071818939</v>
+        <v>1205.405520097671</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46150.51041666666</v>
+        <v>46154.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>807.0183897609312</v>
+        <v>1194.794556012341</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46150.52083333334</v>
+        <v>46154.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>796.0354723399685</v>
+        <v>1184.183591927012</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46150.53125</v>
+        <v>46154.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>785.0525549190057</v>
+        <v>1173.572627841682</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46150.54166666666</v>
+        <v>46154.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>774.069637498043</v>
+        <v>1162.961663756352</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46150.55208333334</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>784.1483922257618</v>
+        <v>1169.637105950903</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46150.5625</v>
+        <v>46154.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>794.2271469534805</v>
+        <v>1176.312548145454</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46150.57291666666</v>
+        <v>46154.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>804.3059016811994</v>
+        <v>1182.987990340004</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46150.58333333334</v>
+        <v>46154.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>814.3846564089182</v>
+        <v>1189.663432534555</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46150.59375</v>
+        <v>46154.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>872.1358323548834</v>
+        <v>1250.409956504877</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46150.60416666666</v>
+        <v>46154.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>929.8870083008487</v>
+        <v>1311.156480475199</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46150.61458333334</v>
+        <v>46154.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>987.6381842468139</v>
+        <v>1371.903004445521</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46150.625</v>
+        <v>46154.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1045.389360192779</v>
+        <v>1432.649528415843</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46150.63541666666</v>
+        <v>46154.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1106.75718691169</v>
+        <v>1486.680756805665</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46150.64583333334</v>
+        <v>46154.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1168.125013630601</v>
+        <v>1540.711985195486</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46150.65625</v>
+        <v>46154.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1229.492840349512</v>
+        <v>1594.743213585308</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46150.66666666666</v>
+        <v>46154.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>1290.860667068423</v>
+        <v>1648.77444197513</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46150.67708333334</v>
+        <v>46154.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>1419.89000199823</v>
+        <v>1781.217207784087</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46150.6875</v>
+        <v>46154.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>1548.919336928037</v>
+        <v>1913.659973593045</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46150.69791666666</v>
+        <v>46154.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>1677.948671857845</v>
+        <v>2046.102739402003</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46150.70833333334</v>
+        <v>46154.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>1806.978006787652</v>
+        <v>2178.545505210961</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46150.71875</v>
+        <v>46154.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>1892.793683584877</v>
+        <v>2248.039847460263</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46150.72916666666</v>
+        <v>46154.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>1978.609360382102</v>
+        <v>2317.534189709566</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46150.73958333334</v>
+        <v>46154.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>2064.425037179328</v>
+        <v>2387.028531958869</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46150.75</v>
+        <v>46154.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>2150.240713976553</v>
+        <v>2456.522874208172</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46150.76041666666</v>
+        <v>46154.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2187.213876657873</v>
+        <v>2462.710112421408</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46150.77083333334</v>
+        <v>46154.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2224.187039339193</v>
+        <v>2468.897350634645</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46150.78125</v>
+        <v>46154.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2261.160202020514</v>
+        <v>2475.084588847881</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46150.79166666666</v>
+        <v>46154.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2298.133364701834</v>
+        <v>2481.271827061117</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46150.80208333334</v>
+        <v>46154.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2312.803847616985</v>
+        <v>2478.651466916013</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46150.8125</v>
+        <v>46154.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2327.474330532137</v>
+        <v>2476.03110677091</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46150.82291666666</v>
+        <v>46154.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2342.144813447289</v>
+        <v>2473.410746625806</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46150.83333333334</v>
+        <v>46154.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2356.815296362441</v>
+        <v>2470.790386480703</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46150.84375</v>
+        <v>46154.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2326.410609716991</v>
+        <v>2449.349264685594</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46150.85416666666</v>
+        <v>46154.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2296.005923071541</v>
+        <v>2427.908142890486</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46150.86458333334</v>
+        <v>46154.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2265.601236426092</v>
+        <v>2406.467021095378</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46150.875</v>
+        <v>46154.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2235.196549780642</v>
+        <v>2385.02589930027</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46150.88541666666</v>
+        <v>46154.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2192.266550531658</v>
+        <v>2327.019295633811</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46150.89583333334</v>
+        <v>46154.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2149.336551282674</v>
+        <v>2269.012691967351</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46150.90625</v>
+        <v>46154.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2106.406552033689</v>
+        <v>2211.006088300892</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46150.91666666666</v>
+        <v>46154.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2063.476552784705</v>
+        <v>2152.999484634433</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46150.92708333334</v>
+        <v>46154.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>1990.39893275437</v>
+        <v>2070.911472334391</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46150.9375</v>
+        <v>46154.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>1917.321312724035</v>
+        <v>1988.823460034348</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46150.94791666666</v>
+        <v>46154.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>1844.2436926937</v>
+        <v>1906.735447734307</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46150.95833333334</v>
+        <v>46154.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>1771.166072663364</v>
+        <v>1824.647435434265</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46150.96875</v>
+        <v>46154.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>1696.421320721274</v>
+        <v>1798.094683297409</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46150.97916666666</v>
+        <v>46154.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>1621.676568779183</v>
+        <v>1771.541931160553</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46150.98958333334</v>
+        <v>46154.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1546.931816837092</v>
+        <v>1744.989179023697</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46151</v>
+        <v>46155</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1472.187064895001</v>
+        <v>1718.436426886841</v>
       </c>
       <c r="E97">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -412,891 +412,891 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46154.01041666666</v>
+        <v>46155.01041666666</v>
       </c>
       <c r="B2">
-        <v>604</v>
+        <v>634</v>
       </c>
       <c r="C2">
-        <v>965</v>
+        <v>943</v>
       </c>
       <c r="D2">
-        <v>1761.390148130992</v>
+        <v>1805.561909274593</v>
       </c>
       <c r="E2">
-        <v>1569</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46154.02083333334</v>
+        <v>46155.02083333334</v>
       </c>
       <c r="B3">
-        <v>599</v>
+        <v>636</v>
       </c>
       <c r="C3">
-        <v>964</v>
+        <v>933</v>
       </c>
       <c r="D3">
-        <v>1752.652293198724</v>
+        <v>1800.729897028541</v>
       </c>
       <c r="E3">
-        <v>1563</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46154.03125</v>
+        <v>46155.03125</v>
       </c>
       <c r="B4">
-        <v>595</v>
+        <v>639</v>
       </c>
       <c r="C4">
-        <v>961</v>
+        <v>934</v>
       </c>
       <c r="D4">
-        <v>1743.914438266456</v>
+        <v>1795.89788478249</v>
       </c>
       <c r="E4">
-        <v>1556</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46154.04166666666</v>
+        <v>46155.04166666666</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>638</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>932</v>
       </c>
       <c r="D5">
-        <v>1735.176583334188</v>
+        <v>1791.065872536438</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46154.05208333334</v>
+        <v>46155.05208333334</v>
       </c>
       <c r="B6">
-        <v>584</v>
+        <v>639</v>
       </c>
       <c r="C6">
-        <v>964</v>
+        <v>915</v>
       </c>
       <c r="D6">
-        <v>1729.726632766399</v>
+        <v>1784.24360471558</v>
       </c>
       <c r="E6">
-        <v>1548</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46154.0625</v>
+        <v>46155.0625</v>
       </c>
       <c r="B7">
-        <v>581</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>960</v>
+        <v>914</v>
       </c>
       <c r="D7">
-        <v>1724.27668219861</v>
+        <v>1777.421336894721</v>
       </c>
       <c r="E7">
-        <v>1541</v>
+        <v>914</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46154.07291666666</v>
+        <v>46155.07291666666</v>
       </c>
       <c r="B8">
-        <v>577</v>
+        <v>640</v>
       </c>
       <c r="C8">
-        <v>961</v>
+        <v>947</v>
       </c>
       <c r="D8">
-        <v>1718.826731630822</v>
+        <v>1770.599069073863</v>
       </c>
       <c r="E8">
-        <v>1538</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46154.08333333334</v>
+        <v>46155.08333333334</v>
       </c>
       <c r="B9">
-        <v>566</v>
+        <v>636</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>946</v>
       </c>
       <c r="D9">
-        <v>1713.376781063033</v>
+        <v>1763.776801253005</v>
       </c>
       <c r="E9">
-        <v>566</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46154.09375</v>
+        <v>46155.09375</v>
       </c>
       <c r="B10">
-        <v>572</v>
+        <v>640</v>
       </c>
       <c r="C10">
-        <v>957</v>
+        <v>905</v>
       </c>
       <c r="D10">
-        <v>1711.453855177303</v>
+        <v>1761.817322826474</v>
       </c>
       <c r="E10">
-        <v>1529</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46154.10416666666</v>
+        <v>46155.10416666666</v>
       </c>
       <c r="B11">
-        <v>570</v>
+        <v>639</v>
       </c>
       <c r="C11">
-        <v>954</v>
+        <v>903</v>
       </c>
       <c r="D11">
-        <v>1709.530929291573</v>
+        <v>1759.857844399944</v>
       </c>
       <c r="E11">
-        <v>1524</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46154.11458333334</v>
+        <v>46155.11458333334</v>
       </c>
       <c r="B12">
-        <v>564</v>
+        <v>637</v>
       </c>
       <c r="C12">
-        <v>956</v>
+        <v>901</v>
       </c>
       <c r="D12">
-        <v>1707.608003405843</v>
+        <v>1757.898365973413</v>
       </c>
       <c r="E12">
-        <v>1520</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46154.125</v>
+        <v>46155.125</v>
       </c>
       <c r="B13">
-        <v>528</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D13">
-        <v>1705.685077520113</v>
+        <v>1755.938887546883</v>
       </c>
       <c r="E13">
-        <v>1446</v>
+        <v>916</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46154.13541666666</v>
+        <v>46155.13541666666</v>
       </c>
       <c r="B14">
-        <v>530</v>
+        <v>632</v>
       </c>
       <c r="C14">
-        <v>945</v>
+        <v>928</v>
       </c>
       <c r="D14">
-        <v>1719.773249554585</v>
+        <v>1767.777830502073</v>
       </c>
       <c r="E14">
-        <v>1475</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46154.14583333334</v>
+        <v>46155.14583333334</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>624</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>1733.861421589057</v>
+        <v>1779.616773457264</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>624</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46154.15625</v>
+        <v>46155.15625</v>
       </c>
       <c r="B16">
-        <v>559</v>
+        <v>638</v>
       </c>
       <c r="C16">
-        <v>967</v>
+        <v>929</v>
       </c>
       <c r="D16">
-        <v>1747.949593623529</v>
+        <v>1791.455716412455</v>
       </c>
       <c r="E16">
-        <v>1526</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46154.16666666666</v>
+        <v>46155.16666666666</v>
       </c>
       <c r="B17">
-        <v>581</v>
+        <v>623</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>1762.037765658001</v>
+        <v>1803.294659367646</v>
       </c>
       <c r="E17">
-        <v>581</v>
+        <v>623</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46154.17708333334</v>
+        <v>46155.17708333334</v>
       </c>
       <c r="B18">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>932</v>
       </c>
       <c r="D18">
-        <v>1783.708044423779</v>
+        <v>1823.351100855982</v>
       </c>
       <c r="E18">
-        <v>637</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46154.1875</v>
+        <v>46155.1875</v>
       </c>
       <c r="B19">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="C19">
-        <v>997</v>
+        <v>933</v>
       </c>
       <c r="D19">
-        <v>1805.378323189557</v>
+        <v>1843.407542344318</v>
       </c>
       <c r="E19">
-        <v>1647</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46154.19791666666</v>
+        <v>46155.19791666666</v>
       </c>
       <c r="B20">
-        <v>634</v>
+        <v>665</v>
       </c>
       <c r="C20">
-        <v>1022</v>
+        <v>938</v>
       </c>
       <c r="D20">
-        <v>1827.048601955335</v>
+        <v>1863.463983832653</v>
       </c>
       <c r="E20">
-        <v>1656</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46154.20833333334</v>
+        <v>46155.20833333334</v>
       </c>
       <c r="B21">
-        <v>639</v>
+        <v>668</v>
       </c>
       <c r="C21">
-        <v>1025</v>
+        <v>949</v>
       </c>
       <c r="D21">
-        <v>1848.718880721113</v>
+        <v>1883.520425320989</v>
       </c>
       <c r="E21">
-        <v>1664</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46154.21875</v>
+        <v>46155.21875</v>
       </c>
       <c r="B22">
-        <v>686</v>
+        <v>718</v>
       </c>
       <c r="C22">
-        <v>1041</v>
+        <v>937</v>
       </c>
       <c r="D22">
-        <v>1877.393392118063</v>
+        <v>1904.161632622656</v>
       </c>
       <c r="E22">
-        <v>1727</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46154.22916666666</v>
+        <v>46155.22916666666</v>
       </c>
       <c r="B23">
-        <v>688</v>
+        <v>713</v>
       </c>
       <c r="C23">
-        <v>1033</v>
+        <v>943</v>
       </c>
       <c r="D23">
-        <v>1906.067903515013</v>
+        <v>1924.802839924322</v>
       </c>
       <c r="E23">
-        <v>1721</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46154.23958333334</v>
+        <v>46155.23958333334</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>708</v>
       </c>
       <c r="C24">
-        <v>1042</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>1934.742414911964</v>
+        <v>1945.444047225988</v>
       </c>
       <c r="E24">
-        <v>1042</v>
+        <v>708</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46154.25</v>
+        <v>46155.25</v>
       </c>
       <c r="B25">
-        <v>691</v>
+        <v>719</v>
       </c>
       <c r="C25">
-        <v>1043</v>
+        <v>946</v>
       </c>
       <c r="D25">
-        <v>1963.416926308914</v>
+        <v>1966.085254527655</v>
       </c>
       <c r="E25">
-        <v>1734</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46154.26041666666</v>
+        <v>46155.26041666666</v>
       </c>
       <c r="B26">
-        <v>711</v>
+        <v>782</v>
       </c>
       <c r="C26">
-        <v>1045</v>
+        <v>978</v>
       </c>
       <c r="D26">
-        <v>1934.104760732186</v>
+        <v>1956.811073910969</v>
       </c>
       <c r="E26">
-        <v>1756</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46154.27083333334</v>
+        <v>46155.27083333334</v>
       </c>
       <c r="B27">
-        <v>759</v>
+        <v>793</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>973</v>
       </c>
       <c r="D27">
-        <v>1904.792595155458</v>
+        <v>1947.536893294283</v>
       </c>
       <c r="E27">
-        <v>759</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46154.28125</v>
+        <v>46155.28125</v>
       </c>
       <c r="B28">
-        <v>750</v>
+        <v>792</v>
       </c>
       <c r="C28">
-        <v>1053</v>
+        <v>968</v>
       </c>
       <c r="D28">
-        <v>1875.480429578729</v>
+        <v>1938.262712677597</v>
       </c>
       <c r="E28">
-        <v>1803</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46154.29166666666</v>
+        <v>46155.29166666666</v>
       </c>
       <c r="B29">
-        <v>749</v>
+        <v>795</v>
       </c>
       <c r="C29">
-        <v>1054</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>1846.168264002001</v>
+        <v>1928.988532060911</v>
       </c>
       <c r="E29">
-        <v>1803</v>
+        <v>795</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46154.30208333334</v>
+        <v>46155.30208333334</v>
       </c>
       <c r="B30">
-        <v>745</v>
+        <v>764</v>
       </c>
       <c r="C30">
-        <v>1022</v>
+        <v>950</v>
       </c>
       <c r="D30">
-        <v>1827.038638608663</v>
+        <v>1903.279354378094</v>
       </c>
       <c r="E30">
-        <v>1767</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46154.3125</v>
+        <v>46155.3125</v>
       </c>
       <c r="B31">
-        <v>733</v>
+        <v>763</v>
       </c>
       <c r="C31">
-        <v>1014</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>1807.909013215326</v>
+        <v>1877.570176695278</v>
       </c>
       <c r="E31">
-        <v>1747</v>
+        <v>763</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46154.32291666666</v>
+        <v>46155.32291666666</v>
       </c>
       <c r="B32">
-        <v>731</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>1023</v>
+        <v>948</v>
       </c>
       <c r="D32">
-        <v>1788.779387821989</v>
+        <v>1851.860999012461</v>
       </c>
       <c r="E32">
-        <v>1754</v>
+        <v>948</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46154.33333333334</v>
+        <v>46155.33333333334</v>
       </c>
       <c r="B33">
-        <v>734</v>
+        <v>761</v>
       </c>
       <c r="C33">
-        <v>974</v>
+        <v>949</v>
       </c>
       <c r="D33">
-        <v>1769.649762428651</v>
+        <v>1826.151821329645</v>
       </c>
       <c r="E33">
-        <v>1708</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46154.34375</v>
+        <v>46155.34375</v>
       </c>
       <c r="B34">
-        <v>597</v>
+        <v>738</v>
       </c>
       <c r="C34">
-        <v>863</v>
+        <v>951</v>
       </c>
       <c r="D34">
-        <v>1739.281482116676</v>
+        <v>1806.187711285446</v>
       </c>
       <c r="E34">
-        <v>1460</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46154.35416666666</v>
+        <v>46155.35416666666</v>
       </c>
       <c r="B35">
-        <v>644</v>
+        <v>735</v>
       </c>
       <c r="C35">
-        <v>852</v>
+        <v>950</v>
       </c>
       <c r="D35">
-        <v>1708.913201804701</v>
+        <v>1786.223601241248</v>
       </c>
       <c r="E35">
-        <v>1496</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46154.36458333334</v>
+        <v>46155.36458333334</v>
       </c>
       <c r="B36">
-        <v>723</v>
+        <v>732</v>
       </c>
       <c r="C36">
-        <v>952</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>1678.544921492725</v>
+        <v>1766.25949119705</v>
       </c>
       <c r="E36">
-        <v>1675</v>
+        <v>732</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46154.375</v>
+        <v>46155.375</v>
       </c>
       <c r="B37">
-        <v>748</v>
+        <v>721</v>
       </c>
       <c r="C37">
-        <v>975</v>
+        <v>948</v>
       </c>
       <c r="D37">
-        <v>1648.17664118075</v>
+        <v>1746.295381152851</v>
       </c>
       <c r="E37">
-        <v>1723</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46154.38541666666</v>
+        <v>46155.38541666666</v>
       </c>
       <c r="B38">
-        <v>782</v>
+        <v>689</v>
       </c>
       <c r="C38">
-        <v>1013</v>
+        <v>942</v>
       </c>
       <c r="D38">
-        <v>1568.599392213873</v>
+        <v>1669.178107153886</v>
       </c>
       <c r="E38">
-        <v>1795</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46154.39583333334</v>
+        <v>46155.39583333334</v>
       </c>
       <c r="B39">
-        <v>826</v>
+        <v>684</v>
       </c>
       <c r="C39">
-        <v>1222</v>
+        <v>939</v>
       </c>
       <c r="D39">
-        <v>1489.022143246996</v>
+        <v>1592.060833154922</v>
       </c>
       <c r="E39">
-        <v>2048</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46154.40625</v>
+        <v>46155.40625</v>
       </c>
       <c r="B40">
-        <v>804</v>
+        <v>692</v>
       </c>
       <c r="C40">
-        <v>1329</v>
+        <v>943</v>
       </c>
       <c r="D40">
-        <v>1409.444894280119</v>
+        <v>1514.943559155957</v>
       </c>
       <c r="E40">
-        <v>2133</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46154.41666666666</v>
+        <v>46155.41666666666</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>683</v>
       </c>
       <c r="C41">
-        <v>1342</v>
+        <v>942</v>
       </c>
       <c r="D41">
-        <v>1329.867645313242</v>
+        <v>1437.826285156992</v>
       </c>
       <c r="E41">
-        <v>1342</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46154.42708333334</v>
+        <v>46155.42708333334</v>
       </c>
       <c r="B42">
-        <v>914</v>
+        <v>613</v>
       </c>
       <c r="C42">
-        <v>1170</v>
+        <v>930</v>
       </c>
       <c r="D42">
-        <v>1312.491568914291</v>
+        <v>1425.576980227337</v>
       </c>
       <c r="E42">
-        <v>2084</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46154.4375</v>
+        <v>46155.4375</v>
       </c>
       <c r="B43">
-        <v>672</v>
+        <v>611</v>
       </c>
       <c r="C43">
-        <v>948</v>
+        <v>925</v>
       </c>
       <c r="D43">
-        <v>1295.115492515341</v>
+        <v>1413.327675297682</v>
       </c>
       <c r="E43">
-        <v>1620</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46154.44791666666</v>
+        <v>46155.44791666666</v>
       </c>
       <c r="B44">
-        <v>681</v>
+        <v>604</v>
       </c>
       <c r="C44">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="D44">
-        <v>1277.739416116391</v>
+        <v>1401.078370368027</v>
       </c>
       <c r="E44">
-        <v>1621</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46154.45833333334</v>
+        <v>46155.45833333334</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>607</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="D45">
-        <v>1260.36333971744</v>
+        <v>1388.829065438373</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46154.46875</v>
+        <v>46155.46875</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>921</v>
       </c>
       <c r="D46">
-        <v>1246.623884812498</v>
+        <v>1389.547198893284</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46154.47916666666</v>
+        <v>46155.47916666666</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>595</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>918</v>
       </c>
       <c r="D47">
-        <v>1232.884429907556</v>
+        <v>1390.265332348195</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46154.48958333334</v>
+        <v>46155.48958333334</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>921</v>
       </c>
       <c r="D48">
-        <v>1219.144975002614</v>
+        <v>1390.983465803106</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46154.5</v>
+        <v>46155.5</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>595</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>917</v>
       </c>
       <c r="D49">
-        <v>1205.405520097671</v>
+        <v>1391.701599258018</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46154.51041666666</v>
+        <v>46155.51041666666</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>587</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>928</v>
       </c>
       <c r="D50">
-        <v>1194.794556012341</v>
+        <v>1384.150938932976</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46154.52083333334</v>
+        <v>46155.52083333334</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>582</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>929</v>
       </c>
       <c r="D51">
-        <v>1184.183591927012</v>
+        <v>1376.600278607934</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46154.53125</v>
+        <v>46155.53125</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>578</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>930</v>
       </c>
       <c r="D52">
-        <v>1173.572627841682</v>
+        <v>1369.049618282892</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46154.54166666666</v>
+        <v>46155.54166666666</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53">
-        <v>1162.961663756352</v>
+        <v>1361.49895795785</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46154.55208333334</v>
+        <v>46155.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>1169.637105950903</v>
+        <v>1364.781853751305</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46154.5625</v>
+        <v>46155.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1176.312548145454</v>
+        <v>1368.06474954476</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46154.57291666666</v>
+        <v>46155.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1182.987990340004</v>
+        <v>1371.347645338215</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46154.58333333334</v>
+        <v>46155.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>1189.663432534555</v>
+        <v>1374.63054113167</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46154.59375</v>
+        <v>46155.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>1250.409956504877</v>
+        <v>1399.970393037807</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46154.60416666666</v>
+        <v>46155.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1311.156480475199</v>
+        <v>1425.310244943945</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46154.61458333334</v>
+        <v>46155.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>1371.903004445521</v>
+        <v>1450.650096850082</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46154.625</v>
+        <v>46155.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1432.649528415843</v>
+        <v>1475.98994875622</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46154.63541666666</v>
+        <v>46155.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1486.680756805665</v>
+        <v>1539.965380531886</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46154.64583333334</v>
+        <v>46155.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1540.711985195486</v>
+        <v>1603.940812307553</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46154.65625</v>
+        <v>46155.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1594.743213585308</v>
+        <v>1667.91624408322</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46154.66666666666</v>
+        <v>46155.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>1648.77444197513</v>
+        <v>1731.891675858887</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46154.67708333334</v>
+        <v>46155.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>1781.217207784087</v>
+        <v>1872.163657685364</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46154.6875</v>
+        <v>46155.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>1913.659973593045</v>
+        <v>2012.435639511841</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46154.69791666666</v>
+        <v>46155.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>2046.102739402003</v>
+        <v>2152.707621338318</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46154.70833333334</v>
+        <v>46155.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>2178.545505210961</v>
+        <v>2292.979603164795</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46154.71875</v>
+        <v>46155.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>2248.039847460263</v>
+        <v>2363.325904589805</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46154.72916666666</v>
+        <v>46155.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>2317.534189709566</v>
+        <v>2433.672206014814</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46154.73958333334</v>
+        <v>46155.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>2387.028531958869</v>
+        <v>2504.018507439823</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46154.75</v>
+        <v>46155.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>2456.522874208172</v>
+        <v>2574.364808864833</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46154.76041666666</v>
+        <v>46155.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2462.710112421408</v>
+        <v>2580.284280342716</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46154.77083333334</v>
+        <v>46155.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2468.897350634645</v>
+        <v>2586.203751820599</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46154.78125</v>
+        <v>46155.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2475.084588847881</v>
+        <v>2592.123223298482</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46154.79166666666</v>
+        <v>46155.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2481.271827061117</v>
+        <v>2598.042694776365</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46154.80208333334</v>
+        <v>46155.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2478.651466916013</v>
+        <v>2595.488191486816</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46154.8125</v>
+        <v>46155.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2476.03110677091</v>
+        <v>2592.933688197266</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46154.82291666666</v>
+        <v>46155.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2473.410746625806</v>
+        <v>2590.379184907717</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46154.83333333334</v>
+        <v>46155.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2470.790386480703</v>
+        <v>2587.824681618167</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46154.84375</v>
+        <v>46155.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2449.349264685594</v>
+        <v>2565.357363531503</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46154.85416666666</v>
+        <v>46155.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2427.908142890486</v>
+        <v>2542.890045444839</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46154.86458333334</v>
+        <v>46155.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2406.467021095378</v>
+        <v>2520.422727358176</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46154.875</v>
+        <v>46155.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2385.02589930027</v>
+        <v>2497.955409271512</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46154.88541666666</v>
+        <v>46155.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2327.019295633811</v>
+        <v>2434.698110950508</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46154.89583333334</v>
+        <v>46155.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2269.012691967351</v>
+        <v>2371.440812629504</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46154.90625</v>
+        <v>46155.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2211.006088300892</v>
+        <v>2308.1835143085</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46154.91666666666</v>
+        <v>46155.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2152.999484634433</v>
+        <v>2244.926215987495</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46154.92708333334</v>
+        <v>46155.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>2070.911472334391</v>
+        <v>2163.592472703629</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46154.9375</v>
+        <v>46155.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>1988.823460034348</v>
+        <v>2082.258729419762</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46154.94791666666</v>
+        <v>46155.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>1906.735447734307</v>
+        <v>2000.924986135895</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46154.95833333334</v>
+        <v>46155.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>1824.647435434265</v>
+        <v>1919.591242852028</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46154.96875</v>
+        <v>46155.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>1798.094683297409</v>
+        <v>1922.913168022234</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46154.97916666666</v>
+        <v>46155.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>1771.541931160553</v>
+        <v>1926.23509319244</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46154.98958333334</v>
+        <v>46155.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1744.989179023697</v>
+        <v>1929.557018362646</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1718.436426886841</v>
+        <v>1932.878943532853</v>
       </c>
       <c r="E97">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -412,891 +412,891 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46155.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B2">
-        <v>634</v>
+        <v>448</v>
       </c>
       <c r="C2">
-        <v>943</v>
+        <v>1279</v>
       </c>
       <c r="D2">
-        <v>1805.561909274593</v>
+        <v>1820.759182765764</v>
       </c>
       <c r="E2">
-        <v>1577</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46155.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B3">
-        <v>636</v>
+        <v>447</v>
       </c>
       <c r="C3">
-        <v>933</v>
+        <v>1274</v>
       </c>
       <c r="D3">
-        <v>1800.729897028541</v>
+        <v>1803.939461560394</v>
       </c>
       <c r="E3">
-        <v>1569</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46155.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B4">
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>934</v>
+        <v>1273</v>
       </c>
       <c r="D4">
-        <v>1795.89788478249</v>
+        <v>1787.119740355024</v>
       </c>
       <c r="E4">
-        <v>1573</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46155.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B5">
-        <v>638</v>
+        <v>446</v>
       </c>
       <c r="C5">
-        <v>932</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1791.065872536438</v>
+        <v>1770.300019149654</v>
       </c>
       <c r="E5">
-        <v>1570</v>
+        <v>446</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46155.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B6">
-        <v>639</v>
+        <v>418</v>
       </c>
       <c r="C6">
-        <v>915</v>
+        <v>1212</v>
       </c>
       <c r="D6">
-        <v>1784.24360471558</v>
+        <v>1767.123177253391</v>
       </c>
       <c r="E6">
-        <v>1554</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46155.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="C7">
-        <v>914</v>
+        <v>1206</v>
       </c>
       <c r="D7">
-        <v>1777.421336894721</v>
+        <v>1763.946335357128</v>
       </c>
       <c r="E7">
-        <v>914</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46155.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B8">
-        <v>640</v>
+        <v>415</v>
       </c>
       <c r="C8">
-        <v>947</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1770.599069073863</v>
+        <v>1760.769493460864</v>
       </c>
       <c r="E8">
-        <v>1587</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46155.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
       <c r="B9">
-        <v>636</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>946</v>
+        <v>1207</v>
       </c>
       <c r="D9">
-        <v>1763.776801253005</v>
+        <v>1757.592651564601</v>
       </c>
       <c r="E9">
-        <v>1582</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46155.09375</v>
+        <v>46163.09375</v>
       </c>
       <c r="B10">
-        <v>640</v>
+        <v>399</v>
       </c>
       <c r="C10">
-        <v>905</v>
+        <v>1210</v>
       </c>
       <c r="D10">
-        <v>1761.817322826474</v>
+        <v>1771.878695183833</v>
       </c>
       <c r="E10">
-        <v>1545</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46155.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
       <c r="B11">
-        <v>639</v>
+        <v>392</v>
       </c>
       <c r="C11">
-        <v>903</v>
+        <v>1209</v>
       </c>
       <c r="D11">
-        <v>1759.857844399944</v>
+        <v>1786.164738803066</v>
       </c>
       <c r="E11">
-        <v>1542</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46155.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
       <c r="B12">
-        <v>637</v>
+        <v>397</v>
       </c>
       <c r="C12">
-        <v>901</v>
+        <v>1216</v>
       </c>
       <c r="D12">
-        <v>1757.898365973413</v>
+        <v>1800.450782422298</v>
       </c>
       <c r="E12">
-        <v>1538</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46155.125</v>
+        <v>46163.125</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="C13">
-        <v>916</v>
+        <v>1217</v>
       </c>
       <c r="D13">
-        <v>1755.938887546883</v>
+        <v>1814.736826041531</v>
       </c>
       <c r="E13">
-        <v>916</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46155.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
       <c r="B14">
-        <v>632</v>
+        <v>392</v>
       </c>
       <c r="C14">
-        <v>928</v>
+        <v>1223</v>
       </c>
       <c r="D14">
-        <v>1767.777830502073</v>
+        <v>1828.058123195489</v>
       </c>
       <c r="E14">
-        <v>1560</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46155.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
       <c r="B15">
-        <v>624</v>
+        <v>390</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1220</v>
       </c>
       <c r="D15">
-        <v>1779.616773457264</v>
+        <v>1841.379420349448</v>
       </c>
       <c r="E15">
-        <v>624</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46155.15625</v>
+        <v>46163.15625</v>
       </c>
       <c r="B16">
-        <v>638</v>
+        <v>391</v>
       </c>
       <c r="C16">
-        <v>929</v>
+        <v>1218</v>
       </c>
       <c r="D16">
-        <v>1791.455716412455</v>
+        <v>1854.700717503406</v>
       </c>
       <c r="E16">
-        <v>1567</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46155.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
       <c r="B17">
-        <v>623</v>
+        <v>390</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1221</v>
       </c>
       <c r="D17">
-        <v>1803.294659367646</v>
+        <v>1868.022014657364</v>
       </c>
       <c r="E17">
-        <v>623</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46155.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
       <c r="B18">
-        <v>645</v>
+        <v>395</v>
       </c>
       <c r="C18">
-        <v>932</v>
+        <v>1239</v>
       </c>
       <c r="D18">
-        <v>1823.351100855982</v>
+        <v>1886.673779655722</v>
       </c>
       <c r="E18">
-        <v>1577</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46155.1875</v>
+        <v>46163.1875</v>
       </c>
       <c r="B19">
-        <v>656</v>
+        <v>393</v>
       </c>
       <c r="C19">
-        <v>933</v>
+        <v>1238</v>
       </c>
       <c r="D19">
-        <v>1843.407542344318</v>
+        <v>1905.32554465408</v>
       </c>
       <c r="E19">
-        <v>1589</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46155.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
       <c r="B20">
-        <v>665</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>938</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>1863.463983832653</v>
+        <v>1923.977309652437</v>
       </c>
       <c r="E20">
-        <v>1603</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46155.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
       <c r="B21">
-        <v>668</v>
+        <v>404</v>
       </c>
       <c r="C21">
-        <v>949</v>
+        <v>1239</v>
       </c>
       <c r="D21">
-        <v>1883.520425320989</v>
+        <v>1942.629074650795</v>
       </c>
       <c r="E21">
-        <v>1617</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46155.21875</v>
+        <v>46163.21875</v>
       </c>
       <c r="B22">
-        <v>718</v>
+        <v>507</v>
       </c>
       <c r="C22">
-        <v>937</v>
+        <v>1206</v>
       </c>
       <c r="D22">
-        <v>1904.161632622656</v>
+        <v>1953.085367149785</v>
       </c>
       <c r="E22">
-        <v>1655</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46155.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
       <c r="B23">
-        <v>713</v>
+        <v>505</v>
       </c>
       <c r="C23">
-        <v>943</v>
+        <v>1199</v>
       </c>
       <c r="D23">
-        <v>1924.802839924322</v>
+        <v>1963.541659648775</v>
       </c>
       <c r="E23">
-        <v>1656</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46155.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
       <c r="B24">
-        <v>708</v>
+        <v>506</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1201</v>
       </c>
       <c r="D24">
-        <v>1945.444047225988</v>
+        <v>1973.997952147765</v>
       </c>
       <c r="E24">
-        <v>708</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46155.25</v>
+        <v>46163.25</v>
       </c>
       <c r="B25">
-        <v>719</v>
+        <v>520</v>
       </c>
       <c r="C25">
-        <v>946</v>
+        <v>1200</v>
       </c>
       <c r="D25">
-        <v>1966.085254527655</v>
+        <v>1984.454244646755</v>
       </c>
       <c r="E25">
-        <v>1665</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46155.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
       <c r="B26">
-        <v>782</v>
+        <v>615</v>
       </c>
       <c r="C26">
-        <v>978</v>
+        <v>1181</v>
       </c>
       <c r="D26">
-        <v>1956.811073910969</v>
+        <v>1973.598410682284</v>
       </c>
       <c r="E26">
-        <v>1760</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46155.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
       <c r="B27">
-        <v>793</v>
+        <v>638</v>
       </c>
       <c r="C27">
-        <v>973</v>
+        <v>1180</v>
       </c>
       <c r="D27">
-        <v>1947.536893294283</v>
+        <v>1962.742576717813</v>
       </c>
       <c r="E27">
-        <v>1766</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46155.28125</v>
+        <v>46163.28125</v>
       </c>
       <c r="B28">
-        <v>792</v>
+        <v>635</v>
       </c>
       <c r="C28">
-        <v>968</v>
+        <v>1181</v>
       </c>
       <c r="D28">
-        <v>1938.262712677597</v>
+        <v>1951.886742753342</v>
       </c>
       <c r="E28">
-        <v>1760</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46155.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
       <c r="B29">
-        <v>795</v>
+        <v>600</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>1928.988532060911</v>
+        <v>1941.030908788871</v>
       </c>
       <c r="E29">
-        <v>795</v>
+        <v>600</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46155.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
       <c r="B30">
-        <v>764</v>
+        <v>571</v>
       </c>
       <c r="C30">
-        <v>950</v>
+        <v>1164</v>
       </c>
       <c r="D30">
-        <v>1903.279354378094</v>
+        <v>1916.366531980771</v>
       </c>
       <c r="E30">
-        <v>1714</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46155.3125</v>
+        <v>46163.3125</v>
       </c>
       <c r="B31">
-        <v>763</v>
+        <v>578</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1160</v>
       </c>
       <c r="D31">
-        <v>1877.570176695278</v>
+        <v>1891.702155172671</v>
       </c>
       <c r="E31">
-        <v>763</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46155.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>585</v>
       </c>
       <c r="C32">
-        <v>948</v>
+        <v>1161</v>
       </c>
       <c r="D32">
-        <v>1851.860999012461</v>
+        <v>1867.037778364571</v>
       </c>
       <c r="E32">
-        <v>948</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46155.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
       <c r="B33">
-        <v>761</v>
+        <v>605</v>
       </c>
       <c r="C33">
-        <v>949</v>
+        <v>1164</v>
       </c>
       <c r="D33">
-        <v>1826.151821329645</v>
+        <v>1842.373401556471</v>
       </c>
       <c r="E33">
-        <v>1710</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46155.34375</v>
+        <v>46163.34375</v>
       </c>
       <c r="B34">
-        <v>738</v>
+        <v>467</v>
       </c>
       <c r="C34">
-        <v>951</v>
+        <v>1118</v>
       </c>
       <c r="D34">
-        <v>1806.187711285446</v>
+        <v>1801.503233111914</v>
       </c>
       <c r="E34">
-        <v>1689</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46155.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
       <c r="B35">
-        <v>735</v>
+        <v>456</v>
       </c>
       <c r="C35">
-        <v>950</v>
+        <v>1107</v>
       </c>
       <c r="D35">
-        <v>1786.223601241248</v>
+        <v>1760.633064667358</v>
       </c>
       <c r="E35">
-        <v>1685</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46155.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
       <c r="B36">
-        <v>732</v>
+        <v>468</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>1106</v>
       </c>
       <c r="D36">
-        <v>1766.25949119705</v>
+        <v>1719.762896222801</v>
       </c>
       <c r="E36">
-        <v>732</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46155.375</v>
+        <v>46163.375</v>
       </c>
       <c r="B37">
-        <v>721</v>
+        <v>464</v>
       </c>
       <c r="C37">
-        <v>948</v>
+        <v>1104</v>
       </c>
       <c r="D37">
-        <v>1746.295381152851</v>
+        <v>1678.892727778245</v>
       </c>
       <c r="E37">
-        <v>1669</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46155.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="B38">
-        <v>689</v>
+        <v>416</v>
       </c>
       <c r="C38">
-        <v>942</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>1669.178107153886</v>
+        <v>1639.581745540398</v>
       </c>
       <c r="E38">
-        <v>1631</v>
+        <v>416</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46155.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
       <c r="B39">
-        <v>684</v>
+        <v>421</v>
       </c>
       <c r="C39">
-        <v>939</v>
+        <v>1105</v>
       </c>
       <c r="D39">
-        <v>1592.060833154922</v>
+        <v>1600.270763302552</v>
       </c>
       <c r="E39">
-        <v>1623</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46155.40625</v>
+        <v>46163.40625</v>
       </c>
       <c r="B40">
-        <v>692</v>
+        <v>457</v>
       </c>
       <c r="C40">
-        <v>943</v>
+        <v>1109</v>
       </c>
       <c r="D40">
-        <v>1514.943559155957</v>
+        <v>1560.959781064705</v>
       </c>
       <c r="E40">
-        <v>1635</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46155.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
       <c r="B41">
-        <v>683</v>
+        <v>451</v>
       </c>
       <c r="C41">
-        <v>942</v>
+        <v>1104</v>
       </c>
       <c r="D41">
-        <v>1437.826285156992</v>
+        <v>1521.648798826858</v>
       </c>
       <c r="E41">
-        <v>1625</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46155.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
       <c r="B42">
-        <v>613</v>
+        <v>190</v>
       </c>
       <c r="C42">
-        <v>930</v>
+        <v>998</v>
       </c>
       <c r="D42">
-        <v>1425.576980227337</v>
+        <v>1495.922226415535</v>
       </c>
       <c r="E42">
-        <v>1543</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46155.4375</v>
+        <v>46163.4375</v>
       </c>
       <c r="B43">
-        <v>611</v>
+        <v>288</v>
       </c>
       <c r="C43">
-        <v>925</v>
+        <v>970</v>
       </c>
       <c r="D43">
-        <v>1413.327675297682</v>
+        <v>1470.195654004212</v>
       </c>
       <c r="E43">
-        <v>1536</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46155.44791666666</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="B44">
-        <v>604</v>
+        <v>276</v>
       </c>
       <c r="C44">
-        <v>937</v>
+        <v>1036</v>
       </c>
       <c r="D44">
-        <v>1401.078370368027</v>
+        <v>1444.469081592888</v>
       </c>
       <c r="E44">
-        <v>1541</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46155.45833333334</v>
+        <v>46163.45833333334</v>
       </c>
       <c r="B45">
-        <v>607</v>
+        <v>189</v>
       </c>
       <c r="C45">
-        <v>940</v>
+        <v>1049</v>
       </c>
       <c r="D45">
-        <v>1388.829065438373</v>
+        <v>1418.742509181565</v>
       </c>
       <c r="E45">
-        <v>1547</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46155.46875</v>
+        <v>46163.46875</v>
       </c>
       <c r="B46">
-        <v>608</v>
+        <v>162</v>
       </c>
       <c r="C46">
-        <v>921</v>
+        <v>1036</v>
       </c>
       <c r="D46">
-        <v>1389.547198893284</v>
+        <v>1413.577704871524</v>
       </c>
       <c r="E46">
-        <v>1529</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46155.47916666666</v>
+        <v>46163.47916666666</v>
       </c>
       <c r="B47">
-        <v>595</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>918</v>
+        <v>1015</v>
       </c>
       <c r="D47">
-        <v>1390.265332348195</v>
+        <v>1408.412900561483</v>
       </c>
       <c r="E47">
-        <v>1513</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46155.48958333334</v>
+        <v>46163.48958333334</v>
       </c>
       <c r="B48">
-        <v>609</v>
+        <v>161</v>
       </c>
       <c r="C48">
-        <v>921</v>
+        <v>1002</v>
       </c>
       <c r="D48">
-        <v>1390.983465803106</v>
+        <v>1403.248096251443</v>
       </c>
       <c r="E48">
-        <v>1530</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46155.5</v>
+        <v>46163.5</v>
       </c>
       <c r="B49">
-        <v>595</v>
+        <v>160</v>
       </c>
       <c r="C49">
-        <v>917</v>
+        <v>1005</v>
       </c>
       <c r="D49">
-        <v>1391.701599258018</v>
+        <v>1398.083291941402</v>
       </c>
       <c r="E49">
-        <v>1512</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46155.51041666666</v>
+        <v>46163.51041666666</v>
       </c>
       <c r="B50">
-        <v>587</v>
+        <v>156</v>
       </c>
       <c r="C50">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="D50">
-        <v>1384.150938932976</v>
+        <v>1422.435831508234</v>
       </c>
       <c r="E50">
-        <v>1515</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46155.52083333334</v>
+        <v>46163.52083333334</v>
       </c>
       <c r="B51">
-        <v>582</v>
+        <v>160</v>
       </c>
       <c r="C51">
-        <v>929</v>
+        <v>908</v>
       </c>
       <c r="D51">
-        <v>1376.600278607934</v>
+        <v>1446.788371075065</v>
       </c>
       <c r="E51">
-        <v>1511</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46155.53125</v>
+        <v>46163.53125</v>
       </c>
       <c r="B52">
-        <v>578</v>
+        <v>175</v>
       </c>
       <c r="C52">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="D52">
-        <v>1369.049618282892</v>
+        <v>1471.140910641897</v>
       </c>
       <c r="E52">
-        <v>1508</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46155.54166666666</v>
+        <v>46163.54166666666</v>
       </c>
       <c r="B53">
-        <v>600</v>
+        <v>204</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>902</v>
       </c>
       <c r="D53">
-        <v>1361.49895795785</v>
+        <v>1495.493450208729</v>
       </c>
       <c r="E53">
-        <v>600</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46155.55208333334</v>
+        <v>46163.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>1364.781853751305</v>
+        <v>1493.866049605516</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46155.5625</v>
+        <v>46163.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1368.06474954476</v>
+        <v>1492.238649002304</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46155.57291666666</v>
+        <v>46163.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1371.347645338215</v>
+        <v>1490.611248399091</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46155.58333333334</v>
+        <v>46163.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>1374.63054113167</v>
+        <v>1488.983847795879</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46155.59375</v>
+        <v>46163.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>1399.970393037807</v>
+        <v>1487.804713226802</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46155.60416666666</v>
+        <v>46163.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1425.310244943945</v>
+        <v>1486.625578657724</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46155.61458333334</v>
+        <v>46163.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>1450.650096850082</v>
+        <v>1485.446444088647</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46155.625</v>
+        <v>46163.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1475.98994875622</v>
+        <v>1484.26730951957</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46155.63541666666</v>
+        <v>46163.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1539.965380531886</v>
+        <v>1550.805580893008</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46155.64583333334</v>
+        <v>46163.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1603.940812307553</v>
+        <v>1617.343852266446</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46155.65625</v>
+        <v>46163.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1667.91624408322</v>
+        <v>1683.882123639884</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46155.66666666666</v>
+        <v>46163.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>1731.891675858887</v>
+        <v>1750.420395013321</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46155.67708333334</v>
+        <v>46163.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>1872.163657685364</v>
+        <v>1877.903357242981</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46155.6875</v>
+        <v>46163.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>2012.435639511841</v>
+        <v>2005.38631947264</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46155.69791666666</v>
+        <v>46163.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>2152.707621338318</v>
+        <v>2132.8692817023</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46155.70833333334</v>
+        <v>46163.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>2292.979603164795</v>
+        <v>2260.352243931959</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46155.71875</v>
+        <v>46163.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>2363.325904589805</v>
+        <v>2367.156499094878</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46155.72916666666</v>
+        <v>46163.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>2433.672206014814</v>
+        <v>2473.960754257797</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46155.73958333334</v>
+        <v>46163.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>2504.018507439823</v>
+        <v>2580.765009420716</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46155.75</v>
+        <v>46163.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>2574.364808864833</v>
+        <v>2687.569264583635</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46155.76041666666</v>
+        <v>46163.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2580.284280342716</v>
+        <v>2699.302140789225</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46155.77083333334</v>
+        <v>46163.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2586.203751820599</v>
+        <v>2711.035016994815</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46155.78125</v>
+        <v>46163.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2592.123223298482</v>
+        <v>2722.767893200405</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46155.79166666666</v>
+        <v>46163.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2598.042694776365</v>
+        <v>2734.500769405994</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46155.80208333334</v>
+        <v>46163.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2595.488191486816</v>
+        <v>2736.342558112965</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46155.8125</v>
+        <v>46163.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2592.933688197266</v>
+        <v>2738.184346819937</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46155.82291666666</v>
+        <v>46163.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2590.379184907717</v>
+        <v>2740.026135526908</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46155.83333333334</v>
+        <v>46163.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2587.824681618167</v>
+        <v>2741.867924233879</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46155.84375</v>
+        <v>46163.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2565.357363531503</v>
+        <v>2699.165711995921</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46155.85416666666</v>
+        <v>46163.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2542.890045444839</v>
+        <v>2656.463499757963</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46155.86458333334</v>
+        <v>46163.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2520.422727358176</v>
+        <v>2613.761287520005</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46155.875</v>
+        <v>46163.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2497.955409271512</v>
+        <v>2571.059075282047</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46155.88541666666</v>
+        <v>46163.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2434.698110950508</v>
+        <v>2495.935534858419</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46155.89583333334</v>
+        <v>46163.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2371.440812629504</v>
+        <v>2420.811994434793</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46155.90625</v>
+        <v>46163.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2308.1835143085</v>
+        <v>2345.688454011166</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46155.91666666666</v>
+        <v>46163.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2244.926215987495</v>
+        <v>2270.564913587539</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46155.92708333334</v>
+        <v>46163.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>2163.592472703629</v>
+        <v>2208.840629627192</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46155.9375</v>
+        <v>46163.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>2082.258729419762</v>
+        <v>2147.116345666846</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46155.94791666666</v>
+        <v>46163.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>2000.924986135895</v>
+        <v>2085.392061706499</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46155.95833333334</v>
+        <v>46163.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>1919.591242852028</v>
+        <v>2023.667777746153</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46155.96875</v>
+        <v>46163.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>1922.913168022234</v>
+        <v>2003.118112185007</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46155.97916666666</v>
+        <v>46163.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>1926.23509319244</v>
+        <v>1982.568446623861</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46155.98958333334</v>
+        <v>46163.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1929.557018362646</v>
+        <v>1962.018781062715</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46156</v>
+        <v>46164</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1932.878943532853</v>
+        <v>1941.469115501569</v>
       </c>
       <c r="E97">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -412,891 +412,891 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B2">
-        <v>448</v>
+        <v>328</v>
       </c>
       <c r="C2">
-        <v>1279</v>
+        <v>1401</v>
       </c>
       <c r="D2">
-        <v>1820.759182765764</v>
+        <v>1857.121652501407</v>
       </c>
       <c r="E2">
-        <v>1727</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B3">
-        <v>447</v>
+        <v>320</v>
       </c>
       <c r="C3">
-        <v>1274</v>
+        <v>1392</v>
       </c>
       <c r="D3">
-        <v>1803.939461560394</v>
+        <v>1837.50200485601</v>
       </c>
       <c r="E3">
-        <v>1721</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1273</v>
+        <v>1391</v>
       </c>
       <c r="D4">
-        <v>1787.119740355024</v>
+        <v>1817.882357210612</v>
       </c>
       <c r="E4">
-        <v>1273</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B5">
-        <v>446</v>
+        <v>321</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1392</v>
       </c>
       <c r="D5">
-        <v>1770.300019149654</v>
+        <v>1798.262709565214</v>
       </c>
       <c r="E5">
-        <v>446</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B6">
-        <v>418</v>
+        <v>457</v>
       </c>
       <c r="C6">
-        <v>1212</v>
+        <v>1246</v>
       </c>
       <c r="D6">
-        <v>1767.123177253391</v>
+        <v>1795.574678972746</v>
       </c>
       <c r="E6">
-        <v>1630</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B7">
-        <v>416</v>
+        <v>460</v>
       </c>
       <c r="C7">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="D7">
-        <v>1763.946335357128</v>
+        <v>1792.886648380277</v>
       </c>
       <c r="E7">
-        <v>1622</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B8">
-        <v>415</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1223</v>
       </c>
       <c r="D8">
-        <v>1760.769493460864</v>
+        <v>1790.198617787809</v>
       </c>
       <c r="E8">
-        <v>415</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="C9">
-        <v>1207</v>
+        <v>1224</v>
       </c>
       <c r="D9">
-        <v>1757.592651564601</v>
+        <v>1787.51058719534</v>
       </c>
       <c r="E9">
-        <v>1207</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
       <c r="B10">
-        <v>399</v>
+        <v>454</v>
       </c>
       <c r="C10">
-        <v>1210</v>
+        <v>1229</v>
       </c>
       <c r="D10">
-        <v>1771.878695183833</v>
+        <v>1801.446686761406</v>
       </c>
       <c r="E10">
-        <v>1609</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B11">
-        <v>392</v>
+        <v>451</v>
       </c>
       <c r="C11">
-        <v>1209</v>
+        <v>1225</v>
       </c>
       <c r="D11">
-        <v>1786.164738803066</v>
+        <v>1815.382786327472</v>
       </c>
       <c r="E11">
-        <v>1601</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="B12">
-        <v>397</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>1216</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>1800.450782422298</v>
+        <v>1829.318885893537</v>
       </c>
       <c r="E12">
-        <v>1613</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
       <c r="B13">
-        <v>398</v>
+        <v>452</v>
       </c>
       <c r="C13">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="D13">
-        <v>1814.736826041531</v>
+        <v>1843.254985459603</v>
       </c>
       <c r="E13">
-        <v>1615</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
       <c r="B14">
-        <v>392</v>
+        <v>468</v>
       </c>
       <c r="C14">
-        <v>1223</v>
+        <v>1230</v>
       </c>
       <c r="D14">
-        <v>1828.058123195489</v>
+        <v>1855.911542788032</v>
       </c>
       <c r="E14">
-        <v>1615</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
       <c r="B15">
-        <v>390</v>
+        <v>469</v>
       </c>
       <c r="C15">
-        <v>1220</v>
+        <v>1229</v>
       </c>
       <c r="D15">
-        <v>1841.379420349448</v>
+        <v>1868.568100116461</v>
       </c>
       <c r="E15">
-        <v>1610</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
       <c r="B16">
-        <v>391</v>
+        <v>476</v>
       </c>
       <c r="C16">
-        <v>1218</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>1854.700717503406</v>
+        <v>1881.22465744489</v>
       </c>
       <c r="E16">
-        <v>1609</v>
+        <v>476</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
       <c r="B17">
-        <v>390</v>
+        <v>478</v>
       </c>
       <c r="C17">
-        <v>1221</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>1868.022014657364</v>
+        <v>1893.88121477332</v>
       </c>
       <c r="E17">
-        <v>1611</v>
+        <v>478</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
       <c r="B18">
-        <v>395</v>
+        <v>515</v>
       </c>
       <c r="C18">
-        <v>1239</v>
+        <v>1225</v>
       </c>
       <c r="D18">
-        <v>1886.673779655722</v>
+        <v>1912.370104161993</v>
       </c>
       <c r="E18">
-        <v>1634</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
       <c r="B19">
-        <v>393</v>
+        <v>513</v>
       </c>
       <c r="C19">
-        <v>1238</v>
+        <v>1224</v>
       </c>
       <c r="D19">
-        <v>1905.32554465408</v>
+        <v>1930.858993550666</v>
       </c>
       <c r="E19">
-        <v>1631</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>1923.977309652437</v>
+        <v>1949.347882939339</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>512</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
       <c r="B21">
-        <v>404</v>
+        <v>527</v>
       </c>
       <c r="C21">
-        <v>1239</v>
+        <v>1218</v>
       </c>
       <c r="D21">
-        <v>1942.629074650795</v>
+        <v>1967.836772328012</v>
       </c>
       <c r="E21">
-        <v>1643</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
       <c r="B22">
-        <v>507</v>
+        <v>595</v>
       </c>
       <c r="C22">
-        <v>1206</v>
+        <v>1225</v>
       </c>
       <c r="D22">
-        <v>1953.085367149785</v>
+        <v>1980.106491305615</v>
       </c>
       <c r="E22">
-        <v>1713</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
       <c r="B23">
-        <v>505</v>
+        <v>592</v>
       </c>
       <c r="C23">
-        <v>1199</v>
+        <v>1224</v>
       </c>
       <c r="D23">
-        <v>1963.541659648775</v>
+        <v>1992.376210283217</v>
       </c>
       <c r="E23">
-        <v>1704</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
       <c r="B24">
-        <v>506</v>
+        <v>591</v>
       </c>
       <c r="C24">
-        <v>1201</v>
+        <v>1222</v>
       </c>
       <c r="D24">
-        <v>1973.997952147765</v>
+        <v>2004.64592926082</v>
       </c>
       <c r="E24">
-        <v>1707</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
       <c r="B25">
-        <v>520</v>
+        <v>619</v>
       </c>
       <c r="C25">
-        <v>1200</v>
+        <v>1223</v>
       </c>
       <c r="D25">
-        <v>1984.454244646755</v>
+        <v>2016.915648238423</v>
       </c>
       <c r="E25">
-        <v>1720</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
       <c r="B26">
-        <v>615</v>
+        <v>717</v>
       </c>
       <c r="C26">
-        <v>1181</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>1973.598410682284</v>
+        <v>2005.677498196789</v>
       </c>
       <c r="E26">
-        <v>1796</v>
+        <v>717</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
       <c r="B27">
-        <v>638</v>
+        <v>724</v>
       </c>
       <c r="C27">
-        <v>1180</v>
+        <v>1218</v>
       </c>
       <c r="D27">
-        <v>1962.742576717813</v>
+        <v>1994.439348155156</v>
       </c>
       <c r="E27">
-        <v>1818</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
       <c r="B28">
-        <v>635</v>
+        <v>725</v>
       </c>
       <c r="C28">
-        <v>1181</v>
+        <v>1222</v>
       </c>
       <c r="D28">
-        <v>1951.886742753342</v>
+        <v>1983.201198113522</v>
       </c>
       <c r="E28">
-        <v>1816</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
       <c r="B29">
-        <v>600</v>
+        <v>732</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1223</v>
       </c>
       <c r="D29">
-        <v>1941.030908788871</v>
+        <v>1971.963048071889</v>
       </c>
       <c r="E29">
-        <v>600</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
       <c r="B30">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C30">
-        <v>1164</v>
+        <v>1269</v>
       </c>
       <c r="D30">
-        <v>1916.366531980771</v>
+        <v>1943.723848452748</v>
       </c>
       <c r="E30">
-        <v>1735</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
       <c r="B31">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="C31">
-        <v>1160</v>
+        <v>1277</v>
       </c>
       <c r="D31">
-        <v>1891.702155172671</v>
+        <v>1915.484648833607</v>
       </c>
       <c r="E31">
-        <v>1738</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
       <c r="B32">
-        <v>585</v>
+        <v>569</v>
       </c>
       <c r="C32">
-        <v>1161</v>
+        <v>1279</v>
       </c>
       <c r="D32">
-        <v>1867.037778364571</v>
+        <v>1887.245449214467</v>
       </c>
       <c r="E32">
-        <v>1746</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
       <c r="B33">
-        <v>605</v>
+        <v>638</v>
       </c>
       <c r="C33">
-        <v>1164</v>
+        <v>1309</v>
       </c>
       <c r="D33">
-        <v>1842.373401556471</v>
+        <v>1859.006249595326</v>
       </c>
       <c r="E33">
-        <v>1769</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
       <c r="B34">
-        <v>467</v>
+        <v>543</v>
       </c>
       <c r="C34">
-        <v>1118</v>
+        <v>1276</v>
       </c>
       <c r="D34">
-        <v>1801.503233111914</v>
+        <v>1820.530712074455</v>
       </c>
       <c r="E34">
-        <v>1585</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
       <c r="B35">
-        <v>456</v>
+        <v>541</v>
       </c>
       <c r="C35">
-        <v>1107</v>
+        <v>1272</v>
       </c>
       <c r="D35">
-        <v>1760.633064667358</v>
+        <v>1782.055174553584</v>
       </c>
       <c r="E35">
-        <v>1563</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
       <c r="B36">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="C36">
-        <v>1106</v>
+        <v>1248</v>
       </c>
       <c r="D36">
-        <v>1719.762896222801</v>
+        <v>1743.579637032712</v>
       </c>
       <c r="E36">
-        <v>1574</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
       <c r="B37">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="C37">
-        <v>1104</v>
+        <v>1247</v>
       </c>
       <c r="D37">
-        <v>1678.892727778245</v>
+        <v>1705.104099511841</v>
       </c>
       <c r="E37">
-        <v>1568</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="B38">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1202</v>
       </c>
       <c r="D38">
-        <v>1639.581745540398</v>
+        <v>1654.864708549283</v>
       </c>
       <c r="E38">
-        <v>416</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
       <c r="B39">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C39">
-        <v>1105</v>
+        <v>1197</v>
       </c>
       <c r="D39">
-        <v>1600.270763302552</v>
+        <v>1604.625317586725</v>
       </c>
       <c r="E39">
-        <v>1526</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
       <c r="B40">
-        <v>457</v>
+        <v>425</v>
       </c>
       <c r="C40">
-        <v>1109</v>
+        <v>1182</v>
       </c>
       <c r="D40">
-        <v>1560.959781064705</v>
+        <v>1554.385926624168</v>
       </c>
       <c r="E40">
-        <v>1566</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
       <c r="B41">
-        <v>451</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>1104</v>
+        <v>1183</v>
       </c>
       <c r="D41">
-        <v>1521.648798826858</v>
+        <v>1504.146535661611</v>
       </c>
       <c r="E41">
-        <v>1555</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
       <c r="B42">
-        <v>190</v>
+        <v>413</v>
       </c>
       <c r="C42">
-        <v>998</v>
+        <v>1184</v>
       </c>
       <c r="D42">
-        <v>1495.922226415535</v>
+        <v>1481.035423925545</v>
       </c>
       <c r="E42">
-        <v>1188</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
       <c r="B43">
-        <v>288</v>
+        <v>411</v>
       </c>
       <c r="C43">
-        <v>970</v>
+        <v>1185</v>
       </c>
       <c r="D43">
-        <v>1470.195654004212</v>
+        <v>1457.924312189479</v>
       </c>
       <c r="E43">
-        <v>1258</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
       <c r="B44">
-        <v>276</v>
+        <v>414</v>
       </c>
       <c r="C44">
-        <v>1036</v>
+        <v>1182</v>
       </c>
       <c r="D44">
-        <v>1444.469081592888</v>
+        <v>1434.813200453413</v>
       </c>
       <c r="E44">
-        <v>1312</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
       <c r="B45">
-        <v>189</v>
+        <v>411</v>
       </c>
       <c r="C45">
-        <v>1049</v>
+        <v>1184</v>
       </c>
       <c r="D45">
-        <v>1418.742509181565</v>
+        <v>1411.702088717347</v>
       </c>
       <c r="E45">
-        <v>1238</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
       <c r="B46">
-        <v>162</v>
+        <v>224</v>
       </c>
       <c r="C46">
-        <v>1036</v>
+        <v>1006</v>
       </c>
       <c r="D46">
-        <v>1413.577704871524</v>
+        <v>1414.757119796692</v>
       </c>
       <c r="E46">
-        <v>1198</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="C47">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="D47">
-        <v>1408.412900561483</v>
+        <v>1417.812150876037</v>
       </c>
       <c r="E47">
-        <v>1015</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
       <c r="B48">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="C48">
-        <v>1002</v>
+        <v>1014</v>
       </c>
       <c r="D48">
-        <v>1403.248096251443</v>
+        <v>1420.867181955382</v>
       </c>
       <c r="E48">
-        <v>1163</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
       <c r="B49">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="C49">
-        <v>1005</v>
+        <v>1013</v>
       </c>
       <c r="D49">
-        <v>1398.083291941402</v>
+        <v>1423.922213034727</v>
       </c>
       <c r="E49">
-        <v>1165</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46163.51041666666</v>
+        <v>46164.51041666666</v>
       </c>
       <c r="B50">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="C50">
-        <v>914</v>
+        <v>998</v>
       </c>
       <c r="D50">
-        <v>1422.435831508234</v>
+        <v>1452.578007800932</v>
       </c>
       <c r="E50">
-        <v>1070</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46163.52083333334</v>
+        <v>46164.52083333334</v>
       </c>
       <c r="B51">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="C51">
-        <v>908</v>
+        <v>1001</v>
       </c>
       <c r="D51">
-        <v>1446.788371075065</v>
+        <v>1481.233802567137</v>
       </c>
       <c r="E51">
-        <v>1068</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46163.53125</v>
+        <v>46164.53125</v>
       </c>
       <c r="B52">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>1471.140910641897</v>
+        <v>1509.889597333342</v>
       </c>
       <c r="E52">
-        <v>1085</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46163.54166666666</v>
+        <v>46164.54166666666</v>
       </c>
       <c r="B53">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>902</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>1495.493450208729</v>
+        <v>1538.545392099547</v>
       </c>
       <c r="E53">
-        <v>1106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46163.55208333334</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>1493.866049605516</v>
+        <v>1539.269474141061</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46163.5625</v>
+        <v>46164.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1492.238649002304</v>
+        <v>1539.993556182575</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46163.57291666666</v>
+        <v>46164.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1490.611248399091</v>
+        <v>1540.717638224088</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46163.58333333334</v>
+        <v>46164.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>1488.983847795879</v>
+        <v>1541.441720265602</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46163.59375</v>
+        <v>46164.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>1487.804713226802</v>
+        <v>1533.94300761637</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46163.60416666666</v>
+        <v>46164.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1486.625578657724</v>
+        <v>1526.444294967138</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46163.61458333334</v>
+        <v>46164.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>1485.446444088647</v>
+        <v>1518.945582317906</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46163.625</v>
+        <v>46164.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1484.26730951957</v>
+        <v>1511.446869668674</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46163.63541666666</v>
+        <v>46164.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1550.805580893008</v>
+        <v>1576.29684757867</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46163.64583333334</v>
+        <v>46164.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1617.343852266446</v>
+        <v>1641.146825488665</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46163.65625</v>
+        <v>46164.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1683.882123639884</v>
+        <v>1705.996803398661</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46163.66666666666</v>
+        <v>46164.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>1750.420395013321</v>
+        <v>1770.846781308656</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46163.67708333334</v>
+        <v>46164.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>1877.903357242981</v>
+        <v>1900.695521109296</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46163.6875</v>
+        <v>46164.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>2005.38631947264</v>
+        <v>2030.544260909936</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46163.69791666666</v>
+        <v>46164.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>2132.8692817023</v>
+        <v>2160.393000710576</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46163.70833333334</v>
+        <v>46164.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>2260.352243931959</v>
+        <v>2290.241740511216</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46163.71875</v>
+        <v>46164.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>2367.156499094878</v>
+        <v>2396.106502553332</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46163.72916666666</v>
+        <v>46164.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>2473.960754257797</v>
+        <v>2501.971264595447</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46163.73958333334</v>
+        <v>46164.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>2580.765009420716</v>
+        <v>2607.836026637563</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46163.75</v>
+        <v>46164.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>2687.569264583635</v>
+        <v>2713.700788679678</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46163.76041666666</v>
+        <v>46164.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2699.302140789225</v>
+        <v>2735.691061091125</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46163.77083333334</v>
+        <v>46164.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2711.035016994815</v>
+        <v>2757.681333502571</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46163.78125</v>
+        <v>46164.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2722.767893200405</v>
+        <v>2779.671605914017</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46163.79166666666</v>
+        <v>46164.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2734.500769405994</v>
+        <v>2801.661878325464</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46163.80208333334</v>
+        <v>46164.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2736.342558112965</v>
+        <v>2801.721391917999</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46163.8125</v>
+        <v>46164.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2738.184346819937</v>
+        <v>2801.780905510533</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46163.82291666666</v>
+        <v>46164.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2740.026135526908</v>
+        <v>2801.840419103067</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46163.83333333334</v>
+        <v>46164.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2741.867924233879</v>
+        <v>2801.899932695602</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46163.84375</v>
+        <v>46164.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2699.165711995921</v>
+        <v>2757.22506262734</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46163.85416666666</v>
+        <v>46164.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2656.463499757963</v>
+        <v>2712.550192559079</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46163.86458333334</v>
+        <v>46164.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2613.761287520005</v>
+        <v>2667.875322490817</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46163.875</v>
+        <v>46164.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2571.059075282047</v>
+        <v>2623.200452422556</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46163.88541666666</v>
+        <v>46164.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2495.935534858419</v>
+        <v>2549.234975935408</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46163.89583333334</v>
+        <v>46164.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2420.811994434793</v>
+        <v>2475.26949944826</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46163.90625</v>
+        <v>46164.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2345.688454011166</v>
+        <v>2401.304022961112</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46163.91666666666</v>
+        <v>46164.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2270.564913587539</v>
+        <v>2327.338546473964</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46163.92708333334</v>
+        <v>46164.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>2208.840629627192</v>
+        <v>2262.617514681193</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46163.9375</v>
+        <v>46164.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>2147.116345666846</v>
+        <v>2197.896482888422</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46163.94791666666</v>
+        <v>46164.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>2085.392061706499</v>
+        <v>2133.175451095651</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46163.95833333334</v>
+        <v>46164.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>2023.667777746153</v>
+        <v>2068.454419302881</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46163.96875</v>
+        <v>46164.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>2003.118112185007</v>
+        <v>1984.373982760731</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46163.97916666666</v>
+        <v>46164.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>1982.568446623861</v>
+        <v>1900.293546218581</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46163.98958333334</v>
+        <v>46164.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1962.018781062715</v>
+        <v>1816.213109676431</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1941.469115501569</v>
+        <v>1732.132673134282</v>
       </c>
       <c r="E97">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -412,857 +412,857 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46164.01041666666</v>
+        <v>46167.01041666666</v>
       </c>
       <c r="B2">
-        <v>328</v>
+        <v>489</v>
       </c>
       <c r="C2">
-        <v>1401</v>
+        <v>1423</v>
       </c>
       <c r="D2">
-        <v>1857.121652501407</v>
+        <v>1847.695117763087</v>
       </c>
       <c r="E2">
-        <v>1729</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46164.02083333334</v>
+        <v>46167.02083333334</v>
       </c>
       <c r="B3">
-        <v>320</v>
+        <v>499</v>
       </c>
       <c r="C3">
-        <v>1392</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>1837.50200485601</v>
+        <v>1824.59322931199</v>
       </c>
       <c r="E3">
-        <v>1712</v>
+        <v>499</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46164.03125</v>
+        <v>46167.03125</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>483</v>
       </c>
       <c r="C4">
-        <v>1391</v>
+        <v>1421</v>
       </c>
       <c r="D4">
-        <v>1817.882357210612</v>
+        <v>1801.491340860892</v>
       </c>
       <c r="E4">
-        <v>1391</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46164.04166666666</v>
+        <v>46167.04166666666</v>
       </c>
       <c r="B5">
-        <v>321</v>
+        <v>482</v>
       </c>
       <c r="C5">
-        <v>1392</v>
+        <v>1420</v>
       </c>
       <c r="D5">
-        <v>1798.262709565214</v>
+        <v>1778.389452409795</v>
       </c>
       <c r="E5">
-        <v>1713</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46164.05208333334</v>
+        <v>46167.05208333334</v>
       </c>
       <c r="B6">
-        <v>457</v>
+        <v>513</v>
       </c>
       <c r="C6">
-        <v>1246</v>
+        <v>1376</v>
       </c>
       <c r="D6">
-        <v>1795.574678972746</v>
+        <v>1771.911044546453</v>
       </c>
       <c r="E6">
-        <v>1703</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46164.0625</v>
+        <v>46167.0625</v>
       </c>
       <c r="B7">
-        <v>460</v>
+        <v>518</v>
       </c>
       <c r="C7">
-        <v>1222</v>
+        <v>1371</v>
       </c>
       <c r="D7">
-        <v>1792.886648380277</v>
+        <v>1765.432636683111</v>
       </c>
       <c r="E7">
-        <v>1682</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46164.07291666666</v>
+        <v>46167.07291666666</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="C8">
-        <v>1223</v>
+        <v>1373</v>
       </c>
       <c r="D8">
-        <v>1790.198617787809</v>
+        <v>1758.954228819769</v>
       </c>
       <c r="E8">
-        <v>1223</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46164.08333333334</v>
+        <v>46167.08333333334</v>
       </c>
       <c r="B9">
-        <v>459</v>
+        <v>512</v>
       </c>
       <c r="C9">
-        <v>1224</v>
+        <v>1368</v>
       </c>
       <c r="D9">
-        <v>1787.51058719534</v>
+        <v>1752.475820956427</v>
       </c>
       <c r="E9">
-        <v>1683</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46164.09375</v>
+        <v>46167.09375</v>
       </c>
       <c r="B10">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="C10">
-        <v>1229</v>
+        <v>1369</v>
       </c>
       <c r="D10">
-        <v>1801.446686761406</v>
+        <v>1760.863554304151</v>
       </c>
       <c r="E10">
-        <v>1683</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46164.10416666666</v>
+        <v>46167.10416666666</v>
       </c>
       <c r="B11">
-        <v>451</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>1225</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>1815.382786327472</v>
+        <v>1769.251287651874</v>
       </c>
       <c r="E11">
-        <v>1676</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46164.11458333334</v>
+        <v>46167.11458333334</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>476</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1363</v>
       </c>
       <c r="D12">
-        <v>1829.318885893537</v>
+        <v>1777.639020999598</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46164.125</v>
+        <v>46167.125</v>
       </c>
       <c r="B13">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="C13">
-        <v>1229</v>
+        <v>1326</v>
       </c>
       <c r="D13">
-        <v>1843.254985459603</v>
+        <v>1786.026754347322</v>
       </c>
       <c r="E13">
-        <v>1681</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46164.13541666666</v>
+        <v>46167.13541666666</v>
       </c>
       <c r="B14">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="C14">
-        <v>1230</v>
+        <v>1361</v>
       </c>
       <c r="D14">
-        <v>1855.911542788032</v>
+        <v>1795.098425182513</v>
       </c>
       <c r="E14">
-        <v>1698</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46164.14583333334</v>
+        <v>46167.14583333334</v>
       </c>
       <c r="B15">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="C15">
-        <v>1229</v>
+        <v>1362</v>
       </c>
       <c r="D15">
-        <v>1868.568100116461</v>
+        <v>1804.170096017705</v>
       </c>
       <c r="E15">
-        <v>1698</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46164.15625</v>
+        <v>46167.15625</v>
       </c>
       <c r="B16">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>1363</v>
       </c>
       <c r="D16">
-        <v>1881.22465744489</v>
+        <v>1813.241766852896</v>
       </c>
       <c r="E16">
-        <v>476</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46164.16666666666</v>
+        <v>46167.16666666666</v>
       </c>
       <c r="B17">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1364</v>
       </c>
       <c r="D17">
-        <v>1893.88121477332</v>
+        <v>1822.313437688087</v>
       </c>
       <c r="E17">
-        <v>478</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46164.17708333334</v>
+        <v>46167.17708333334</v>
       </c>
       <c r="B18">
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="C18">
-        <v>1225</v>
+        <v>1395</v>
       </c>
       <c r="D18">
-        <v>1912.370104161993</v>
+        <v>1844.902373023842</v>
       </c>
       <c r="E18">
-        <v>1740</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46164.1875</v>
+        <v>46167.1875</v>
       </c>
       <c r="B19">
-        <v>513</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>1224</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>1930.858993550666</v>
+        <v>1867.491308359597</v>
       </c>
       <c r="E19">
-        <v>1737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46164.19791666666</v>
+        <v>46167.19791666666</v>
       </c>
       <c r="B20">
-        <v>512</v>
+        <v>492</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1397</v>
       </c>
       <c r="D20">
-        <v>1949.347882939339</v>
+        <v>1890.080243695352</v>
       </c>
       <c r="E20">
-        <v>512</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46164.20833333334</v>
+        <v>46167.20833333334</v>
       </c>
       <c r="B21">
-        <v>527</v>
+        <v>501</v>
       </c>
       <c r="C21">
-        <v>1218</v>
+        <v>1421</v>
       </c>
       <c r="D21">
-        <v>1967.836772328012</v>
+        <v>1912.669179031107</v>
       </c>
       <c r="E21">
-        <v>1745</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46164.21875</v>
+        <v>46167.21875</v>
       </c>
       <c r="B22">
-        <v>595</v>
+        <v>525</v>
       </c>
       <c r="C22">
-        <v>1225</v>
+        <v>1420</v>
       </c>
       <c r="D22">
-        <v>1980.106491305615</v>
+        <v>1929.292659618975</v>
       </c>
       <c r="E22">
-        <v>1820</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46164.22916666666</v>
+        <v>46167.22916666666</v>
       </c>
       <c r="B23">
-        <v>592</v>
+        <v>517</v>
       </c>
       <c r="C23">
-        <v>1224</v>
+        <v>1422</v>
       </c>
       <c r="D23">
-        <v>1992.376210283217</v>
+        <v>1945.916140206843</v>
       </c>
       <c r="E23">
-        <v>1816</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46164.23958333334</v>
+        <v>46167.23958333334</v>
       </c>
       <c r="B24">
-        <v>591</v>
+        <v>514</v>
       </c>
       <c r="C24">
-        <v>1222</v>
+        <v>1424</v>
       </c>
       <c r="D24">
-        <v>2004.64592926082</v>
+        <v>1962.539620794712</v>
       </c>
       <c r="E24">
-        <v>1813</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46164.25</v>
+        <v>46167.25</v>
       </c>
       <c r="B25">
-        <v>619</v>
+        <v>528</v>
       </c>
       <c r="C25">
-        <v>1223</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>2016.915648238423</v>
+        <v>1979.16310138258</v>
       </c>
       <c r="E25">
-        <v>1842</v>
+        <v>528</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46164.26041666666</v>
+        <v>46167.26041666666</v>
       </c>
       <c r="B26">
-        <v>717</v>
+        <v>614</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>2005.677498196789</v>
+        <v>1955.158795413751</v>
       </c>
       <c r="E26">
-        <v>717</v>
+        <v>614</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46164.27083333334</v>
+        <v>46167.27083333334</v>
       </c>
       <c r="B27">
-        <v>724</v>
+        <v>619</v>
       </c>
       <c r="C27">
-        <v>1218</v>
+        <v>1428</v>
       </c>
       <c r="D27">
-        <v>1994.439348155156</v>
+        <v>1931.154489444922</v>
       </c>
       <c r="E27">
-        <v>1942</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46164.28125</v>
+        <v>46167.28125</v>
       </c>
       <c r="B28">
-        <v>725</v>
+        <v>609</v>
       </c>
       <c r="C28">
-        <v>1222</v>
+        <v>1426</v>
       </c>
       <c r="D28">
-        <v>1983.201198113522</v>
+        <v>1907.150183476093</v>
       </c>
       <c r="E28">
-        <v>1947</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46164.29166666666</v>
+        <v>46167.29166666666</v>
       </c>
       <c r="B29">
-        <v>732</v>
+        <v>594</v>
       </c>
       <c r="C29">
-        <v>1223</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>1971.963048071889</v>
+        <v>1883.145877507264</v>
       </c>
       <c r="E29">
-        <v>1955</v>
+        <v>594</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46164.30208333334</v>
+        <v>46167.30208333334</v>
       </c>
       <c r="B30">
-        <v>575</v>
+        <v>537</v>
       </c>
       <c r="C30">
-        <v>1269</v>
+        <v>1396</v>
       </c>
       <c r="D30">
-        <v>1943.723848452748</v>
+        <v>1859.293557646947</v>
       </c>
       <c r="E30">
-        <v>1844</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46164.3125</v>
+        <v>46167.3125</v>
       </c>
       <c r="B31">
-        <v>566</v>
+        <v>504</v>
       </c>
       <c r="C31">
-        <v>1277</v>
+        <v>1342</v>
       </c>
       <c r="D31">
-        <v>1915.484648833607</v>
+        <v>1835.44123778663</v>
       </c>
       <c r="E31">
-        <v>1843</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46164.32291666666</v>
+        <v>46167.32291666666</v>
       </c>
       <c r="B32">
-        <v>569</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>1279</v>
+        <v>1336</v>
       </c>
       <c r="D32">
-        <v>1887.245449214467</v>
+        <v>1811.588917926313</v>
       </c>
       <c r="E32">
-        <v>1848</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46164.33333333334</v>
+        <v>46167.33333333334</v>
       </c>
       <c r="B33">
-        <v>638</v>
+        <v>505</v>
       </c>
       <c r="C33">
-        <v>1309</v>
+        <v>1346</v>
       </c>
       <c r="D33">
-        <v>1859.006249595326</v>
+        <v>1787.736598065996</v>
       </c>
       <c r="E33">
-        <v>1947</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46164.34375</v>
+        <v>46167.34375</v>
       </c>
       <c r="B34">
-        <v>543</v>
+        <v>235</v>
       </c>
       <c r="C34">
-        <v>1276</v>
+        <v>1288</v>
       </c>
       <c r="D34">
-        <v>1820.530712074455</v>
+        <v>1748.001729895232</v>
       </c>
       <c r="E34">
-        <v>1819</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46164.35416666666</v>
+        <v>46167.35416666666</v>
       </c>
       <c r="B35">
-        <v>541</v>
+        <v>203</v>
       </c>
       <c r="C35">
-        <v>1272</v>
+        <v>1282</v>
       </c>
       <c r="D35">
-        <v>1782.055174553584</v>
+        <v>1708.266861724468</v>
       </c>
       <c r="E35">
-        <v>1813</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46164.36458333334</v>
+        <v>46167.36458333334</v>
       </c>
       <c r="B36">
-        <v>492</v>
+        <v>198</v>
       </c>
       <c r="C36">
-        <v>1248</v>
+        <v>1278</v>
       </c>
       <c r="D36">
-        <v>1743.579637032712</v>
+        <v>1668.531993553704</v>
       </c>
       <c r="E36">
-        <v>1740</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46164.375</v>
+        <v>46167.375</v>
       </c>
       <c r="B37">
-        <v>478</v>
+        <v>195</v>
       </c>
       <c r="C37">
-        <v>1247</v>
+        <v>1279</v>
       </c>
       <c r="D37">
-        <v>1705.104099511841</v>
+        <v>1628.79712538294</v>
       </c>
       <c r="E37">
-        <v>1725</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46164.38541666666</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="B38">
-        <v>432</v>
+        <v>141</v>
       </c>
       <c r="C38">
-        <v>1202</v>
+        <v>1229</v>
       </c>
       <c r="D38">
-        <v>1654.864708549283</v>
+        <v>1594.647746689777</v>
       </c>
       <c r="E38">
-        <v>1634</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46164.39583333334</v>
+        <v>46167.39583333334</v>
       </c>
       <c r="B39">
-        <v>429</v>
+        <v>170</v>
       </c>
       <c r="C39">
-        <v>1197</v>
+        <v>1336</v>
       </c>
       <c r="D39">
-        <v>1604.625317586725</v>
+        <v>1560.498367996613</v>
       </c>
       <c r="E39">
-        <v>1626</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46164.40625</v>
+        <v>46167.40625</v>
       </c>
       <c r="B40">
-        <v>425</v>
+        <v>174</v>
       </c>
       <c r="C40">
-        <v>1182</v>
+        <v>1345</v>
       </c>
       <c r="D40">
-        <v>1554.385926624168</v>
+        <v>1526.348989303449</v>
       </c>
       <c r="E40">
-        <v>1607</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46164.41666666666</v>
+        <v>46167.41666666666</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="C41">
-        <v>1183</v>
+        <v>1237</v>
       </c>
       <c r="D41">
-        <v>1504.146535661611</v>
+        <v>1492.199610610286</v>
       </c>
       <c r="E41">
-        <v>1183</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46164.42708333334</v>
+        <v>46167.42708333334</v>
       </c>
       <c r="B42">
-        <v>413</v>
+        <v>107</v>
       </c>
       <c r="C42">
-        <v>1184</v>
+        <v>938</v>
       </c>
       <c r="D42">
-        <v>1481.035423925545</v>
+        <v>1455.466468077409</v>
       </c>
       <c r="E42">
-        <v>1597</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46164.4375</v>
+        <v>46167.4375</v>
       </c>
       <c r="B43">
-        <v>411</v>
+        <v>106</v>
       </c>
       <c r="C43">
-        <v>1185</v>
+        <v>894</v>
       </c>
       <c r="D43">
-        <v>1457.924312189479</v>
+        <v>1418.733325544533</v>
       </c>
       <c r="E43">
-        <v>1596</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46164.44791666666</v>
+        <v>46167.44791666666</v>
       </c>
       <c r="B44">
-        <v>414</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>1182</v>
+        <v>1028</v>
       </c>
       <c r="D44">
-        <v>1434.813200453413</v>
+        <v>1382.000183011656</v>
       </c>
       <c r="E44">
-        <v>1596</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46164.45833333334</v>
+        <v>46167.45833333334</v>
       </c>
       <c r="B45">
-        <v>411</v>
+        <v>103</v>
       </c>
       <c r="C45">
-        <v>1184</v>
+        <v>1037</v>
       </c>
       <c r="D45">
-        <v>1411.702088717347</v>
+        <v>1345.26704047878</v>
       </c>
       <c r="E45">
-        <v>1595</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46164.46875</v>
+        <v>46167.46875</v>
       </c>
       <c r="B46">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>1006</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>1414.757119796692</v>
+        <v>1336.166872248336</v>
       </c>
       <c r="E46">
-        <v>1230</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46164.47916666666</v>
+        <v>46167.47916666666</v>
       </c>
       <c r="B47">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>1011</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>1417.812150876037</v>
+        <v>1327.066704017893</v>
       </c>
       <c r="E47">
-        <v>1227</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46164.48958333334</v>
+        <v>46167.48958333334</v>
       </c>
       <c r="B48">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>1014</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>1420.867181955382</v>
+        <v>1317.966535787449</v>
       </c>
       <c r="E48">
-        <v>1208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46164.5</v>
+        <v>46167.5</v>
       </c>
       <c r="B49">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>1013</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>1423.922213034727</v>
+        <v>1308.866367557005</v>
       </c>
       <c r="E49">
-        <v>1205</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46164.51041666666</v>
+        <v>46167.51041666666</v>
       </c>
       <c r="B50">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>998</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>1452.578007800932</v>
+        <v>1317.662563570825</v>
       </c>
       <c r="E50">
-        <v>1181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46164.52083333334</v>
+        <v>46167.52083333334</v>
       </c>
       <c r="B51">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>1481.233802567137</v>
+        <v>1326.458759584645</v>
       </c>
       <c r="E51">
-        <v>1176</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46164.53125</v>
+        <v>46167.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>1509.889597333342</v>
+        <v>1335.254955598465</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46164.54166666666</v>
+        <v>46167.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>1538.545392099547</v>
+        <v>1344.051151612285</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46164.55208333334</v>
+        <v>46167.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>1539.269474141061</v>
+        <v>1349.342168005235</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46164.5625</v>
+        <v>46167.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1539.993556182575</v>
+        <v>1354.633184398185</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46164.57291666666</v>
+        <v>46167.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1540.717638224088</v>
+        <v>1359.924200791135</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46164.58333333334</v>
+        <v>46167.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>1541.441720265602</v>
+        <v>1365.215217184086</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46164.59375</v>
+        <v>46167.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>1533.94300761637</v>
+        <v>1377.364606710623</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46164.60416666666</v>
+        <v>46167.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1526.444294967138</v>
+        <v>1389.51399623716</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46164.61458333334</v>
+        <v>46167.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>1518.945582317906</v>
+        <v>1401.663385763698</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46164.625</v>
+        <v>46167.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1511.446869668674</v>
+        <v>1413.812775290235</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46164.63541666666</v>
+        <v>46167.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1576.29684757867</v>
+        <v>1466.589951373636</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46164.64583333334</v>
+        <v>46167.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1641.146825488665</v>
+        <v>1519.367127457036</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46164.65625</v>
+        <v>46167.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1705.996803398661</v>
+        <v>1572.144303540437</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46164.66666666666</v>
+        <v>46167.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>1770.846781308656</v>
+        <v>1624.921479623837</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46164.67708333334</v>
+        <v>46167.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>1900.695521109296</v>
+        <v>1747.783249864689</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46164.6875</v>
+        <v>46167.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>2030.544260909936</v>
+        <v>1870.645020105541</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46164.69791666666</v>
+        <v>46167.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>2160.393000710576</v>
+        <v>1993.506790346393</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46164.70833333334</v>
+        <v>46167.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>2290.241740511216</v>
+        <v>2116.368560587246</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46164.71875</v>
+        <v>46167.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>2396.106502553332</v>
+        <v>2242.849500030826</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46164.72916666666</v>
+        <v>46167.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>2501.971264595447</v>
+        <v>2369.330439474407</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46164.73958333334</v>
+        <v>46167.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>2607.836026637563</v>
+        <v>2495.811378917987</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46164.75</v>
+        <v>46167.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>2713.700788679678</v>
+        <v>2622.292318361568</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46164.76041666666</v>
+        <v>46167.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2735.691061091125</v>
+        <v>2641.176592309093</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46164.77083333334</v>
+        <v>46167.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2757.681333502571</v>
+        <v>2660.060866256618</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46164.78125</v>
+        <v>46167.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2779.671605914017</v>
+        <v>2678.945140204143</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46164.79166666666</v>
+        <v>46167.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2801.661878325464</v>
+        <v>2697.829414151668</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46164.80208333334</v>
+        <v>46167.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2801.721391917999</v>
+        <v>2697.981400259898</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46164.8125</v>
+        <v>46167.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2801.780905510533</v>
+        <v>2698.133386368129</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46164.82291666666</v>
+        <v>46167.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2801.840419103067</v>
+        <v>2698.28537247636</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46164.83333333334</v>
+        <v>46167.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2801.899932695602</v>
+        <v>2698.437358584591</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46164.84375</v>
+        <v>46167.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2757.22506262734</v>
+        <v>2662.844111863356</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46164.85416666666</v>
+        <v>46167.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2712.550192559079</v>
+        <v>2627.250865142121</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46164.86458333334</v>
+        <v>46167.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2667.875322490817</v>
+        <v>2591.657618420887</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46164.875</v>
+        <v>46167.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2623.200452422556</v>
+        <v>2556.064371699652</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46164.88541666666</v>
+        <v>46167.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2549.234975935408</v>
+        <v>2508.483220691626</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46164.89583333334</v>
+        <v>46167.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2475.26949944826</v>
+        <v>2460.902069683601</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46164.90625</v>
+        <v>46167.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2401.304022961112</v>
+        <v>2413.320918675576</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46164.91666666666</v>
+        <v>46167.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2327.338546473964</v>
+        <v>2365.73976766755</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46164.92708333334</v>
+        <v>46167.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>2262.617514681193</v>
+        <v>2308.08003785753</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46164.9375</v>
+        <v>46167.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>2197.896482888422</v>
+        <v>2250.420308047509</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46164.94791666666</v>
+        <v>46167.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>2133.175451095651</v>
+        <v>2192.760578237488</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46164.95833333334</v>
+        <v>46167.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>2068.454419302881</v>
+        <v>2135.100848427467</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46164.96875</v>
+        <v>46167.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>1984.373982760731</v>
+        <v>2063.584314844044</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46164.97916666666</v>
+        <v>46167.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>1900.293546218581</v>
+        <v>1992.067781260621</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46164.98958333334</v>
+        <v>46167.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1816.213109676431</v>
+        <v>1920.551247677198</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46165</v>
+        <v>46168</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1732.132673134282</v>
+        <v>1849.034714093775</v>
       </c>
       <c r="E97">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -412,118 +412,118 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46167.01041666666</v>
+        <v>46168.01041666666</v>
       </c>
       <c r="B2">
-        <v>489</v>
+        <v>671</v>
       </c>
       <c r="C2">
-        <v>1423</v>
+        <v>1290</v>
       </c>
       <c r="D2">
-        <v>1847.695117763087</v>
+        <v>1732.236030544386</v>
       </c>
       <c r="E2">
-        <v>1912</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46167.02083333334</v>
+        <v>46168.02083333334</v>
       </c>
       <c r="B3">
-        <v>499</v>
+        <v>669</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1824.59322931199</v>
+        <v>1712.11691281402</v>
       </c>
       <c r="E3">
-        <v>499</v>
+        <v>669</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46167.03125</v>
+        <v>46168.03125</v>
       </c>
       <c r="B4">
-        <v>483</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>1421</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1801.491340860892</v>
+        <v>1691.997795083655</v>
       </c>
       <c r="E4">
-        <v>1904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46167.04166666666</v>
+        <v>46168.04166666666</v>
       </c>
       <c r="B5">
-        <v>482</v>
+        <v>666</v>
       </c>
       <c r="C5">
-        <v>1420</v>
+        <v>1288</v>
       </c>
       <c r="D5">
-        <v>1778.389452409795</v>
+        <v>1671.878677353289</v>
       </c>
       <c r="E5">
-        <v>1902</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46167.05208333334</v>
+        <v>46168.05208333334</v>
       </c>
       <c r="B6">
-        <v>513</v>
+        <v>609</v>
       </c>
       <c r="C6">
-        <v>1376</v>
+        <v>1297</v>
       </c>
       <c r="D6">
-        <v>1771.911044546453</v>
+        <v>1665.128813384951</v>
       </c>
       <c r="E6">
-        <v>1889</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46167.0625</v>
+        <v>46168.0625</v>
       </c>
       <c r="B7">
-        <v>518</v>
+        <v>612</v>
       </c>
       <c r="C7">
-        <v>1371</v>
+        <v>1284</v>
       </c>
       <c r="D7">
-        <v>1765.432636683111</v>
+        <v>1658.378949416614</v>
       </c>
       <c r="E7">
-        <v>1889</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46167.07291666666</v>
+        <v>46168.07291666666</v>
       </c>
       <c r="B8">
-        <v>520</v>
+        <v>611</v>
       </c>
       <c r="C8">
-        <v>1373</v>
+        <v>1282</v>
       </c>
       <c r="D8">
-        <v>1758.954228819769</v>
+        <v>1651.629085448277</v>
       </c>
       <c r="E8">
         <v>1893</v>
@@ -531,636 +531,636 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46167.08333333334</v>
+        <v>46168.08333333334</v>
       </c>
       <c r="B9">
-        <v>512</v>
+        <v>612</v>
       </c>
       <c r="C9">
-        <v>1368</v>
+        <v>1281</v>
       </c>
       <c r="D9">
-        <v>1752.475820956427</v>
+        <v>1644.87922147994</v>
       </c>
       <c r="E9">
-        <v>1880</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46167.09375</v>
+        <v>46168.09375</v>
       </c>
       <c r="B10">
-        <v>475</v>
+        <v>594</v>
       </c>
       <c r="C10">
-        <v>1369</v>
+        <v>1286</v>
       </c>
       <c r="D10">
-        <v>1760.863554304151</v>
+        <v>1649.880731507696</v>
       </c>
       <c r="E10">
-        <v>1844</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46167.10416666666</v>
+        <v>46168.10416666666</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1284</v>
       </c>
       <c r="D11">
-        <v>1769.251287651874</v>
+        <v>1654.882241535451</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46167.11458333334</v>
+        <v>46168.11458333334</v>
       </c>
       <c r="B12">
-        <v>476</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>1363</v>
+        <v>1260</v>
       </c>
       <c r="D12">
-        <v>1777.639020999598</v>
+        <v>1659.883751563207</v>
       </c>
       <c r="E12">
-        <v>1839</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46167.125</v>
+        <v>46168.125</v>
       </c>
       <c r="B13">
-        <v>475</v>
+        <v>582</v>
       </c>
       <c r="C13">
-        <v>1326</v>
+        <v>1211</v>
       </c>
       <c r="D13">
-        <v>1786.026754347322</v>
+        <v>1664.885261590963</v>
       </c>
       <c r="E13">
-        <v>1801</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46167.13541666666</v>
+        <v>46168.13541666666</v>
       </c>
       <c r="B14">
-        <v>478</v>
+        <v>608</v>
       </c>
       <c r="C14">
-        <v>1361</v>
+        <v>1216</v>
       </c>
       <c r="D14">
-        <v>1795.098425182513</v>
+        <v>1673.305194994982</v>
       </c>
       <c r="E14">
-        <v>1839</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46167.14583333334</v>
+        <v>46168.14583333334</v>
       </c>
       <c r="B15">
-        <v>458</v>
+        <v>607</v>
       </c>
       <c r="C15">
-        <v>1362</v>
+        <v>1201</v>
       </c>
       <c r="D15">
-        <v>1804.170096017705</v>
+        <v>1681.725128399001</v>
       </c>
       <c r="E15">
-        <v>1820</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46167.15625</v>
+        <v>46168.15625</v>
       </c>
       <c r="B16">
-        <v>440</v>
+        <v>609</v>
       </c>
       <c r="C16">
-        <v>1363</v>
+        <v>1196</v>
       </c>
       <c r="D16">
-        <v>1813.241766852896</v>
+        <v>1690.145061803021</v>
       </c>
       <c r="E16">
-        <v>1803</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46167.16666666666</v>
+        <v>46168.16666666666</v>
       </c>
       <c r="B17">
-        <v>479</v>
+        <v>630</v>
       </c>
       <c r="C17">
-        <v>1364</v>
+        <v>1204</v>
       </c>
       <c r="D17">
-        <v>1822.313437688087</v>
+        <v>1698.56499520704</v>
       </c>
       <c r="E17">
-        <v>1843</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46167.17708333334</v>
+        <v>46168.17708333334</v>
       </c>
       <c r="B18">
-        <v>493</v>
+        <v>674</v>
       </c>
       <c r="C18">
-        <v>1395</v>
+        <v>1207</v>
       </c>
       <c r="D18">
-        <v>1844.902373023842</v>
+        <v>1718.710207772212</v>
       </c>
       <c r="E18">
-        <v>1888</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46167.1875</v>
+        <v>46168.1875</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>534</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>1867.491308359597</v>
+        <v>1738.855420337385</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>534</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46167.19791666666</v>
+        <v>46168.19791666666</v>
       </c>
       <c r="B20">
-        <v>492</v>
+        <v>519</v>
       </c>
       <c r="C20">
-        <v>1397</v>
+        <v>1205</v>
       </c>
       <c r="D20">
-        <v>1890.080243695352</v>
+        <v>1759.000632902557</v>
       </c>
       <c r="E20">
-        <v>1889</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46167.20833333334</v>
+        <v>46168.20833333334</v>
       </c>
       <c r="B21">
-        <v>501</v>
+        <v>533</v>
       </c>
       <c r="C21">
-        <v>1421</v>
+        <v>1204</v>
       </c>
       <c r="D21">
-        <v>1912.669179031107</v>
+        <v>1779.145845467729</v>
       </c>
       <c r="E21">
-        <v>1922</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46167.21875</v>
+        <v>46168.21875</v>
       </c>
       <c r="B22">
-        <v>525</v>
+        <v>570</v>
       </c>
       <c r="C22">
-        <v>1420</v>
+        <v>1238</v>
       </c>
       <c r="D22">
-        <v>1929.292659618975</v>
+        <v>1796.551100365456</v>
       </c>
       <c r="E22">
-        <v>1945</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46167.22916666666</v>
+        <v>46168.22916666666</v>
       </c>
       <c r="B23">
-        <v>517</v>
+        <v>581</v>
       </c>
       <c r="C23">
-        <v>1422</v>
+        <v>1239</v>
       </c>
       <c r="D23">
-        <v>1945.916140206843</v>
+        <v>1813.956355263182</v>
       </c>
       <c r="E23">
-        <v>1939</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46167.23958333334</v>
+        <v>46168.23958333334</v>
       </c>
       <c r="B24">
-        <v>514</v>
+        <v>723</v>
       </c>
       <c r="C24">
-        <v>1424</v>
+        <v>1264</v>
       </c>
       <c r="D24">
-        <v>1962.539620794712</v>
+        <v>1831.361610160908</v>
       </c>
       <c r="E24">
-        <v>1938</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46167.25</v>
+        <v>46168.25</v>
       </c>
       <c r="B25">
-        <v>528</v>
+        <v>735</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1265</v>
       </c>
       <c r="D25">
-        <v>1979.16310138258</v>
+        <v>1848.766865058634</v>
       </c>
       <c r="E25">
-        <v>528</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46167.26041666666</v>
+        <v>46168.26041666666</v>
       </c>
       <c r="B26">
-        <v>614</v>
+        <v>709</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1287</v>
       </c>
       <c r="D26">
-        <v>1955.158795413751</v>
+        <v>1824.002866710895</v>
       </c>
       <c r="E26">
-        <v>614</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46167.27083333334</v>
+        <v>46168.27083333334</v>
       </c>
       <c r="B27">
-        <v>619</v>
+        <v>706</v>
       </c>
       <c r="C27">
-        <v>1428</v>
+        <v>1291</v>
       </c>
       <c r="D27">
-        <v>1931.154489444922</v>
+        <v>1799.238868363155</v>
       </c>
       <c r="E27">
-        <v>2047</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46167.28125</v>
+        <v>46168.28125</v>
       </c>
       <c r="B28">
-        <v>609</v>
+        <v>708</v>
       </c>
       <c r="C28">
-        <v>1426</v>
+        <v>1298</v>
       </c>
       <c r="D28">
-        <v>1907.150183476093</v>
+        <v>1774.474870015415</v>
       </c>
       <c r="E28">
-        <v>2035</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46167.29166666666</v>
+        <v>46168.29166666666</v>
       </c>
       <c r="B29">
-        <v>594</v>
+        <v>712</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1296</v>
       </c>
       <c r="D29">
-        <v>1883.145877507264</v>
+        <v>1749.710871667676</v>
       </c>
       <c r="E29">
-        <v>594</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46167.30208333334</v>
+        <v>46168.30208333334</v>
       </c>
       <c r="B30">
-        <v>537</v>
+        <v>655</v>
       </c>
       <c r="C30">
-        <v>1396</v>
+        <v>1254</v>
       </c>
       <c r="D30">
-        <v>1859.293557646947</v>
+        <v>1715.317879231408</v>
       </c>
       <c r="E30">
-        <v>1933</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46167.3125</v>
+        <v>46168.3125</v>
       </c>
       <c r="B31">
-        <v>504</v>
+        <v>658</v>
       </c>
       <c r="C31">
-        <v>1342</v>
+        <v>1255</v>
       </c>
       <c r="D31">
-        <v>1835.44123778663</v>
+        <v>1680.924886795141</v>
       </c>
       <c r="E31">
-        <v>1846</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46167.32291666666</v>
+        <v>46168.32291666666</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>681</v>
       </c>
       <c r="C32">
-        <v>1336</v>
+        <v>1266</v>
       </c>
       <c r="D32">
-        <v>1811.588917926313</v>
+        <v>1646.531894358874</v>
       </c>
       <c r="E32">
-        <v>1336</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46167.33333333334</v>
+        <v>46168.33333333334</v>
       </c>
       <c r="B33">
-        <v>505</v>
+        <v>668</v>
       </c>
       <c r="C33">
-        <v>1346</v>
+        <v>1293</v>
       </c>
       <c r="D33">
-        <v>1787.736598065996</v>
+        <v>1612.138901922606</v>
       </c>
       <c r="E33">
-        <v>1851</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46167.34375</v>
+        <v>46168.34375</v>
       </c>
       <c r="B34">
-        <v>235</v>
+        <v>410</v>
       </c>
       <c r="C34">
-        <v>1288</v>
+        <v>1278</v>
       </c>
       <c r="D34">
-        <v>1748.001729895232</v>
+        <v>1573.675115236661</v>
       </c>
       <c r="E34">
-        <v>1523</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46167.35416666666</v>
+        <v>46168.35416666666</v>
       </c>
       <c r="B35">
-        <v>203</v>
+        <v>402</v>
       </c>
       <c r="C35">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D35">
-        <v>1708.266861724468</v>
+        <v>1535.211328550716</v>
       </c>
       <c r="E35">
-        <v>1485</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46167.36458333334</v>
+        <v>46168.36458333334</v>
       </c>
       <c r="B36">
-        <v>198</v>
+        <v>408</v>
       </c>
       <c r="C36">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="D36">
-        <v>1668.531993553704</v>
+        <v>1496.747541864771</v>
       </c>
       <c r="E36">
-        <v>1476</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46167.375</v>
+        <v>46168.375</v>
       </c>
       <c r="B37">
-        <v>195</v>
+        <v>407</v>
       </c>
       <c r="C37">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="D37">
-        <v>1628.79712538294</v>
+        <v>1458.283755178826</v>
       </c>
       <c r="E37">
-        <v>1474</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46167.38541666666</v>
+        <v>46168.38541666666</v>
       </c>
       <c r="B38">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>1229</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>1594.647746689777</v>
+        <v>1411.965423179726</v>
       </c>
       <c r="E38">
-        <v>1370</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46167.39583333334</v>
+        <v>46168.39583333334</v>
       </c>
       <c r="B39">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>1336</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>1560.498367996613</v>
+        <v>1365.647091180625</v>
       </c>
       <c r="E39">
-        <v>1506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46167.40625</v>
+        <v>46168.40625</v>
       </c>
       <c r="B40">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>1345</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>1526.348989303449</v>
+        <v>1319.328759181525</v>
       </c>
       <c r="E40">
-        <v>1519</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46167.41666666666</v>
+        <v>46168.41666666666</v>
       </c>
       <c r="B41">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>1237</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>1492.199610610286</v>
+        <v>1273.010427182425</v>
       </c>
       <c r="E41">
-        <v>1410</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46167.42708333334</v>
+        <v>46168.42708333334</v>
       </c>
       <c r="B42">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>938</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>1455.466468077409</v>
+        <v>1246.158842040355</v>
       </c>
       <c r="E42">
-        <v>1045</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46167.4375</v>
+        <v>46168.4375</v>
       </c>
       <c r="B43">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>894</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>1418.733325544533</v>
+        <v>1219.307256898286</v>
       </c>
       <c r="E43">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46167.44791666666</v>
+        <v>46168.44791666666</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44">
-        <v>1028</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>1382.000183011656</v>
+        <v>1192.455671756216</v>
       </c>
       <c r="E44">
-        <v>1028</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46167.45833333334</v>
+        <v>46168.45833333334</v>
       </c>
       <c r="B45">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>1037</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>1345.26704047878</v>
+        <v>1165.604086614147</v>
       </c>
       <c r="E45">
-        <v>1140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46167.46875</v>
+        <v>46168.46875</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1169,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>1336.166872248336</v>
+        <v>1165.073491637408</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46167.47916666666</v>
+        <v>46168.47916666666</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>1327.066704017893</v>
+        <v>1164.542896660669</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46167.48958333334</v>
+        <v>46168.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>1317.966535787449</v>
+        <v>1164.01230168393</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46167.5</v>
+        <v>46168.5</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>1308.866367557005</v>
+        <v>1163.481706707192</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46167.51041666666</v>
+        <v>46168.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>1317.662563570825</v>
+        <v>1175.05911513734</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46167.52083333334</v>
+        <v>46168.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>1326.458759584645</v>
+        <v>1186.636523567488</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46167.53125</v>
+        <v>46168.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>1335.254955598465</v>
+        <v>1198.213931997636</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46167.54166666666</v>
+        <v>46168.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>1344.051151612285</v>
+        <v>1209.791340427784</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46167.55208333334</v>
+        <v>46168.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>1349.342168005235</v>
+        <v>1217.237066660733</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46167.5625</v>
+        <v>46168.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1354.633184398185</v>
+        <v>1224.682792893681</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46167.57291666666</v>
+        <v>46168.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1359.924200791135</v>
+        <v>1232.12851912663</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46167.58333333334</v>
+        <v>46168.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>1365.215217184086</v>
+        <v>1239.574245359579</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46167.59375</v>
+        <v>46168.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>1377.364606710623</v>
+        <v>1248.324713339311</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46167.60416666666</v>
+        <v>46168.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1389.51399623716</v>
+        <v>1257.075181319044</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46167.61458333334</v>
+        <v>46168.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>1401.663385763698</v>
+        <v>1265.825649298776</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46167.625</v>
+        <v>46168.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1413.812775290235</v>
+        <v>1274.576117278508</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46167.63541666666</v>
+        <v>46168.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1466.589951373636</v>
+        <v>1321.72078571714</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46167.64583333334</v>
+        <v>46168.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1519.367127457036</v>
+        <v>1368.865454155771</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46167.65625</v>
+        <v>46168.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1572.144303540437</v>
+        <v>1416.010122594402</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46167.66666666666</v>
+        <v>46168.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>1624.921479623837</v>
+        <v>1463.154791033033</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46167.67708333334</v>
+        <v>46168.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>1747.783249864689</v>
+        <v>1574.179615377801</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46167.6875</v>
+        <v>46168.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>1870.645020105541</v>
+        <v>1685.20443972257</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46167.69791666666</v>
+        <v>46168.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>1993.506790346393</v>
+        <v>1796.229264067338</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46167.70833333334</v>
+        <v>46168.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>2116.368560587246</v>
+        <v>1907.254088412107</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46167.71875</v>
+        <v>46168.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>2242.849500030826</v>
+        <v>2028.595070833104</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46167.72916666666</v>
+        <v>46168.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>2369.330439474407</v>
+        <v>2149.936053254101</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46167.73958333334</v>
+        <v>46168.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>2495.811378917987</v>
+        <v>2271.277035675099</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46167.75</v>
+        <v>46168.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>2622.292318361568</v>
+        <v>2392.618018096096</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46167.76041666666</v>
+        <v>46168.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2641.176592309093</v>
+        <v>2410.675643866897</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46167.77083333334</v>
+        <v>46168.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2660.060866256618</v>
+        <v>2428.733269637699</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46167.78125</v>
+        <v>46168.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2678.945140204143</v>
+        <v>2446.7908954085</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46167.79166666666</v>
+        <v>46168.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2697.829414151668</v>
+        <v>2464.848521179301</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46167.80208333334</v>
+        <v>46168.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2697.981400259898</v>
+        <v>2466.744745850655</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46167.8125</v>
+        <v>46168.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2698.133386368129</v>
+        <v>2468.640970522009</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46167.82291666666</v>
+        <v>46168.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2698.28537247636</v>
+        <v>2470.537195193363</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46167.83333333334</v>
+        <v>46168.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2698.437358584591</v>
+        <v>2472.433419864718</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46167.84375</v>
+        <v>46168.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2662.844111863356</v>
+        <v>2440.336772902048</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46167.85416666666</v>
+        <v>46168.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2627.250865142121</v>
+        <v>2408.240125939379</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46167.86458333334</v>
+        <v>46168.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2591.657618420887</v>
+        <v>2376.14347897671</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46167.875</v>
+        <v>46168.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2556.064371699652</v>
+        <v>2344.046832014041</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46167.88541666666</v>
+        <v>46168.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2508.483220691626</v>
+        <v>2301.077337163928</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46167.89583333334</v>
+        <v>46168.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2460.902069683601</v>
+        <v>2258.107842313815</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46167.90625</v>
+        <v>46168.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2413.320918675576</v>
+        <v>2215.138347463701</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46167.91666666666</v>
+        <v>46168.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2365.73976766755</v>
+        <v>2172.168852613588</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46167.92708333334</v>
+        <v>46168.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>2308.08003785753</v>
+        <v>2119.674743014757</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46167.9375</v>
+        <v>46168.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>2250.420308047509</v>
+        <v>2067.180633415926</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46167.94791666666</v>
+        <v>46168.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>2192.760578237488</v>
+        <v>2014.686523817096</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46167.95833333334</v>
+        <v>46168.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>2135.100848427467</v>
+        <v>1962.192414218265</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46167.96875</v>
+        <v>46168.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>2063.584314844044</v>
+        <v>1932.564560401434</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46167.97916666666</v>
+        <v>46168.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>1992.067781260621</v>
+        <v>1902.936706584602</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46167.98958333334</v>
+        <v>46168.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1920.551247677198</v>
+        <v>1873.308852767771</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1849.034714093775</v>
+        <v>1843.680998950939</v>
       </c>
       <c r="E97">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -412,577 +412,577 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46168.01041666666</v>
+        <v>46185.01041666666</v>
       </c>
       <c r="B2">
-        <v>671</v>
+        <v>455</v>
       </c>
       <c r="C2">
-        <v>1290</v>
+        <v>1048</v>
       </c>
       <c r="D2">
-        <v>1732.236030544386</v>
+        <v>1355.996445995879</v>
       </c>
       <c r="E2">
-        <v>1961</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46168.02083333334</v>
+        <v>46185.02083333334</v>
       </c>
       <c r="B3">
-        <v>669</v>
+        <v>462</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1031</v>
       </c>
       <c r="D3">
-        <v>1712.11691281402</v>
+        <v>1350.51285952239</v>
       </c>
       <c r="E3">
-        <v>669</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46168.03125</v>
+        <v>46185.03125</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1027</v>
       </c>
       <c r="D4">
-        <v>1691.997795083655</v>
+        <v>1345.0292730489</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46168.04166666666</v>
+        <v>46185.04166666666</v>
       </c>
       <c r="B5">
-        <v>666</v>
+        <v>460</v>
       </c>
       <c r="C5">
-        <v>1288</v>
+        <v>1029</v>
       </c>
       <c r="D5">
-        <v>1671.878677353289</v>
+        <v>1339.545686575411</v>
       </c>
       <c r="E5">
-        <v>1954</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46168.05208333334</v>
+        <v>46185.05208333334</v>
       </c>
       <c r="B6">
-        <v>609</v>
+        <v>444</v>
       </c>
       <c r="C6">
-        <v>1297</v>
+        <v>1032</v>
       </c>
       <c r="D6">
-        <v>1665.128813384951</v>
+        <v>1336.743323532258</v>
       </c>
       <c r="E6">
-        <v>1906</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46168.0625</v>
+        <v>46185.0625</v>
       </c>
       <c r="B7">
-        <v>612</v>
+        <v>442</v>
       </c>
       <c r="C7">
-        <v>1284</v>
+        <v>1037</v>
       </c>
       <c r="D7">
-        <v>1658.378949416614</v>
+        <v>1333.940960489105</v>
       </c>
       <c r="E7">
-        <v>1896</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46168.07291666666</v>
+        <v>46185.07291666666</v>
       </c>
       <c r="B8">
-        <v>611</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1282</v>
+        <v>1036</v>
       </c>
       <c r="D8">
-        <v>1651.629085448277</v>
+        <v>1331.138597445953</v>
       </c>
       <c r="E8">
-        <v>1893</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46168.08333333334</v>
+        <v>46185.08333333334</v>
       </c>
       <c r="B9">
-        <v>612</v>
+        <v>444</v>
       </c>
       <c r="C9">
-        <v>1281</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1644.87922147994</v>
+        <v>1328.3362344028</v>
       </c>
       <c r="E9">
-        <v>1893</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46168.09375</v>
+        <v>46185.09375</v>
       </c>
       <c r="B10">
-        <v>594</v>
+        <v>434</v>
       </c>
       <c r="C10">
-        <v>1286</v>
+        <v>1039</v>
       </c>
       <c r="D10">
-        <v>1649.880731507696</v>
+        <v>1329.34573117627</v>
       </c>
       <c r="E10">
-        <v>1880</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46168.10416666666</v>
+        <v>46185.10416666666</v>
       </c>
       <c r="B11">
-        <v>593</v>
+        <v>429</v>
       </c>
       <c r="C11">
-        <v>1284</v>
+        <v>1036</v>
       </c>
       <c r="D11">
-        <v>1654.882241535451</v>
+        <v>1330.35522794974</v>
       </c>
       <c r="E11">
-        <v>1877</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46168.11458333334</v>
+        <v>46185.11458333334</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>435</v>
       </c>
       <c r="C12">
-        <v>1260</v>
+        <v>1038</v>
       </c>
       <c r="D12">
-        <v>1659.883751563207</v>
+        <v>1331.36472472321</v>
       </c>
       <c r="E12">
-        <v>1260</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46168.125</v>
+        <v>46185.125</v>
       </c>
       <c r="B13">
-        <v>582</v>
+        <v>438</v>
       </c>
       <c r="C13">
-        <v>1211</v>
+        <v>1037</v>
       </c>
       <c r="D13">
-        <v>1664.885261590963</v>
+        <v>1332.37422149668</v>
       </c>
       <c r="E13">
-        <v>1793</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46168.13541666666</v>
+        <v>46185.13541666666</v>
       </c>
       <c r="B14">
-        <v>608</v>
+        <v>443</v>
       </c>
       <c r="C14">
-        <v>1216</v>
+        <v>1045</v>
       </c>
       <c r="D14">
-        <v>1673.305194994982</v>
+        <v>1338.301986550601</v>
       </c>
       <c r="E14">
-        <v>1824</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46168.14583333334</v>
+        <v>46185.14583333334</v>
       </c>
       <c r="B15">
-        <v>607</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>1201</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>1681.725128399001</v>
+        <v>1344.229751604521</v>
       </c>
       <c r="E15">
-        <v>1808</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46168.15625</v>
+        <v>46185.15625</v>
       </c>
       <c r="B16">
-        <v>609</v>
+        <v>445</v>
       </c>
       <c r="C16">
-        <v>1196</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>1690.145061803021</v>
+        <v>1350.157516658442</v>
       </c>
       <c r="E16">
-        <v>1805</v>
+        <v>445</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46168.16666666666</v>
+        <v>46185.16666666666</v>
       </c>
       <c r="B17">
-        <v>630</v>
+        <v>450</v>
       </c>
       <c r="C17">
-        <v>1204</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>1698.56499520704</v>
+        <v>1356.085281712363</v>
       </c>
       <c r="E17">
-        <v>1834</v>
+        <v>450</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46168.17708333334</v>
+        <v>46185.17708333334</v>
       </c>
       <c r="B18">
-        <v>674</v>
+        <v>478</v>
       </c>
       <c r="C18">
-        <v>1207</v>
+        <v>1041</v>
       </c>
       <c r="D18">
-        <v>1718.710207772212</v>
+        <v>1363.88667277742</v>
       </c>
       <c r="E18">
-        <v>1881</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46168.1875</v>
+        <v>46185.1875</v>
       </c>
       <c r="B19">
-        <v>534</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="D19">
-        <v>1738.855420337385</v>
+        <v>1371.688063842478</v>
       </c>
       <c r="E19">
-        <v>534</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46168.19791666666</v>
+        <v>46185.19791666666</v>
       </c>
       <c r="B20">
-        <v>519</v>
+        <v>475</v>
       </c>
       <c r="C20">
-        <v>1205</v>
+        <v>1039</v>
       </c>
       <c r="D20">
-        <v>1759.000632902557</v>
+        <v>1379.489454907535</v>
       </c>
       <c r="E20">
-        <v>1724</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46168.20833333334</v>
+        <v>46185.20833333334</v>
       </c>
       <c r="B21">
-        <v>533</v>
+        <v>484</v>
       </c>
       <c r="C21">
-        <v>1204</v>
+        <v>1041</v>
       </c>
       <c r="D21">
-        <v>1779.145845467729</v>
+        <v>1387.290845972592</v>
       </c>
       <c r="E21">
-        <v>1737</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46168.21875</v>
+        <v>46185.21875</v>
       </c>
       <c r="B22">
-        <v>570</v>
+        <v>545</v>
       </c>
       <c r="C22">
-        <v>1238</v>
+        <v>1046</v>
       </c>
       <c r="D22">
-        <v>1796.551100365456</v>
+        <v>1402.239474194462</v>
       </c>
       <c r="E22">
-        <v>1808</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46168.22916666666</v>
+        <v>46185.22916666666</v>
       </c>
       <c r="B23">
-        <v>581</v>
+        <v>548</v>
       </c>
       <c r="C23">
-        <v>1239</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>1813.956355263182</v>
+        <v>1417.188102416333</v>
       </c>
       <c r="E23">
-        <v>1820</v>
+        <v>548</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46168.23958333334</v>
+        <v>46185.23958333334</v>
       </c>
       <c r="B24">
-        <v>723</v>
+        <v>550</v>
       </c>
       <c r="C24">
-        <v>1264</v>
+        <v>1042</v>
       </c>
       <c r="D24">
-        <v>1831.361610160908</v>
+        <v>1432.136730638203</v>
       </c>
       <c r="E24">
-        <v>1987</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46168.25</v>
+        <v>46185.25</v>
       </c>
       <c r="B25">
-        <v>735</v>
+        <v>580</v>
       </c>
       <c r="C25">
-        <v>1265</v>
+        <v>1043</v>
       </c>
       <c r="D25">
-        <v>1848.766865058634</v>
+        <v>1447.085358860073</v>
       </c>
       <c r="E25">
-        <v>2000</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46168.26041666666</v>
+        <v>46185.26041666666</v>
       </c>
       <c r="B26">
-        <v>709</v>
+        <v>661</v>
       </c>
       <c r="C26">
-        <v>1287</v>
+        <v>1056</v>
       </c>
       <c r="D26">
-        <v>1824.002866710895</v>
+        <v>1443.103903585506</v>
       </c>
       <c r="E26">
-        <v>1996</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46168.27083333334</v>
+        <v>46185.27083333334</v>
       </c>
       <c r="B27">
-        <v>706</v>
+        <v>654</v>
       </c>
       <c r="C27">
-        <v>1291</v>
+        <v>1058</v>
       </c>
       <c r="D27">
-        <v>1799.238868363155</v>
+        <v>1439.122448310939</v>
       </c>
       <c r="E27">
-        <v>1997</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46168.28125</v>
+        <v>46185.28125</v>
       </c>
       <c r="B28">
-        <v>708</v>
+        <v>655</v>
       </c>
       <c r="C28">
-        <v>1298</v>
+        <v>1056</v>
       </c>
       <c r="D28">
-        <v>1774.474870015415</v>
+        <v>1435.140993036372</v>
       </c>
       <c r="E28">
-        <v>2006</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46168.29166666666</v>
+        <v>46185.29166666666</v>
       </c>
       <c r="B29">
-        <v>712</v>
+        <v>657</v>
       </c>
       <c r="C29">
-        <v>1296</v>
+        <v>1057</v>
       </c>
       <c r="D29">
-        <v>1749.710871667676</v>
+        <v>1431.159537761805</v>
       </c>
       <c r="E29">
-        <v>2008</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46168.30208333334</v>
+        <v>46185.30208333334</v>
       </c>
       <c r="B30">
-        <v>655</v>
+        <v>678</v>
       </c>
       <c r="C30">
-        <v>1254</v>
+        <v>1058</v>
       </c>
       <c r="D30">
-        <v>1715.317879231408</v>
+        <v>1419.691654414968</v>
       </c>
       <c r="E30">
-        <v>1909</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46168.3125</v>
+        <v>46185.3125</v>
       </c>
       <c r="B31">
-        <v>658</v>
+        <v>680</v>
       </c>
       <c r="C31">
-        <v>1255</v>
+        <v>1061</v>
       </c>
       <c r="D31">
-        <v>1680.924886795141</v>
+        <v>1408.223771068131</v>
       </c>
       <c r="E31">
-        <v>1913</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46168.32291666666</v>
+        <v>46185.32291666666</v>
       </c>
       <c r="B32">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="C32">
-        <v>1266</v>
+        <v>1052</v>
       </c>
       <c r="D32">
-        <v>1646.531894358874</v>
+        <v>1396.755887721294</v>
       </c>
       <c r="E32">
-        <v>1947</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46168.33333333334</v>
+        <v>46185.33333333334</v>
       </c>
       <c r="B33">
-        <v>668</v>
+        <v>681</v>
       </c>
       <c r="C33">
-        <v>1293</v>
+        <v>1042</v>
       </c>
       <c r="D33">
-        <v>1612.138901922606</v>
+        <v>1385.288004374457</v>
       </c>
       <c r="E33">
-        <v>1961</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46168.34375</v>
+        <v>46185.34375</v>
       </c>
       <c r="B34">
-        <v>410</v>
+        <v>640</v>
       </c>
       <c r="C34">
-        <v>1278</v>
+        <v>1043</v>
       </c>
       <c r="D34">
-        <v>1573.675115236661</v>
+        <v>1363.385962377358</v>
       </c>
       <c r="E34">
-        <v>1688</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46168.35416666666</v>
+        <v>46185.35416666666</v>
       </c>
       <c r="B35">
-        <v>402</v>
+        <v>629</v>
       </c>
       <c r="C35">
-        <v>1277</v>
+        <v>1050</v>
       </c>
       <c r="D35">
-        <v>1535.211328550716</v>
+        <v>1341.483920380259</v>
       </c>
       <c r="E35">
         <v>1679</v>
@@ -990,330 +990,330 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46168.36458333334</v>
+        <v>46185.36458333334</v>
       </c>
       <c r="B36">
-        <v>408</v>
+        <v>633</v>
       </c>
       <c r="C36">
-        <v>1275</v>
+        <v>1054</v>
       </c>
       <c r="D36">
-        <v>1496.747541864771</v>
+        <v>1319.581878383161</v>
       </c>
       <c r="E36">
-        <v>1683</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46168.375</v>
+        <v>46185.375</v>
       </c>
       <c r="B37">
-        <v>407</v>
+        <v>654</v>
       </c>
       <c r="C37">
-        <v>1276</v>
+        <v>1051</v>
       </c>
       <c r="D37">
-        <v>1458.283755178826</v>
+        <v>1297.679836386062</v>
       </c>
       <c r="E37">
-        <v>1683</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46168.38541666666</v>
+        <v>46185.38541666666</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>757</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="D38">
-        <v>1411.965423179726</v>
+        <v>1267.532224743244</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46168.39583333334</v>
+        <v>46185.39583333334</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>746</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>938</v>
       </c>
       <c r="D39">
-        <v>1365.647091180625</v>
+        <v>1237.384613100426</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46168.40625</v>
+        <v>46185.40625</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>866</v>
       </c>
       <c r="D40">
-        <v>1319.328759181525</v>
+        <v>1207.237001457608</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46168.41666666666</v>
+        <v>46185.41666666666</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>756</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>839</v>
       </c>
       <c r="D41">
-        <v>1273.010427182425</v>
+        <v>1177.08938981479</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46168.42708333334</v>
+        <v>46185.42708333334</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>755</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>802</v>
       </c>
       <c r="D42">
-        <v>1246.158842040355</v>
+        <v>1157.828191376806</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46168.4375</v>
+        <v>46185.4375</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>749</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="D43">
-        <v>1219.307256898286</v>
+        <v>1138.566992938822</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46168.44791666666</v>
+        <v>46185.44791666666</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>827</v>
       </c>
       <c r="D44">
-        <v>1192.455671756216</v>
+        <v>1119.305794500838</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46168.45833333334</v>
+        <v>46185.45833333334</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>733</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="D45">
-        <v>1165.604086614147</v>
+        <v>1100.044596062854</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46168.46875</v>
+        <v>46185.46875</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>734</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="D46">
-        <v>1165.073491637408</v>
+        <v>1094.674073228079</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46168.47916666666</v>
+        <v>46185.47916666666</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>719</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="D47">
-        <v>1164.542896660669</v>
+        <v>1089.303550393303</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46168.48958333334</v>
+        <v>46185.48958333334</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>716</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>829</v>
       </c>
       <c r="D48">
-        <v>1164.01230168393</v>
+        <v>1083.933027558528</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46168.5</v>
+        <v>46185.5</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>730</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>827</v>
       </c>
       <c r="D49">
-        <v>1163.481706707192</v>
+        <v>1078.562504723752</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46168.51041666666</v>
+        <v>46185.51041666666</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>685</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="D50">
-        <v>1175.05911513734</v>
+        <v>1081.009524902643</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46168.52083333334</v>
+        <v>46185.52083333334</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>675</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>877</v>
       </c>
       <c r="D51">
-        <v>1186.636523567488</v>
+        <v>1083.456545081535</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46168.53125</v>
+        <v>46185.53125</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52">
-        <v>1198.213931997636</v>
+        <v>1085.903565260426</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>678</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46168.54166666666</v>
+        <v>46185.54166666666</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53">
-        <v>1209.791340427784</v>
+        <v>1088.350585439317</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>673</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46168.55208333334</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>652</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="D54">
-        <v>1217.237066660733</v>
+        <v>1094.827516737815</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46168.5625</v>
+        <v>46185.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1224.682792893681</v>
+        <v>1101.304448036313</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46168.57291666666</v>
+        <v>46185.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1232.12851912663</v>
+        <v>1107.78137933481</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46168.58333333334</v>
+        <v>46185.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>1239.574245359579</v>
+        <v>1114.258310633308</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46168.59375</v>
+        <v>46185.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>1248.324713339311</v>
+        <v>1150.422523046282</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46168.60416666666</v>
+        <v>46185.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1257.075181319044</v>
+        <v>1186.586735459255</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46168.61458333334</v>
+        <v>46185.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>1265.825649298776</v>
+        <v>1222.750947872229</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46168.625</v>
+        <v>46185.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1274.576117278508</v>
+        <v>1258.915160285202</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46168.63541666666</v>
+        <v>46185.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1321.72078571714</v>
+        <v>1291.469412235859</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46168.64583333334</v>
+        <v>46185.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1368.865454155771</v>
+        <v>1324.023664186516</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46168.65625</v>
+        <v>46185.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1416.010122594402</v>
+        <v>1356.577916137173</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46168.66666666666</v>
+        <v>46185.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>1463.154791033033</v>
+        <v>1389.13216808783</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46168.67708333334</v>
+        <v>46185.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>1574.179615377801</v>
+        <v>1474.293315897868</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46168.6875</v>
+        <v>46185.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>1685.20443972257</v>
+        <v>1559.454463707907</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46168.69791666666</v>
+        <v>46185.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>1796.229264067338</v>
+        <v>1644.615611517946</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46168.70833333334</v>
+        <v>46185.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>1907.254088412107</v>
+        <v>1729.776759327985</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46168.71875</v>
+        <v>46185.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>2028.595070833104</v>
+        <v>1803.365036127012</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46168.72916666666</v>
+        <v>46185.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>2149.936053254101</v>
+        <v>1876.953312926039</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46168.73958333334</v>
+        <v>46185.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>2271.277035675099</v>
+        <v>1950.541589725067</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46168.75</v>
+        <v>46185.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>2392.618018096096</v>
+        <v>2024.129866524094</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46168.76041666666</v>
+        <v>46185.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2410.675643866897</v>
+        <v>2063.298341334575</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46168.77083333334</v>
+        <v>46185.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2428.733269637699</v>
+        <v>2102.466816145055</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46168.78125</v>
+        <v>46185.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2446.7908954085</v>
+        <v>2141.635290955536</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46168.79166666666</v>
+        <v>46185.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2464.848521179301</v>
+        <v>2180.803765766017</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46168.80208333334</v>
+        <v>46185.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2466.744745850655</v>
+        <v>2176.240840349765</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46168.8125</v>
+        <v>46185.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2468.640970522009</v>
+        <v>2171.677914933513</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46168.82291666666</v>
+        <v>46185.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2470.537195193363</v>
+        <v>2167.114989517262</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46168.83333333334</v>
+        <v>46185.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2472.433419864718</v>
+        <v>2162.55206410101</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46168.84375</v>
+        <v>46185.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2440.336772902048</v>
+        <v>2133.769292095842</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46168.85416666666</v>
+        <v>46185.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2408.240125939379</v>
+        <v>2104.986520090673</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46168.86458333334</v>
+        <v>46185.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2376.14347897671</v>
+        <v>2076.203748085505</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46168.875</v>
+        <v>46185.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2344.046832014041</v>
+        <v>2047.420976080336</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46168.88541666666</v>
+        <v>46185.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2301.077337163928</v>
+        <v>1998.973206928264</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46168.89583333334</v>
+        <v>46185.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2258.107842313815</v>
+        <v>1950.525437776192</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46168.90625</v>
+        <v>46185.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2215.138347463701</v>
+        <v>1902.07766862412</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46168.91666666666</v>
+        <v>46185.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2172.168852613588</v>
+        <v>1853.629899472048</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46168.92708333334</v>
+        <v>46185.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>2119.674743014757</v>
+        <v>1752.946729272986</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46168.9375</v>
+        <v>46185.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>2067.180633415926</v>
+        <v>1652.263559073924</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46168.94791666666</v>
+        <v>46185.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>2014.686523817096</v>
+        <v>1551.580388874862</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46168.95833333334</v>
+        <v>46185.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>1962.192414218265</v>
+        <v>1450.897218675801</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46168.96875</v>
+        <v>46185.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>1932.564560401434</v>
+        <v>1362.346419069983</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46168.97916666666</v>
+        <v>46185.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>1902.936706584602</v>
+        <v>1273.795619464164</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46168.98958333334</v>
+        <v>46185.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1873.308852767771</v>
+        <v>1185.244819858346</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46169</v>
+        <v>46186</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1843.680998950939</v>
+        <v>1096.694020252528</v>
       </c>
       <c r="E97">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -412,886 +412,767 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B2">
-        <v>575</v>
+        <v>774</v>
       </c>
       <c r="C2">
-        <v>692</v>
+        <v>530</v>
       </c>
       <c r="D2">
-        <v>1234.774780771215</v>
+        <v>1191.259194003182</v>
       </c>
       <c r="E2">
-        <v>1267</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46216.01041666666</v>
+        <v>46218.01041666666</v>
       </c>
       <c r="B3">
-        <v>572</v>
+        <v>774</v>
       </c>
       <c r="C3">
-        <v>681</v>
+        <v>527</v>
       </c>
       <c r="D3">
-        <v>1227.282500451394</v>
+        <v>1183.311524870176</v>
       </c>
       <c r="E3">
-        <v>1253</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46216.02083333334</v>
+        <v>46218.02083333334</v>
       </c>
       <c r="B4">
-        <v>575</v>
+        <v>771</v>
       </c>
       <c r="C4">
-        <v>681</v>
+        <v>526</v>
       </c>
       <c r="D4">
-        <v>1219.790220131573</v>
+        <v>1175.363855737171</v>
       </c>
       <c r="E4">
-        <v>1256</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46216.03125</v>
+        <v>46218.03125</v>
       </c>
       <c r="B5">
-        <v>572</v>
+        <v>772</v>
       </c>
       <c r="C5">
-        <v>682</v>
+        <v>525</v>
       </c>
       <c r="D5">
-        <v>1212.297939811752</v>
+        <v>1167.416186604165</v>
       </c>
       <c r="E5">
-        <v>1254</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46216.04166666666</v>
+        <v>46218.04166666666</v>
       </c>
       <c r="B6">
-        <v>575</v>
+        <v>761</v>
       </c>
       <c r="C6">
-        <v>654</v>
+        <v>503</v>
       </c>
       <c r="D6">
-        <v>1204.805659491931</v>
+        <v>1159.46851747116</v>
       </c>
       <c r="E6">
-        <v>1229</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46216.05208333334</v>
+        <v>46218.05208333334</v>
       </c>
       <c r="B7">
-        <v>580</v>
+        <v>743</v>
       </c>
       <c r="C7">
-        <v>635</v>
+        <v>499</v>
       </c>
       <c r="D7">
-        <v>1195.861907172861</v>
+        <v>1150.459538800515</v>
       </c>
       <c r="E7">
-        <v>1215</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46216.0625</v>
+        <v>46218.0625</v>
       </c>
       <c r="B8">
-        <v>578</v>
+        <v>742</v>
       </c>
       <c r="C8">
-        <v>635</v>
+        <v>499</v>
       </c>
       <c r="D8">
-        <v>1186.918154853791</v>
+        <v>1141.450560129871</v>
       </c>
       <c r="E8">
-        <v>1213</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46216.07291666666</v>
+        <v>46218.07291666666</v>
       </c>
       <c r="B9">
-        <v>576</v>
+        <v>745</v>
       </c>
       <c r="C9">
-        <v>635</v>
+        <v>499</v>
       </c>
       <c r="D9">
-        <v>1177.974402534722</v>
+        <v>1132.441581459227</v>
       </c>
       <c r="E9">
-        <v>1211</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46216.08333333334</v>
+        <v>46218.08333333334</v>
       </c>
       <c r="B10">
-        <v>580</v>
+        <v>788</v>
       </c>
       <c r="C10">
-        <v>604</v>
+        <v>448</v>
       </c>
       <c r="D10">
-        <v>1169.030650215652</v>
+        <v>1123.432602788583</v>
       </c>
       <c r="E10">
-        <v>1184</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46216.09375</v>
+        <v>46218.09375</v>
       </c>
       <c r="B11">
-        <v>579</v>
+        <v>789</v>
       </c>
       <c r="C11">
-        <v>641</v>
+        <v>445</v>
       </c>
       <c r="D11">
-        <v>1168.510469499044</v>
+        <v>1122.201159660941</v>
       </c>
       <c r="E11">
-        <v>1220</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46216.10416666666</v>
+        <v>46218.10416666666</v>
       </c>
       <c r="B12">
-        <v>592</v>
+        <v>791</v>
       </c>
       <c r="C12">
-        <v>642</v>
+        <v>445</v>
       </c>
       <c r="D12">
-        <v>1167.990288782436</v>
+        <v>1120.969716533299</v>
       </c>
       <c r="E12">
-        <v>1234</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46216.11458333334</v>
+        <v>46218.11458333334</v>
       </c>
       <c r="B13">
-        <v>593</v>
+        <v>790</v>
       </c>
       <c r="C13">
-        <v>643</v>
+        <v>440</v>
       </c>
       <c r="D13">
-        <v>1167.470108065828</v>
+        <v>1119.738273405656</v>
       </c>
       <c r="E13">
-        <v>1236</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46216.125</v>
+        <v>46218.125</v>
       </c>
       <c r="B14">
-        <v>594</v>
+        <v>790</v>
       </c>
       <c r="C14">
-        <v>644</v>
+        <v>442</v>
       </c>
       <c r="D14">
-        <v>1166.94992734922</v>
+        <v>1118.506830278014</v>
       </c>
       <c r="E14">
-        <v>1238</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46216.13541666666</v>
+        <v>46218.13541666666</v>
       </c>
       <c r="B15">
-        <v>603</v>
+        <v>787</v>
       </c>
       <c r="C15">
-        <v>644</v>
+        <v>444</v>
       </c>
       <c r="D15">
-        <v>1172.143344502599</v>
+        <v>1124.315677136694</v>
       </c>
       <c r="E15">
-        <v>1247</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46216.14583333334</v>
+        <v>46218.14583333334</v>
       </c>
       <c r="B16">
-        <v>591</v>
+        <v>788</v>
       </c>
       <c r="C16">
-        <v>642</v>
+        <v>463</v>
       </c>
       <c r="D16">
-        <v>1177.336761655978</v>
+        <v>1130.124523995374</v>
       </c>
       <c r="E16">
-        <v>1233</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46216.15625</v>
+        <v>46218.15625</v>
       </c>
       <c r="B17">
-        <v>593</v>
+        <v>788</v>
       </c>
       <c r="C17">
-        <v>644</v>
+        <v>471</v>
       </c>
       <c r="D17">
-        <v>1182.530178809356</v>
+        <v>1135.933370854054</v>
       </c>
       <c r="E17">
-        <v>1237</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46216.16666666666</v>
+        <v>46218.16666666666</v>
       </c>
       <c r="B18">
-        <v>593</v>
+        <v>826</v>
       </c>
       <c r="C18">
-        <v>676</v>
+        <v>470</v>
       </c>
       <c r="D18">
-        <v>1187.723595962735</v>
+        <v>1141.742217712734</v>
       </c>
       <c r="E18">
-        <v>1269</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46216.17708333334</v>
+        <v>46218.17708333334</v>
       </c>
       <c r="B19">
-        <v>592</v>
+        <v>824</v>
       </c>
       <c r="C19">
-        <v>677</v>
+        <v>470</v>
       </c>
       <c r="D19">
-        <v>1198.311790546845</v>
+        <v>1151.990741110424</v>
       </c>
       <c r="E19">
-        <v>1269</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46216.1875</v>
+        <v>46218.1875</v>
       </c>
       <c r="B20">
-        <v>593</v>
+        <v>827</v>
       </c>
       <c r="C20">
-        <v>679</v>
+        <v>470</v>
       </c>
       <c r="D20">
-        <v>1208.899985130956</v>
+        <v>1162.239264508114</v>
       </c>
       <c r="E20">
-        <v>1272</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46216.19791666666</v>
+        <v>46218.19791666666</v>
       </c>
       <c r="B21">
-        <v>595</v>
+        <v>834</v>
       </c>
       <c r="C21">
-        <v>683</v>
+        <v>471</v>
       </c>
       <c r="D21">
-        <v>1219.488179715066</v>
+        <v>1172.487787905803</v>
       </c>
       <c r="E21">
-        <v>1278</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46216.20833333334</v>
+        <v>46218.20833333334</v>
       </c>
       <c r="B22">
-        <v>559</v>
+        <v>890</v>
       </c>
       <c r="C22">
-        <v>768</v>
+        <v>487</v>
       </c>
       <c r="D22">
-        <v>1230.076374299176</v>
+        <v>1182.736311303493</v>
       </c>
       <c r="E22">
-        <v>1327</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46216.21875</v>
+        <v>46218.21875</v>
       </c>
       <c r="B23">
-        <v>558</v>
+        <v>892</v>
       </c>
       <c r="C23">
-        <v>770</v>
+        <v>488</v>
       </c>
       <c r="D23">
-        <v>1249.734171375569</v>
+        <v>1203.209053300791</v>
       </c>
       <c r="E23">
-        <v>1328</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46216.22916666666</v>
+        <v>46218.22916666666</v>
       </c>
       <c r="B24">
-        <v>565</v>
+        <v>895</v>
       </c>
       <c r="C24">
-        <v>771</v>
+        <v>488</v>
       </c>
       <c r="D24">
-        <v>1269.391968451962</v>
+        <v>1223.68179529809</v>
       </c>
       <c r="E24">
-        <v>1336</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46216.23958333334</v>
+        <v>46218.23958333334</v>
       </c>
       <c r="B25">
-        <v>583</v>
+        <v>899</v>
       </c>
       <c r="C25">
-        <v>758</v>
+        <v>495</v>
       </c>
       <c r="D25">
-        <v>1289.049765528356</v>
+        <v>1244.154537295388</v>
       </c>
       <c r="E25">
-        <v>1341</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46216.25</v>
+        <v>46218.25</v>
       </c>
       <c r="B26">
-        <v>729</v>
+        <v>1027</v>
       </c>
       <c r="C26">
-        <v>730</v>
+        <v>473</v>
       </c>
       <c r="D26">
-        <v>1308.707562604749</v>
+        <v>1264.627279292686</v>
       </c>
       <c r="E26">
-        <v>1459</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46216.26041666666</v>
+        <v>46218.26041666666</v>
       </c>
       <c r="B27">
-        <v>732</v>
+        <v>1042</v>
       </c>
       <c r="C27">
-        <v>724</v>
+        <v>454</v>
       </c>
       <c r="D27">
-        <v>1313.322068961258</v>
+        <v>1270.614361340764</v>
       </c>
       <c r="E27">
-        <v>1456</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46216.27083333334</v>
+        <v>46218.27083333334</v>
       </c>
       <c r="B28">
-        <v>749</v>
+        <v>1028</v>
       </c>
       <c r="C28">
-        <v>724</v>
+        <v>454</v>
       </c>
       <c r="D28">
-        <v>1317.936575317768</v>
+        <v>1276.601443388842</v>
       </c>
       <c r="E28">
-        <v>1473</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46216.28125</v>
+        <v>46218.28125</v>
       </c>
       <c r="B29">
-        <v>752</v>
+        <v>1031</v>
       </c>
       <c r="C29">
-        <v>727</v>
+        <v>455</v>
       </c>
       <c r="D29">
-        <v>1322.551081674278</v>
+        <v>1282.58852543692</v>
       </c>
       <c r="E29">
-        <v>1479</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46216.29166666666</v>
+        <v>46218.29166666666</v>
       </c>
       <c r="B30">
-        <v>760</v>
+        <v>1000</v>
       </c>
       <c r="C30">
-        <v>739</v>
+        <v>487</v>
       </c>
       <c r="D30">
-        <v>1327.165588030787</v>
+        <v>1288.575607484998</v>
       </c>
       <c r="E30">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46216.30208333334</v>
+        <v>46218.30208333334</v>
       </c>
       <c r="B31">
-        <v>758</v>
+        <v>1002</v>
       </c>
       <c r="C31">
-        <v>739</v>
+        <v>488</v>
       </c>
       <c r="D31">
-        <v>1309.496223692729</v>
+        <v>1267.843614303182</v>
       </c>
       <c r="E31">
-        <v>1497</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46216.3125</v>
+        <v>46218.3125</v>
       </c>
       <c r="B32">
-        <v>755</v>
+        <v>1002</v>
       </c>
       <c r="C32">
-        <v>749</v>
+        <v>489</v>
       </c>
       <c r="D32">
-        <v>1291.826859354672</v>
+        <v>1247.111621121367</v>
       </c>
       <c r="E32">
-        <v>1504</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46216.32291666666</v>
+        <v>46218.32291666666</v>
       </c>
       <c r="B33">
-        <v>763</v>
+        <v>1002</v>
       </c>
       <c r="C33">
-        <v>740</v>
+        <v>508</v>
       </c>
       <c r="D33">
-        <v>1274.157495016615</v>
+        <v>1226.379627939551</v>
       </c>
       <c r="E33">
-        <v>1503</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46216.33333333334</v>
+        <v>46218.33333333334</v>
       </c>
       <c r="B34">
-        <v>763</v>
+        <v>904</v>
       </c>
       <c r="C34">
-        <v>684</v>
+        <v>540</v>
       </c>
       <c r="D34">
-        <v>1256.488130678557</v>
+        <v>1205.647634757736</v>
       </c>
       <c r="E34">
-        <v>1447</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46216.34375</v>
+        <v>46218.34375</v>
       </c>
       <c r="B35">
-        <v>759</v>
+        <v>888</v>
       </c>
       <c r="C35">
-        <v>676</v>
+        <v>533</v>
       </c>
       <c r="D35">
-        <v>1186.238563917262</v>
+        <v>1130.715940760716</v>
       </c>
       <c r="E35">
-        <v>1435</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46216.35416666666</v>
+        <v>46218.35416666666</v>
       </c>
       <c r="B36">
-        <v>763</v>
+        <v>895</v>
       </c>
       <c r="C36">
-        <v>675</v>
+        <v>509</v>
       </c>
       <c r="D36">
-        <v>1115.988997155967</v>
+        <v>1055.784246763696</v>
       </c>
       <c r="E36">
-        <v>1438</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46216.36458333334</v>
+        <v>46218.36458333334</v>
       </c>
       <c r="B37">
-        <v>774</v>
+        <v>900</v>
       </c>
       <c r="C37">
-        <v>675</v>
+        <v>506</v>
       </c>
       <c r="D37">
-        <v>1045.739430394671</v>
+        <v>980.8525527666753</v>
       </c>
       <c r="E37">
-        <v>1449</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46216.375</v>
+        <v>46218.375</v>
       </c>
       <c r="B38">
-        <v>342</v>
+        <v>871</v>
       </c>
       <c r="C38">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="D38">
-        <v>975.4898636333763</v>
+        <v>905.9208587696551</v>
       </c>
       <c r="E38">
-        <v>806</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46216.38541666666</v>
+        <v>46218.38541666666</v>
       </c>
       <c r="B39">
-        <v>305</v>
+        <v>848</v>
       </c>
       <c r="C39">
-        <v>427</v>
+        <v>450</v>
       </c>
       <c r="D39">
-        <v>929.7643006512064</v>
+        <v>848.2212669598458</v>
       </c>
       <c r="E39">
-        <v>732</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46216.39583333334</v>
+        <v>46218.39583333334</v>
       </c>
       <c r="B40">
-        <v>199</v>
+        <v>840</v>
       </c>
       <c r="C40">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="D40">
-        <v>884.0387376690364</v>
+        <v>790.5216751500366</v>
       </c>
       <c r="E40">
-        <v>625</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46216.40625</v>
+        <v>46218.40625</v>
       </c>
       <c r="B41">
-        <v>292</v>
+        <v>853</v>
       </c>
       <c r="C41">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="D41">
-        <v>838.3131746868665</v>
+        <v>732.8220833402274</v>
       </c>
       <c r="E41">
-        <v>717</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46216.41666666666</v>
+        <v>46218.41666666666</v>
       </c>
       <c r="B42">
-        <v>242</v>
+        <v>757</v>
       </c>
       <c r="C42">
-        <v>316</v>
+        <v>398</v>
       </c>
       <c r="D42">
-        <v>792.5876117046967</v>
+        <v>675.1224915304182</v>
       </c>
       <c r="E42">
-        <v>558</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46216.42708333334</v>
+        <v>46218.42708333334</v>
       </c>
       <c r="B43">
-        <v>238</v>
+        <v>755</v>
       </c>
       <c r="C43">
-        <v>302</v>
+        <v>395</v>
       </c>
       <c r="D43">
-        <v>792.6211717511552</v>
+        <v>684.7309885659043</v>
       </c>
       <c r="E43">
-        <v>540</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46216.4375</v>
+        <v>46218.4375</v>
       </c>
       <c r="B44">
-        <v>224</v>
+        <v>756</v>
       </c>
       <c r="C44">
-        <v>302</v>
+        <v>441</v>
       </c>
       <c r="D44">
-        <v>792.6547317976137</v>
+        <v>694.3394856013906</v>
       </c>
       <c r="E44">
-        <v>526</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46216.44791666666</v>
+        <v>46218.44791666666</v>
       </c>
       <c r="B45">
-        <v>259</v>
+        <v>755</v>
       </c>
       <c r="C45">
-        <v>303</v>
+        <v>442</v>
       </c>
       <c r="D45">
-        <v>792.6882918440722</v>
+        <v>703.9479826368768</v>
       </c>
       <c r="E45">
-        <v>562</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46216.45833333334</v>
+        <v>46218.45833333334</v>
       </c>
       <c r="B46">
-        <v>503</v>
+        <v>617</v>
       </c>
       <c r="C46">
-        <v>357</v>
+        <v>467</v>
       </c>
       <c r="D46">
-        <v>792.7218518905307</v>
+        <v>713.5564796723629</v>
       </c>
       <c r="E46">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="2">
-        <v>46216.46875</v>
-      </c>
-      <c r="B47">
-        <v>506</v>
-      </c>
-      <c r="C47">
-        <v>357</v>
-      </c>
-      <c r="D47">
-        <v>772.560654120473</v>
-      </c>
-      <c r="E47">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="2">
-        <v>46216.47916666666</v>
-      </c>
-      <c r="B48">
-        <v>497</v>
-      </c>
-      <c r="C48">
-        <v>358</v>
-      </c>
-      <c r="D48">
-        <v>752.3994563504152</v>
-      </c>
-      <c r="E48">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="2">
-        <v>46216.48958333334</v>
-      </c>
-      <c r="B49">
-        <v>503</v>
-      </c>
-      <c r="C49">
-        <v>359</v>
-      </c>
-      <c r="D49">
-        <v>732.2382585803575</v>
-      </c>
-      <c r="E49">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="2">
-        <v>46216.5</v>
-      </c>
-      <c r="B50">
-        <v>466</v>
-      </c>
-      <c r="C50">
-        <v>385</v>
-      </c>
-      <c r="D50">
-        <v>712.0770608102998</v>
-      </c>
-      <c r="E50">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="2">
-        <v>46216.51041666666</v>
-      </c>
-      <c r="B51">
-        <v>472</v>
-      </c>
-      <c r="C51">
-        <v>383</v>
-      </c>
-      <c r="D51">
-        <v>679.0371953014613</v>
-      </c>
-      <c r="E51">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="2">
-        <v>46216.52083333334</v>
-      </c>
-      <c r="B52">
-        <v>469</v>
-      </c>
-      <c r="C52">
-        <v>387</v>
-      </c>
-      <c r="D52">
-        <v>645.9973297926228</v>
-      </c>
-      <c r="E52">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="2">
-        <v>46216.53125</v>
-      </c>
-      <c r="B53">
-        <v>479</v>
-      </c>
-      <c r="C53">
-        <v>386</v>
-      </c>
-      <c r="D53">
-        <v>612.9574642837842</v>
-      </c>
-      <c r="E53">
-        <v>865</v>
+        <v>1084</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_71C8050753081726F6FF31D2F8375B062413B259" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F152F4B5-876C-455D-8DF8-6A374726BE07}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -34,11 +53,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,13 +121,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -146,7 +173,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -180,6 +207,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -214,9 +242,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -389,11 +418,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E46"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E44"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -410,769 +446,735 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B2">
-        <v>774</v>
+        <v>875</v>
       </c>
       <c r="C2">
-        <v>530</v>
+        <v>491</v>
       </c>
       <c r="D2">
-        <v>1191.259194003182</v>
+        <v>1271.9294378532809</v>
       </c>
       <c r="E2">
-        <v>1304</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>46218.01041666666</v>
+        <v>46219.010416666657</v>
       </c>
       <c r="B3">
-        <v>774</v>
+        <v>869</v>
       </c>
       <c r="C3">
-        <v>527</v>
+        <v>484</v>
       </c>
       <c r="D3">
-        <v>1183.311524870176</v>
+        <v>1263.5614810252989</v>
       </c>
       <c r="E3">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>46218.02083333334</v>
+        <v>46219.020833333343</v>
       </c>
       <c r="B4">
-        <v>771</v>
+        <v>868</v>
       </c>
       <c r="C4">
-        <v>526</v>
+        <v>479</v>
       </c>
       <c r="D4">
-        <v>1175.363855737171</v>
+        <v>1255.1935241973169</v>
       </c>
       <c r="E4">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>46218.03125</v>
+        <v>46219.03125</v>
       </c>
       <c r="B5">
-        <v>772</v>
+        <v>867</v>
       </c>
       <c r="C5">
-        <v>525</v>
+        <v>483</v>
       </c>
       <c r="D5">
-        <v>1167.416186604165</v>
+        <v>1246.825567369335</v>
       </c>
       <c r="E5">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>46218.04166666666</v>
+        <v>46219.041666666657</v>
       </c>
       <c r="B6">
-        <v>761</v>
+        <v>841</v>
       </c>
       <c r="C6">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="D6">
-        <v>1159.46851747116</v>
+        <v>1238.457610541353</v>
       </c>
       <c r="E6">
-        <v>1264</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>46218.05208333334</v>
+        <v>46219.052083333343</v>
       </c>
       <c r="B7">
-        <v>743</v>
+        <v>839</v>
       </c>
       <c r="C7">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="D7">
-        <v>1150.459538800515</v>
+        <v>1228.2493976474659</v>
       </c>
       <c r="E7">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>46218.0625</v>
+        <v>46219.0625</v>
       </c>
       <c r="B8">
-        <v>742</v>
+        <v>839</v>
       </c>
       <c r="C8">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="D8">
-        <v>1141.450560129871</v>
+        <v>1218.041184753579</v>
       </c>
       <c r="E8">
-        <v>1241</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>46218.07291666666</v>
+        <v>46219.072916666657</v>
       </c>
       <c r="B9">
-        <v>745</v>
+        <v>837</v>
       </c>
       <c r="C9">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="D9">
-        <v>1132.441581459227</v>
+        <v>1207.832971859692</v>
       </c>
       <c r="E9">
-        <v>1244</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>46218.08333333334</v>
+        <v>46219.083333333343</v>
       </c>
       <c r="B10">
-        <v>788</v>
+        <v>831</v>
       </c>
       <c r="C10">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="D10">
-        <v>1123.432602788583</v>
+        <v>1197.6247589658051</v>
       </c>
       <c r="E10">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>46218.09375</v>
+        <v>46219.09375</v>
       </c>
       <c r="B11">
-        <v>789</v>
+        <v>821</v>
       </c>
       <c r="C11">
-        <v>445</v>
+        <v>484</v>
       </c>
       <c r="D11">
-        <v>1122.201159660941</v>
+        <v>1196.1838037442751</v>
       </c>
       <c r="E11">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>46218.10416666666</v>
+        <v>46219.104166666657</v>
       </c>
       <c r="B12">
-        <v>791</v>
+        <v>822</v>
       </c>
       <c r="C12">
-        <v>445</v>
+        <v>484</v>
       </c>
       <c r="D12">
-        <v>1120.969716533299</v>
+        <v>1194.742848522744</v>
       </c>
       <c r="E12">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>46218.11458333334</v>
+        <v>46219.114583333343</v>
       </c>
       <c r="B13">
-        <v>790</v>
+        <v>827</v>
       </c>
       <c r="C13">
-        <v>440</v>
+        <v>484</v>
       </c>
       <c r="D13">
-        <v>1119.738273405656</v>
+        <v>1193.301893301214</v>
       </c>
       <c r="E13">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>46218.125</v>
+        <v>46219.125</v>
       </c>
       <c r="B14">
-        <v>790</v>
+        <v>823</v>
       </c>
       <c r="C14">
-        <v>442</v>
+        <v>484</v>
       </c>
       <c r="D14">
-        <v>1118.506830278014</v>
+        <v>1191.860938079684</v>
       </c>
       <c r="E14">
-        <v>1232</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>46218.13541666666</v>
+        <v>46219.135416666657</v>
       </c>
       <c r="B15">
-        <v>787</v>
+        <v>823</v>
       </c>
       <c r="C15">
-        <v>444</v>
+        <v>484</v>
       </c>
       <c r="D15">
-        <v>1124.315677136694</v>
+        <v>1199.057033733854</v>
       </c>
       <c r="E15">
-        <v>1231</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>46218.14583333334</v>
+        <v>46219.145833333343</v>
       </c>
       <c r="B16">
-        <v>788</v>
+        <v>822</v>
       </c>
       <c r="C16">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="D16">
-        <v>1130.124523995374</v>
+        <v>1206.253129388024</v>
       </c>
       <c r="E16">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>46218.15625</v>
+        <v>46219.15625</v>
       </c>
       <c r="B17">
-        <v>788</v>
+        <v>823</v>
       </c>
       <c r="C17">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="D17">
-        <v>1135.933370854054</v>
+        <v>1213.4492250421949</v>
       </c>
       <c r="E17">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>46218.16666666666</v>
+        <v>46219.166666666657</v>
       </c>
       <c r="B18">
-        <v>826</v>
+        <v>857</v>
       </c>
       <c r="C18">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="D18">
-        <v>1141.742217712734</v>
+        <v>1220.6453206963649</v>
       </c>
       <c r="E18">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>46218.17708333334</v>
+        <v>46219.177083333343</v>
       </c>
       <c r="B19">
-        <v>824</v>
+        <v>871</v>
       </c>
       <c r="C19">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="D19">
-        <v>1151.990741110424</v>
+        <v>1232.363932436801</v>
       </c>
       <c r="E19">
-        <v>1294</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>46218.1875</v>
+        <v>46219.1875</v>
       </c>
       <c r="B20">
-        <v>827</v>
+        <v>866</v>
       </c>
       <c r="C20">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="D20">
-        <v>1162.239264508114</v>
+        <v>1244.082544177237</v>
       </c>
       <c r="E20">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>46218.19791666666</v>
+        <v>46219.197916666657</v>
       </c>
       <c r="B21">
-        <v>834</v>
+        <v>874</v>
       </c>
       <c r="C21">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="D21">
-        <v>1172.487787905803</v>
+        <v>1255.801155917673</v>
       </c>
       <c r="E21">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>46218.20833333334</v>
+        <v>46219.208333333343</v>
       </c>
       <c r="B22">
-        <v>890</v>
+        <v>914</v>
       </c>
       <c r="C22">
-        <v>487</v>
+        <v>510</v>
       </c>
       <c r="D22">
-        <v>1182.736311303493</v>
+        <v>1267.519767658109</v>
       </c>
       <c r="E22">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>46218.21875</v>
+        <v>46219.21875</v>
       </c>
       <c r="B23">
-        <v>892</v>
+        <v>910</v>
       </c>
       <c r="C23">
-        <v>488</v>
+        <v>512</v>
       </c>
       <c r="D23">
-        <v>1203.209053300791</v>
+        <v>1290.0455435590391</v>
       </c>
       <c r="E23">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>46218.22916666666</v>
+        <v>46219.229166666657</v>
       </c>
       <c r="B24">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C24">
-        <v>488</v>
+        <v>512</v>
       </c>
       <c r="D24">
-        <v>1223.68179529809</v>
+        <v>1312.5713194599689</v>
       </c>
       <c r="E24">
-        <v>1383</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>46218.23958333334</v>
+        <v>46219.239583333343</v>
       </c>
       <c r="B25">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C25">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="D25">
-        <v>1244.154537295388</v>
+        <v>1335.097095360898</v>
       </c>
       <c r="E25">
-        <v>1394</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>46218.25</v>
+        <v>46219.25</v>
       </c>
       <c r="B26">
-        <v>1027</v>
+        <v>944</v>
       </c>
       <c r="C26">
-        <v>473</v>
+        <v>561</v>
       </c>
       <c r="D26">
-        <v>1264.627279292686</v>
+        <v>1357.6228712618281</v>
       </c>
       <c r="E26">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>46219.260416666657</v>
+      </c>
+      <c r="B27">
+        <v>956</v>
+      </c>
+      <c r="C27">
+        <v>566</v>
+      </c>
+      <c r="D27">
+        <v>1363.395372600633</v>
+      </c>
+      <c r="E27">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>46219.270833333343</v>
+      </c>
+      <c r="B28">
+        <v>946</v>
+      </c>
+      <c r="C28">
+        <v>593</v>
+      </c>
+      <c r="D28">
+        <v>1369.1678739394381</v>
+      </c>
+      <c r="E28">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>46219.28125</v>
+      </c>
+      <c r="B29">
+        <v>946</v>
+      </c>
+      <c r="C29">
+        <v>595</v>
+      </c>
+      <c r="D29">
+        <v>1374.940375278243</v>
+      </c>
+      <c r="E29">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>46219.291666666657</v>
+      </c>
+      <c r="B30">
+        <v>930</v>
+      </c>
+      <c r="C30">
+        <v>592</v>
+      </c>
+      <c r="D30">
+        <v>1380.712876617049</v>
+      </c>
+      <c r="E30">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>46219.302083333343</v>
+      </c>
+      <c r="B31">
+        <v>935</v>
+      </c>
+      <c r="C31">
+        <v>593</v>
+      </c>
+      <c r="D31">
+        <v>1355.765254289764</v>
+      </c>
+      <c r="E31">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>46219.3125</v>
+      </c>
+      <c r="B32">
+        <v>939</v>
+      </c>
+      <c r="C32">
+        <v>587</v>
+      </c>
+      <c r="D32">
+        <v>1330.8176319624799</v>
+      </c>
+      <c r="E32">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>46219.322916666657</v>
+      </c>
+      <c r="B33">
+        <v>934</v>
+      </c>
+      <c r="C33">
+        <v>558</v>
+      </c>
+      <c r="D33">
+        <v>1305.8700096351961</v>
+      </c>
+      <c r="E33">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>46219.333333333343</v>
+      </c>
+      <c r="B34">
+        <v>933</v>
+      </c>
+      <c r="C34">
+        <v>554</v>
+      </c>
+      <c r="D34">
+        <v>1280.9223873079111</v>
+      </c>
+      <c r="E34">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>46219.34375</v>
+      </c>
+      <c r="B35">
+        <v>944</v>
+      </c>
+      <c r="C35">
+        <v>556</v>
+      </c>
+      <c r="D35">
+        <v>1196.374773713771</v>
+      </c>
+      <c r="E35">
         <v>1500</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="2">
-        <v>46218.26041666666</v>
-      </c>
-      <c r="B27">
-        <v>1042</v>
-      </c>
-      <c r="C27">
-        <v>454</v>
-      </c>
-      <c r="D27">
-        <v>1270.614361340764</v>
-      </c>
-      <c r="E27">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="2">
-        <v>46218.27083333334</v>
-      </c>
-      <c r="B28">
-        <v>1028</v>
-      </c>
-      <c r="C28">
-        <v>454</v>
-      </c>
-      <c r="D28">
-        <v>1276.601443388842</v>
-      </c>
-      <c r="E28">
-        <v>1482</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="2">
-        <v>46218.28125</v>
-      </c>
-      <c r="B29">
-        <v>1031</v>
-      </c>
-      <c r="C29">
-        <v>455</v>
-      </c>
-      <c r="D29">
-        <v>1282.58852543692</v>
-      </c>
-      <c r="E29">
-        <v>1486</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="2">
-        <v>46218.29166666666</v>
-      </c>
-      <c r="B30">
-        <v>1000</v>
-      </c>
-      <c r="C30">
-        <v>487</v>
-      </c>
-      <c r="D30">
-        <v>1288.575607484998</v>
-      </c>
-      <c r="E30">
-        <v>1487</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="2">
-        <v>46218.30208333334</v>
-      </c>
-      <c r="B31">
-        <v>1002</v>
-      </c>
-      <c r="C31">
-        <v>488</v>
-      </c>
-      <c r="D31">
-        <v>1267.843614303182</v>
-      </c>
-      <c r="E31">
-        <v>1490</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="2">
-        <v>46218.3125</v>
-      </c>
-      <c r="B32">
-        <v>1002</v>
-      </c>
-      <c r="C32">
-        <v>489</v>
-      </c>
-      <c r="D32">
-        <v>1247.111621121367</v>
-      </c>
-      <c r="E32">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="2">
-        <v>46218.32291666666</v>
-      </c>
-      <c r="B33">
-        <v>1002</v>
-      </c>
-      <c r="C33">
-        <v>508</v>
-      </c>
-      <c r="D33">
-        <v>1226.379627939551</v>
-      </c>
-      <c r="E33">
-        <v>1510</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="2">
-        <v>46218.33333333334</v>
-      </c>
-      <c r="B34">
-        <v>904</v>
-      </c>
-      <c r="C34">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
+        <v>46219.354166666657</v>
+      </c>
+      <c r="B36">
+        <v>951</v>
+      </c>
+      <c r="C36">
+        <v>582</v>
+      </c>
+      <c r="D36">
+        <v>1111.82716011963</v>
+      </c>
+      <c r="E36">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>46219.364583333343</v>
+      </c>
+      <c r="B37">
+        <v>934</v>
+      </c>
+      <c r="C37">
+        <v>584</v>
+      </c>
+      <c r="D37">
+        <v>1027.2795465254901</v>
+      </c>
+      <c r="E37">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>46219.375</v>
+      </c>
+      <c r="B38">
+        <v>759</v>
+      </c>
+      <c r="C38">
+        <v>552</v>
+      </c>
+      <c r="D38">
+        <v>942.73193293134932</v>
+      </c>
+      <c r="E38">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>46219.385416666657</v>
+      </c>
+      <c r="B39">
+        <v>749</v>
+      </c>
+      <c r="C39">
         <v>540</v>
       </c>
-      <c r="D34">
-        <v>1205.647634757736</v>
-      </c>
-      <c r="E34">
-        <v>1444</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="2">
-        <v>46218.34375</v>
-      </c>
-      <c r="B35">
-        <v>888</v>
-      </c>
-      <c r="C35">
-        <v>533</v>
-      </c>
-      <c r="D35">
-        <v>1130.715940760716</v>
-      </c>
-      <c r="E35">
-        <v>1421</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="2">
-        <v>46218.35416666666</v>
-      </c>
-      <c r="B36">
-        <v>895</v>
-      </c>
-      <c r="C36">
-        <v>509</v>
-      </c>
-      <c r="D36">
-        <v>1055.784246763696</v>
-      </c>
-      <c r="E36">
-        <v>1404</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="2">
-        <v>46218.36458333334</v>
-      </c>
-      <c r="B37">
-        <v>900</v>
-      </c>
-      <c r="C37">
-        <v>506</v>
-      </c>
-      <c r="D37">
-        <v>980.8525527666753</v>
-      </c>
-      <c r="E37">
-        <v>1406</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="2">
-        <v>46218.375</v>
-      </c>
-      <c r="B38">
-        <v>871</v>
-      </c>
-      <c r="C38">
-        <v>452</v>
-      </c>
-      <c r="D38">
-        <v>905.9208587696551</v>
-      </c>
-      <c r="E38">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="2">
-        <v>46218.38541666666</v>
-      </c>
-      <c r="B39">
-        <v>848</v>
-      </c>
-      <c r="C39">
-        <v>450</v>
-      </c>
       <c r="D39">
-        <v>848.2212669598458</v>
+        <v>878.45317742195414</v>
       </c>
       <c r="E39">
-        <v>1298</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>46218.39583333334</v>
+        <v>46219.395833333343</v>
       </c>
       <c r="B40">
-        <v>840</v>
+        <v>808</v>
       </c>
       <c r="C40">
-        <v>452</v>
+        <v>548</v>
       </c>
       <c r="D40">
-        <v>790.5216751500366</v>
+        <v>814.17442191255896</v>
       </c>
       <c r="E40">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>46218.40625</v>
+        <v>46219.40625</v>
       </c>
       <c r="B41">
-        <v>853</v>
+        <v>811</v>
       </c>
       <c r="C41">
-        <v>441</v>
+        <v>553</v>
       </c>
       <c r="D41">
-        <v>732.8220833402274</v>
+        <v>749.89566640316377</v>
       </c>
       <c r="E41">
-        <v>1294</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>46218.41666666666</v>
+        <v>46219.416666666657</v>
       </c>
       <c r="B42">
-        <v>757</v>
+        <v>655</v>
       </c>
       <c r="C42">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="D42">
-        <v>675.1224915304182</v>
+        <v>685.61691089376859</v>
       </c>
       <c r="E42">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>46218.42708333334</v>
+        <v>46219.427083333343</v>
       </c>
       <c r="B43">
-        <v>755</v>
+        <v>596</v>
       </c>
       <c r="C43">
-        <v>395</v>
+        <v>461</v>
       </c>
       <c r="D43">
-        <v>684.7309885659043</v>
+        <v>692.70016065680795</v>
       </c>
       <c r="E43">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>46218.4375</v>
+        <v>46219.4375</v>
       </c>
       <c r="B44">
-        <v>756</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>441</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>694.3394856013906</v>
+        <v>699.78341041984731</v>
       </c>
       <c r="E44">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="2">
-        <v>46218.44791666666</v>
-      </c>
-      <c r="B45">
-        <v>755</v>
-      </c>
-      <c r="C45">
-        <v>442</v>
-      </c>
-      <c r="D45">
-        <v>703.9479826368768</v>
-      </c>
-      <c r="E45">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="2">
-        <v>46218.45833333334</v>
-      </c>
-      <c r="B46">
-        <v>617</v>
-      </c>
-      <c r="C46">
-        <v>467</v>
-      </c>
-      <c r="D46">
-        <v>713.5564796723629</v>
-      </c>
-      <c r="E46">
-        <v>1084</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -412,529 +412,546 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46227</v>
+        <v>46229</v>
       </c>
       <c r="B2">
-        <v>472</v>
+        <v>388</v>
       </c>
       <c r="C2">
-        <v>812</v>
+        <v>871</v>
       </c>
       <c r="D2">
-        <v>1385.727242861732</v>
+        <v>1034.728461838386</v>
       </c>
       <c r="E2">
-        <v>1284</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46227.01041666666</v>
+        <v>46229.01041666666</v>
       </c>
       <c r="B3">
-        <v>511</v>
+        <v>386</v>
       </c>
       <c r="C3">
-        <v>812</v>
+        <v>869</v>
       </c>
       <c r="D3">
-        <v>1378.398750505186</v>
+        <v>1029.520672432679</v>
       </c>
       <c r="E3">
-        <v>1323</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46227.02083333334</v>
+        <v>46229.02083333334</v>
       </c>
       <c r="B4">
-        <v>511</v>
+        <v>384</v>
       </c>
       <c r="C4">
-        <v>809</v>
+        <v>869</v>
       </c>
       <c r="D4">
-        <v>1371.07025814864</v>
+        <v>1024.312883026972</v>
       </c>
       <c r="E4">
-        <v>1320</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46227.03125</v>
+        <v>46229.03125</v>
       </c>
       <c r="B5">
-        <v>510</v>
+        <v>384</v>
       </c>
       <c r="C5">
-        <v>810</v>
+        <v>870</v>
       </c>
       <c r="D5">
-        <v>1363.741765792094</v>
+        <v>1019.105093621266</v>
       </c>
       <c r="E5">
-        <v>1320</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46227.04166666666</v>
+        <v>46229.04166666666</v>
       </c>
       <c r="B6">
-        <v>476</v>
+        <v>305</v>
       </c>
       <c r="C6">
-        <v>813</v>
+        <v>916</v>
       </c>
       <c r="D6">
-        <v>1356.413273435548</v>
+        <v>1013.897304215559</v>
       </c>
       <c r="E6">
-        <v>1289</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46227.05208333334</v>
+        <v>46229.05208333334</v>
       </c>
       <c r="B7">
-        <v>475</v>
+        <v>307</v>
       </c>
       <c r="C7">
-        <v>810</v>
+        <v>919</v>
       </c>
       <c r="D7">
-        <v>1352.191835183774</v>
+        <v>1010.325432195184</v>
       </c>
       <c r="E7">
-        <v>1285</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46227.0625</v>
+        <v>46229.0625</v>
       </c>
       <c r="B8">
-        <v>475</v>
+        <v>305</v>
       </c>
       <c r="C8">
-        <v>810</v>
+        <v>917</v>
       </c>
       <c r="D8">
-        <v>1347.970396932001</v>
+        <v>1006.753560174809</v>
       </c>
       <c r="E8">
-        <v>1285</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46227.07291666666</v>
+        <v>46229.07291666666</v>
       </c>
       <c r="B9">
-        <v>486</v>
+        <v>303</v>
       </c>
       <c r="C9">
-        <v>805</v>
+        <v>918</v>
       </c>
       <c r="D9">
-        <v>1343.748958680228</v>
+        <v>1003.181688154434</v>
       </c>
       <c r="E9">
-        <v>1291</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46227.08333333334</v>
+        <v>46229.08333333334</v>
       </c>
       <c r="B10">
-        <v>466</v>
+        <v>293</v>
       </c>
       <c r="C10">
-        <v>808</v>
+        <v>917</v>
       </c>
       <c r="D10">
-        <v>1339.527520428455</v>
+        <v>999.6098161340592</v>
       </c>
       <c r="E10">
-        <v>1274</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46227.09375</v>
+        <v>46229.09375</v>
       </c>
       <c r="B11">
-        <v>463</v>
+        <v>291</v>
       </c>
       <c r="C11">
-        <v>805</v>
+        <v>917</v>
       </c>
       <c r="D11">
-        <v>1341.010217979972</v>
+        <v>999.1097540512067</v>
       </c>
       <c r="E11">
-        <v>1268</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46227.10416666666</v>
+        <v>46229.10416666666</v>
       </c>
       <c r="B12">
-        <v>465</v>
+        <v>289</v>
       </c>
       <c r="C12">
-        <v>805</v>
+        <v>918</v>
       </c>
       <c r="D12">
-        <v>1342.49291553149</v>
+        <v>998.6096919683541</v>
       </c>
       <c r="E12">
-        <v>1270</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46227.11458333334</v>
+        <v>46229.11458333334</v>
       </c>
       <c r="B13">
-        <v>463</v>
+        <v>288</v>
       </c>
       <c r="C13">
-        <v>804</v>
+        <v>917</v>
       </c>
       <c r="D13">
-        <v>1343.975613083007</v>
+        <v>998.1096298855017</v>
       </c>
       <c r="E13">
-        <v>1267</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46227.125</v>
+        <v>46229.125</v>
       </c>
       <c r="B14">
-        <v>475</v>
+        <v>307</v>
       </c>
       <c r="C14">
-        <v>797</v>
+        <v>897</v>
       </c>
       <c r="D14">
-        <v>1345.458310634525</v>
+        <v>997.6095678026492</v>
       </c>
       <c r="E14">
-        <v>1272</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46227.13541666666</v>
+        <v>46229.13541666666</v>
       </c>
       <c r="B15">
-        <v>474</v>
+        <v>306</v>
       </c>
       <c r="C15">
-        <v>798</v>
+        <v>897</v>
       </c>
       <c r="D15">
-        <v>1353.957850738766</v>
+        <v>1003.703181469534</v>
       </c>
       <c r="E15">
-        <v>1272</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46227.14583333334</v>
+        <v>46229.14583333334</v>
       </c>
       <c r="B16">
-        <v>474</v>
+        <v>306</v>
       </c>
       <c r="C16">
-        <v>798</v>
+        <v>895</v>
       </c>
       <c r="D16">
-        <v>1362.457390843008</v>
+        <v>1009.796795136418</v>
       </c>
       <c r="E16">
-        <v>1272</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46227.15625</v>
+        <v>46229.15625</v>
       </c>
       <c r="B17">
-        <v>475</v>
+        <v>307</v>
       </c>
       <c r="C17">
-        <v>799</v>
+        <v>896</v>
       </c>
       <c r="D17">
-        <v>1370.956930947249</v>
+        <v>1015.890408803303</v>
       </c>
       <c r="E17">
-        <v>1274</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46227.16666666666</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="B18">
-        <v>500</v>
+        <v>314</v>
       </c>
       <c r="C18">
-        <v>808</v>
+        <v>894</v>
       </c>
       <c r="D18">
-        <v>1379.456471051491</v>
+        <v>1021.984022470187</v>
       </c>
       <c r="E18">
-        <v>1308</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46227.17708333334</v>
+        <v>46229.17708333334</v>
       </c>
       <c r="B19">
-        <v>490</v>
+        <v>313</v>
       </c>
       <c r="C19">
-        <v>807</v>
+        <v>889</v>
       </c>
       <c r="D19">
-        <v>1382.516305489018</v>
+        <v>1024.698645205674</v>
       </c>
       <c r="E19">
-        <v>1297</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46227.1875</v>
+        <v>46229.1875</v>
       </c>
       <c r="B20">
-        <v>485</v>
+        <v>314</v>
       </c>
       <c r="C20">
-        <v>807</v>
+        <v>889</v>
       </c>
       <c r="D20">
-        <v>1385.576139926545</v>
+        <v>1027.41326794116</v>
       </c>
       <c r="E20">
-        <v>1292</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46227.19791666666</v>
+        <v>46229.19791666666</v>
       </c>
       <c r="B21">
-        <v>507</v>
+        <v>322</v>
       </c>
       <c r="C21">
-        <v>807</v>
+        <v>891</v>
       </c>
       <c r="D21">
-        <v>1388.635974364072</v>
+        <v>1030.127890676646</v>
       </c>
       <c r="E21">
-        <v>1314</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46227.20833333334</v>
+        <v>46229.20833333334</v>
       </c>
       <c r="B22">
-        <v>553</v>
+        <v>290</v>
       </c>
       <c r="C22">
-        <v>818</v>
+        <v>914</v>
       </c>
       <c r="D22">
-        <v>1391.695808801599</v>
+        <v>1032.842513412132</v>
       </c>
       <c r="E22">
-        <v>1371</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46227.21875</v>
+        <v>46229.21875</v>
       </c>
       <c r="B23">
-        <v>552</v>
+        <v>287</v>
       </c>
       <c r="C23">
-        <v>813</v>
+        <v>916</v>
       </c>
       <c r="D23">
-        <v>1416.769452108981</v>
+        <v>1051.866303792523</v>
       </c>
       <c r="E23">
-        <v>1365</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46227.22916666666</v>
+        <v>46229.22916666666</v>
       </c>
       <c r="B24">
-        <v>550</v>
+        <v>284</v>
       </c>
       <c r="C24">
-        <v>811</v>
+        <v>916</v>
       </c>
       <c r="D24">
-        <v>1441.843095416363</v>
+        <v>1070.890094172914</v>
       </c>
       <c r="E24">
-        <v>1361</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46227.23958333334</v>
+        <v>46229.23958333334</v>
       </c>
       <c r="B25">
-        <v>565</v>
+        <v>284</v>
       </c>
       <c r="C25">
-        <v>806</v>
+        <v>916</v>
       </c>
       <c r="D25">
-        <v>1466.916738723745</v>
+        <v>1089.913884553305</v>
       </c>
       <c r="E25">
-        <v>1371</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46227.25</v>
+        <v>46229.25</v>
       </c>
       <c r="B26">
-        <v>642</v>
+        <v>306</v>
       </c>
       <c r="C26">
-        <v>830</v>
+        <v>925</v>
       </c>
       <c r="D26">
-        <v>1491.990382031127</v>
+        <v>1108.937674933696</v>
       </c>
       <c r="E26">
-        <v>1472</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46227.26041666666</v>
+        <v>46229.26041666666</v>
       </c>
       <c r="B27">
-        <v>629</v>
+        <v>309</v>
       </c>
       <c r="C27">
-        <v>832</v>
+        <v>923</v>
       </c>
       <c r="D27">
-        <v>1479.241071874895</v>
+        <v>1081.784303834928</v>
       </c>
       <c r="E27">
-        <v>1461</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46227.27083333334</v>
+        <v>46229.27083333334</v>
       </c>
       <c r="B28">
-        <v>615</v>
+        <v>313</v>
       </c>
       <c r="C28">
-        <v>832</v>
+        <v>923</v>
       </c>
       <c r="D28">
-        <v>1466.491761718663</v>
+        <v>1054.63093273616</v>
       </c>
       <c r="E28">
-        <v>1447</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46227.28125</v>
+        <v>46229.28125</v>
       </c>
       <c r="B29">
-        <v>620</v>
+        <v>317</v>
       </c>
       <c r="C29">
-        <v>834</v>
+        <v>927</v>
       </c>
       <c r="D29">
-        <v>1453.742451562431</v>
+        <v>1027.477561637391</v>
       </c>
       <c r="E29">
-        <v>1454</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46227.29166666666</v>
+        <v>46229.29166666666</v>
       </c>
       <c r="B30">
-        <v>586</v>
+        <v>134</v>
       </c>
       <c r="C30">
-        <v>737</v>
+        <v>755</v>
       </c>
       <c r="D30">
-        <v>1440.993141406199</v>
+        <v>1000.324190538623</v>
       </c>
       <c r="E30">
-        <v>1323</v>
+        <v>889</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46227.30208333334</v>
+        <v>46229.30208333334</v>
       </c>
       <c r="B31">
-        <v>486</v>
+        <v>129</v>
       </c>
       <c r="C31">
-        <v>817</v>
+        <v>624</v>
       </c>
       <c r="D31">
-        <v>1432.95635404109</v>
+        <v>988.6941752401597</v>
       </c>
       <c r="E31">
-        <v>1303</v>
+        <v>753</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46227.3125</v>
+        <v>46229.3125</v>
       </c>
       <c r="B32">
-        <v>484</v>
+        <v>128</v>
       </c>
       <c r="C32">
-        <v>823</v>
+        <v>623</v>
       </c>
       <c r="D32">
-        <v>1424.91956667598</v>
+        <v>977.0641599416965</v>
       </c>
       <c r="E32">
-        <v>1307</v>
+        <v>751</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="2">
+        <v>46229.32291666666</v>
+      </c>
+      <c r="B33">
+        <v>129</v>
+      </c>
+      <c r="C33">
+        <v>622</v>
+      </c>
+      <c r="D33">
+        <v>965.4341446432335</v>
+      </c>
+      <c r="E33">
+        <v>751</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -412,546 +412,937 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46229</v>
+        <v>46246</v>
       </c>
       <c r="B2">
-        <v>388</v>
+        <v>633</v>
       </c>
       <c r="C2">
-        <v>871</v>
+        <v>529</v>
       </c>
       <c r="D2">
-        <v>1034.728461838386</v>
+        <v>904.8564067628906</v>
       </c>
       <c r="E2">
-        <v>1259</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46229.01041666666</v>
+        <v>46246.01041666666</v>
       </c>
       <c r="B3">
-        <v>386</v>
+        <v>632</v>
       </c>
       <c r="C3">
-        <v>869</v>
+        <v>522</v>
       </c>
       <c r="D3">
-        <v>1029.520672432679</v>
+        <v>896.0136325415331</v>
       </c>
       <c r="E3">
-        <v>1255</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46229.02083333334</v>
+        <v>46246.02083333334</v>
       </c>
       <c r="B4">
-        <v>384</v>
+        <v>629</v>
       </c>
       <c r="C4">
-        <v>869</v>
+        <v>522</v>
       </c>
       <c r="D4">
-        <v>1024.312883026972</v>
+        <v>887.1708583201754</v>
       </c>
       <c r="E4">
-        <v>1253</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46229.03125</v>
+        <v>46246.03125</v>
       </c>
       <c r="B5">
-        <v>384</v>
+        <v>628</v>
       </c>
       <c r="C5">
-        <v>870</v>
+        <v>521</v>
       </c>
       <c r="D5">
-        <v>1019.105093621266</v>
+        <v>878.3280840988177</v>
       </c>
       <c r="E5">
-        <v>1254</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46229.04166666666</v>
+        <v>46246.04166666666</v>
       </c>
       <c r="B6">
-        <v>305</v>
+        <v>616</v>
       </c>
       <c r="C6">
-        <v>916</v>
+        <v>522</v>
       </c>
       <c r="D6">
-        <v>1013.897304215559</v>
+        <v>869.4853098774602</v>
       </c>
       <c r="E6">
-        <v>1221</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46229.05208333334</v>
+        <v>46246.05208333334</v>
       </c>
       <c r="B7">
-        <v>307</v>
+        <v>614</v>
       </c>
       <c r="C7">
-        <v>919</v>
+        <v>523</v>
       </c>
       <c r="D7">
-        <v>1010.325432195184</v>
+        <v>855.2966415292801</v>
       </c>
       <c r="E7">
-        <v>1226</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46229.0625</v>
+        <v>46246.0625</v>
       </c>
       <c r="B8">
-        <v>305</v>
+        <v>615</v>
       </c>
       <c r="C8">
-        <v>917</v>
+        <v>522</v>
       </c>
       <c r="D8">
-        <v>1006.753560174809</v>
+        <v>841.1079731811001</v>
       </c>
       <c r="E8">
-        <v>1222</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46229.07291666666</v>
+        <v>46246.07291666666</v>
       </c>
       <c r="B9">
-        <v>303</v>
+        <v>614</v>
       </c>
       <c r="C9">
-        <v>918</v>
+        <v>522</v>
       </c>
       <c r="D9">
-        <v>1003.181688154434</v>
+        <v>826.91930483292</v>
       </c>
       <c r="E9">
-        <v>1221</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46229.08333333334</v>
+        <v>46246.08333333334</v>
       </c>
       <c r="B10">
-        <v>293</v>
+        <v>667</v>
       </c>
       <c r="C10">
-        <v>917</v>
+        <v>452</v>
       </c>
       <c r="D10">
-        <v>999.6098161340592</v>
+        <v>812.73063648474</v>
       </c>
       <c r="E10">
-        <v>1210</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46229.09375</v>
+        <v>46246.09375</v>
       </c>
       <c r="B11">
-        <v>291</v>
+        <v>664</v>
       </c>
       <c r="C11">
-        <v>917</v>
+        <v>445</v>
       </c>
       <c r="D11">
-        <v>999.1097540512067</v>
+        <v>808.1738613173038</v>
       </c>
       <c r="E11">
-        <v>1208</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46229.10416666666</v>
+        <v>46246.10416666666</v>
       </c>
       <c r="B12">
-        <v>289</v>
+        <v>600</v>
       </c>
       <c r="C12">
-        <v>918</v>
+        <v>445</v>
       </c>
       <c r="D12">
-        <v>998.6096919683541</v>
+        <v>803.6170861498675</v>
       </c>
       <c r="E12">
-        <v>1207</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46229.11458333334</v>
+        <v>46246.11458333334</v>
       </c>
       <c r="B13">
-        <v>288</v>
+        <v>639</v>
       </c>
       <c r="C13">
-        <v>917</v>
+        <v>445</v>
       </c>
       <c r="D13">
-        <v>998.1096298855017</v>
+        <v>799.0603109824312</v>
       </c>
       <c r="E13">
-        <v>1205</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46229.125</v>
+        <v>46246.125</v>
       </c>
       <c r="B14">
-        <v>307</v>
+        <v>630</v>
       </c>
       <c r="C14">
-        <v>897</v>
+        <v>431</v>
       </c>
       <c r="D14">
-        <v>997.6095678026492</v>
+        <v>794.5035358149951</v>
       </c>
       <c r="E14">
-        <v>1204</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46229.13541666666</v>
+        <v>46246.13541666666</v>
       </c>
       <c r="B15">
-        <v>306</v>
+        <v>631</v>
       </c>
       <c r="C15">
-        <v>897</v>
+        <v>429</v>
       </c>
       <c r="D15">
-        <v>1003.703181469534</v>
+        <v>797.6909574940846</v>
       </c>
       <c r="E15">
-        <v>1203</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46229.14583333334</v>
+        <v>46246.14583333334</v>
       </c>
       <c r="B16">
-        <v>306</v>
+        <v>635</v>
       </c>
       <c r="C16">
-        <v>895</v>
+        <v>430</v>
       </c>
       <c r="D16">
-        <v>1009.796795136418</v>
+        <v>800.8783791731742</v>
       </c>
       <c r="E16">
-        <v>1201</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46229.15625</v>
+        <v>46246.15625</v>
       </c>
       <c r="B17">
-        <v>307</v>
+        <v>634</v>
       </c>
       <c r="C17">
-        <v>896</v>
+        <v>429</v>
       </c>
       <c r="D17">
-        <v>1015.890408803303</v>
+        <v>804.0658008522636</v>
       </c>
       <c r="E17">
-        <v>1203</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46229.16666666666</v>
+        <v>46246.16666666666</v>
       </c>
       <c r="B18">
-        <v>314</v>
+        <v>661</v>
       </c>
       <c r="C18">
-        <v>894</v>
+        <v>419</v>
       </c>
       <c r="D18">
-        <v>1021.984022470187</v>
+        <v>807.2532225313531</v>
       </c>
       <c r="E18">
-        <v>1208</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46229.17708333334</v>
+        <v>46246.17708333334</v>
       </c>
       <c r="B19">
-        <v>313</v>
+        <v>662</v>
       </c>
       <c r="C19">
-        <v>889</v>
+        <v>419</v>
       </c>
       <c r="D19">
-        <v>1024.698645205674</v>
+        <v>819.608349767901</v>
       </c>
       <c r="E19">
-        <v>1202</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46229.1875</v>
+        <v>46246.1875</v>
       </c>
       <c r="B20">
-        <v>314</v>
+        <v>663</v>
       </c>
       <c r="C20">
-        <v>889</v>
+        <v>419</v>
       </c>
       <c r="D20">
-        <v>1027.41326794116</v>
+        <v>831.9634770044488</v>
       </c>
       <c r="E20">
-        <v>1203</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46229.19791666666</v>
+        <v>46246.19791666666</v>
       </c>
       <c r="B21">
-        <v>322</v>
+        <v>671</v>
       </c>
       <c r="C21">
-        <v>891</v>
+        <v>420</v>
       </c>
       <c r="D21">
-        <v>1030.127890676646</v>
+        <v>844.3186042409967</v>
       </c>
       <c r="E21">
-        <v>1213</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46229.20833333334</v>
+        <v>46246.20833333334</v>
       </c>
       <c r="B22">
-        <v>290</v>
+        <v>708</v>
       </c>
       <c r="C22">
-        <v>914</v>
+        <v>395</v>
       </c>
       <c r="D22">
-        <v>1032.842513412132</v>
+        <v>856.6737314775446</v>
       </c>
       <c r="E22">
-        <v>1204</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46229.21875</v>
+        <v>46246.21875</v>
       </c>
       <c r="B23">
-        <v>287</v>
+        <v>706</v>
       </c>
       <c r="C23">
-        <v>916</v>
+        <v>415</v>
       </c>
       <c r="D23">
-        <v>1051.866303792523</v>
+        <v>883.5037760968598</v>
       </c>
       <c r="E23">
-        <v>1203</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46229.22916666666</v>
+        <v>46246.22916666666</v>
       </c>
       <c r="B24">
-        <v>284</v>
+        <v>698</v>
       </c>
       <c r="C24">
-        <v>916</v>
+        <v>415</v>
       </c>
       <c r="D24">
-        <v>1070.890094172914</v>
+        <v>910.3338207161752</v>
       </c>
       <c r="E24">
-        <v>1200</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46229.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="B25">
-        <v>284</v>
+        <v>718</v>
       </c>
       <c r="C25">
-        <v>916</v>
+        <v>417</v>
       </c>
       <c r="D25">
-        <v>1089.913884553305</v>
+        <v>937.1638653354905</v>
       </c>
       <c r="E25">
-        <v>1200</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46229.25</v>
+        <v>46246.25</v>
       </c>
       <c r="B26">
-        <v>306</v>
+        <v>731</v>
       </c>
       <c r="C26">
-        <v>925</v>
+        <v>486</v>
       </c>
       <c r="D26">
-        <v>1108.937674933696</v>
+        <v>963.9939099548058</v>
       </c>
       <c r="E26">
-        <v>1231</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46229.26041666666</v>
+        <v>46246.26041666666</v>
       </c>
       <c r="B27">
-        <v>309</v>
+        <v>709</v>
       </c>
       <c r="C27">
-        <v>923</v>
+        <v>494</v>
       </c>
       <c r="D27">
-        <v>1081.784303834928</v>
+        <v>948.4358881181513</v>
       </c>
       <c r="E27">
-        <v>1232</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46229.27083333334</v>
+        <v>46246.27083333334</v>
       </c>
       <c r="B28">
-        <v>313</v>
+        <v>700</v>
       </c>
       <c r="C28">
-        <v>923</v>
+        <v>493</v>
       </c>
       <c r="D28">
-        <v>1054.63093273616</v>
+        <v>932.8778662814969</v>
       </c>
       <c r="E28">
-        <v>1236</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46229.28125</v>
+        <v>46246.28125</v>
       </c>
       <c r="B29">
-        <v>317</v>
+        <v>699</v>
       </c>
       <c r="C29">
-        <v>927</v>
+        <v>492</v>
       </c>
       <c r="D29">
-        <v>1027.477561637391</v>
+        <v>917.3198444448426</v>
       </c>
       <c r="E29">
-        <v>1244</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46229.29166666666</v>
+        <v>46246.29166666666</v>
       </c>
       <c r="B30">
-        <v>134</v>
+        <v>719</v>
       </c>
       <c r="C30">
-        <v>755</v>
+        <v>485</v>
       </c>
       <c r="D30">
-        <v>1000.324190538623</v>
+        <v>901.7618226081881</v>
       </c>
       <c r="E30">
-        <v>889</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46229.30208333334</v>
+        <v>46246.30208333334</v>
       </c>
       <c r="B31">
-        <v>129</v>
+        <v>732</v>
       </c>
       <c r="C31">
-        <v>624</v>
+        <v>483</v>
       </c>
       <c r="D31">
-        <v>988.6941752401597</v>
+        <v>880.672231595745</v>
       </c>
       <c r="E31">
-        <v>753</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46229.3125</v>
+        <v>46246.3125</v>
       </c>
       <c r="B32">
-        <v>128</v>
+        <v>763</v>
       </c>
       <c r="C32">
-        <v>623</v>
+        <v>484</v>
       </c>
       <c r="D32">
-        <v>977.0641599416965</v>
+        <v>859.5826405833019</v>
       </c>
       <c r="E32">
-        <v>751</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46229.32291666666</v>
+        <v>46246.32291666666</v>
       </c>
       <c r="B33">
-        <v>129</v>
+        <v>770</v>
       </c>
       <c r="C33">
-        <v>622</v>
+        <v>484</v>
       </c>
       <c r="D33">
-        <v>965.4341446432335</v>
+        <v>838.4930495708588</v>
       </c>
       <c r="E33">
-        <v>751</v>
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="2">
+        <v>46246.33333333334</v>
+      </c>
+      <c r="B34">
+        <v>437</v>
+      </c>
+      <c r="C34">
+        <v>440</v>
+      </c>
+      <c r="D34">
+        <v>817.4034585584157</v>
+      </c>
+      <c r="E34">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="2">
+        <v>46246.34375</v>
+      </c>
+      <c r="B35">
+        <v>419</v>
+      </c>
+      <c r="C35">
+        <v>430</v>
+      </c>
+      <c r="D35">
+        <v>758.7688252917516</v>
+      </c>
+      <c r="E35">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="2">
+        <v>46246.35416666666</v>
+      </c>
+      <c r="B36">
+        <v>422</v>
+      </c>
+      <c r="C36">
+        <v>432</v>
+      </c>
+      <c r="D36">
+        <v>700.1341920250875</v>
+      </c>
+      <c r="E36">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="2">
+        <v>46246.36458333334</v>
+      </c>
+      <c r="B37">
+        <v>422</v>
+      </c>
+      <c r="C37">
+        <v>429</v>
+      </c>
+      <c r="D37">
+        <v>641.4995587584235</v>
+      </c>
+      <c r="E37">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="2">
+        <v>46246.375</v>
+      </c>
+      <c r="B38">
+        <v>143</v>
+      </c>
+      <c r="C38">
+        <v>262</v>
+      </c>
+      <c r="D38">
+        <v>582.8649254917594</v>
+      </c>
+      <c r="E38">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="2">
+        <v>46246.38541666666</v>
+      </c>
+      <c r="B39">
+        <v>114</v>
+      </c>
+      <c r="C39">
+        <v>254</v>
+      </c>
+      <c r="D39">
+        <v>523.2787075976649</v>
+      </c>
+      <c r="E39">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="2">
+        <v>46246.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>113</v>
+      </c>
+      <c r="C40">
+        <v>255</v>
+      </c>
+      <c r="D40">
+        <v>463.6924897035703</v>
+      </c>
+      <c r="E40">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="2">
+        <v>46246.40625</v>
+      </c>
+      <c r="B41">
+        <v>101</v>
+      </c>
+      <c r="C41">
+        <v>266</v>
+      </c>
+      <c r="D41">
+        <v>404.1062718094759</v>
+      </c>
+      <c r="E41">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="2">
+        <v>46246.41666666666</v>
+      </c>
+      <c r="B42">
+        <v>97</v>
+      </c>
+      <c r="C42">
+        <v>239</v>
+      </c>
+      <c r="D42">
+        <v>344.5200539153813</v>
+      </c>
+      <c r="E42">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="2">
+        <v>46246.42708333334</v>
+      </c>
+      <c r="B43">
+        <v>91</v>
+      </c>
+      <c r="C43">
+        <v>236</v>
+      </c>
+      <c r="D43">
+        <v>337.9053802853226</v>
+      </c>
+      <c r="E43">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="2">
+        <v>46246.4375</v>
+      </c>
+      <c r="B44">
+        <v>82</v>
+      </c>
+      <c r="C44">
+        <v>235</v>
+      </c>
+      <c r="D44">
+        <v>331.2907066552639</v>
+      </c>
+      <c r="E44">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="2">
+        <v>46246.44791666666</v>
+      </c>
+      <c r="B45">
+        <v>90</v>
+      </c>
+      <c r="C45">
+        <v>235</v>
+      </c>
+      <c r="D45">
+        <v>324.6760330252051</v>
+      </c>
+      <c r="E45">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="2">
+        <v>46246.45833333334</v>
+      </c>
+      <c r="B46">
+        <v>47</v>
+      </c>
+      <c r="C46">
+        <v>245</v>
+      </c>
+      <c r="D46">
+        <v>318.0613593951464</v>
+      </c>
+      <c r="E46">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="2">
+        <v>46246.46875</v>
+      </c>
+      <c r="B47">
+        <v>48</v>
+      </c>
+      <c r="C47">
+        <v>245</v>
+      </c>
+      <c r="D47">
+        <v>318.9897346414616</v>
+      </c>
+      <c r="E47">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="2">
+        <v>46246.47916666666</v>
+      </c>
+      <c r="B48">
+        <v>41</v>
+      </c>
+      <c r="C48">
+        <v>245</v>
+      </c>
+      <c r="D48">
+        <v>319.9181098877768</v>
+      </c>
+      <c r="E48">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="2">
+        <v>46246.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>41</v>
+      </c>
+      <c r="C49">
+        <v>245</v>
+      </c>
+      <c r="D49">
+        <v>320.8464851340921</v>
+      </c>
+      <c r="E49">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="2">
+        <v>46246.5</v>
+      </c>
+      <c r="B50">
+        <v>40</v>
+      </c>
+      <c r="C50">
+        <v>245</v>
+      </c>
+      <c r="D50">
+        <v>321.7748603804073</v>
+      </c>
+      <c r="E50">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="2">
+        <v>46246.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>39</v>
+      </c>
+      <c r="C51">
+        <v>245</v>
+      </c>
+      <c r="D51">
+        <v>329.1477071283284</v>
+      </c>
+      <c r="E51">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="2">
+        <v>46246.52083333334</v>
+      </c>
+      <c r="B52">
+        <v>27</v>
+      </c>
+      <c r="C52">
+        <v>246</v>
+      </c>
+      <c r="D52">
+        <v>336.5205538762494</v>
+      </c>
+      <c r="E52">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="2">
+        <v>46246.53125</v>
+      </c>
+      <c r="B53">
+        <v>37</v>
+      </c>
+      <c r="C53">
+        <v>245</v>
+      </c>
+      <c r="D53">
+        <v>343.8934006241705</v>
+      </c>
+      <c r="E53">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="2">
+        <v>46246.54166666666</v>
+      </c>
+      <c r="B54">
+        <v>33</v>
+      </c>
+      <c r="C54">
+        <v>245</v>
+      </c>
+      <c r="D54">
+        <v>351.2662473720915</v>
+      </c>
+      <c r="E54">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="2">
+        <v>46246.55208333334</v>
+      </c>
+      <c r="B55">
+        <v>46</v>
+      </c>
+      <c r="C55">
+        <v>246</v>
+      </c>
+      <c r="D55">
+        <v>366.7933233670935</v>
+      </c>
+      <c r="E55">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="2">
+        <v>46246.5625</v>
+      </c>
+      <c r="B56">
+        <v>51</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>382.3203993620955</v>
+      </c>
+      <c r="E56">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -412,937 +412,631 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="B2">
-        <v>633</v>
+        <v>730</v>
       </c>
       <c r="C2">
-        <v>529</v>
+        <v>396</v>
       </c>
       <c r="D2">
-        <v>904.8564067628906</v>
+        <v>1042.404460948878</v>
       </c>
       <c r="E2">
-        <v>1162</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46246.01041666666</v>
+        <v>46252.01041666666</v>
       </c>
       <c r="B3">
-        <v>632</v>
+        <v>727</v>
       </c>
       <c r="C3">
-        <v>522</v>
+        <v>388</v>
       </c>
       <c r="D3">
-        <v>896.0136325415331</v>
+        <v>1035.295791998481</v>
       </c>
       <c r="E3">
-        <v>1154</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46246.02083333334</v>
+        <v>46252.02083333334</v>
       </c>
       <c r="B4">
-        <v>629</v>
+        <v>726</v>
       </c>
       <c r="C4">
-        <v>522</v>
+        <v>388</v>
       </c>
       <c r="D4">
-        <v>887.1708583201754</v>
+        <v>1028.187123048083</v>
       </c>
       <c r="E4">
-        <v>1151</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46246.03125</v>
+        <v>46252.03125</v>
       </c>
       <c r="B5">
-        <v>628</v>
+        <v>724</v>
       </c>
       <c r="C5">
-        <v>521</v>
+        <v>388</v>
       </c>
       <c r="D5">
-        <v>878.3280840988177</v>
+        <v>1021.078454097685</v>
       </c>
       <c r="E5">
-        <v>1149</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46246.04166666666</v>
+        <v>46252.04166666666</v>
       </c>
       <c r="B6">
-        <v>616</v>
+        <v>751</v>
       </c>
       <c r="C6">
-        <v>522</v>
+        <v>343</v>
       </c>
       <c r="D6">
-        <v>869.4853098774602</v>
+        <v>1013.969785147287</v>
       </c>
       <c r="E6">
-        <v>1138</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46246.05208333334</v>
+        <v>46252.05208333334</v>
       </c>
       <c r="B7">
-        <v>614</v>
+        <v>751</v>
       </c>
       <c r="C7">
-        <v>523</v>
+        <v>339</v>
       </c>
       <c r="D7">
-        <v>855.2966415292801</v>
+        <v>1010.308702028228</v>
       </c>
       <c r="E7">
-        <v>1137</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46246.0625</v>
+        <v>46252.0625</v>
       </c>
       <c r="B8">
-        <v>615</v>
+        <v>750</v>
       </c>
       <c r="C8">
-        <v>522</v>
+        <v>340</v>
       </c>
       <c r="D8">
-        <v>841.1079731811001</v>
+        <v>1006.647618909169</v>
       </c>
       <c r="E8">
-        <v>1137</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46246.07291666666</v>
+        <v>46252.07291666666</v>
       </c>
       <c r="B9">
-        <v>614</v>
+        <v>750</v>
       </c>
       <c r="C9">
-        <v>522</v>
+        <v>339</v>
       </c>
       <c r="D9">
-        <v>826.91930483292</v>
+        <v>1002.98653579011</v>
       </c>
       <c r="E9">
-        <v>1136</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46246.08333333334</v>
+        <v>46252.08333333334</v>
       </c>
       <c r="B10">
-        <v>667</v>
+        <v>739</v>
       </c>
       <c r="C10">
-        <v>452</v>
+        <v>339</v>
       </c>
       <c r="D10">
-        <v>812.73063648474</v>
+        <v>999.3254526710506</v>
       </c>
       <c r="E10">
-        <v>1119</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46246.09375</v>
+        <v>46252.09375</v>
       </c>
       <c r="B11">
-        <v>664</v>
+        <v>738</v>
       </c>
       <c r="C11">
-        <v>445</v>
+        <v>340</v>
       </c>
       <c r="D11">
-        <v>808.1738613173038</v>
+        <v>998.7244973425893</v>
       </c>
       <c r="E11">
-        <v>1109</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46246.10416666666</v>
+        <v>46252.10416666666</v>
       </c>
       <c r="B12">
-        <v>600</v>
+        <v>739</v>
       </c>
       <c r="C12">
-        <v>445</v>
+        <v>340</v>
       </c>
       <c r="D12">
-        <v>803.6170861498675</v>
+        <v>998.123542014128</v>
       </c>
       <c r="E12">
-        <v>1045</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46246.11458333334</v>
+        <v>46252.11458333334</v>
       </c>
       <c r="B13">
-        <v>639</v>
+        <v>736</v>
       </c>
       <c r="C13">
-        <v>445</v>
+        <v>339</v>
       </c>
       <c r="D13">
-        <v>799.0603109824312</v>
+        <v>997.5225866856667</v>
       </c>
       <c r="E13">
-        <v>1084</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46246.125</v>
+        <v>46252.125</v>
       </c>
       <c r="B14">
-        <v>630</v>
+        <v>745</v>
       </c>
       <c r="C14">
-        <v>431</v>
+        <v>340</v>
       </c>
       <c r="D14">
-        <v>794.5035358149951</v>
+        <v>996.9216313572055</v>
       </c>
       <c r="E14">
-        <v>1061</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46246.13541666666</v>
+        <v>46252.13541666666</v>
       </c>
       <c r="B15">
-        <v>631</v>
+        <v>740</v>
       </c>
       <c r="C15">
-        <v>429</v>
+        <v>339</v>
       </c>
       <c r="D15">
-        <v>797.6909574940846</v>
+        <v>999.8552422366871</v>
       </c>
       <c r="E15">
-        <v>1060</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46246.14583333334</v>
+        <v>46252.14583333334</v>
       </c>
       <c r="B16">
-        <v>635</v>
+        <v>745</v>
       </c>
       <c r="C16">
-        <v>430</v>
+        <v>339</v>
       </c>
       <c r="D16">
-        <v>800.8783791731742</v>
+        <v>1002.788853116169</v>
       </c>
       <c r="E16">
-        <v>1065</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46246.15625</v>
+        <v>46252.15625</v>
       </c>
       <c r="B17">
-        <v>634</v>
+        <v>742</v>
       </c>
       <c r="C17">
-        <v>429</v>
+        <v>340</v>
       </c>
       <c r="D17">
-        <v>804.0658008522636</v>
+        <v>1005.72246399565</v>
       </c>
       <c r="E17">
-        <v>1063</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46246.16666666666</v>
+        <v>46252.16666666666</v>
       </c>
       <c r="B18">
-        <v>661</v>
+        <v>726</v>
       </c>
       <c r="C18">
-        <v>419</v>
+        <v>373</v>
       </c>
       <c r="D18">
-        <v>807.2532225313531</v>
+        <v>1008.656074875132</v>
       </c>
       <c r="E18">
-        <v>1080</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46246.17708333334</v>
+        <v>46252.17708333334</v>
       </c>
       <c r="B19">
-        <v>662</v>
+        <v>726</v>
       </c>
       <c r="C19">
-        <v>419</v>
+        <v>374</v>
       </c>
       <c r="D19">
-        <v>819.608349767901</v>
+        <v>1016.183831094149</v>
       </c>
       <c r="E19">
-        <v>1081</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46246.1875</v>
+        <v>46252.1875</v>
       </c>
       <c r="B20">
-        <v>663</v>
+        <v>726</v>
       </c>
       <c r="C20">
-        <v>419</v>
+        <v>374</v>
       </c>
       <c r="D20">
-        <v>831.9634770044488</v>
+        <v>1023.711587313166</v>
       </c>
       <c r="E20">
-        <v>1082</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46246.19791666666</v>
+        <v>46252.19791666666</v>
       </c>
       <c r="B21">
-        <v>671</v>
+        <v>729</v>
       </c>
       <c r="C21">
-        <v>420</v>
+        <v>367</v>
       </c>
       <c r="D21">
-        <v>844.3186042409967</v>
+        <v>1031.239343532184</v>
       </c>
       <c r="E21">
-        <v>1091</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46246.20833333334</v>
+        <v>46252.20833333334</v>
       </c>
       <c r="B22">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="C22">
-        <v>395</v>
+        <v>442</v>
       </c>
       <c r="D22">
-        <v>856.6737314775446</v>
+        <v>1038.767099751201</v>
       </c>
       <c r="E22">
-        <v>1103</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46246.21875</v>
+        <v>46252.21875</v>
       </c>
       <c r="B23">
-        <v>706</v>
+        <v>723</v>
       </c>
       <c r="C23">
-        <v>415</v>
+        <v>453</v>
       </c>
       <c r="D23">
-        <v>883.5037760968598</v>
+        <v>1062.077840647155</v>
       </c>
       <c r="E23">
-        <v>1121</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46246.22916666666</v>
+        <v>46252.22916666666</v>
       </c>
       <c r="B24">
-        <v>698</v>
+        <v>726</v>
       </c>
       <c r="C24">
-        <v>415</v>
+        <v>453</v>
       </c>
       <c r="D24">
-        <v>910.3338207161752</v>
+        <v>1085.388581543109</v>
       </c>
       <c r="E24">
-        <v>1113</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46246.23958333334</v>
+        <v>46252.23958333334</v>
       </c>
       <c r="B25">
-        <v>718</v>
+        <v>732</v>
       </c>
       <c r="C25">
-        <v>417</v>
+        <v>451</v>
       </c>
       <c r="D25">
-        <v>937.1638653354905</v>
+        <v>1108.699322439063</v>
       </c>
       <c r="E25">
-        <v>1135</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46246.25</v>
+        <v>46252.25</v>
       </c>
       <c r="B26">
-        <v>731</v>
+        <v>771</v>
       </c>
       <c r="C26">
-        <v>486</v>
+        <v>525</v>
       </c>
       <c r="D26">
-        <v>963.9939099548058</v>
+        <v>1132.010063335017</v>
       </c>
       <c r="E26">
-        <v>1217</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46246.26041666666</v>
+        <v>46252.26041666666</v>
       </c>
       <c r="B27">
-        <v>709</v>
+        <v>768</v>
       </c>
       <c r="C27">
-        <v>494</v>
+        <v>535</v>
       </c>
       <c r="D27">
-        <v>948.4358881181513</v>
+        <v>1138.921049611886</v>
       </c>
       <c r="E27">
-        <v>1203</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46246.27083333334</v>
+        <v>46252.27083333334</v>
       </c>
       <c r="B28">
-        <v>700</v>
+        <v>771</v>
       </c>
       <c r="C28">
-        <v>493</v>
+        <v>536</v>
       </c>
       <c r="D28">
-        <v>932.8778662814969</v>
+        <v>1145.832035888756</v>
       </c>
       <c r="E28">
-        <v>1193</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46246.28125</v>
+        <v>46252.28125</v>
       </c>
       <c r="B29">
-        <v>699</v>
+        <v>771</v>
       </c>
       <c r="C29">
-        <v>492</v>
+        <v>534</v>
       </c>
       <c r="D29">
-        <v>917.3198444448426</v>
+        <v>1152.743022165625</v>
       </c>
       <c r="E29">
-        <v>1191</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46246.29166666666</v>
+        <v>46252.29166666666</v>
       </c>
       <c r="B30">
-        <v>719</v>
+        <v>774</v>
       </c>
       <c r="C30">
-        <v>485</v>
+        <v>515</v>
       </c>
       <c r="D30">
-        <v>901.7618226081881</v>
+        <v>1159.654008442495</v>
       </c>
       <c r="E30">
-        <v>1204</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46246.30208333334</v>
+        <v>46252.30208333334</v>
       </c>
       <c r="B31">
-        <v>732</v>
+        <v>762</v>
       </c>
       <c r="C31">
-        <v>483</v>
+        <v>516</v>
       </c>
       <c r="D31">
-        <v>880.672231595745</v>
+        <v>1106.516905720753</v>
       </c>
       <c r="E31">
-        <v>1215</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46246.3125</v>
+        <v>46252.3125</v>
       </c>
       <c r="B32">
-        <v>763</v>
+        <v>817</v>
       </c>
       <c r="C32">
-        <v>484</v>
+        <v>561</v>
       </c>
       <c r="D32">
-        <v>859.5826405833019</v>
+        <v>1053.379802999011</v>
       </c>
       <c r="E32">
-        <v>1247</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46246.32291666666</v>
+        <v>46252.32291666666</v>
       </c>
       <c r="B33">
-        <v>770</v>
+        <v>865</v>
       </c>
       <c r="C33">
-        <v>484</v>
+        <v>574</v>
       </c>
       <c r="D33">
-        <v>838.4930495708588</v>
+        <v>1000.242700277268</v>
       </c>
       <c r="E33">
-        <v>1254</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46246.33333333334</v>
+        <v>46252.33333333334</v>
       </c>
       <c r="B34">
-        <v>437</v>
+        <v>745</v>
       </c>
       <c r="C34">
-        <v>440</v>
+        <v>542</v>
       </c>
       <c r="D34">
-        <v>817.4034585584157</v>
+        <v>947.1055975555262</v>
       </c>
       <c r="E34">
-        <v>877</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46246.34375</v>
+        <v>46252.34375</v>
       </c>
       <c r="B35">
-        <v>419</v>
+        <v>671</v>
       </c>
       <c r="C35">
-        <v>430</v>
+        <v>529</v>
       </c>
       <c r="D35">
-        <v>758.7688252917516</v>
+        <v>865.810574775846</v>
       </c>
       <c r="E35">
-        <v>849</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46246.35416666666</v>
+        <v>46252.35416666666</v>
       </c>
       <c r="B36">
-        <v>422</v>
+        <v>669</v>
       </c>
       <c r="C36">
-        <v>432</v>
+        <v>519</v>
       </c>
       <c r="D36">
-        <v>700.1341920250875</v>
+        <v>784.5155519961659</v>
       </c>
       <c r="E36">
-        <v>854</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46246.36458333334</v>
+        <v>46252.36458333334</v>
       </c>
       <c r="B37">
-        <v>422</v>
+        <v>630</v>
       </c>
       <c r="C37">
-        <v>429</v>
+        <v>528</v>
       </c>
       <c r="D37">
-        <v>641.4995587584235</v>
+        <v>703.2205292164856</v>
       </c>
       <c r="E37">
-        <v>851</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46246.375</v>
+        <v>46252.375</v>
       </c>
       <c r="B38">
-        <v>143</v>
+        <v>632</v>
       </c>
       <c r="C38">
-        <v>262</v>
+        <v>443</v>
       </c>
       <c r="D38">
-        <v>582.8649254917594</v>
+        <v>621.9255064368054</v>
       </c>
       <c r="E38">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="2">
-        <v>46246.38541666666</v>
-      </c>
-      <c r="B39">
-        <v>114</v>
-      </c>
-      <c r="C39">
-        <v>254</v>
-      </c>
-      <c r="D39">
-        <v>523.2787075976649</v>
-      </c>
-      <c r="E39">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="2">
-        <v>46246.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>113</v>
-      </c>
-      <c r="C40">
-        <v>255</v>
-      </c>
-      <c r="D40">
-        <v>463.6924897035703</v>
-      </c>
-      <c r="E40">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="2">
-        <v>46246.40625</v>
-      </c>
-      <c r="B41">
-        <v>101</v>
-      </c>
-      <c r="C41">
-        <v>266</v>
-      </c>
-      <c r="D41">
-        <v>404.1062718094759</v>
-      </c>
-      <c r="E41">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="2">
-        <v>46246.41666666666</v>
-      </c>
-      <c r="B42">
-        <v>97</v>
-      </c>
-      <c r="C42">
-        <v>239</v>
-      </c>
-      <c r="D42">
-        <v>344.5200539153813</v>
-      </c>
-      <c r="E42">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="2">
-        <v>46246.42708333334</v>
-      </c>
-      <c r="B43">
-        <v>91</v>
-      </c>
-      <c r="C43">
-        <v>236</v>
-      </c>
-      <c r="D43">
-        <v>337.9053802853226</v>
-      </c>
-      <c r="E43">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="2">
-        <v>46246.4375</v>
-      </c>
-      <c r="B44">
-        <v>82</v>
-      </c>
-      <c r="C44">
-        <v>235</v>
-      </c>
-      <c r="D44">
-        <v>331.2907066552639</v>
-      </c>
-      <c r="E44">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="2">
-        <v>46246.44791666666</v>
-      </c>
-      <c r="B45">
-        <v>90</v>
-      </c>
-      <c r="C45">
-        <v>235</v>
-      </c>
-      <c r="D45">
-        <v>324.6760330252051</v>
-      </c>
-      <c r="E45">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="2">
-        <v>46246.45833333334</v>
-      </c>
-      <c r="B46">
-        <v>47</v>
-      </c>
-      <c r="C46">
-        <v>245</v>
-      </c>
-      <c r="D46">
-        <v>318.0613593951464</v>
-      </c>
-      <c r="E46">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="2">
-        <v>46246.46875</v>
-      </c>
-      <c r="B47">
-        <v>48</v>
-      </c>
-      <c r="C47">
-        <v>245</v>
-      </c>
-      <c r="D47">
-        <v>318.9897346414616</v>
-      </c>
-      <c r="E47">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="2">
-        <v>46246.47916666666</v>
-      </c>
-      <c r="B48">
-        <v>41</v>
-      </c>
-      <c r="C48">
-        <v>245</v>
-      </c>
-      <c r="D48">
-        <v>319.9181098877768</v>
-      </c>
-      <c r="E48">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="2">
-        <v>46246.48958333334</v>
-      </c>
-      <c r="B49">
-        <v>41</v>
-      </c>
-      <c r="C49">
-        <v>245</v>
-      </c>
-      <c r="D49">
-        <v>320.8464851340921</v>
-      </c>
-      <c r="E49">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="2">
-        <v>46246.5</v>
-      </c>
-      <c r="B50">
-        <v>40</v>
-      </c>
-      <c r="C50">
-        <v>245</v>
-      </c>
-      <c r="D50">
-        <v>321.7748603804073</v>
-      </c>
-      <c r="E50">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="2">
-        <v>46246.51041666666</v>
-      </c>
-      <c r="B51">
-        <v>39</v>
-      </c>
-      <c r="C51">
-        <v>245</v>
-      </c>
-      <c r="D51">
-        <v>329.1477071283284</v>
-      </c>
-      <c r="E51">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="2">
-        <v>46246.52083333334</v>
-      </c>
-      <c r="B52">
-        <v>27</v>
-      </c>
-      <c r="C52">
-        <v>246</v>
-      </c>
-      <c r="D52">
-        <v>336.5205538762494</v>
-      </c>
-      <c r="E52">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="2">
-        <v>46246.53125</v>
-      </c>
-      <c r="B53">
-        <v>37</v>
-      </c>
-      <c r="C53">
-        <v>245</v>
-      </c>
-      <c r="D53">
-        <v>343.8934006241705</v>
-      </c>
-      <c r="E53">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="2">
-        <v>46246.54166666666</v>
-      </c>
-      <c r="B54">
-        <v>33</v>
-      </c>
-      <c r="C54">
-        <v>245</v>
-      </c>
-      <c r="D54">
-        <v>351.2662473720915</v>
-      </c>
-      <c r="E54">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="2">
-        <v>46246.55208333334</v>
-      </c>
-      <c r="B55">
-        <v>46</v>
-      </c>
-      <c r="C55">
-        <v>246</v>
-      </c>
-      <c r="D55">
-        <v>366.7933233670935</v>
-      </c>
-      <c r="E55">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="2">
-        <v>46246.5625</v>
-      </c>
-      <c r="B56">
-        <v>51</v>
-      </c>
-      <c r="C56">
-        <v>0</v>
-      </c>
-      <c r="D56">
-        <v>382.3203993620955</v>
-      </c>
-      <c r="E56">
-        <v>51</v>
+        <v>1075</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -412,631 +412,512 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="B2">
-        <v>730</v>
+        <v>842</v>
       </c>
       <c r="C2">
-        <v>396</v>
+        <v>531</v>
       </c>
       <c r="D2">
-        <v>1042.404460948878</v>
+        <v>1268.19630101477</v>
       </c>
       <c r="E2">
-        <v>1126</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46252.01041666666</v>
+        <v>46259.01041666666</v>
       </c>
       <c r="B3">
-        <v>727</v>
+        <v>919</v>
       </c>
       <c r="C3">
-        <v>388</v>
+        <v>528</v>
       </c>
       <c r="D3">
-        <v>1035.295791998481</v>
+        <v>1266.958015547219</v>
       </c>
       <c r="E3">
-        <v>1115</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46252.02083333334</v>
+        <v>46259.02083333334</v>
       </c>
       <c r="B4">
-        <v>726</v>
+        <v>870</v>
       </c>
       <c r="C4">
-        <v>388</v>
+        <v>529</v>
       </c>
       <c r="D4">
-        <v>1028.187123048083</v>
+        <v>1265.719730079669</v>
       </c>
       <c r="E4">
-        <v>1114</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46252.03125</v>
+        <v>46259.03125</v>
       </c>
       <c r="B5">
-        <v>724</v>
+        <v>735</v>
       </c>
       <c r="C5">
-        <v>388</v>
+        <v>529</v>
       </c>
       <c r="D5">
-        <v>1021.078454097685</v>
+        <v>1264.481444612118</v>
       </c>
       <c r="E5">
-        <v>1112</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46252.04166666666</v>
+        <v>46259.04166666666</v>
       </c>
       <c r="B6">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="C6">
-        <v>343</v>
+        <v>498</v>
       </c>
       <c r="D6">
-        <v>1013.969785147287</v>
+        <v>1263.243159144567</v>
       </c>
       <c r="E6">
-        <v>1094</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46252.05208333334</v>
+        <v>46259.05208333334</v>
       </c>
       <c r="B7">
-        <v>751</v>
+        <v>731</v>
       </c>
       <c r="C7">
-        <v>339</v>
+        <v>495</v>
       </c>
       <c r="D7">
-        <v>1010.308702028228</v>
+        <v>1257.397299844271</v>
       </c>
       <c r="E7">
-        <v>1090</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46252.0625</v>
+        <v>46259.0625</v>
       </c>
       <c r="B8">
-        <v>750</v>
+        <v>730</v>
       </c>
       <c r="C8">
-        <v>340</v>
+        <v>495</v>
       </c>
       <c r="D8">
-        <v>1006.647618909169</v>
+        <v>1251.551440543974</v>
       </c>
       <c r="E8">
-        <v>1090</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46252.07291666666</v>
+        <v>46259.07291666666</v>
       </c>
       <c r="B9">
-        <v>750</v>
+        <v>730</v>
       </c>
       <c r="C9">
-        <v>339</v>
+        <v>495</v>
       </c>
       <c r="D9">
-        <v>1002.98653579011</v>
+        <v>1245.705581243677</v>
       </c>
       <c r="E9">
-        <v>1089</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46252.08333333334</v>
+        <v>46259.08333333334</v>
       </c>
       <c r="B10">
-        <v>739</v>
+        <v>716</v>
       </c>
       <c r="C10">
-        <v>339</v>
+        <v>482</v>
       </c>
       <c r="D10">
-        <v>999.3254526710506</v>
+        <v>1239.859721943381</v>
       </c>
       <c r="E10">
-        <v>1078</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46252.09375</v>
+        <v>46259.09375</v>
       </c>
       <c r="B11">
-        <v>738</v>
+        <v>714</v>
       </c>
       <c r="C11">
-        <v>340</v>
+        <v>476</v>
       </c>
       <c r="D11">
-        <v>998.7244973425893</v>
+        <v>1238.247071101679</v>
       </c>
       <c r="E11">
-        <v>1078</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46252.10416666666</v>
+        <v>46259.10416666666</v>
       </c>
       <c r="B12">
-        <v>739</v>
+        <v>712</v>
       </c>
       <c r="C12">
-        <v>340</v>
+        <v>474</v>
       </c>
       <c r="D12">
-        <v>998.123542014128</v>
+        <v>1236.634420259977</v>
       </c>
       <c r="E12">
-        <v>1079</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46252.11458333334</v>
+        <v>46259.11458333334</v>
       </c>
       <c r="B13">
-        <v>736</v>
+        <v>717</v>
       </c>
       <c r="C13">
-        <v>339</v>
+        <v>475</v>
       </c>
       <c r="D13">
-        <v>997.5225866856667</v>
+        <v>1235.021769418275</v>
       </c>
       <c r="E13">
-        <v>1075</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46252.125</v>
+        <v>46259.125</v>
       </c>
       <c r="B14">
-        <v>745</v>
+        <v>794</v>
       </c>
       <c r="C14">
-        <v>340</v>
+        <v>403</v>
       </c>
       <c r="D14">
-        <v>996.9216313572055</v>
+        <v>1233.409118576573</v>
       </c>
       <c r="E14">
-        <v>1085</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46252.13541666666</v>
+        <v>46259.13541666666</v>
       </c>
       <c r="B15">
-        <v>740</v>
+        <v>794</v>
       </c>
       <c r="C15">
-        <v>339</v>
+        <v>424</v>
       </c>
       <c r="D15">
-        <v>999.8552422366871</v>
+        <v>1235.271346334034</v>
       </c>
       <c r="E15">
-        <v>1079</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46252.14583333334</v>
+        <v>46259.14583333334</v>
       </c>
       <c r="B16">
-        <v>745</v>
+        <v>792</v>
       </c>
       <c r="C16">
-        <v>339</v>
+        <v>424</v>
       </c>
       <c r="D16">
-        <v>1002.788853116169</v>
+        <v>1237.133574091494</v>
       </c>
       <c r="E16">
-        <v>1084</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46252.15625</v>
+        <v>46259.15625</v>
       </c>
       <c r="B17">
-        <v>742</v>
+        <v>792</v>
       </c>
       <c r="C17">
-        <v>340</v>
+        <v>424</v>
       </c>
       <c r="D17">
-        <v>1005.72246399565</v>
+        <v>1238.995801848955</v>
       </c>
       <c r="E17">
-        <v>1082</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46252.16666666666</v>
+        <v>46259.16666666666</v>
       </c>
       <c r="B18">
-        <v>726</v>
+        <v>791</v>
       </c>
       <c r="C18">
-        <v>373</v>
+        <v>445</v>
       </c>
       <c r="D18">
-        <v>1008.656074875132</v>
+        <v>1240.858029606416</v>
       </c>
       <c r="E18">
-        <v>1099</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46252.17708333334</v>
+        <v>46259.17708333334</v>
       </c>
       <c r="B19">
-        <v>726</v>
+        <v>790</v>
       </c>
       <c r="C19">
-        <v>374</v>
+        <v>447</v>
       </c>
       <c r="D19">
-        <v>1016.183831094149</v>
+        <v>1248.326138860445</v>
       </c>
       <c r="E19">
-        <v>1100</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46252.1875</v>
+        <v>46259.1875</v>
       </c>
       <c r="B20">
-        <v>726</v>
+        <v>791</v>
       </c>
       <c r="C20">
-        <v>374</v>
+        <v>447</v>
       </c>
       <c r="D20">
-        <v>1023.711587313166</v>
+        <v>1255.794248114474</v>
       </c>
       <c r="E20">
-        <v>1100</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46252.19791666666</v>
+        <v>46259.19791666666</v>
       </c>
       <c r="B21">
-        <v>729</v>
+        <v>791</v>
       </c>
       <c r="C21">
-        <v>367</v>
+        <v>448</v>
       </c>
       <c r="D21">
-        <v>1031.239343532184</v>
+        <v>1263.262357368503</v>
       </c>
       <c r="E21">
-        <v>1096</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46252.20833333334</v>
+        <v>46259.20833333334</v>
       </c>
       <c r="B22">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="C22">
-        <v>442</v>
+        <v>554</v>
       </c>
       <c r="D22">
-        <v>1038.767099751201</v>
+        <v>1270.730466622532</v>
       </c>
       <c r="E22">
-        <v>1156</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46252.21875</v>
+        <v>46259.21875</v>
       </c>
       <c r="B23">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="C23">
-        <v>453</v>
+        <v>567</v>
       </c>
       <c r="D23">
-        <v>1062.077840647155</v>
+        <v>1296.081721814715</v>
       </c>
       <c r="E23">
-        <v>1176</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46252.22916666666</v>
+        <v>46259.22916666666</v>
       </c>
       <c r="B24">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="C24">
-        <v>453</v>
+        <v>574</v>
       </c>
       <c r="D24">
-        <v>1085.388581543109</v>
+        <v>1321.432977006899</v>
       </c>
       <c r="E24">
-        <v>1179</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46252.23958333334</v>
+        <v>46259.23958333334</v>
       </c>
       <c r="B25">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C25">
-        <v>451</v>
+        <v>575</v>
       </c>
       <c r="D25">
-        <v>1108.699322439063</v>
+        <v>1346.784232199082</v>
       </c>
       <c r="E25">
-        <v>1183</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46252.25</v>
+        <v>46259.25</v>
       </c>
       <c r="B26">
-        <v>771</v>
+        <v>866</v>
       </c>
       <c r="C26">
-        <v>525</v>
+        <v>565</v>
       </c>
       <c r="D26">
-        <v>1132.010063335017</v>
+        <v>1372.135487391266</v>
       </c>
       <c r="E26">
-        <v>1296</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46252.26041666666</v>
+        <v>46259.26041666666</v>
       </c>
       <c r="B27">
-        <v>768</v>
+        <v>862</v>
       </c>
       <c r="C27">
-        <v>535</v>
+        <v>559</v>
       </c>
       <c r="D27">
-        <v>1138.921049611886</v>
+        <v>1366.894372156387</v>
       </c>
       <c r="E27">
-        <v>1303</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46252.27083333334</v>
+        <v>46259.27083333334</v>
       </c>
       <c r="B28">
-        <v>771</v>
+        <v>869</v>
       </c>
       <c r="C28">
-        <v>536</v>
+        <v>559</v>
       </c>
       <c r="D28">
-        <v>1145.832035888756</v>
+        <v>1361.653256921508</v>
       </c>
       <c r="E28">
-        <v>1307</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46252.28125</v>
+        <v>46259.28125</v>
       </c>
       <c r="B29">
-        <v>771</v>
+        <v>829</v>
       </c>
       <c r="C29">
-        <v>534</v>
+        <v>561</v>
       </c>
       <c r="D29">
-        <v>1152.743022165625</v>
+        <v>1356.41214168663</v>
       </c>
       <c r="E29">
-        <v>1305</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46252.29166666666</v>
+        <v>46259.29166666666</v>
       </c>
       <c r="B30">
-        <v>774</v>
+        <v>701</v>
       </c>
       <c r="C30">
-        <v>515</v>
+        <v>539</v>
       </c>
       <c r="D30">
-        <v>1159.654008442495</v>
+        <v>1351.171026451751</v>
       </c>
       <c r="E30">
-        <v>1289</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46252.30208333334</v>
+        <v>46259.30208333334</v>
       </c>
       <c r="B31">
-        <v>762</v>
+        <v>687</v>
       </c>
       <c r="C31">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="D31">
-        <v>1106.516905720753</v>
+        <v>1290.46624120553</v>
       </c>
       <c r="E31">
-        <v>1278</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="2">
-        <v>46252.3125</v>
-      </c>
-      <c r="B32">
-        <v>817</v>
-      </c>
-      <c r="C32">
-        <v>561</v>
-      </c>
-      <c r="D32">
-        <v>1053.379802999011</v>
-      </c>
-      <c r="E32">
-        <v>1378</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="2">
-        <v>46252.32291666666</v>
-      </c>
-      <c r="B33">
-        <v>865</v>
-      </c>
-      <c r="C33">
-        <v>574</v>
-      </c>
-      <c r="D33">
-        <v>1000.242700277268</v>
-      </c>
-      <c r="E33">
-        <v>1439</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="2">
-        <v>46252.33333333334</v>
-      </c>
-      <c r="B34">
-        <v>745</v>
-      </c>
-      <c r="C34">
-        <v>542</v>
-      </c>
-      <c r="D34">
-        <v>947.1055975555262</v>
-      </c>
-      <c r="E34">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="2">
-        <v>46252.34375</v>
-      </c>
-      <c r="B35">
-        <v>671</v>
-      </c>
-      <c r="C35">
-        <v>529</v>
-      </c>
-      <c r="D35">
-        <v>865.810574775846</v>
-      </c>
-      <c r="E35">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="2">
-        <v>46252.35416666666</v>
-      </c>
-      <c r="B36">
-        <v>669</v>
-      </c>
-      <c r="C36">
-        <v>519</v>
-      </c>
-      <c r="D36">
-        <v>784.5155519961659</v>
-      </c>
-      <c r="E36">
-        <v>1188</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="2">
-        <v>46252.36458333334</v>
-      </c>
-      <c r="B37">
-        <v>630</v>
-      </c>
-      <c r="C37">
-        <v>528</v>
-      </c>
-      <c r="D37">
-        <v>703.2205292164856</v>
-      </c>
-      <c r="E37">
-        <v>1158</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="2">
-        <v>46252.375</v>
-      </c>
-      <c r="B38">
-        <v>632</v>
-      </c>
-      <c r="C38">
-        <v>443</v>
-      </c>
-      <c r="D38">
-        <v>621.9255064368054</v>
-      </c>
-      <c r="E38">
-        <v>1075</v>
+        <v>1215</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -412,512 +412,852 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="B2">
-        <v>842</v>
+        <v>711</v>
       </c>
       <c r="C2">
-        <v>531</v>
+        <v>550</v>
       </c>
       <c r="D2">
-        <v>1268.19630101477</v>
+        <v>1232.968572829843</v>
       </c>
       <c r="E2">
-        <v>1373</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46259.01041666666</v>
+        <v>46262.01041666666</v>
       </c>
       <c r="B3">
-        <v>919</v>
+        <v>711</v>
       </c>
       <c r="C3">
-        <v>528</v>
+        <v>547</v>
       </c>
       <c r="D3">
-        <v>1266.958015547219</v>
+        <v>1226.862230667739</v>
       </c>
       <c r="E3">
-        <v>1447</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46259.02083333334</v>
+        <v>46262.02083333334</v>
       </c>
       <c r="B4">
-        <v>870</v>
+        <v>709</v>
       </c>
       <c r="C4">
-        <v>529</v>
+        <v>546</v>
       </c>
       <c r="D4">
-        <v>1265.719730079669</v>
+        <v>1220.755888505635</v>
       </c>
       <c r="E4">
-        <v>1399</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46259.03125</v>
+        <v>46262.03125</v>
       </c>
       <c r="B5">
-        <v>735</v>
+        <v>710</v>
       </c>
       <c r="C5">
-        <v>529</v>
+        <v>547</v>
       </c>
       <c r="D5">
-        <v>1264.481444612118</v>
+        <v>1214.64954634353</v>
       </c>
       <c r="E5">
-        <v>1264</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46259.04166666666</v>
+        <v>46262.04166666666</v>
       </c>
       <c r="B6">
-        <v>732</v>
+        <v>714</v>
       </c>
       <c r="C6">
-        <v>498</v>
+        <v>528</v>
       </c>
       <c r="D6">
-        <v>1263.243159144567</v>
+        <v>1208.543204181426</v>
       </c>
       <c r="E6">
-        <v>1230</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46259.05208333334</v>
+        <v>46262.05208333334</v>
       </c>
       <c r="B7">
-        <v>731</v>
+        <v>712</v>
       </c>
       <c r="C7">
-        <v>495</v>
+        <v>528</v>
       </c>
       <c r="D7">
-        <v>1257.397299844271</v>
+        <v>1201.747578823021</v>
       </c>
       <c r="E7">
-        <v>1226</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46259.0625</v>
+        <v>46262.0625</v>
       </c>
       <c r="B8">
-        <v>730</v>
+        <v>714</v>
       </c>
       <c r="C8">
-        <v>495</v>
+        <v>527</v>
       </c>
       <c r="D8">
-        <v>1251.551440543974</v>
+        <v>1194.951953464616</v>
       </c>
       <c r="E8">
-        <v>1225</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46259.07291666666</v>
+        <v>46262.07291666666</v>
       </c>
       <c r="B9">
-        <v>730</v>
+        <v>712</v>
       </c>
       <c r="C9">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="D9">
-        <v>1245.705581243677</v>
+        <v>1188.15632810621</v>
       </c>
       <c r="E9">
-        <v>1225</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46259.08333333334</v>
+        <v>46262.08333333334</v>
       </c>
       <c r="B10">
-        <v>716</v>
+        <v>671</v>
       </c>
       <c r="C10">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="D10">
-        <v>1239.859721943381</v>
+        <v>1181.360702747805</v>
       </c>
       <c r="E10">
-        <v>1198</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46259.09375</v>
+        <v>46262.09375</v>
       </c>
       <c r="B11">
-        <v>714</v>
+        <v>670</v>
       </c>
       <c r="C11">
-        <v>476</v>
+        <v>502</v>
       </c>
       <c r="D11">
-        <v>1238.247071101679</v>
+        <v>1180.079342959749</v>
       </c>
       <c r="E11">
-        <v>1190</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46259.10416666666</v>
+        <v>46262.10416666666</v>
       </c>
       <c r="B12">
-        <v>712</v>
+        <v>669</v>
       </c>
       <c r="C12">
-        <v>474</v>
+        <v>502</v>
       </c>
       <c r="D12">
-        <v>1236.634420259977</v>
+        <v>1178.797983171693</v>
       </c>
       <c r="E12">
-        <v>1186</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46259.11458333334</v>
+        <v>46262.11458333334</v>
       </c>
       <c r="B13">
-        <v>717</v>
+        <v>669</v>
       </c>
       <c r="C13">
-        <v>475</v>
+        <v>503</v>
       </c>
       <c r="D13">
-        <v>1235.021769418275</v>
+        <v>1177.516623383638</v>
       </c>
       <c r="E13">
-        <v>1192</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46259.125</v>
+        <v>46262.125</v>
       </c>
       <c r="B14">
-        <v>794</v>
+        <v>655</v>
       </c>
       <c r="C14">
-        <v>403</v>
+        <v>379</v>
       </c>
       <c r="D14">
-        <v>1233.409118576573</v>
+        <v>1176.235263595582</v>
       </c>
       <c r="E14">
-        <v>1197</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46259.13541666666</v>
+        <v>46262.13541666666</v>
       </c>
       <c r="B15">
-        <v>794</v>
+        <v>654</v>
       </c>
       <c r="C15">
-        <v>424</v>
+        <v>360</v>
       </c>
       <c r="D15">
-        <v>1235.271346334034</v>
+        <v>1181.334191855521</v>
       </c>
       <c r="E15">
-        <v>1218</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46259.14583333334</v>
+        <v>46262.14583333334</v>
       </c>
       <c r="B16">
-        <v>792</v>
+        <v>653</v>
       </c>
       <c r="C16">
-        <v>424</v>
+        <v>360</v>
       </c>
       <c r="D16">
-        <v>1237.133574091494</v>
+        <v>1186.433120115459</v>
       </c>
       <c r="E16">
-        <v>1216</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46259.15625</v>
+        <v>46262.15625</v>
       </c>
       <c r="B17">
-        <v>792</v>
+        <v>635</v>
       </c>
       <c r="C17">
-        <v>424</v>
+        <v>360</v>
       </c>
       <c r="D17">
-        <v>1238.995801848955</v>
+        <v>1191.532048375397</v>
       </c>
       <c r="E17">
-        <v>1216</v>
+        <v>995</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46259.16666666666</v>
+        <v>46262.16666666666</v>
       </c>
       <c r="B18">
-        <v>791</v>
+        <v>512</v>
       </c>
       <c r="C18">
-        <v>445</v>
+        <v>366</v>
       </c>
       <c r="D18">
-        <v>1240.858029606416</v>
+        <v>1196.630976635336</v>
       </c>
       <c r="E18">
-        <v>1236</v>
+        <v>878</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46259.17708333334</v>
+        <v>46262.17708333334</v>
       </c>
       <c r="B19">
-        <v>790</v>
+        <v>495</v>
       </c>
       <c r="C19">
-        <v>447</v>
+        <v>371</v>
       </c>
       <c r="D19">
-        <v>1248.326138860445</v>
+        <v>1214.269556889341</v>
       </c>
       <c r="E19">
-        <v>1237</v>
+        <v>866</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46259.1875</v>
+        <v>46262.1875</v>
       </c>
       <c r="B20">
-        <v>791</v>
+        <v>496</v>
       </c>
       <c r="C20">
-        <v>447</v>
+        <v>368</v>
       </c>
       <c r="D20">
-        <v>1255.794248114474</v>
+        <v>1231.908137143347</v>
       </c>
       <c r="E20">
-        <v>1238</v>
+        <v>864</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46259.19791666666</v>
+        <v>46262.19791666666</v>
       </c>
       <c r="B21">
-        <v>791</v>
+        <v>506</v>
       </c>
       <c r="C21">
-        <v>448</v>
+        <v>407</v>
       </c>
       <c r="D21">
-        <v>1263.262357368503</v>
+        <v>1249.546717397353</v>
       </c>
       <c r="E21">
-        <v>1239</v>
+        <v>913</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46259.20833333334</v>
+        <v>46262.20833333334</v>
       </c>
       <c r="B22">
-        <v>718</v>
+        <v>672</v>
       </c>
       <c r="C22">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="D22">
-        <v>1270.730466622532</v>
+        <v>1267.185297651358</v>
       </c>
       <c r="E22">
-        <v>1272</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46259.21875</v>
+        <v>46262.21875</v>
       </c>
       <c r="B23">
-        <v>719</v>
+        <v>693</v>
       </c>
       <c r="C23">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="D23">
-        <v>1296.081721814715</v>
+        <v>1294.783136395572</v>
       </c>
       <c r="E23">
-        <v>1286</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46259.22916666666</v>
+        <v>46262.22916666666</v>
       </c>
       <c r="B24">
-        <v>722</v>
+        <v>836</v>
       </c>
       <c r="C24">
-        <v>574</v>
+        <v>533</v>
       </c>
       <c r="D24">
-        <v>1321.432977006899</v>
+        <v>1322.380975139785</v>
       </c>
       <c r="E24">
-        <v>1296</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46259.23958333334</v>
+        <v>46262.23958333334</v>
       </c>
       <c r="B25">
-        <v>735</v>
+        <v>839</v>
       </c>
       <c r="C25">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="D25">
-        <v>1346.784232199082</v>
+        <v>1349.978813883998</v>
       </c>
       <c r="E25">
-        <v>1310</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46259.25</v>
+        <v>46262.25</v>
       </c>
       <c r="B26">
-        <v>866</v>
+        <v>907</v>
       </c>
       <c r="C26">
-        <v>565</v>
+        <v>707</v>
       </c>
       <c r="D26">
-        <v>1372.135487391266</v>
+        <v>1377.576652628211</v>
       </c>
       <c r="E26">
-        <v>1431</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46259.26041666666</v>
+        <v>46262.26041666666</v>
       </c>
       <c r="B27">
-        <v>862</v>
+        <v>917</v>
       </c>
       <c r="C27">
-        <v>559</v>
+        <v>717</v>
       </c>
       <c r="D27">
-        <v>1366.894372156387</v>
+        <v>1362.438933201683</v>
       </c>
       <c r="E27">
-        <v>1421</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46259.27083333334</v>
+        <v>46262.27083333334</v>
       </c>
       <c r="B28">
-        <v>869</v>
+        <v>917</v>
       </c>
       <c r="C28">
-        <v>559</v>
+        <v>644</v>
       </c>
       <c r="D28">
-        <v>1361.653256921508</v>
+        <v>1347.301213775155</v>
       </c>
       <c r="E28">
-        <v>1428</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46259.28125</v>
+        <v>46262.28125</v>
       </c>
       <c r="B29">
-        <v>829</v>
+        <v>921</v>
       </c>
       <c r="C29">
-        <v>561</v>
+        <v>636</v>
       </c>
       <c r="D29">
-        <v>1356.41214168663</v>
+        <v>1332.163494348628</v>
       </c>
       <c r="E29">
-        <v>1390</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46259.29166666666</v>
+        <v>46262.29166666666</v>
       </c>
       <c r="B30">
-        <v>701</v>
+        <v>938</v>
       </c>
       <c r="C30">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D30">
-        <v>1351.171026451751</v>
+        <v>1317.0257749221</v>
       </c>
       <c r="E30">
-        <v>1240</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46259.30208333334</v>
+        <v>46262.30208333334</v>
       </c>
       <c r="B31">
-        <v>687</v>
+        <v>932</v>
       </c>
       <c r="C31">
-        <v>528</v>
+        <v>634</v>
       </c>
       <c r="D31">
-        <v>1290.46624120553</v>
+        <v>1259.656204276175</v>
       </c>
       <c r="E31">
-        <v>1215</v>
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="2">
+        <v>46262.3125</v>
+      </c>
+      <c r="B32">
+        <v>931</v>
+      </c>
+      <c r="C32">
+        <v>680</v>
+      </c>
+      <c r="D32">
+        <v>1202.28663363025</v>
+      </c>
+      <c r="E32">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="2">
+        <v>46262.32291666666</v>
+      </c>
+      <c r="B33">
+        <v>943</v>
+      </c>
+      <c r="C33">
+        <v>725</v>
+      </c>
+      <c r="D33">
+        <v>1144.917062984326</v>
+      </c>
+      <c r="E33">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="2">
+        <v>46262.33333333334</v>
+      </c>
+      <c r="B34">
+        <v>885</v>
+      </c>
+      <c r="C34">
+        <v>682</v>
+      </c>
+      <c r="D34">
+        <v>1087.547492338401</v>
+      </c>
+      <c r="E34">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="2">
+        <v>46262.34375</v>
+      </c>
+      <c r="B35">
+        <v>884</v>
+      </c>
+      <c r="C35">
+        <v>679</v>
+      </c>
+      <c r="D35">
+        <v>1038.095841485863</v>
+      </c>
+      <c r="E35">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="2">
+        <v>46262.35416666666</v>
+      </c>
+      <c r="B36">
+        <v>884</v>
+      </c>
+      <c r="C36">
+        <v>548</v>
+      </c>
+      <c r="D36">
+        <v>988.6441906333255</v>
+      </c>
+      <c r="E36">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="2">
+        <v>46262.36458333334</v>
+      </c>
+      <c r="B37">
+        <v>832</v>
+      </c>
+      <c r="C37">
+        <v>535</v>
+      </c>
+      <c r="D37">
+        <v>939.1925397807876</v>
+      </c>
+      <c r="E37">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="2">
+        <v>46262.375</v>
+      </c>
+      <c r="B38">
+        <v>270</v>
+      </c>
+      <c r="C38">
+        <v>368</v>
+      </c>
+      <c r="D38">
+        <v>889.7408889282498</v>
+      </c>
+      <c r="E38">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="2">
+        <v>46262.38541666666</v>
+      </c>
+      <c r="B39">
+        <v>191</v>
+      </c>
+      <c r="C39">
+        <v>351</v>
+      </c>
+      <c r="D39">
+        <v>835.5968101622718</v>
+      </c>
+      <c r="E39">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="2">
+        <v>46262.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>111</v>
+      </c>
+      <c r="C40">
+        <v>350</v>
+      </c>
+      <c r="D40">
+        <v>781.452731396294</v>
+      </c>
+      <c r="E40">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="2">
+        <v>46262.40625</v>
+      </c>
+      <c r="B41">
+        <v>98</v>
+      </c>
+      <c r="C41">
+        <v>350</v>
+      </c>
+      <c r="D41">
+        <v>727.308652630316</v>
+      </c>
+      <c r="E41">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="2">
+        <v>46262.41666666666</v>
+      </c>
+      <c r="B42">
+        <v>82</v>
+      </c>
+      <c r="C42">
+        <v>304</v>
+      </c>
+      <c r="D42">
+        <v>673.1645738643381</v>
+      </c>
+      <c r="E42">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="2">
+        <v>46262.42708333334</v>
+      </c>
+      <c r="B43">
+        <v>80</v>
+      </c>
+      <c r="C43">
+        <v>300</v>
+      </c>
+      <c r="D43">
+        <v>645.8760288621521</v>
+      </c>
+      <c r="E43">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="2">
+        <v>46262.4375</v>
+      </c>
+      <c r="B44">
+        <v>81</v>
+      </c>
+      <c r="C44">
+        <v>287</v>
+      </c>
+      <c r="D44">
+        <v>618.5874838599661</v>
+      </c>
+      <c r="E44">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="2">
+        <v>46262.44791666666</v>
+      </c>
+      <c r="B45">
+        <v>82</v>
+      </c>
+      <c r="C45">
+        <v>287</v>
+      </c>
+      <c r="D45">
+        <v>591.2989388577801</v>
+      </c>
+      <c r="E45">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="2">
+        <v>46262.45833333334</v>
+      </c>
+      <c r="B46">
+        <v>82</v>
+      </c>
+      <c r="C46">
+        <v>294</v>
+      </c>
+      <c r="D46">
+        <v>564.0103938555941</v>
+      </c>
+      <c r="E46">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="2">
+        <v>46262.46875</v>
+      </c>
+      <c r="B47">
+        <v>79</v>
+      </c>
+      <c r="C47">
+        <v>282</v>
+      </c>
+      <c r="D47">
+        <v>551.6032963221439</v>
+      </c>
+      <c r="E47">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="2">
+        <v>46262.47916666666</v>
+      </c>
+      <c r="B48">
+        <v>110</v>
+      </c>
+      <c r="C48">
+        <v>273</v>
+      </c>
+      <c r="D48">
+        <v>539.1961987886937</v>
+      </c>
+      <c r="E48">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="2">
+        <v>46262.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>64</v>
+      </c>
+      <c r="C49">
+        <v>288</v>
+      </c>
+      <c r="D49">
+        <v>526.7891012552434</v>
+      </c>
+      <c r="E49">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="2">
+        <v>46262.5</v>
+      </c>
+      <c r="B50">
+        <v>64</v>
+      </c>
+      <c r="C50">
+        <v>261</v>
+      </c>
+      <c r="D50">
+        <v>514.3820037217932</v>
+      </c>
+      <c r="E50">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="2">
+        <v>46262.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>62</v>
+      </c>
+      <c r="C51">
+        <v>243</v>
+      </c>
+      <c r="D51">
+        <v>504.7497129016626</v>
+      </c>
+      <c r="E51">
+        <v>305</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -412,852 +412,784 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B2">
-        <v>711</v>
+        <v>867</v>
       </c>
       <c r="C2">
-        <v>550</v>
+        <v>436</v>
       </c>
       <c r="D2">
-        <v>1232.968572829843</v>
+        <v>1377.148621412836</v>
       </c>
       <c r="E2">
-        <v>1261</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46262.01041666666</v>
+        <v>46269.01041666666</v>
       </c>
       <c r="B3">
-        <v>711</v>
+        <v>867</v>
       </c>
       <c r="C3">
-        <v>547</v>
+        <v>434</v>
       </c>
       <c r="D3">
-        <v>1226.862230667739</v>
+        <v>1366.368006472928</v>
       </c>
       <c r="E3">
-        <v>1258</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46262.02083333334</v>
+        <v>46269.02083333334</v>
       </c>
       <c r="B4">
-        <v>709</v>
+        <v>866</v>
       </c>
       <c r="C4">
-        <v>546</v>
+        <v>435</v>
       </c>
       <c r="D4">
-        <v>1220.755888505635</v>
+        <v>1355.58739153302</v>
       </c>
       <c r="E4">
-        <v>1255</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46262.03125</v>
+        <v>46269.03125</v>
       </c>
       <c r="B5">
-        <v>710</v>
+        <v>863</v>
       </c>
       <c r="C5">
-        <v>547</v>
+        <v>433</v>
       </c>
       <c r="D5">
-        <v>1214.64954634353</v>
+        <v>1344.806776593112</v>
       </c>
       <c r="E5">
-        <v>1257</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46262.04166666666</v>
+        <v>46269.04166666666</v>
       </c>
       <c r="B6">
-        <v>714</v>
+        <v>867</v>
       </c>
       <c r="C6">
-        <v>528</v>
+        <v>416</v>
       </c>
       <c r="D6">
-        <v>1208.543204181426</v>
+        <v>1334.026161653204</v>
       </c>
       <c r="E6">
-        <v>1242</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46262.05208333334</v>
+        <v>46269.05208333334</v>
       </c>
       <c r="B7">
-        <v>712</v>
+        <v>864</v>
       </c>
       <c r="C7">
-        <v>528</v>
+        <v>416</v>
       </c>
       <c r="D7">
-        <v>1201.747578823021</v>
+        <v>1327.710767858109</v>
       </c>
       <c r="E7">
-        <v>1240</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46262.0625</v>
+        <v>46269.0625</v>
       </c>
       <c r="B8">
-        <v>714</v>
+        <v>864</v>
       </c>
       <c r="C8">
-        <v>527</v>
+        <v>415</v>
       </c>
       <c r="D8">
-        <v>1194.951953464616</v>
+        <v>1321.395374063014</v>
       </c>
       <c r="E8">
-        <v>1241</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46262.07291666666</v>
+        <v>46269.07291666666</v>
       </c>
       <c r="B9">
-        <v>712</v>
+        <v>866</v>
       </c>
       <c r="C9">
-        <v>504</v>
+        <v>413</v>
       </c>
       <c r="D9">
-        <v>1188.15632810621</v>
+        <v>1315.079980267919</v>
       </c>
       <c r="E9">
-        <v>1216</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46262.08333333334</v>
+        <v>46269.08333333334</v>
       </c>
       <c r="B10">
-        <v>671</v>
+        <v>853</v>
       </c>
       <c r="C10">
-        <v>502</v>
+        <v>408</v>
       </c>
       <c r="D10">
-        <v>1181.360702747805</v>
+        <v>1308.764586472824</v>
       </c>
       <c r="E10">
-        <v>1173</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46262.09375</v>
+        <v>46269.09375</v>
       </c>
       <c r="B11">
-        <v>670</v>
+        <v>853</v>
       </c>
       <c r="C11">
-        <v>502</v>
+        <v>406</v>
       </c>
       <c r="D11">
-        <v>1180.079342959749</v>
+        <v>1301.756669953941</v>
       </c>
       <c r="E11">
-        <v>1172</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46262.10416666666</v>
+        <v>46269.10416666666</v>
       </c>
       <c r="B12">
-        <v>669</v>
+        <v>854</v>
       </c>
       <c r="C12">
-        <v>502</v>
+        <v>408</v>
       </c>
       <c r="D12">
-        <v>1178.797983171693</v>
+        <v>1294.748753435058</v>
       </c>
       <c r="E12">
-        <v>1171</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46262.11458333334</v>
+        <v>46269.11458333334</v>
       </c>
       <c r="B13">
-        <v>669</v>
+        <v>854</v>
       </c>
       <c r="C13">
-        <v>503</v>
+        <v>418</v>
       </c>
       <c r="D13">
-        <v>1177.516623383638</v>
+        <v>1287.740836916174</v>
       </c>
       <c r="E13">
-        <v>1172</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46262.125</v>
+        <v>46269.125</v>
       </c>
       <c r="B14">
-        <v>655</v>
+        <v>855</v>
       </c>
       <c r="C14">
-        <v>379</v>
+        <v>416</v>
       </c>
       <c r="D14">
-        <v>1176.235263595582</v>
+        <v>1280.732920397291</v>
       </c>
       <c r="E14">
-        <v>1034</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46262.13541666666</v>
+        <v>46269.13541666666</v>
       </c>
       <c r="B15">
-        <v>654</v>
+        <v>855</v>
       </c>
       <c r="C15">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="D15">
-        <v>1181.334191855521</v>
+        <v>1269.259782733705</v>
       </c>
       <c r="E15">
-        <v>1014</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46262.14583333334</v>
+        <v>46269.14583333334</v>
       </c>
       <c r="B16">
-        <v>653</v>
+        <v>854</v>
       </c>
       <c r="C16">
-        <v>360</v>
+        <v>409</v>
       </c>
       <c r="D16">
-        <v>1186.433120115459</v>
+        <v>1257.786645070119</v>
       </c>
       <c r="E16">
-        <v>1013</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46262.15625</v>
+        <v>46269.15625</v>
       </c>
       <c r="B17">
-        <v>635</v>
+        <v>861</v>
       </c>
       <c r="C17">
-        <v>360</v>
+        <v>418</v>
       </c>
       <c r="D17">
-        <v>1191.532048375397</v>
+        <v>1246.313507406534</v>
       </c>
       <c r="E17">
-        <v>995</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46262.16666666666</v>
+        <v>46269.16666666666</v>
       </c>
       <c r="B18">
-        <v>512</v>
+        <v>884</v>
       </c>
       <c r="C18">
-        <v>366</v>
+        <v>413</v>
       </c>
       <c r="D18">
-        <v>1196.630976635336</v>
+        <v>1234.840369742948</v>
       </c>
       <c r="E18">
-        <v>878</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46262.17708333334</v>
+        <v>46269.17708333334</v>
       </c>
       <c r="B19">
-        <v>495</v>
+        <v>884</v>
       </c>
       <c r="C19">
-        <v>371</v>
+        <v>405</v>
       </c>
       <c r="D19">
-        <v>1214.269556889341</v>
+        <v>1269.16675729347</v>
       </c>
       <c r="E19">
-        <v>866</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46262.1875</v>
+        <v>46269.1875</v>
       </c>
       <c r="B20">
-        <v>496</v>
+        <v>885</v>
       </c>
       <c r="C20">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="D20">
-        <v>1231.908137143347</v>
+        <v>1303.493144843992</v>
       </c>
       <c r="E20">
-        <v>864</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46262.19791666666</v>
+        <v>46269.19791666666</v>
       </c>
       <c r="B21">
-        <v>506</v>
+        <v>884</v>
       </c>
       <c r="C21">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D21">
-        <v>1249.546717397353</v>
+        <v>1337.819532394514</v>
       </c>
       <c r="E21">
-        <v>913</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46262.20833333334</v>
+        <v>46269.20833333334</v>
       </c>
       <c r="B22">
-        <v>672</v>
+        <v>924</v>
       </c>
       <c r="C22">
-        <v>544</v>
+        <v>419</v>
       </c>
       <c r="D22">
-        <v>1267.185297651358</v>
+        <v>1372.145919945036</v>
       </c>
       <c r="E22">
-        <v>1216</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46262.21875</v>
+        <v>46269.21875</v>
       </c>
       <c r="B23">
-        <v>693</v>
+        <v>931</v>
       </c>
       <c r="C23">
-        <v>560</v>
+        <v>413</v>
       </c>
       <c r="D23">
-        <v>1294.783136395572</v>
+        <v>1429.790684585443</v>
       </c>
       <c r="E23">
-        <v>1253</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46262.22916666666</v>
+        <v>46269.22916666666</v>
       </c>
       <c r="B24">
-        <v>836</v>
+        <v>958</v>
       </c>
       <c r="C24">
-        <v>533</v>
+        <v>426</v>
       </c>
       <c r="D24">
-        <v>1322.380975139785</v>
+        <v>1487.435449225851</v>
       </c>
       <c r="E24">
-        <v>1369</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46262.23958333334</v>
+        <v>46269.23958333334</v>
       </c>
       <c r="B25">
-        <v>839</v>
+        <v>960</v>
       </c>
       <c r="C25">
-        <v>561</v>
+        <v>434</v>
       </c>
       <c r="D25">
-        <v>1349.978813883998</v>
+        <v>1545.080213866258</v>
       </c>
       <c r="E25">
-        <v>1400</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46262.25</v>
+        <v>46269.25</v>
       </c>
       <c r="B26">
-        <v>907</v>
+        <v>1029</v>
       </c>
       <c r="C26">
-        <v>707</v>
+        <v>536</v>
       </c>
       <c r="D26">
-        <v>1377.576652628211</v>
+        <v>1602.724978506666</v>
       </c>
       <c r="E26">
-        <v>1614</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46262.26041666666</v>
+        <v>46269.26041666666</v>
       </c>
       <c r="B27">
-        <v>917</v>
+        <v>1001</v>
       </c>
       <c r="C27">
-        <v>717</v>
+        <v>541</v>
       </c>
       <c r="D27">
-        <v>1362.438933201683</v>
+        <v>1566.56909062574</v>
       </c>
       <c r="E27">
-        <v>1634</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46262.27083333334</v>
+        <v>46269.27083333334</v>
       </c>
       <c r="B28">
-        <v>917</v>
+        <v>1002</v>
       </c>
       <c r="C28">
-        <v>644</v>
+        <v>533</v>
       </c>
       <c r="D28">
-        <v>1347.301213775155</v>
+        <v>1530.413202744815</v>
       </c>
       <c r="E28">
-        <v>1561</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46262.28125</v>
+        <v>46269.28125</v>
       </c>
       <c r="B29">
-        <v>921</v>
+        <v>991</v>
       </c>
       <c r="C29">
-        <v>636</v>
+        <v>537</v>
       </c>
       <c r="D29">
-        <v>1332.163494348628</v>
+        <v>1494.257314863889</v>
       </c>
       <c r="E29">
-        <v>1557</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46262.29166666666</v>
+        <v>46269.29166666666</v>
       </c>
       <c r="B30">
-        <v>938</v>
+        <v>964</v>
       </c>
       <c r="C30">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D30">
-        <v>1317.0257749221</v>
+        <v>1458.101426982964</v>
       </c>
       <c r="E30">
-        <v>1503</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46262.30208333334</v>
+        <v>46269.30208333334</v>
       </c>
       <c r="B31">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="C31">
-        <v>634</v>
+        <v>565</v>
       </c>
       <c r="D31">
-        <v>1259.656204276175</v>
+        <v>1416.591408192344</v>
       </c>
       <c r="E31">
-        <v>1566</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46262.3125</v>
+        <v>46269.3125</v>
       </c>
       <c r="B32">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C32">
-        <v>680</v>
+        <v>565</v>
       </c>
       <c r="D32">
-        <v>1202.28663363025</v>
+        <v>1375.081389401725</v>
       </c>
       <c r="E32">
-        <v>1611</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46262.32291666666</v>
+        <v>46269.32291666666</v>
       </c>
       <c r="B33">
-        <v>943</v>
+        <v>931</v>
       </c>
       <c r="C33">
-        <v>725</v>
+        <v>559</v>
       </c>
       <c r="D33">
-        <v>1144.917062984326</v>
+        <v>1333.571370611106</v>
       </c>
       <c r="E33">
-        <v>1668</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46262.33333333334</v>
+        <v>46269.33333333334</v>
       </c>
       <c r="B34">
-        <v>885</v>
+        <v>899</v>
       </c>
       <c r="C34">
-        <v>682</v>
+        <v>455</v>
       </c>
       <c r="D34">
-        <v>1087.547492338401</v>
+        <v>1292.061351820487</v>
       </c>
       <c r="E34">
-        <v>1567</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46262.34375</v>
+        <v>46269.34375</v>
       </c>
       <c r="B35">
-        <v>884</v>
+        <v>936</v>
       </c>
       <c r="C35">
-        <v>679</v>
+        <v>449</v>
       </c>
       <c r="D35">
-        <v>1038.095841485863</v>
+        <v>1135.633905511096</v>
       </c>
       <c r="E35">
-        <v>1563</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46262.35416666666</v>
+        <v>46269.35416666666</v>
       </c>
       <c r="B36">
-        <v>884</v>
+        <v>787</v>
       </c>
       <c r="C36">
-        <v>548</v>
+        <v>452</v>
       </c>
       <c r="D36">
-        <v>988.6441906333255</v>
+        <v>979.2064592017061</v>
       </c>
       <c r="E36">
-        <v>1432</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46262.36458333334</v>
+        <v>46269.36458333334</v>
       </c>
       <c r="B37">
-        <v>832</v>
+        <v>766</v>
       </c>
       <c r="C37">
-        <v>535</v>
+        <v>451</v>
       </c>
       <c r="D37">
-        <v>939.1925397807876</v>
+        <v>822.7790128923159</v>
       </c>
       <c r="E37">
-        <v>1367</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46262.375</v>
+        <v>46269.375</v>
       </c>
       <c r="B38">
-        <v>270</v>
+        <v>245</v>
       </c>
       <c r="C38">
-        <v>368</v>
+        <v>298</v>
       </c>
       <c r="D38">
-        <v>889.7408889282498</v>
+        <v>666.3515665829257</v>
       </c>
       <c r="E38">
-        <v>638</v>
+        <v>543</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46262.38541666666</v>
+        <v>46269.38541666666</v>
       </c>
       <c r="B39">
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="C39">
-        <v>351</v>
+        <v>289</v>
       </c>
       <c r="D39">
-        <v>835.5968101622718</v>
+        <v>611.6836160391559</v>
       </c>
       <c r="E39">
-        <v>542</v>
+        <v>517</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46262.39583333334</v>
+        <v>46269.39583333334</v>
       </c>
       <c r="B40">
-        <v>111</v>
+        <v>222</v>
       </c>
       <c r="C40">
-        <v>350</v>
+        <v>289</v>
       </c>
       <c r="D40">
-        <v>781.452731396294</v>
+        <v>557.0156654953862</v>
       </c>
       <c r="E40">
-        <v>461</v>
+        <v>511</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46262.40625</v>
+        <v>46269.40625</v>
       </c>
       <c r="B41">
-        <v>98</v>
+        <v>221</v>
       </c>
       <c r="C41">
-        <v>350</v>
+        <v>289</v>
       </c>
       <c r="D41">
-        <v>727.308652630316</v>
+        <v>502.3477149516165</v>
       </c>
       <c r="E41">
-        <v>448</v>
+        <v>510</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46262.41666666666</v>
+        <v>46269.41666666666</v>
       </c>
       <c r="B42">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="C42">
-        <v>304</v>
+        <v>247</v>
       </c>
       <c r="D42">
-        <v>673.1645738643381</v>
+        <v>447.6797644078467</v>
       </c>
       <c r="E42">
-        <v>386</v>
+        <v>420</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46262.42708333334</v>
+        <v>46269.42708333334</v>
       </c>
       <c r="B43">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="C43">
-        <v>300</v>
+        <v>243</v>
       </c>
       <c r="D43">
-        <v>645.8760288621521</v>
+        <v>444.8166480719765</v>
       </c>
       <c r="E43">
-        <v>380</v>
+        <v>405</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46262.4375</v>
+        <v>46269.4375</v>
       </c>
       <c r="B44">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="C44">
-        <v>287</v>
+        <v>243</v>
       </c>
       <c r="D44">
-        <v>618.5874838599661</v>
+        <v>441.9535317361063</v>
       </c>
       <c r="E44">
-        <v>368</v>
+        <v>405</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46262.44791666666</v>
+        <v>46269.44791666666</v>
       </c>
       <c r="B45">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C45">
-        <v>287</v>
+        <v>244</v>
       </c>
       <c r="D45">
-        <v>591.2989388577801</v>
+        <v>439.0904154002361</v>
       </c>
       <c r="E45">
-        <v>369</v>
+        <v>313</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46262.45833333334</v>
+        <v>46269.45833333334</v>
       </c>
       <c r="B46">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="C46">
-        <v>294</v>
+        <v>250</v>
       </c>
       <c r="D46">
-        <v>564.0103938555941</v>
+        <v>436.2272990643659</v>
       </c>
       <c r="E46">
-        <v>376</v>
+        <v>351</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46262.46875</v>
+        <v>46269.46875</v>
       </c>
       <c r="B47">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>282</v>
+        <v>248</v>
       </c>
       <c r="D47">
-        <v>551.6032963221439</v>
+        <v>428.2064388597516</v>
       </c>
       <c r="E47">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="2">
-        <v>46262.47916666666</v>
-      </c>
-      <c r="B48">
-        <v>110</v>
-      </c>
-      <c r="C48">
-        <v>273</v>
-      </c>
-      <c r="D48">
-        <v>539.1961987886937</v>
-      </c>
-      <c r="E48">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="2">
-        <v>46262.48958333334</v>
-      </c>
-      <c r="B49">
-        <v>64</v>
-      </c>
-      <c r="C49">
-        <v>288</v>
-      </c>
-      <c r="D49">
-        <v>526.7891012552434</v>
-      </c>
-      <c r="E49">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="2">
-        <v>46262.5</v>
-      </c>
-      <c r="B50">
-        <v>64</v>
-      </c>
-      <c r="C50">
-        <v>261</v>
-      </c>
-      <c r="D50">
-        <v>514.3820037217932</v>
-      </c>
-      <c r="E50">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="2">
-        <v>46262.51041666666</v>
-      </c>
-      <c r="B51">
-        <v>62</v>
-      </c>
-      <c r="C51">
-        <v>243</v>
-      </c>
-      <c r="D51">
-        <v>504.7497129016626</v>
-      </c>
-      <c r="E51">
-        <v>305</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
